--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E350505D-9CD8-40D7-AE6E-53E4A33837FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB748D8-8451-49B3-BA58-19281BB0E57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4966,30 +4966,30 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4999,6 +4999,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5008,16 +5017,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5420,13 +5420,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="457" t="s">
+      <c r="B12" s="455" t="s">
         <v>360</v>
       </c>
-      <c r="C12" s="457"/>
-      <c r="D12" s="457"/>
-      <c r="E12" s="457"/>
-      <c r="F12" s="457"/>
+      <c r="C12" s="455"/>
+      <c r="D12" s="455"/>
+      <c r="E12" s="455"/>
+      <c r="F12" s="455"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5604,22 +5604,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="457" t="s">
+      <c r="B29" s="455" t="s">
         <v>361</v>
       </c>
-      <c r="C29" s="457"/>
-      <c r="D29" s="457"/>
-      <c r="E29" s="457"/>
-      <c r="F29" s="457"/>
+      <c r="C29" s="455"/>
+      <c r="D29" s="455"/>
+      <c r="E29" s="455"/>
+      <c r="F29" s="455"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="457" t="s">
         <v>268</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="457"/>
+      <c r="D30" s="457"/>
+      <c r="E30" s="457"/>
+      <c r="F30" s="457"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5631,13 +5631,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="458" t="s">
+      <c r="B33" s="456" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="458"/>
-      <c r="D33" s="458"/>
-      <c r="E33" s="458"/>
-      <c r="F33" s="458"/>
+      <c r="C33" s="456"/>
+      <c r="D33" s="456"/>
+      <c r="E33" s="456"/>
+      <c r="F33" s="456"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5657,13 +5657,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="458" t="s">
+      <c r="B36" s="456" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="458"/>
-      <c r="D36" s="458"/>
-      <c r="E36" s="458"/>
-      <c r="F36" s="458"/>
+      <c r="C36" s="456"/>
+      <c r="D36" s="456"/>
+      <c r="E36" s="456"/>
+      <c r="F36" s="456"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5692,13 +5692,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="458" t="s">
+      <c r="B40" s="456" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="458"/>
-      <c r="D40" s="458"/>
-      <c r="E40" s="458"/>
-      <c r="F40" s="458"/>
+      <c r="C40" s="456"/>
+      <c r="D40" s="456"/>
+      <c r="E40" s="456"/>
+      <c r="F40" s="456"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5714,13 +5714,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="458" t="s">
+      <c r="B43" s="456" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="458"/>
-      <c r="D43" s="458"/>
-      <c r="E43" s="458"/>
-      <c r="F43" s="458"/>
+      <c r="C43" s="456"/>
+      <c r="D43" s="456"/>
+      <c r="E43" s="456"/>
+      <c r="F43" s="456"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5784,13 +5784,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="458" t="s">
+      <c r="B51" s="456" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="458"/>
-      <c r="D51" s="458"/>
-      <c r="E51" s="458"/>
-      <c r="F51" s="458"/>
+      <c r="C51" s="456"/>
+      <c r="D51" s="456"/>
+      <c r="E51" s="456"/>
+      <c r="F51" s="456"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5806,7 +5806,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="458" t="s">
+      <c r="B54" s="456" t="s">
         <v>267</v>
       </c>
       <c r="C54" s="459"/>
@@ -5828,22 +5828,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="457" t="s">
+      <c r="B57" s="455" t="s">
         <v>272</v>
       </c>
-      <c r="C57" s="457"/>
-      <c r="D57" s="457"/>
-      <c r="E57" s="457"/>
-      <c r="F57" s="457"/>
+      <c r="C57" s="455"/>
+      <c r="D57" s="455"/>
+      <c r="E57" s="455"/>
+      <c r="F57" s="455"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="457" t="s">
+      <c r="B58" s="455" t="s">
         <v>285</v>
       </c>
-      <c r="C58" s="457"/>
-      <c r="D58" s="457"/>
-      <c r="E58" s="457"/>
-      <c r="F58" s="457"/>
+      <c r="C58" s="455"/>
+      <c r="D58" s="455"/>
+      <c r="E58" s="455"/>
+      <c r="F58" s="455"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5978,13 +5978,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="457" t="s">
+      <c r="B73" s="455" t="s">
         <v>487</v>
       </c>
-      <c r="C73" s="457"/>
-      <c r="D73" s="457"/>
-      <c r="E73" s="457"/>
-      <c r="F73" s="457"/>
+      <c r="C73" s="455"/>
+      <c r="D73" s="455"/>
+      <c r="E73" s="455"/>
+      <c r="F73" s="455"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6003,13 +6003,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="457" t="s">
+      <c r="B77" s="455" t="s">
         <v>273</v>
       </c>
-      <c r="C77" s="457"/>
-      <c r="D77" s="457"/>
-      <c r="E77" s="457"/>
-      <c r="F77" s="457"/>
+      <c r="C77" s="455"/>
+      <c r="D77" s="455"/>
+      <c r="E77" s="455"/>
+      <c r="F77" s="455"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6178,31 +6178,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="457" t="s">
+      <c r="B96" s="455" t="s">
         <v>494</v>
       </c>
-      <c r="C96" s="457"/>
-      <c r="D96" s="457"/>
-      <c r="E96" s="457"/>
-      <c r="F96" s="457"/>
+      <c r="C96" s="455"/>
+      <c r="D96" s="455"/>
+      <c r="E96" s="455"/>
+      <c r="F96" s="455"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="457" t="s">
         <v>493</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="457"/>
+      <c r="D97" s="457"/>
+      <c r="E97" s="457"/>
+      <c r="F97" s="457"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="457" t="s">
         <v>492</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="457"/>
+      <c r="D98" s="457"/>
+      <c r="E98" s="457"/>
+      <c r="F98" s="457"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6252,22 +6252,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="457" t="s">
+      <c r="B107" s="455" t="s">
         <v>286</v>
       </c>
-      <c r="C107" s="457"/>
-      <c r="D107" s="457"/>
-      <c r="E107" s="457"/>
-      <c r="F107" s="457"/>
+      <c r="C107" s="455"/>
+      <c r="D107" s="455"/>
+      <c r="E107" s="455"/>
+      <c r="F107" s="455"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="457" t="s">
+      <c r="B108" s="455" t="s">
         <v>287</v>
       </c>
-      <c r="C108" s="457"/>
-      <c r="D108" s="457"/>
-      <c r="E108" s="457"/>
-      <c r="F108" s="457"/>
+      <c r="C108" s="455"/>
+      <c r="D108" s="455"/>
+      <c r="E108" s="455"/>
+      <c r="F108" s="455"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6301,13 +6301,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="457" t="s">
+      <c r="B114" s="455" t="s">
         <v>500</v>
       </c>
-      <c r="C114" s="457"/>
-      <c r="D114" s="457"/>
-      <c r="E114" s="457"/>
-      <c r="F114" s="457"/>
+      <c r="C114" s="455"/>
+      <c r="D114" s="455"/>
+      <c r="E114" s="455"/>
+      <c r="F114" s="455"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6442,13 +6442,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="458" t="s">
+      <c r="B124" s="456" t="s">
         <v>362</v>
       </c>
-      <c r="C124" s="458"/>
-      <c r="D124" s="458"/>
-      <c r="E124" s="458"/>
-      <c r="F124" s="458"/>
+      <c r="C124" s="456"/>
+      <c r="D124" s="456"/>
+      <c r="E124" s="456"/>
+      <c r="F124" s="456"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6483,22 +6483,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="458" t="s">
         <v>288</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="458"/>
+      <c r="D131" s="458"/>
+      <c r="E131" s="458"/>
+      <c r="F131" s="458"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="457" t="s">
+      <c r="B132" s="455" t="s">
         <v>364</v>
       </c>
-      <c r="C132" s="457"/>
-      <c r="D132" s="457"/>
-      <c r="E132" s="457"/>
-      <c r="F132" s="457"/>
+      <c r="C132" s="455"/>
+      <c r="D132" s="455"/>
+      <c r="E132" s="455"/>
+      <c r="F132" s="455"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6674,13 +6674,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="456" t="s">
+      <c r="B149" s="462" t="s">
         <v>365</v>
       </c>
-      <c r="C149" s="457"/>
-      <c r="D149" s="457"/>
-      <c r="E149" s="457"/>
-      <c r="F149" s="457"/>
+      <c r="C149" s="455"/>
+      <c r="D149" s="455"/>
+      <c r="E149" s="455"/>
+      <c r="F149" s="455"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6717,13 +6717,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="458" t="s">
+      <c r="B158" s="456" t="s">
         <v>447</v>
       </c>
-      <c r="C158" s="458"/>
-      <c r="D158" s="458"/>
-      <c r="E158" s="458"/>
-      <c r="F158" s="458"/>
+      <c r="C158" s="456"/>
+      <c r="D158" s="456"/>
+      <c r="E158" s="456"/>
+      <c r="F158" s="456"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6731,22 +6731,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="455" t="s">
+      <c r="B161" s="461" t="s">
         <v>297</v>
       </c>
-      <c r="C161" s="455"/>
-      <c r="D161" s="455"/>
-      <c r="E161" s="455"/>
-      <c r="F161" s="455"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="455" t="s">
+      <c r="B162" s="461" t="s">
         <v>298</v>
       </c>
-      <c r="C162" s="455"/>
-      <c r="D162" s="455"/>
-      <c r="E162" s="455"/>
-      <c r="F162" s="455"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6770,6 +6770,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6786,18 +6798,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20028,13 +20028,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="466" t="s">
         <v>506</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="466"/>
+      <c r="D12" s="466"/>
+      <c r="E12" s="466"/>
+      <c r="F12" s="466"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20219,22 +20219,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="466" t="s">
         <v>507</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="466"/>
+      <c r="D29" s="466"/>
+      <c r="E29" s="466"/>
+      <c r="F29" s="466"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="467" t="s">
         <v>508</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20424,10 +20424,10 @@
       <c r="B54" s="465" t="s">
         <v>515</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="468"/>
+      <c r="D54" s="468"/>
+      <c r="E54" s="468"/>
+      <c r="F54" s="468"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20443,22 +20443,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="466" t="s">
         <v>516</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="466"/>
+      <c r="D57" s="466"/>
+      <c r="E57" s="466"/>
+      <c r="F57" s="466"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="466" t="s">
         <v>517</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="466"/>
+      <c r="D58" s="466"/>
+      <c r="E58" s="466"/>
+      <c r="F58" s="466"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20593,22 +20593,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="466" t="s">
         <v>518</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="466"/>
+      <c r="D73" s="466"/>
+      <c r="E73" s="466"/>
+      <c r="F73" s="466"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="467" t="s">
         <v>488</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="467"/>
+      <c r="D74" s="467"/>
+      <c r="E74" s="467"/>
+      <c r="F74" s="467"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20616,13 +20616,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="466" t="s">
         <v>519</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="466"/>
+      <c r="D77" s="466"/>
+      <c r="E77" s="466"/>
+      <c r="F77" s="466"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20771,33 +20771,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="466" t="s">
         <v>522</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="466"/>
+      <c r="D96" s="466"/>
+      <c r="E96" s="466"/>
+      <c r="F96" s="466"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="467" t="s">
         <v>523</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20860,23 +20860,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="466" t="s">
         <v>525</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="466"/>
+      <c r="D107" s="466"/>
+      <c r="E107" s="466"/>
+      <c r="F107" s="466"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="466" t="s">
         <v>544</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="466"/>
+      <c r="D108" s="466"/>
+      <c r="E108" s="466"/>
+      <c r="F108" s="466"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20920,13 +20920,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="466" t="s">
         <v>526</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="466"/>
+      <c r="D114" s="466"/>
+      <c r="E114" s="466"/>
+      <c r="F114" s="466"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21090,13 +21090,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="467" t="s">
+      <c r="B127" s="470" t="s">
         <v>528</v>
       </c>
-      <c r="C127" s="467"/>
-      <c r="D127" s="467"/>
-      <c r="E127" s="467"/>
-      <c r="F127" s="467"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21109,22 +21109,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="471" t="s">
         <v>529</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="466" t="s">
         <v>530</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="466"/>
+      <c r="D132" s="466"/>
+      <c r="E132" s="466"/>
+      <c r="F132" s="466"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21293,13 +21293,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="470" t="s">
+      <c r="B149" s="472" t="s">
         <v>531</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="466"/>
+      <c r="D149" s="466"/>
+      <c r="E149" s="466"/>
+      <c r="F149" s="466"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21307,13 +21307,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="468" t="s">
         <v>532</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="468"/>
+      <c r="D152" s="468"/>
+      <c r="E152" s="468"/>
+      <c r="F152" s="468"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21350,22 +21350,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="469" t="s">
         <v>393</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="469" t="s">
         <v>394</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21389,12 +21389,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21409,15 +21412,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB748D8-8451-49B3-BA58-19281BB0E57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BFACE7-AE6D-4945-8BCA-5E0EEEEE441C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -19,21 +19,35 @@
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId7"/>
-    <sheet name="投资主题" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$M$73</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$9</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$91</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$101</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$E$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$E$16</definedName>
+    <definedName name="FV_adjustments" localSheetId="7">[1]DCF!$F$7</definedName>
     <definedName name="FV_adjustments">DCF!$F$7</definedName>
+    <definedName name="Holding_Period" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="Holding_Period">Thesis!$E$21</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$7</definedName>
     <definedName name="Market_currency">Thesis!$C$7</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$8</definedName>
     <definedName name="Market_Price">Thesis!$C$8</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$E$17</definedName>
     <definedName name="Reporting_currency">Thesis!$E$17</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$17</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="555">
   <si>
     <t>Sales</t>
   </si>
@@ -1257,10 +1271,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1421,10 +1431,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1787,9 +1793,6 @@
   </si>
   <si>
     <t>报告货币:</t>
-  </si>
-  <si>
-    <t>估值输出</t>
   </si>
   <si>
     <t>目标价格</t>
@@ -3250,19 +3253,25 @@
     <t>更新日期:</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
     <t>EBIT</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>中国飞鹤</t>
+  </si>
+  <si>
     <t>6186.HK</t>
   </si>
   <si>
-    <t>中国飞鹤</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3290,7 +3299,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3811,6 +3820,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -4002,11 +4017,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="473">
+  <cellXfs count="476">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4966,30 +4982,35 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4999,30 +5020,31 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{A805E029-490D-4B27-AEA7-98EF5A7E3D42}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5100,6 +5122,93 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+      <sheetName val="投资主题"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>3.96</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>9065251704</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>1.0932867000000002</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="C101">
+            <v>7.2499999999999995E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="91">
+          <cell r="C91">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="7">
+          <cell r="F7">
+            <v>14232912.522995466</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5328,7 +5437,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F3" s="439">
         <v>45930</v>
@@ -5336,30 +5445,30 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C4" s="430" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E4" s="440" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F4" s="441" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>552</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5367,52 +5476,52 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C9" s="48">
         <v>9065251704</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.33366695029787058</v>
+        <v>0.32175851586770188</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>35898.396747839994</v>
+        <v>36079.701781919997</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5420,13 +5529,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="455" t="s">
-        <v>360</v>
-      </c>
-      <c r="C12" s="455"/>
-      <c r="D12" s="455"/>
-      <c r="E12" s="455"/>
-      <c r="F12" s="455"/>
+      <c r="B12" s="460" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5437,13 +5546,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C15" s="427" t="s">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E15" s="260" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5452,30 +5561,30 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C16" s="427" t="s">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0932867000000002</v>
+        <v>1.0931181000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E17" s="228" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5485,10 +5594,10 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>6.4792427673148829</v>
+        <v>6.3918401764541954</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E18" s="428">
         <v>6</v>
@@ -5496,14 +5605,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E19" s="429">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5516,14 +5625,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C21" s="261" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E21" s="452">
         <v>2</v>
@@ -5531,14 +5640,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>3.8669260726007586</v>
+        <v>3.8189685467512731</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5546,14 +5655,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>4.494907371081525</v>
+        <v>4.4389697129306853</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E23" s="453">
         <v>0.25</v>
@@ -5561,14 +5670,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>5.5993325483005094</v>
+        <v>5.5293311085395693</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E24" s="453">
         <v>0.1174</v>
@@ -5576,14 +5685,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>6.0685375691850254</v>
+        <v>5.9925522477745243</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E25" s="454">
         <v>7.2499999999999995E-2</v>
@@ -5595,7 +5704,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="203" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5604,22 +5713,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="455" t="s">
-        <v>361</v>
-      </c>
-      <c r="C29" s="455"/>
-      <c r="D29" s="455"/>
-      <c r="E29" s="455"/>
-      <c r="F29" s="455"/>
+      <c r="B29" s="460" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="457" t="s">
-        <v>268</v>
-      </c>
-      <c r="C30" s="457"/>
-      <c r="D30" s="457"/>
-      <c r="E30" s="457"/>
-      <c r="F30" s="457"/>
+      <c r="B30" s="464" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5631,13 +5740,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="456" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="456"/>
-      <c r="D33" s="456"/>
-      <c r="E33" s="456"/>
-      <c r="F33" s="456"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5657,13 +5766,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="456" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="456"/>
-      <c r="D36" s="456"/>
-      <c r="E36" s="456"/>
-      <c r="F36" s="456"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5692,13 +5801,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="456" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="456"/>
-      <c r="D40" s="456"/>
-      <c r="E40" s="456"/>
-      <c r="F40" s="456"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5714,17 +5823,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="456" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="456"/>
-      <c r="D43" s="456"/>
-      <c r="E43" s="456"/>
-      <c r="F43" s="456"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C44" s="294">
         <f>Normalized_FCF!C46</f>
@@ -5739,7 +5848,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C45" s="294">
         <f>Normalized_FCF!C45</f>
@@ -5784,13 +5893,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="456" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="456"/>
-      <c r="D51" s="456"/>
-      <c r="E51" s="456"/>
-      <c r="F51" s="456"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5806,13 +5915,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="456" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="459"/>
-      <c r="D54" s="459"/>
-      <c r="E54" s="459"/>
-      <c r="F54" s="459"/>
+      <c r="B54" s="461" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" s="462"/>
+      <c r="D54" s="462"/>
+      <c r="E54" s="462"/>
+      <c r="F54" s="462"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5828,22 +5937,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="455" t="s">
-        <v>272</v>
-      </c>
-      <c r="C57" s="455"/>
-      <c r="D57" s="455"/>
-      <c r="E57" s="455"/>
-      <c r="F57" s="455"/>
+      <c r="B57" s="460" t="s">
+        <v>271</v>
+      </c>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="455" t="s">
-        <v>285</v>
-      </c>
-      <c r="C58" s="455"/>
-      <c r="D58" s="455"/>
-      <c r="E58" s="455"/>
-      <c r="F58" s="455"/>
+      <c r="B58" s="460" t="s">
+        <v>283</v>
+      </c>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5873,24 +5982,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="207" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.8902558024574673E-2</v>
+        <v>7.8493956032426218E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="207" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1060606060606058E-2</v>
+        <v>6.0753768844221102E-2</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F63" s="265">
         <f>Normalized_FCF!C90</f>
@@ -5899,18 +6008,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="193" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" s="271" t="s">
         <v>328</v>
       </c>
-      <c r="C65" s="271" t="s">
-        <v>330</v>
-      </c>
       <c r="D65" s="271" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
@@ -5965,7 +6074,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="203" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5978,18 +6087,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="455" t="s">
-        <v>487</v>
-      </c>
-      <c r="C73" s="455"/>
-      <c r="D73" s="455"/>
-      <c r="E73" s="455"/>
-      <c r="F73" s="455"/>
+      <c r="B73" s="460" t="s">
+        <v>484</v>
+      </c>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
       <c r="B74" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6003,13 +6112,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="455" t="s">
-        <v>273</v>
-      </c>
-      <c r="C77" s="455"/>
-      <c r="D77" s="455"/>
-      <c r="E77" s="455"/>
-      <c r="F77" s="455"/>
+      <c r="B77" s="460" t="s">
+        <v>272</v>
+      </c>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6032,7 +6141,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10191018455885338</v>
+        <v>-0.10189446859238584</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6042,7 +6151,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="192"/>
       <c r="B80" s="233" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C80" s="346">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6052,7 +6161,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="192"/>
       <c r="B81" s="233" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C81" s="347">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6065,7 +6174,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="192"/>
       <c r="B83" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6103,7 +6212,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8179101285928718</v>
+        <v>1.8176297815917777</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6140,7 +6249,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1653799464099258E-4</v>
+        <v>5.1645833730509284E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6153,11 +6262,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="192"/>
       <c r="B92" s="44" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>1.7165164820286594</v>
+        <v>1.7162517713366969</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6275,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="203" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6178,31 +6287,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="455" t="s">
-        <v>494</v>
-      </c>
-      <c r="C96" s="455"/>
-      <c r="D96" s="455"/>
-      <c r="E96" s="455"/>
-      <c r="F96" s="455"/>
+      <c r="B96" s="460" t="s">
+        <v>491</v>
+      </c>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="457" t="s">
-        <v>493</v>
-      </c>
-      <c r="C97" s="457"/>
-      <c r="D97" s="457"/>
-      <c r="E97" s="457"/>
-      <c r="F97" s="457"/>
+      <c r="B97" s="464" t="s">
+        <v>490</v>
+      </c>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="457" t="s">
-        <v>492</v>
-      </c>
-      <c r="C98" s="457"/>
-      <c r="D98" s="457"/>
-      <c r="E98" s="457"/>
-      <c r="F98" s="457"/>
+      <c r="B98" s="464" t="s">
+        <v>489</v>
+      </c>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6211,7 +6320,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C101" s="215">
         <f>E25+C103</f>
@@ -6220,7 +6329,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="233" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C102" s="270">
         <f>E25</f>
@@ -6229,7 +6338,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="233" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C103" s="270">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6247,40 +6356,40 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="257" t="s">
+        <v>282</v>
+      </c>
+      <c r="C106" s="117"/>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C106" s="117"/>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="455" t="s">
-        <v>286</v>
-      </c>
-      <c r="C107" s="455"/>
-      <c r="D107" s="455"/>
-      <c r="E107" s="455"/>
-      <c r="F107" s="455"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="455" t="s">
-        <v>287</v>
-      </c>
-      <c r="C108" s="455"/>
-      <c r="D108" s="455"/>
-      <c r="E108" s="455"/>
-      <c r="F108" s="455"/>
+      <c r="B108" s="460" t="s">
+        <v>285</v>
+      </c>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>1.2423523346862815</v>
+        <v>1.2421607466941946</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6289,11 +6398,11 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6301,17 +6410,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="455" t="s">
-        <v>500</v>
-      </c>
-      <c r="C114" s="455"/>
-      <c r="D114" s="455"/>
-      <c r="E114" s="455"/>
-      <c r="F114" s="455"/>
+      <c r="B114" s="460" t="s">
+        <v>497</v>
+      </c>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6346,7 +6455,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.91 HKD</v>
+        <v>7.79 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6368,7 +6477,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>6.72 HKD</v>
+        <v>6.63 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6390,7 +6499,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>6.51 HKD</v>
+        <v>6.42 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6412,7 +6521,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>6.3 HKD</v>
+        <v>6.22 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6434,7 +6543,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.49 HKD</v>
+        <v>4.44 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6442,13 +6551,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="456" t="s">
-        <v>362</v>
-      </c>
-      <c r="C124" s="456"/>
-      <c r="D124" s="456"/>
-      <c r="E124" s="456"/>
-      <c r="F124" s="456"/>
+      <c r="B124" s="461" t="s">
+        <v>359</v>
+      </c>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6456,7 +6565,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>6.4792427673148829</v>
+        <v>6.3918401764541954</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6464,17 +6573,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="460" t="s">
-        <v>363</v>
-      </c>
-      <c r="C127" s="460"/>
-      <c r="D127" s="460"/>
-      <c r="E127" s="460"/>
-      <c r="F127" s="460"/>
+      <c r="B127" s="463" t="s">
+        <v>360</v>
+      </c>
+      <c r="C127" s="463"/>
+      <c r="D127" s="463"/>
+      <c r="E127" s="463"/>
+      <c r="F127" s="463"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="203" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6483,22 +6592,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="458" t="s">
-        <v>288</v>
-      </c>
-      <c r="C131" s="458"/>
-      <c r="D131" s="458"/>
-      <c r="E131" s="458"/>
-      <c r="F131" s="458"/>
+      <c r="B131" s="465" t="s">
+        <v>286</v>
+      </c>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="455" t="s">
-        <v>364</v>
-      </c>
-      <c r="C132" s="455"/>
-      <c r="D132" s="455"/>
-      <c r="E132" s="455"/>
-      <c r="F132" s="455"/>
+      <c r="B132" s="460" t="s">
+        <v>361</v>
+      </c>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6529,33 +6638,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="193" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C138" s="218"/>
       <c r="D138" s="219"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="349" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="345" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C140" s="342">
         <f>Scenarios!C62</f>
@@ -6563,11 +6672,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>3.5551400643703057</v>
+        <v>3.5071825385208202</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>3.8669260726007586</v>
+        <v>3.8189685467512731</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6576,7 +6685,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="345" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C141" s="342">
         <f>Scenarios!C63</f>
@@ -6584,11 +6693,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.146715371081525</v>
+        <v>4.0907777129306853</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>4.494907371081525</v>
+        <v>4.4389697129306853</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6604,26 +6713,26 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="349" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="345" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C144" s="342">
         <f>Scenarios!C66</f>
@@ -6631,11 +6740,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.189277775479523</v>
+        <v>5.1192763357185838</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>5.5993325483005094</v>
+        <v>5.5293311085395693</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6644,7 +6753,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="345" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C145" s="342">
         <f>Scenarios!C67</f>
@@ -6652,11 +6761,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>5.6328689953346336</v>
+        <v>5.5568836739241325</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>6.0685375691850254</v>
+        <v>5.9925522477745243</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6665,7 +6774,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="203" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6674,114 +6783,102 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
-        <v>365</v>
-      </c>
-      <c r="C149" s="455"/>
-      <c r="D149" s="455"/>
-      <c r="E149" s="455"/>
-      <c r="F149" s="455"/>
+      <c r="B149" s="459" t="s">
+        <v>362</v>
+      </c>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="459" t="s">
-        <v>296</v>
-      </c>
-      <c r="C152" s="459"/>
-      <c r="D152" s="459"/>
-      <c r="E152" s="459"/>
-      <c r="F152" s="459"/>
+      <c r="B152" s="462" t="s">
+        <v>294</v>
+      </c>
+      <c r="C152" s="462"/>
+      <c r="D152" s="462"/>
+      <c r="E152" s="462"/>
+      <c r="F152" s="462"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="197" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="197" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="197" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="456" t="s">
-        <v>447</v>
-      </c>
-      <c r="C158" s="456"/>
-      <c r="D158" s="456"/>
-      <c r="E158" s="456"/>
-      <c r="F158" s="456"/>
+      <c r="B158" s="461" t="s">
+        <v>444</v>
+      </c>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
-        <v>297</v>
-      </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="B161" s="458" t="s">
+        <v>295</v>
+      </c>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
-        <v>298</v>
-      </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="B162" s="458" t="s">
+        <v>296</v>
+      </c>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="197" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="197" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="197" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6798,6 +6895,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7330,7 +7439,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C22" s="295">
         <v>4179313</v>
@@ -7364,7 +7473,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C23" s="295">
         <v>-1316832</v>
@@ -7398,7 +7507,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C24" s="295">
         <v>-3031620</v>
@@ -7467,7 +7576,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>188</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8754,7 +8863,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C64" s="278">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -9568,7 +9677,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9640,7 +9749,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C15" s="18">
         <v>80107</v>
@@ -10139,7 +10248,7 @@
         <v>113</v>
       </c>
       <c r="D45" s="165" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F45" s="230" t="s">
         <v>56</v>
@@ -10166,11 +10275,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.088680365713032</v>
+        <v>3.0882040482844384</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2423523346862815</v>
+        <v>1.2421607466941946</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10435,12 +10544,12 @@
         <v>-1267101.2385022666</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="231" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C74" s="232">
         <f>-$C$66/C73</f>
@@ -10464,12 +10573,12 @@
         <v>2534202.4770045332</v>
       </c>
       <c r="F75" s="227" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="233" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C76" s="234"/>
       <c r="D76" s="255">
@@ -10477,7 +10586,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="227" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10576,11 +10685,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923841.47422710015</v>
+        <v>923699.00503530004</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10191018455885338</v>
+        <v>0.10189446859238582</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10593,11 +10702,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16479812.89094539</v>
+        <v>16477271.474816011</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8179101285928718</v>
+        <v>1.8176297815917777</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10610,11 +10719,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4682.5469361000005</v>
+        <v>4681.8248223000001</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1653799464099258E-4</v>
+        <v>5.1645833730509284E-4</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10627,11 +10736,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>17408336.912108589</v>
+        <v>17405652.304673612</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>1.9203368511463663</v>
+        <v>1.9200407085214688</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -10752,7 +10861,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10762,7 +10871,7 @@
       <c r="E3" s="242"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11051,7 +11160,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C9" s="308">
         <f>C61</f>
@@ -11442,7 +11551,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C16" s="274">
         <f>-C4*C82</f>
@@ -11505,7 +11614,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="241" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="280"/>
@@ -11530,7 +11639,7 @@
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="241" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="281"/>
@@ -12145,7 +12254,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="306" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C35" s="284">
         <f>G35</f>
@@ -12213,7 +12322,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="306" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12286,7 +12395,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="239" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12425,7 +12534,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C46" s="274">
         <f>BS!D75*C51</f>
@@ -12480,7 +12589,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="252" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C47" s="286">
         <f>BS!$C$66*C51</f>
@@ -12950,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="240" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G60" s="274">
         <f>Data!C58</f>
@@ -13854,7 +13963,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="240" t="s">
-        <v>282</v>
+        <v>554</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -14190,7 +14299,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C91" s="300">
         <v>0</v>
@@ -14211,32 +14320,32 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1060606060606058E-2</v>
+        <v>6.0753768844221102E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2424242424242428E-2</v>
+        <v>8.2010050251256295E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1540404040404043E-2</v>
+        <v>7.1180904522613067E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.2020202020202026E-2</v>
+        <v>7.165829145728643E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11883838383838384</v>
+        <v>0.11824120603015076</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4772727272727282E-2</v>
+        <v>7.4396984924623127E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -14905,7 +15014,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C112" s="152"/>
       <c r="E112" s="242"/>
@@ -14957,7 +15066,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C113" s="152"/>
       <c r="E113" s="242"/>
@@ -15357,46 +15466,46 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31245412977731568</v>
+        <v>0.31240594500905638</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35101813630152412</v>
+        <v>0.3509640044276246</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.31533868262166259</v>
+        <v>0.3152900530152748</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.49425811778085194</v>
+        <v>0.4941818963115357</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.63005804298506884</v>
+        <v>0.62996087928039068</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.5470558263925509</v>
+        <v>0.54697146278295994</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.36513290546792748</v>
+        <v>0.36507659690050237</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.21376628830520339</v>
+        <v>0.21373332257333427</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>9.3896911031903563E-2</v>
+        <v>9.3882430823555671E-2</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>2.6292905525020161E-2</v>
+        <v>2.6288850793656907E-2</v>
       </c>
       <c r="P123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15414,46 +15523,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8902558024574673E-2</v>
+        <v>7.8493956032426218E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8640943510485889E-2</v>
+        <v>8.8181910660207183E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9630980460015807E-2</v>
+        <v>7.9218606285244922E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12481265600526564</v>
+        <v>0.12416630560591349</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15910556641037094</v>
+        <v>0.15828162795989717</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13814541070518963</v>
+        <v>0.13743001577461306</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.2205279158567549E-2</v>
+        <v>9.1727788165955365E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3981385935657419E-2</v>
+        <v>5.3701839842546298E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3711341169672617E-2</v>
+        <v>2.3588550458179817E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.6396226073283235E-3</v>
+        <v>6.6052388928786194E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15466,44 +15575,44 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1017906182737776</v>
+        <v>0.10127910762918574</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1657352363458414E-2</v>
+        <v>9.1196762653089264E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13783640630964186</v>
+        <v>0.13714376105180445</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1926240898325374</v>
+        <v>0.19165612958212264</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20715777510168226</v>
+        <v>0.20611678125695018</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10960313987383694</v>
+        <v>0.10905237032673222</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2461118131547651E-2</v>
+        <v>6.2147243166062481E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2319716341365878E-2</v>
+        <v>3.2157305706484639E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1313931450836676E-2</v>
+        <v>1.1257077523948049E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16250,15 +16359,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C4" s="283">
         <f>Normalized_FCF!C19</f>
@@ -16269,7 +16378,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F4" s="283">
         <f>-BS!G31</f>
@@ -16280,7 +16389,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="316" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="I4" s="313">
         <f>Normalized_FCF!C4</f>
@@ -16297,7 +16406,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F5" s="283">
         <f>BS!D66</f>
@@ -16308,7 +16417,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="316" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I5" s="313">
         <f>Normalized_FCF!C7</f>
@@ -16329,7 +16438,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F6" s="292">
         <f>BS!H42</f>
@@ -16340,7 +16449,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="316" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
@@ -16351,14 +16460,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="326" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C7" s="283">
         <f>F7</f>
         <v>14232912.522995466</v>
       </c>
       <c r="E7" s="141" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F7" s="291">
         <f>SUM(F4:F6)</f>
@@ -16369,7 +16478,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="320" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="I7" s="321">
         <f>Normalized_FCF!C9</f>
@@ -16381,7 +16490,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="137" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
@@ -16392,11 +16501,11 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="141" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7165164820286594</v>
+        <v>1.7162517713366969</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16421,7 +16530,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0932867000000002</v>
+        <v>1.0931181000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16442,18 +16551,18 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>54629279.237939194</v>
+        <v>54620854.644024782</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="H10" s="316" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I10" s="314">
         <f>Normalized_FCF!C41</f>
@@ -16464,11 +16573,11 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="137" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16589,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16495,25 +16604,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C14" s="317" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F14" s="317" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="140" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C15" s="149">
         <f>Scenarios!C45</f>
@@ -16528,7 +16637,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I15" s="127">
         <f>Terminal_Growth</f>
@@ -16538,49 +16647,49 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C16" s="148">
         <f>Scenarios!C46</f>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E16" s="316" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F16" s="319">
         <f>Scenarios!C41</f>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="316" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C17" s="314">
         <f>Normalized_FCF!C32</f>
         <v>0.68269686315429268</v>
       </c>
       <c r="E17" s="316" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F17" s="319">
         <f>Scenarios!C40</f>
         <v>0.68269686315429268</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="316" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C18" s="314">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="316" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F18" s="145">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16591,7 +16700,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.4797347344821565</v>
+        <v>6.3923675957201311</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16603,41 +16712,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="122" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B20" s="122" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="122" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D20" s="122" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="122" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F20" s="122" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G20" s="122" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="122" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J20" s="122" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="K20" s="122" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="L20" s="123" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16654,7 +16763,7 @@
       </c>
       <c r="D21" s="307">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E21" s="307">
         <f>$C$17</f>
@@ -16703,7 +16812,7 @@
       </c>
       <c r="D22" s="307">
         <f t="shared" si="1"/>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E22" s="307">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16752,7 +16861,7 @@
       </c>
       <c r="D23" s="307">
         <f t="shared" si="1"/>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E23" s="307">
         <f t="shared" si="6"/>
@@ -16809,7 +16918,7 @@
       </c>
       <c r="D24" s="307">
         <f t="shared" si="1"/>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E24" s="307">
         <f t="shared" si="6"/>
@@ -16866,7 +16975,7 @@
       </c>
       <c r="D25" s="307">
         <f t="shared" si="1"/>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E25" s="307">
         <f t="shared" si="6"/>
@@ -18192,7 +18301,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="323" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B51" s="324">
         <f>C15+1</f>
@@ -18223,12 +18332,12 @@
         <v>0</v>
       </c>
       <c r="I51" s="285">
-        <f>(G51+C51*H51)*(1-$I$10)/Equity_Cost</f>
-        <v>40244793.750869378</v>
+        <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
+        <v>39228424.509554625</v>
       </c>
       <c r="J51" s="424">
-        <f>(G51+C51*H51)*(1-$I$10)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>2.5908999762842999E-2</v>
+        <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
+        <v>0</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
@@ -18236,20 +18345,20 @@
       </c>
       <c r="L51" s="285">
         <f>I51*K51</f>
-        <v>28361108.526994426</v>
+        <v>27644857.909961406</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="463" t="s">
-        <v>429</v>
-      </c>
-      <c r="K52" s="463"/>
+      <c r="J52" s="466" t="s">
+        <v>426</v>
+      </c>
+      <c r="K52" s="466"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>39495378.823851019</v>
+        <v>38779128.206817999</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18273,7 +18382,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>39495378.823851019</v>
+        <v>38779128.206817999</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18308,19 +18417,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>22991992.239408404</v>
+        <v>22606308.385835495</v>
       </c>
       <c r="C56" s="119">
-        <v>38030952.57114657</v>
+        <v>37344475.905552879</v>
       </c>
       <c r="D56" s="119">
-        <v>39735566.701144479</v>
+        <v>39014426.395916536</v>
       </c>
       <c r="E56" s="119">
-        <v>41503815.361554481</v>
+        <v>40746625.074973531</v>
       </c>
       <c r="F56" s="119">
-        <v>51364714.006957784</v>
+        <v>50405009.160435244</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18334,19 +18443,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>17303587.46092274</v>
+        <v>17143093.941505715</v>
       </c>
       <c r="C57" s="119">
-        <v>39044984.937389858</v>
+        <v>38536537.404808506</v>
       </c>
       <c r="D57" s="119">
-        <v>42127098.567571491</v>
+        <v>41566006.506477706</v>
       </c>
       <c r="E57" s="119">
-        <v>45459485.015557408</v>
+        <v>44840892.511067405</v>
       </c>
       <c r="F57" s="119">
-        <v>66588889.841605693</v>
+        <v>65595156.271872133</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18360,19 +18469,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>14936487.842127807</v>
+        <v>14869702.132702215</v>
       </c>
       <c r="C58" s="285">
-        <v>39796040.69851777</v>
+        <v>39419452.671065323</v>
       </c>
       <c r="D58" s="119">
-        <v>43987859.274436772</v>
+        <v>43551294.713088393</v>
       </c>
       <c r="E58" s="119">
-        <v>48691100.161142245</v>
+        <v>48185736.19465626</v>
       </c>
       <c r="F58" s="119">
-        <v>82352876.710313052</v>
+        <v>81323907.844318882</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18395,19 +18504,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>13951473.444683544</v>
+        <v>13923682.09834332</v>
       </c>
       <c r="C59" s="285">
-        <v>40352319.546315514</v>
+        <v>40073394.911357567</v>
       </c>
       <c r="D59" s="119">
-        <v>45435646.969353318</v>
+        <v>45095972.556826845</v>
       </c>
       <c r="E59" s="119">
-        <v>51331193.334394284</v>
+        <v>50918332.304283679</v>
       </c>
       <c r="F59" s="119">
-        <v>98675814.956416398</v>
+        <v>97610361.439062446</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18430,19 +18539,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>13541582.219376165</v>
+        <v>13530017.485871872</v>
       </c>
       <c r="C60" s="285">
-        <v>40764334.435919009</v>
+        <v>40557745.41472064</v>
       </c>
       <c r="D60" s="119">
-        <v>46562115.946163833</v>
+        <v>46297828.102531157</v>
       </c>
       <c r="E60" s="119">
-        <v>53488038.023334056</v>
+        <v>53150747.987858765</v>
       </c>
       <c r="F60" s="119">
-        <v>115577523.59174928</v>
+        <v>114474291.76894274</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18465,19 +18574,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>13371015.355561882</v>
+        <v>13366202.956069319</v>
       </c>
       <c r="C61" s="285">
-        <v>41069498.419642329</v>
+        <v>40916485.675944962</v>
       </c>
       <c r="D61" s="119">
-        <v>47438578.952564552</v>
+        <v>47232946.553666785</v>
       </c>
       <c r="E61" s="119">
-        <v>55250089.09764424</v>
+        <v>54974537.375069574</v>
       </c>
       <c r="F61" s="119">
-        <v>133078524.36052203</v>
+        <v>131936174.70844549</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18574,23 +18683,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18606,23 +18715,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4893947365570916</v>
+        <v>4.4421953719798868</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>6.3031221265270831</v>
+        <v>6.219372465642544</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>6.508701852033929</v>
+        <v>6.4207406313289876</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>6.7219560236600797</v>
+        <v>6.6296148899486136</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>7.9111992671003559</v>
+        <v>7.7942548586227964</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18638,23 +18747,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>3.8033622366772835</v>
+        <v>3.7834228647980681</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>6.4254163700387261</v>
+        <v>6.3631151926728915</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>6.7971251708301548</v>
+        <v>6.7284186190481492</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>7.1990173522944252</v>
+        <v>7.123315229086467</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>9.7472640010930913</v>
+        <v>9.6259331496787066</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18670,23 +18779,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>3.5178854936915744</v>
+        <v>3.5092897446445139</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>6.5159951318217235</v>
+        <v>6.4695800421691043</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>7.0215364722616167</v>
+        <v>6.9678112518423507</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>7.5887563218839302</v>
+        <v>7.5266475679544902</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>11.648430978610962</v>
+        <v>11.522558152011349</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18702,23 +18811,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>3.3990908727370175</v>
+        <v>3.395215513030621</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>6.5830834251914752</v>
+        <v>6.5484345651938298</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>7.1961424383130046</v>
+        <v>7.1540736265444709</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>7.9071566098542743</v>
+        <v>7.8561530648735989</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>13.617008561681471</v>
+        <v>13.48643271286538</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18734,23 +18843,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>3.3496572067222585</v>
+        <v>3.3477461291378221</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>6.632773209183541</v>
+        <v>6.6068391544162859</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>7.3319967521834215</v>
+        <v>7.298997352160943</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>8.1672762060198192</v>
+        <v>8.1253451480192904</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>15.655386961051351</v>
+        <v>15.519941332664331</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18766,23 +18875,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3290865166015875</v>
+        <v>3.3279928301211892</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.669576569489192</v>
+        <v>6.6500972442683297</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>7.4376998676873312</v>
+        <v>7.4117570347331636</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>8.3797829369045225</v>
+        <v>8.3452637178333404</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>17.766041138336512</v>
+        <v>17.625553060227197</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18805,7 +18914,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="155" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G73" s="332"/>
       <c r="H73" s="332"/>
@@ -18829,7 +18938,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.9111992671003559</v>
+        <v>7.7942548586227964</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18857,7 +18966,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>6.7219560236600797</v>
+        <v>6.6296148899486136</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -18885,7 +18994,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>6.508701852033929</v>
+        <v>6.4207406313289876</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -18913,7 +19022,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>6.3031221265270831</v>
+        <v>6.219372465642544</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -18941,7 +19050,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.4893947365570916</v>
+        <v>4.4421953719798868</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19097,17 +19206,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="116"/>
-      <c r="E4" s="464" t="str">
+      <c r="E4" s="467" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C18&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C4&amp;"("&amp;Thesis!C5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 5-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国飞鹤(6186.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F4" s="464"/>
-      <c r="G4" s="464"/>
+      <c r="F4" s="467"/>
+      <c r="G4" s="467"/>
     </row>
     <row r="5" spans="2:7">
-      <c r="E5" s="464"/>
-      <c r="F5" s="464"/>
-      <c r="G5" s="464"/>
+      <c r="E5" s="467"/>
+      <c r="F5" s="467"/>
+      <c r="G5" s="467"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="146" t="s">
@@ -19117,9 +19226,9 @@
         <f>DCF!C3</f>
         <v>1000</v>
       </c>
-      <c r="E6" s="464"/>
-      <c r="F6" s="464"/>
-      <c r="G6" s="464"/>
+      <c r="E6" s="467"/>
+      <c r="F6" s="467"/>
+      <c r="G6" s="467"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19133,9 +19242,9 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="464"/>
-      <c r="F7" s="464"/>
-      <c r="G7" s="464"/>
+      <c r="E7" s="467"/>
+      <c r="F7" s="467"/>
+      <c r="G7" s="467"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19149,9 +19258,9 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="464"/>
-      <c r="F8" s="464"/>
-      <c r="G8" s="464"/>
+      <c r="E8" s="467"/>
+      <c r="F8" s="467"/>
+      <c r="G8" s="467"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19165,22 +19274,22 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="464"/>
-      <c r="F9" s="464"/>
-      <c r="G9" s="464"/>
+      <c r="E9" s="467"/>
+      <c r="F9" s="467"/>
+      <c r="G9" s="467"/>
     </row>
     <row r="10" spans="2:7">
-      <c r="E10" s="464"/>
-      <c r="F10" s="464"/>
-      <c r="G10" s="464"/>
+      <c r="E10" s="467"/>
+      <c r="F10" s="467"/>
+      <c r="G10" s="467"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="146" t="s">
-        <v>324</v>
-      </c>
-      <c r="E11" s="464"/>
-      <c r="F11" s="464"/>
-      <c r="G11" s="464"/>
+        <v>322</v>
+      </c>
+      <c r="E11" s="467"/>
+      <c r="F11" s="467"/>
+      <c r="G11" s="467"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19191,9 +19300,9 @@
         <v>-1.328292424848343E-2</v>
       </c>
       <c r="D12" s="145"/>
-      <c r="E12" s="464"/>
-      <c r="F12" s="464"/>
-      <c r="G12" s="464"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
+      <c r="G12" s="467"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="136" t="s">
@@ -19203,9 +19312,9 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-8.6152390653333799E-2</v>
       </c>
-      <c r="E13" s="464"/>
-      <c r="F13" s="464"/>
-      <c r="G13" s="464"/>
+      <c r="E13" s="467"/>
+      <c r="F13" s="467"/>
+      <c r="G13" s="467"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19215,13 +19324,13 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15727112921242259</v>
       </c>
-      <c r="E14" s="464"/>
-      <c r="F14" s="464"/>
-      <c r="G14" s="464"/>
+      <c r="E14" s="467"/>
+      <c r="F14" s="467"/>
+      <c r="G14" s="467"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19251,35 +19360,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E20" s="328"/>
       <c r="F20" s="328"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="154" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C21" s="154" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E21" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="155" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G21" s="155" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="310" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C22" s="333">
         <v>0.03</v>
@@ -19290,7 +19399,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>6.7219560236600797</v>
+        <v>6.6296148899486136</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19303,7 +19412,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="310" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C23" s="333">
         <v>0.02</v>
@@ -19314,7 +19423,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>6.508701852033929</v>
+        <v>6.4207406313289876</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19326,7 +19435,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="310" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C24" s="333">
         <v>0.01</v>
@@ -19337,7 +19446,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>6.3031221265270831</v>
+        <v>6.219372465642544</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19349,11 +19458,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="142" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.5102367412577902</v>
+        <v>6.4222418499156237</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19363,33 +19472,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="154" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C28" s="154" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D28" s="154" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E28" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="155" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G28" s="155" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="310" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C29" s="333">
         <v>0.08</v>
@@ -19400,7 +19509,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>7.9111992671003559</v>
+        <v>7.7942548586227964</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19412,7 +19521,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="323" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C30" s="333">
         <v>-0.1</v>
@@ -19423,7 +19532,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>4.4893947365570916</v>
+        <v>4.4421953719798868</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19439,12 +19548,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="146" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C33" s="156">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19455,7 +19564,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
@@ -19468,62 +19577,62 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.33366695029787058</v>
+        <v>0.32175851586770188</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>7.6329705858594984E-2</v>
+        <v>6.952575301434466E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.4792427673148829</v>
+        <v>6.3918401764541954</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F36" s="340" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19542,29 +19651,29 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C40" s="139">
         <f>DCF!C17</f>
         <v>0.68269686315429268</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C41" s="139">
         <f>DCF!C16</f>
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="E41" s="97"/>
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -19590,7 +19699,7 @@
       </c>
       <c r="D45" s="138"/>
       <c r="E45" s="225" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -19598,7 +19707,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="139">
-        <v>1.8613012126595961E-2</v>
+        <v>1.8613012126595999E-2</v>
       </c>
       <c r="D46" s="139"/>
       <c r="E46" s="225" t="s">
@@ -19611,7 +19720,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>6.4797347344821565</v>
+        <v>6.3923675957201311</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19623,7 +19732,7 @@
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E49" s="226" t="s">
         <v>255</v>
@@ -19670,11 +19779,11 @@
         <v>N</v>
       </c>
       <c r="E53" s="127" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.29638291388519605</v>
+        <v>0.30038934884423074</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19704,7 +19813,7 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C58" s="156">
         <f>C33</f>
@@ -19717,13 +19826,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E60" s="422"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="154" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>103</v>
@@ -19736,15 +19845,15 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="155" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="310" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C62" s="120">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
@@ -19752,11 +19861,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.5551400643703057</v>
+        <v>3.5071825385208202</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>3.8669260726007586</v>
+        <v>3.8189685467512731</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19764,12 +19873,12 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.40318240703870345</v>
+        <v>0.40252439965265141</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="310" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C63" s="120">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
@@ -19777,11 +19886,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.146715371081525</v>
+        <v>4.0907777129306853</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>4.494907371081525</v>
+        <v>4.4389697129306853</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19789,12 +19898,12 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.30626038682228651</v>
+        <v>0.30552554657379494</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="154" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>103</v>
@@ -19807,15 +19916,15 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="155" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G65" s="155" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="310" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C66" s="120">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
@@ -19823,11 +19932,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.189277775479523</v>
+        <v>5.1192763357185838</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>5.5993325483005094</v>
+        <v>5.5293311085395693</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19835,12 +19944,12 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.13587009688784835</v>
+        <v>0.135010459623503</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="310" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C67" s="120">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
@@ -19848,11 +19957,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.6328689953346336</v>
+        <v>5.5568836739241325</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>6.0685375691850254</v>
+        <v>5.9925522477745243</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19860,7 +19969,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>6.33878391162771E-2</v>
+        <v>6.2468384323897785E-2</v>
       </c>
     </row>
   </sheetData>
@@ -19874,29 +19983,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
-  <dimension ref="B2:E2"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="5" width="20.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -19913,7 +19999,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="354" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B2" s="354"/>
       <c r="C2" s="354"/>
@@ -19927,7 +20013,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="445" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F3" s="446">
         <f>Thesis!F3</f>
@@ -19936,7 +20022,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="432" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
@@ -19944,7 +20030,7 @@
       </c>
       <c r="D4" s="358"/>
       <c r="E4" s="444" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
@@ -19953,14 +20039,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="352" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C5" s="364" t="str">
         <f>Thesis!C5</f>
         <v>6186.HK</v>
       </c>
       <c r="E5" s="448" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
@@ -19969,7 +20055,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="359" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C6" s="361" t="str">
         <f>Thesis!C6</f>
@@ -19979,7 +20065,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="352" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C7" s="361" t="str">
         <f>Market_currency</f>
@@ -19990,23 +20076,23 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="360" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.33366695029787058</v>
+        <v>0.32175851586770188</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="360" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C9" s="362">
         <f>Common_Shares</f>
@@ -20015,11 +20101,11 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="360" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>35898.396747839994</v>
+        <v>36079.701781919997</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20028,31 +20114,31 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="466" t="s">
-        <v>506</v>
-      </c>
-      <c r="C12" s="466"/>
-      <c r="D12" s="466"/>
-      <c r="E12" s="466"/>
-      <c r="F12" s="466"/>
+      <c r="B12" s="472" t="s">
+        <v>503</v>
+      </c>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C14" s="357"/>
       <c r="D14" s="358"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="352" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C15" s="367" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="360" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E15" s="353" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20061,30 +20147,30 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="352" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C16" s="367" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="360" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0932867000000002</v>
+        <v>1.0931181000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C17" s="434">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="D17" s="360" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E17" s="353" t="str">
         <f>Reporting_currency</f>
@@ -20098,10 +20184,10 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>6.4792427673148829</v>
+        <v>6.3918401764541954</v>
       </c>
       <c r="D18" s="359" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E18" s="436">
         <f>Thesis!E18</f>
@@ -20110,14 +20196,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="359" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C19" s="361" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="352" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E19" s="437">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20130,14 +20216,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="356" t="s">
-        <v>344</v>
+        <v>499</v>
       </c>
       <c r="C21" s="370" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="371" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E21" s="372">
         <f>Holding_Period</f>
@@ -20146,14 +20232,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="352" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>3.8669260726007586</v>
+        <v>3.8189685467512731</v>
       </c>
       <c r="D22" s="374" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E22" s="375">
         <f>Thesis!E22</f>
@@ -20162,14 +20248,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="352" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>4.494907371081525</v>
+        <v>4.4389697129306853</v>
       </c>
       <c r="D23" s="374" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E23" s="377">
         <f>Thesis!E23</f>
@@ -20178,14 +20264,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="352" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>5.5993325483005094</v>
+        <v>5.5293311085395693</v>
       </c>
       <c r="D24" s="374" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E24" s="377">
         <f>Thesis!E24</f>
@@ -20194,14 +20280,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="352" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>6.0685375691850254</v>
+        <v>5.9925522477745243</v>
       </c>
       <c r="D25" s="374" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E25" s="377">
         <f>Thesis!E25</f>
@@ -20210,7 +20296,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="354" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B27" s="354"/>
       <c r="C27" s="354"/>
@@ -20219,26 +20305,26 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="466" t="s">
-        <v>507</v>
-      </c>
-      <c r="C29" s="466"/>
-      <c r="D29" s="466"/>
-      <c r="E29" s="466"/>
-      <c r="F29" s="466"/>
+      <c r="B29" s="472" t="s">
+        <v>504</v>
+      </c>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
-        <v>508</v>
-      </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="B30" s="475" t="s">
+        <v>505</v>
+      </c>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C32" s="379">
         <f>scaling_factor</f>
@@ -20246,13 +20332,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="465" t="s">
-        <v>509</v>
-      </c>
-      <c r="C33" s="465"/>
-      <c r="D33" s="465"/>
-      <c r="E33" s="465"/>
-      <c r="F33" s="465"/>
+      <c r="B33" s="468" t="s">
+        <v>506</v>
+      </c>
+      <c r="C33" s="468"/>
+      <c r="D33" s="468"/>
+      <c r="E33" s="468"/>
+      <c r="F33" s="468"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="381" t="s">
@@ -20272,13 +20358,13 @@
       <c r="C35" s="383"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="465" t="s">
-        <v>510</v>
-      </c>
-      <c r="C36" s="465"/>
-      <c r="D36" s="465"/>
-      <c r="E36" s="465"/>
-      <c r="F36" s="465"/>
+      <c r="B36" s="468" t="s">
+        <v>507</v>
+      </c>
+      <c r="C36" s="468"/>
+      <c r="D36" s="468"/>
+      <c r="E36" s="468"/>
+      <c r="F36" s="468"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="381" t="s">
@@ -20307,13 +20393,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="465" t="s">
-        <v>511</v>
-      </c>
-      <c r="C40" s="465"/>
-      <c r="D40" s="465"/>
-      <c r="E40" s="465"/>
-      <c r="F40" s="465"/>
+      <c r="B40" s="468" t="s">
+        <v>508</v>
+      </c>
+      <c r="C40" s="468"/>
+      <c r="D40" s="468"/>
+      <c r="E40" s="468"/>
+      <c r="F40" s="468"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="381" t="s">
@@ -20329,17 +20415,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="465" t="s">
-        <v>512</v>
-      </c>
-      <c r="C43" s="465"/>
-      <c r="D43" s="465"/>
-      <c r="E43" s="465"/>
-      <c r="F43" s="465"/>
+      <c r="B43" s="468" t="s">
+        <v>509</v>
+      </c>
+      <c r="C43" s="468"/>
+      <c r="D43" s="468"/>
+      <c r="E43" s="468"/>
+      <c r="F43" s="468"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="381" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C44" s="385">
         <f>Normalized_FCF!C46</f>
@@ -20354,7 +20440,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C45" s="385">
         <f>Normalized_FCF!C45</f>
@@ -20382,7 +20468,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20399,17 +20485,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="465" t="s">
-        <v>514</v>
-      </c>
-      <c r="C51" s="465"/>
-      <c r="D51" s="465"/>
-      <c r="E51" s="465"/>
-      <c r="F51" s="465"/>
+      <c r="B51" s="468" t="s">
+        <v>511</v>
+      </c>
+      <c r="C51" s="468"/>
+      <c r="D51" s="468"/>
+      <c r="E51" s="468"/>
+      <c r="F51" s="468"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="381" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C52" s="382">
         <f>Normalized_FCF!C12</f>
@@ -20421,13 +20507,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="465" t="s">
-        <v>515</v>
-      </c>
-      <c r="C54" s="468"/>
-      <c r="D54" s="468"/>
-      <c r="E54" s="468"/>
-      <c r="F54" s="468"/>
+      <c r="B54" s="468" t="s">
+        <v>512</v>
+      </c>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20443,26 +20529,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="466" t="s">
-        <v>516</v>
-      </c>
-      <c r="C57" s="466"/>
-      <c r="D57" s="466"/>
-      <c r="E57" s="466"/>
-      <c r="F57" s="466"/>
+      <c r="B57" s="472" t="s">
+        <v>513</v>
+      </c>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="466" t="s">
-        <v>517</v>
-      </c>
-      <c r="C58" s="466"/>
-      <c r="D58" s="466"/>
-      <c r="E58" s="466"/>
-      <c r="F58" s="466"/>
+      <c r="B58" s="472" t="s">
+        <v>514</v>
+      </c>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C60" s="382">
         <f>Normalized_FCF!G19</f>
@@ -20488,24 +20574,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="386" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>7.8902558024574673E-2</v>
+        <v>7.8493956032426218E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="386" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>6.1060606060606058E-2</v>
+        <v>6.0753768844221102E-2</v>
       </c>
       <c r="E63" s="381" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F63" s="389">
         <f>Normalized_FCF!C90</f>
@@ -20514,18 +20600,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="378" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C65" s="390" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D65" s="390" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="381" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C66" s="387">
         <f>Normalized_FCF!C119</f>
@@ -20580,7 +20666,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="354" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B71" s="354"/>
       <c r="C71" s="354"/>
@@ -20593,36 +20679,36 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="466" t="s">
-        <v>518</v>
-      </c>
-      <c r="C73" s="466"/>
-      <c r="D73" s="466"/>
-      <c r="E73" s="466"/>
-      <c r="F73" s="466"/>
+      <c r="B73" s="472" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="467" t="s">
-        <v>488</v>
-      </c>
-      <c r="C74" s="467"/>
-      <c r="D74" s="467"/>
-      <c r="E74" s="467"/>
-      <c r="F74" s="467"/>
+      <c r="B74" s="475" t="s">
+        <v>485</v>
+      </c>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="466" t="s">
-        <v>519</v>
-      </c>
-      <c r="C77" s="466"/>
-      <c r="D77" s="466"/>
-      <c r="E77" s="466"/>
-      <c r="F77" s="466"/>
+      <c r="B77" s="472" t="s">
+        <v>516</v>
+      </c>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20643,7 +20729,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10191018455885338</v>
+        <v>-0.10189446859238584</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20652,7 +20738,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="B80" s="391" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C80" s="397">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -20661,7 +20747,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="391" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C81" s="398">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -20670,7 +20756,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20688,7 +20774,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="391" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C85" s="399">
         <f>BS!C66</f>
@@ -20705,7 +20791,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8179101285928718</v>
+        <v>1.8176297815917777</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20714,7 +20800,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20736,7 +20822,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1653799464099258E-4</v>
+        <v>5.1645833730509284E-4</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20745,11 +20831,11 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="381" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>1.7165164820286594</v>
+        <v>1.7162517713366969</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20758,7 +20844,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="354" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B94" s="354"/>
       <c r="C94" s="354"/>
@@ -20771,33 +20857,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="466" t="s">
-        <v>522</v>
-      </c>
-      <c r="C96" s="466"/>
-      <c r="D96" s="466"/>
-      <c r="E96" s="466"/>
-      <c r="F96" s="466"/>
+      <c r="B96" s="472" t="s">
+        <v>519</v>
+      </c>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="467" t="s">
-        <v>523</v>
-      </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="B97" s="475" t="s">
+        <v>520</v>
+      </c>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="467" t="s">
-        <v>524</v>
-      </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="B98" s="475" t="s">
+        <v>521</v>
+      </c>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20805,7 +20891,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="394"/>
       <c r="B100" s="378" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -20821,7 +20907,7 @@
     <row r="102" spans="1:6">
       <c r="A102" s="394"/>
       <c r="B102" s="391" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C102" s="392">
         <f>E25</f>
@@ -20831,7 +20917,7 @@
     <row r="103" spans="1:6">
       <c r="A103" s="394"/>
       <c r="B103" s="391" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C103" s="392">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -20841,7 +20927,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -20854,29 +20940,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="394"/>
       <c r="B106" s="402" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C106" s="401"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="466" t="s">
-        <v>525</v>
-      </c>
-      <c r="C107" s="466"/>
-      <c r="D107" s="466"/>
-      <c r="E107" s="466"/>
-      <c r="F107" s="466"/>
+      <c r="B107" s="472" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="466" t="s">
-        <v>544</v>
-      </c>
-      <c r="C108" s="466"/>
-      <c r="D108" s="466"/>
-      <c r="E108" s="466"/>
-      <c r="F108" s="466"/>
+      <c r="B108" s="472" t="s">
+        <v>541</v>
+      </c>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20884,17 +20970,17 @@
     <row r="110" spans="1:6">
       <c r="A110" s="394"/>
       <c r="B110" s="378" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="394"/>
       <c r="B111" s="384" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>1.2423523346862815</v>
+        <v>1.2421607466941946</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -20904,11 +20990,11 @@
     <row r="112" spans="1:6">
       <c r="A112" s="394"/>
       <c r="B112" s="381" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>6.0262286168881865</v>
+        <v>6.0252992887029917</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -20920,13 +21006,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="466" t="s">
-        <v>526</v>
-      </c>
-      <c r="C114" s="466"/>
-      <c r="D114" s="466"/>
-      <c r="E114" s="466"/>
-      <c r="F114" s="466"/>
+      <c r="B114" s="472" t="s">
+        <v>523</v>
+      </c>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -20934,25 +21020,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="394"/>
       <c r="B116" s="378" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="394"/>
       <c r="B117" s="351" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C117" s="351" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D117" s="351" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="351" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F117" s="351" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -20971,7 +21057,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.91 HKD</v>
+        <v>7.79 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -20994,7 +21080,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>6.72 HKD</v>
+        <v>6.63 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21016,7 +21102,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>6.51 HKD</v>
+        <v>6.42 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21038,7 +21124,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>6.3 HKD</v>
+        <v>6.22 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21060,7 +21146,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>4.49 HKD</v>
+        <v>4.44 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21068,13 +21154,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="465" t="s">
-        <v>527</v>
-      </c>
-      <c r="C124" s="465"/>
-      <c r="D124" s="465"/>
-      <c r="E124" s="465"/>
-      <c r="F124" s="465"/>
+      <c r="B124" s="468" t="s">
+        <v>524</v>
+      </c>
+      <c r="C124" s="468"/>
+      <c r="D124" s="468"/>
+      <c r="E124" s="468"/>
+      <c r="F124" s="468"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="381" t="s">
@@ -21082,7 +21168,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>6.4792427673148829</v>
+        <v>6.3918401764541954</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21091,7 +21177,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="470" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C127" s="470"/>
       <c r="D127" s="470"/>
@@ -21100,7 +21186,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B129" s="354"/>
       <c r="C129" s="354"/>
@@ -21110,7 +21196,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="471" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C131" s="471"/>
       <c r="D131" s="471"/>
@@ -21118,22 +21204,22 @@
       <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="466" t="s">
-        <v>530</v>
-      </c>
-      <c r="C132" s="466"/>
-      <c r="D132" s="466"/>
-      <c r="E132" s="466"/>
-      <c r="F132" s="466"/>
+      <c r="B132" s="472" t="s">
+        <v>527</v>
+      </c>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="352" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C135" s="414">
         <f>E21</f>
@@ -21142,7 +21228,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="352" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C136" s="415">
         <f>Scenarios!C58</f>
@@ -21155,33 +21241,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="378" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C138" s="416"/>
       <c r="D138" s="416"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="349" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="417" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C140" s="418">
         <f>Scenarios!C62</f>
@@ -21189,11 +21275,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>3.5551400643703057</v>
+        <v>3.5071825385208202</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>3.8669260726007586</v>
+        <v>3.8189685467512731</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21202,7 +21288,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="417" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C141" s="418">
         <f>Scenarios!C63</f>
@@ -21210,11 +21296,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.146715371081525</v>
+        <v>4.0907777129306853</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>4.494907371081525</v>
+        <v>4.4389697129306853</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21223,26 +21309,26 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="349" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="417" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C144" s="418">
         <f>Scenarios!C66</f>
@@ -21250,11 +21336,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.189277775479523</v>
+        <v>5.1192763357185838</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>5.5993325483005094</v>
+        <v>5.5293311085395693</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21263,7 +21349,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="417" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C145" s="418">
         <f>Scenarios!C67</f>
@@ -21271,11 +21357,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>5.6328689953346336</v>
+        <v>5.5568836739241325</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>6.0685375691850254</v>
+        <v>5.9925522477745243</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21284,7 +21370,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="354" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B147" s="354"/>
       <c r="C147" s="354"/>
@@ -21293,65 +21379,65 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="472" t="s">
-        <v>531</v>
-      </c>
-      <c r="C149" s="466"/>
-      <c r="D149" s="466"/>
-      <c r="E149" s="466"/>
-      <c r="F149" s="466"/>
+      <c r="B149" s="473" t="s">
+        <v>528</v>
+      </c>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="468" t="s">
-        <v>532</v>
-      </c>
-      <c r="C152" s="468"/>
-      <c r="D152" s="468"/>
-      <c r="E152" s="468"/>
-      <c r="F152" s="468"/>
+      <c r="B152" s="474" t="s">
+        <v>529</v>
+      </c>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="421" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="421" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="465" t="s">
-        <v>448</v>
-      </c>
-      <c r="C158" s="465"/>
-      <c r="D158" s="465"/>
-      <c r="E158" s="465"/>
-      <c r="F158" s="465"/>
+      <c r="B158" s="468" t="s">
+        <v>445</v>
+      </c>
+      <c r="C158" s="468"/>
+      <c r="D158" s="468"/>
+      <c r="E158" s="468"/>
+      <c r="F158" s="468"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="469" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C161" s="469"/>
       <c r="D161" s="469"/>
@@ -21360,7 +21446,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="469" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C162" s="469"/>
       <c r="D162" s="469"/>
@@ -21369,35 +21455,32 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="421" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="421" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="421" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21412,12 +21495,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21436,4 +21522,28 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7863D3CA-A3C6-44A1-B68F-4C39E6E16D28}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" style="457" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="457" customWidth="1"/>
+    <col min="3" max="5" width="20.6640625" style="457" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="457"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="455" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2" s="456"/>
+      <c r="D2" s="456"/>
+      <c r="E2" s="456"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BFACE7-AE6D-4945-8BCA-5E0EEEEE441C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A619CB48-CDAC-44F4-AF80-4525B097D47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3824,6 +3824,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4987,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5020,6 +5021,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5029,16 +5039,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5507,13 +5508,6 @@
       <c r="C9" s="48">
         <v>9065251704</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E9" s="311">
-        <f>Scenarios!F34</f>
-        <v>0.32175851586770188</v>
-      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
@@ -5523,19 +5517,26 @@
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>36079.701781919997</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E10" s="311">
+        <f>Scenarios!F34</f>
+        <v>0.32175851586770188</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5713,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5740,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5766,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5801,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5823,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5893,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5915,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5937,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6087,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6112,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6287,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6361,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6410,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6551,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6592,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6783,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6826,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6840,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6879,6 +6880,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6895,18 +6908,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20114,13 +20115,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20305,22 +20306,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20510,10 +20511,10 @@
       <c r="B54" s="468" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20529,22 +20530,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20679,22 +20680,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20702,13 +20703,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20857,33 +20858,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20946,23 +20947,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>522</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>541</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21006,13 +21007,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21176,13 +21177,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21195,22 +21196,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21379,13 +21380,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21393,13 +21394,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21436,22 +21437,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21475,12 +21476,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21495,15 +21499,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A619CB48-CDAC-44F4-AF80-4525B097D47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F4D37-1FFA-4DDE-8AE6-B71EE56EBB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,25 +5021,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5497,7 +5497,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>36079.701781919997</v>
+        <v>36261.006816000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>0.32175851586770188</v>
+        <v>0.31835640522615205</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5571,7 +5571,7 @@
         <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0931181000000001</v>
+        <v>1.0930900000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>6.3918401764541954</v>
+        <v>6.3916758660206225</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>349</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>3.8189685467512731</v>
+        <v>3.8188783901347723</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>411</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>4.4389697129306853</v>
+        <v>4.4388645542531986</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>412</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>5.5293311085395693</v>
+        <v>5.5291995109884606</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>413</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>5.9925522477745243</v>
+        <v>5.99240940096663</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>414</v>
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.8493956032426218E-2</v>
+        <v>7.8099478553586621E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0753768844221102E-2</v>
+        <v>6.0449999999999997E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189446859238584</v>
+        <v>-0.10189184926464123</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8176297815917777</v>
+        <v>1.8175830570915956</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1645833730509284E-4</v>
+        <v>5.1644506108244306E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>1.7162517713366969</v>
+        <v>1.7162076528880366</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
+      <c r="B97" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
+      <c r="B98" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>1.2421607466941946</v>
+        <v>1.2421288153621801</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="460" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>6.3918401764541954</v>
+        <v>6.3916758660206225</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6673,11 +6673,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>3.5071825385208202</v>
+        <v>3.5070923819043194</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>3.8189685467512731</v>
+        <v>3.8188783901347723</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.0907777129306853</v>
+        <v>4.0906725542531985</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>4.4389697129306853</v>
+        <v>4.4388645542531986</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6741,11 +6741,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.1192763357185838</v>
+        <v>5.1191447381674751</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>5.5293311085395693</v>
+        <v>5.5291995109884606</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6762,11 +6762,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>5.5568836739241325</v>
+        <v>5.5567408271162382</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>5.9925522477745243</v>
+        <v>5.99240940096663</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="461" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="464" t="s">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,18 +6880,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6908,6 +6896,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10276,11 +10276,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0882040482844384</v>
+        <v>3.0881246620463396</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2421607466941946</v>
+        <v>1.2421288153621801</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10686,11 +10686,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923699.00503530004</v>
+        <v>923675.26017000014</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10189446859238582</v>
+        <v>0.10189184926464125</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10703,11 +10703,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16477271.474816011</v>
+        <v>16476847.905461116</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8176297815917777</v>
+        <v>1.8175830570915954</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10720,11 +10720,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4681.8248223000001</v>
+        <v>4681.7044700000006</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1645833730509284E-4</v>
+        <v>5.1644506108244306E-4</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10737,11 +10737,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>17405652.304673612</v>
+        <v>17405204.870101117</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>1.9200407085214688</v>
+        <v>1.919991351417319</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -14325,28 +14325,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0753768844221102E-2</v>
+        <v>6.0449999999999997E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2010050251256295E-2</v>
+        <v>8.1600000000000006E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1180904522613067E-2</v>
+        <v>7.0824999999999999E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.165829145728643E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11824120603015076</v>
+        <v>0.11765</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4396984924623127E-2</v>
+        <v>7.4025000000000007E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15467,46 +15467,46 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31240594500905638</v>
+        <v>0.31239791421434654</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.3509640044276246</v>
+        <v>0.35095498244864132</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.3152900530152748</v>
+        <v>0.31528194808087678</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.4941818963115357</v>
+        <v>0.49416919273331633</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.62996087928039068</v>
+        <v>0.62994468532961101</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.54697146278295994</v>
+        <v>0.54695740218136146</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.36507659690050237</v>
+        <v>0.36506721213926491</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.21373332257333427</v>
+        <v>0.21372782828468942</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>9.3882430823555671E-2</v>
+        <v>9.3880017455497691E-2</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>2.6288850793656907E-2</v>
+        <v>2.6288175005096365E-2</v>
       </c>
       <c r="P123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15524,46 +15524,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8493956032426218E-2</v>
+        <v>7.8099478553586621E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8181910660207183E-2</v>
+        <v>8.7738745612160329E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9218606285244922E-2</v>
+        <v>7.8820487020219196E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12416630560591349</v>
+        <v>0.12354229818332908</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15828162795989717</v>
+        <v>0.15748617133240275</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13743001577461306</v>
+        <v>0.13673935054534037</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1727788165955365E-2</v>
+        <v>9.1266803034816227E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3701839842546298E-2</v>
+        <v>5.3431957071172355E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3588550458179817E-2</v>
+        <v>2.3470004363874423E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.6052388928786194E-3</v>
+        <v>6.5720437512740912E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15581,39 +15581,39 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10127910762918574</v>
+        <v>0.1007727120910398</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1196762653089264E-2</v>
+        <v>9.0740778839823816E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13714376105180445</v>
+        <v>0.13645804224654542</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19165612958212264</v>
+        <v>0.19069784893421202</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20611678125695018</v>
+        <v>0.20508619735066541</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10905237032673222</v>
+        <v>0.10850710847509855</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2147243166062481E-2</v>
+        <v>6.183650695023217E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2157305706484639E-2</v>
+        <v>3.1996519177952217E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1257077523948049E-2</v>
+        <v>1.1200792136328309E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7162517713366969</v>
+        <v>1.7162076528880366</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0931181000000001</v>
+        <v>1.0930900000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>54620854.644024782</v>
+        <v>54619450.54503905</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3923675957201311</v>
+        <v>6.3922032717285706</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18684,23 +18684,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18716,23 +18716,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4421953719798868</v>
+        <v>4.4420811796616437</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>6.219372465642544</v>
+        <v>6.2192125887122431</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>6.4207406313289876</v>
+        <v>6.4205755779722278</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>6.6296148899486136</v>
+        <v>6.629444467211667</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>7.7942548586227964</v>
+        <v>7.794054497324665</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>3.7834228647980681</v>
+        <v>3.7833256070703798</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>6.3631151926728915</v>
+        <v>6.3629516206517955</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>6.7284186190481492</v>
+        <v>6.7282456564348729</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>7.123315229086467</v>
+        <v>7.1231321151503453</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>9.6259331496787066</v>
+        <v>9.6256857027454732</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>3.5092897446445139</v>
+        <v>3.5091995338595816</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>6.4695800421691043</v>
+        <v>6.4694137333327717</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>6.9678112518423507</v>
+        <v>6.9676321353350161</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>7.5266475679544902</v>
+        <v>7.5264540858443141</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>11.522558152011349</v>
+        <v>11.522261949904669</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18812,23 +18812,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>3.395215513030621</v>
+        <v>3.3951282346698326</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>6.5484345651938298</v>
+        <v>6.5482662293010456</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>7.1540736265444709</v>
+        <v>7.1538897219243704</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>7.8561530648735989</v>
+        <v>7.8559511124028436</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>13.48643271286538</v>
+        <v>13.486086026849266</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>3.3477461291378221</v>
+        <v>3.3476600710383098</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>6.6068391544162859</v>
+        <v>6.6066693171587749</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>7.298997352160943</v>
+        <v>7.2988097220909669</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>8.1253451480192904</v>
+        <v>8.1251362756214593</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>15.519941332664331</v>
+        <v>15.519542372706164</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18876,23 +18876,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3279928301211892</v>
+        <v>3.3279072798055132</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.6500972442683297</v>
+        <v>6.6499262950062477</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>7.4117570347331636</v>
+        <v>7.4115665060312095</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>8.3452637178333404</v>
+        <v>8.345049192147167</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>17.625553060227197</v>
+        <v>17.625099972824298</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.7942548586227964</v>
+        <v>7.794054497324665</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>6.6296148899486136</v>
+        <v>6.629444467211667</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>6.4207406313289876</v>
+        <v>6.4205755779722278</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>6.219372465642544</v>
+        <v>6.2192125887122431</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.4421953719798868</v>
+        <v>4.4420811796616437</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>6.6296148899486136</v>
+        <v>6.629444467211667</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>6.4207406313289876</v>
+        <v>6.4205755779722278</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>6.219372465642544</v>
+        <v>6.2192125887122431</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4222418499156237</v>
+        <v>6.4220767579681182</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19510,7 +19510,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>7.7942548586227964</v>
+        <v>7.794054497324665</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>4.4421953719798868</v>
+        <v>4.4420811796616437</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.32175851586770188</v>
+        <v>0.31835640522615205</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.952575301434466E-2</v>
+        <v>6.952677020620103E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3918401764541954</v>
+        <v>6.3916758660206225</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>6.3923675957201311</v>
+        <v>6.3922032717285706</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.30038934884423074</v>
+        <v>0.30038934884423069</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19862,11 +19862,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.5071825385208202</v>
+        <v>3.5070923819043194</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>3.8189685467512731</v>
+        <v>3.8188783901347723</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.40252439965265141</v>
+        <v>0.40252314570007164</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19887,11 +19887,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.0907777129306853</v>
+        <v>4.0906725542531985</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>4.4389697129306853</v>
+        <v>4.4388645542531986</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.30552554657379494</v>
+        <v>0.30552414620224166</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19933,11 +19933,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.1192763357185838</v>
+        <v>5.1191447381674751</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>5.5293311085395693</v>
+        <v>5.5291995109884606</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.135010459623503</v>
+        <v>0.13500881058601533</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19958,11 +19958,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.5568836739241325</v>
+        <v>5.5567408271162382</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>5.9925522477745243</v>
+        <v>5.99240940096663</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>6.2468384323897785E-2</v>
+        <v>6.2466632135801836E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20081,14 +20081,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="D8" s="352" t="s">
         <v>534</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.32175851586770188</v>
+        <v>0.31835640522615205</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>36079.701781919997</v>
+        <v>36261.006816000001</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20115,13 +20115,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="472" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0931181000000001</v>
+        <v>1.0930900000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>6.3918401764541954</v>
+        <v>6.3916758660206225</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>364</v>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>3.8189685467512731</v>
+        <v>3.8188783901347723</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>446</v>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>4.4389697129306853</v>
+        <v>4.4388645542531986</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>447</v>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>5.5293311085395693</v>
+        <v>5.5291995109884606</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>449</v>
@@ -20285,7 +20285,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>5.9925522477745243</v>
+        <v>5.99240940096663</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>448</v>
@@ -20306,22 +20306,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="472" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="470" t="s">
+      <c r="B30" s="475" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20511,10 +20511,10 @@
       <c r="B54" s="468" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20530,22 +20530,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>7.8493956032426218E-2</v>
+        <v>7.8099478553586621E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>6.0753768844221102E-2</v>
+        <v>6.0449999999999997E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>375</v>
@@ -20680,22 +20680,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
+      <c r="B74" s="475" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20703,13 +20703,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189446859238584</v>
+        <v>-0.10189184926464123</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8176297815917777</v>
+        <v>1.8175830570915956</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1645833730509284E-4</v>
+        <v>5.1644506108244306E-4</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>1.7162517713366969</v>
+        <v>1.7162076528880366</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20858,33 +20858,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
+      <c r="B97" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
+      <c r="B98" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20947,23 +20947,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="472" t="s">
         <v>541</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>1.2421607466941946</v>
+        <v>1.2421288153621801</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>6.0252992887029917</v>
+        <v>6.0251444006721258</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21007,13 +21007,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>6.3918401764541954</v>
+        <v>6.3916758660206225</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21177,13 +21177,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21196,22 +21196,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21276,11 +21276,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>3.5071825385208202</v>
+        <v>3.5070923819043194</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>3.8189685467512731</v>
+        <v>3.8188783901347723</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21297,11 +21297,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.0907777129306853</v>
+        <v>4.0906725542531985</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>4.4389697129306853</v>
+        <v>4.4388645542531986</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21337,11 +21337,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.1192763357185838</v>
+        <v>5.1191447381674751</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>5.5293311085395693</v>
+        <v>5.5291995109884606</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21358,11 +21358,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>5.5568836739241325</v>
+        <v>5.5567408271162382</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>5.9925522477745243</v>
+        <v>5.99240940096663</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21380,13 +21380,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="473" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21394,13 +21394,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="474" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21437,22 +21437,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21476,15 +21476,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21499,12 +21496,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F4D37-1FFA-4DDE-8AE6-B71EE56EBB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A194AF-FD19-4101-AD2D-86F4E072C85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,6 +5021,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5030,16 +5039,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>0.31835640522615205</v>
+        <v>0.31839626623399109</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5571,7 +5571,7 @@
         <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0930900000000001</v>
+        <v>1.0931602500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>6.3916758660206225</v>
+        <v>6.3920866421045561</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>349</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>3.8188783901347723</v>
+        <v>3.8191037816760249</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>411</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>4.4388645542531986</v>
+        <v>4.4391274509469163</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>412</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>5.5291995109884606</v>
+        <v>5.529528504866235</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>413</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>5.99240940096663</v>
+        <v>5.9927665179863672</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>414</v>
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.8099478553586621E-2</v>
+        <v>7.8104497800280309E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189184926464123</v>
+        <v>-0.10189839758400272</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8175830570915956</v>
+        <v>1.8176998683420513</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1644506108244306E-4</v>
+        <v>5.1647825163906788E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>1.7162076528880366</v>
+        <v>1.7163179490096876</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>1.2421288153621801</v>
+        <v>1.2422086436922164</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>6.3916758660206225</v>
+        <v>6.3920866421045561</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6673,11 +6673,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>3.5070923819043194</v>
+        <v>3.5073177734455721</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>3.8188783901347723</v>
+        <v>3.8191037816760249</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.0906725542531985</v>
+        <v>4.0909354509469162</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>4.4388645542531986</v>
+        <v>4.4391274509469163</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6741,11 +6741,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.1191447381674751</v>
+        <v>5.1194737320452486</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>5.5291995109884606</v>
+        <v>5.529528504866235</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6762,11 +6762,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>5.5567408271162382</v>
+        <v>5.5570979441359754</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>5.99240940096663</v>
+        <v>5.9927665179863672</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,6 +6880,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6896,18 +6908,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10276,11 +10276,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0881246620463396</v>
+        <v>3.088323127641587</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2421288153621801</v>
+        <v>1.2422086436922164</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10686,11 +10686,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923675.26017000014</v>
+        <v>923734.62233325012</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10189184926464125</v>
+        <v>0.10189839758400272</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10703,11 +10703,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16476847.905461116</v>
+        <v>16477906.828848356</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8175830570915954</v>
+        <v>1.8176998683420513</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10720,11 +10720,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4681.7044700000006</v>
+        <v>4682.0053507500006</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1644506108244306E-4</v>
+        <v>5.1647825163906778E-4</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10737,11 +10737,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>17405204.870101117</v>
+        <v>17406323.456532355</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>1.919991351417319</v>
+        <v>1.9201147441776931</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -15467,46 +15467,46 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31239791421434654</v>
+        <v>0.31241799120112124</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35095498244864132</v>
+        <v>0.35097753739609949</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.31528194808087678</v>
+        <v>0.31530221041687173</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.49416919273331633</v>
+        <v>0.4942009516788648</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.62994468532961101</v>
+        <v>0.62998517020656031</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.54695740218136146</v>
+        <v>0.54699255368535771</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.36506721213926491</v>
+        <v>0.36509067404235868</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.21372782828468942</v>
+        <v>0.21374156400630157</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>9.3880017455497691E-2</v>
+        <v>9.388605087564264E-2</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>2.6288175005096365E-2</v>
+        <v>2.6289864476497719E-2</v>
       </c>
       <c r="P123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15524,46 +15524,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8099478553586621E-2</v>
+        <v>7.8104497800280309E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7738745612160329E-2</v>
+        <v>8.7744384349024873E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8820487020219196E-2</v>
+        <v>7.8825552604217933E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12354229818332908</v>
+        <v>0.1235502379197162</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15748617133240275</v>
+        <v>0.15749629255164008</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13673935054534037</v>
+        <v>0.13674813842133943</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1266803034816227E-2</v>
+        <v>9.1272668510589669E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3431957071172355E-2</v>
+        <v>5.3435391001575391E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3470004363874423E-2</v>
+        <v>2.347151271891066E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.5720437512740912E-3</v>
+        <v>6.5724661191244298E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7162076528880366</v>
+        <v>1.7163179490096876</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0930900000000001</v>
+        <v>1.0931602500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>54619450.54503905</v>
+        <v>54622960.792503387</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3922032717285706</v>
+        <v>6.3926140817074746</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18684,23 +18684,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18716,23 +18716,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4420811796616437</v>
+        <v>4.4423666604572514</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>6.2192125887122431</v>
+        <v>6.2196122810379961</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>6.4205755779722278</v>
+        <v>6.4209882113641292</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>6.629444467211667</v>
+        <v>6.6298705240540334</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>7.794054497324665</v>
+        <v>7.794555400569994</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>3.7833256070703798</v>
+        <v>3.7835687513896006</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>6.3629516206517955</v>
+        <v>6.3633605507045363</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>6.7282456564348729</v>
+        <v>6.7286780629680631</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>7.1231321151503453</v>
+        <v>7.1235898999906508</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>9.6256857027454732</v>
+        <v>9.626304320078555</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>3.5091995338595816</v>
+        <v>3.5094250608219122</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>6.4694137333327717</v>
+        <v>6.4698295054236032</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>6.9676321353350161</v>
+        <v>6.9680799266033544</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>7.5264540858443141</v>
+        <v>7.5269377911197539</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>11.522261949904669</v>
+        <v>11.523002455171373</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18812,23 +18812,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>3.3951282346698326</v>
+        <v>3.395346430571804</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>6.5482662293010456</v>
+        <v>6.5486870690330061</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>7.1538897219243704</v>
+        <v>7.1543494834746229</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>7.8559511124028436</v>
+        <v>7.8564559935797336</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>13.486086026849266</v>
+        <v>13.486952741889553</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>3.3476600710383098</v>
+        <v>3.3478752162870911</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>6.6066693171587749</v>
+        <v>6.6070939103025523</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>7.2988097220909669</v>
+        <v>7.2992787972659086</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>8.1251362756214593</v>
+        <v>8.125658456616037</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>15.519542372706164</v>
+        <v>15.520539772601582</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18876,23 +18876,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3279072798055132</v>
+        <v>3.3281211555947037</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.6499262950062477</v>
+        <v>6.6503536681614541</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>7.4115665060312095</v>
+        <v>7.4120428277860961</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>8.345049192147167</v>
+        <v>8.3455855063626014</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>17.625099972824298</v>
+        <v>17.626232691331548</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.794054497324665</v>
+        <v>7.794555400569994</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>6.629444467211667</v>
+        <v>6.6298705240540334</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>6.4205755779722278</v>
+        <v>6.4209882113641292</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>6.2192125887122431</v>
+        <v>6.2196122810379961</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.4420811796616437</v>
+        <v>4.4423666604572514</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>6.629444467211667</v>
+        <v>6.6298705240540334</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>6.4205755779722278</v>
+        <v>6.4209882113641292</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>6.2192125887122431</v>
+        <v>6.2196122810379961</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4220767579681182</v>
+        <v>6.4224894878368834</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19510,7 +19510,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>7.794054497324665</v>
+        <v>7.794555400569994</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>4.4420811796616437</v>
+        <v>4.4423666604572514</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.31835640522615205</v>
+        <v>0.31839626623399109</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.952677020620103E-2</v>
+        <v>6.9524227324638463E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3916758660206225</v>
+        <v>6.3920866421045561</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>6.3922032717285706</v>
+        <v>6.3926140817074746</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.30038934884423069</v>
+        <v>0.30038934884423074</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19862,11 +19862,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.5070923819043194</v>
+        <v>3.5073177734455721</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>3.8188783901347723</v>
+        <v>3.8191037816760249</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.40252314570007164</v>
+        <v>0.40252628046064653</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19887,11 +19887,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.0906725542531985</v>
+        <v>4.0909354509469162</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>4.4388645542531986</v>
+        <v>4.4391274509469163</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.30552414620224166</v>
+        <v>0.30552764699613644</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19933,11 +19933,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.1191447381674751</v>
+        <v>5.1194737320452486</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>5.5291995109884606</v>
+        <v>5.529528504866235</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.13500881058601533</v>
+        <v>0.13501293302077577</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19958,11 +19958,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.5567408271162382</v>
+        <v>5.5570979441359754</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>5.99240940096663</v>
+        <v>5.9927665179863672</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>6.2466632135801836E-2</v>
+        <v>6.2471012437139817E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.31835640522615205</v>
+        <v>0.31839626623399109</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20115,13 +20115,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0930900000000001</v>
+        <v>1.0931602500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>6.3916758660206225</v>
+        <v>6.3920866421045561</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>364</v>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>3.8188783901347723</v>
+        <v>3.8191037816760249</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>446</v>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>4.4388645542531986</v>
+        <v>4.4391274509469163</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>447</v>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>5.5291995109884606</v>
+        <v>5.529528504866235</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>449</v>
@@ -20285,7 +20285,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>5.99240940096663</v>
+        <v>5.9927665179863672</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>448</v>
@@ -20306,22 +20306,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20511,10 +20511,10 @@
       <c r="B54" s="468" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20530,22 +20530,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>7.8099478553586621E-2</v>
+        <v>7.8104497800280309E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20680,22 +20680,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20703,13 +20703,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189184926464123</v>
+        <v>-0.10189839758400272</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8175830570915956</v>
+        <v>1.8176998683420513</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1644506108244306E-4</v>
+        <v>5.1647825163906788E-4</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>1.7162076528880366</v>
+        <v>1.7163179490096876</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20858,33 +20858,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20947,23 +20947,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>522</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>541</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>1.2421288153621801</v>
+        <v>1.2422086436922164</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>6.0251444006721258</v>
+        <v>6.0255316207492902</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21007,13 +21007,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>6.3916758660206225</v>
+        <v>6.3920866421045561</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21177,13 +21177,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21196,22 +21196,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21276,11 +21276,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>3.5070923819043194</v>
+        <v>3.5073177734455721</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>3.8188783901347723</v>
+        <v>3.8191037816760249</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21297,11 +21297,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.0906725542531985</v>
+        <v>4.0909354509469162</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>4.4388645542531986</v>
+        <v>4.4391274509469163</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21337,11 +21337,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.1191447381674751</v>
+        <v>5.1194737320452486</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>5.5291995109884606</v>
+        <v>5.529528504866235</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21358,11 +21358,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>5.5567408271162382</v>
+        <v>5.5570979441359754</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>5.99240940096663</v>
+        <v>5.9927665179863672</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21380,13 +21380,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21394,13 +21394,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21437,22 +21437,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21476,12 +21476,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21496,15 +21499,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A194AF-FD19-4101-AD2D-86F4E072C85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5BC168-D272-4C6A-97AA-9AAC7E65354F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,25 +5021,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5497,7 +5497,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>36261.006816000001</v>
+        <v>36351.659333039999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>0.31839626623399109</v>
+        <v>0.31685611828363341</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5571,7 +5571,7 @@
         <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0931602500000002</v>
+        <v>1.0934131500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>6.3920866421045561</v>
+        <v>6.3935654360067202</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>349</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>3.8191037816760249</v>
+        <v>3.8199151912245375</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>411</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>4.4391274509469163</v>
+        <v>4.4400738790443013</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>412</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>5.529528504866235</v>
+        <v>5.5307128828262222</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>413</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>5.9927665179863672</v>
+        <v>5.9940521392574224</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>414</v>
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.8104497800280309E-2</v>
+        <v>7.7927747719079829E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0449999999999997E-2</v>
+        <v>6.0299251870324193E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189839758400272</v>
+        <v>-0.10192197153370405</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8176998683420513</v>
+        <v>1.8181203888436921</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1647825163906788E-4</v>
+        <v>5.1659773764291728E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>1.7163179490096876</v>
+        <v>1.7167150150476309</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
+      <c r="B97" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
+      <c r="B98" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>1.2422086436922164</v>
+        <v>1.2424960256803463</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="460" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.79 HKD</v>
+        <v>7.8 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>6.3920866421045561</v>
+        <v>6.3935654360067202</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6673,11 +6673,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>3.5073177734455721</v>
+        <v>3.5081291829940846</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>3.8191037816760249</v>
+        <v>3.8199151912245375</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>4.0909354509469162</v>
+        <v>4.0918818790443012</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>4.4391274509469163</v>
+        <v>4.4400738790443013</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6741,11 +6741,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>5.1194737320452486</v>
+        <v>5.1206581100052357</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>5.529528504866235</v>
+        <v>5.5307128828262222</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6762,11 +6762,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>5.5570979441359754</v>
+        <v>5.5583835654070306</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>5.9927665179863672</v>
+        <v>5.9940521392574224</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="461" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="464" t="s">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,18 +6880,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6908,6 +6896,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10276,11 +10276,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.088323127641587</v>
+        <v>3.0890376037844769</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2422086436922164</v>
+        <v>1.2424960256803463</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10686,11 +10686,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923734.62233325012</v>
+        <v>923948.32612095017</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10189839758400272</v>
+        <v>0.10192197153370405</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10703,11 +10703,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16477906.828848356</v>
+        <v>16481718.953042423</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8176998683420513</v>
+        <v>1.8181203888436921</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10720,11 +10720,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4682.0053507500006</v>
+        <v>4683.0885214500004</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1647825163906778E-4</v>
+        <v>5.1659773764291728E-4</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10737,11 +10737,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>17406323.456532355</v>
+        <v>17410350.367684823</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>1.9201147441776931</v>
+        <v>1.9205589581150391</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -14325,28 +14325,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0449999999999997E-2</v>
+        <v>6.0299251870324193E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.1600000000000006E-2</v>
+        <v>8.1396508728179565E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.0824999999999999E-2</v>
+        <v>7.0648379052369079E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1300000000000002E-2</v>
+        <v>7.1122194513715722E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11765</v>
+        <v>0.117356608478803</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4025000000000007E-2</v>
+        <v>7.384039900249377E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15467,46 +15467,46 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31241799120112124</v>
+        <v>0.31249026835351018</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35097753739609949</v>
+        <v>0.3510587352069488</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.31530221041687173</v>
+        <v>0.31537515482645345</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.4942009516788648</v>
+        <v>0.49431528388283907</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.62998517020656031</v>
+        <v>0.63013091576357738</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.54699255368535771</v>
+        <v>0.5471190990997441</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.36509067404235868</v>
+        <v>0.36517513689349629</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.21374156400630157</v>
+        <v>0.21379101260410521</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>9.388605087564264E-2</v>
+        <v>9.3907771188164485E-2</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>2.6289864476497719E-2</v>
+        <v>2.6295946573542603E-2</v>
       </c>
       <c r="P123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15524,46 +15524,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8104497800280309E-2</v>
+        <v>7.7927747719079829E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7744384349024873E-2</v>
+        <v>8.7545819253603191E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8825552604217933E-2</v>
+        <v>7.8647170779664211E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.1235502379197162</v>
+        <v>0.12327064435981025</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15749629255164008</v>
+        <v>0.15713987924278738</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13674813842133943</v>
+        <v>0.1364386780797367</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1272668510589669E-2</v>
+        <v>9.1066118926058925E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3435391001575391E-2</v>
+        <v>5.3314466983567385E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.347151271891066E-2</v>
+        <v>2.3418396805028552E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.5724661191244298E-3</v>
+        <v>6.5575926617313226E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15581,39 +15581,39 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1007727120910398</v>
+        <v>0.10052140856961576</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0740778839823816E-2</v>
+        <v>9.0514492608303063E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13645804224654542</v>
+        <v>0.1361177478768533</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19069784893421202</v>
+        <v>0.19022229320120898</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20508619735066541</v>
+        <v>0.20457476044954157</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10850710847509855</v>
+        <v>0.10823651718214319</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.183650695023217E-2</v>
+        <v>6.1682301197239067E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1996519177952217E-2</v>
+        <v>3.191672735955333E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1200792136328309E-2</v>
+        <v>1.1172859986362402E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7163179490096876</v>
+        <v>1.7167150150476309</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0931602500000002</v>
+        <v>1.0934131500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>54622960.792503387</v>
+        <v>54635597.683374994</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3926140817074746</v>
+        <v>6.3940929976315246</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18684,23 +18684,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18716,23 +18716,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4423666604572514</v>
+        <v>4.4433943913214407</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>6.2196122810379961</v>
+        <v>6.2210511734107063</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>6.4209882113641292</v>
+        <v>6.4224736915749707</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>6.6298705240540334</v>
+        <v>6.6314043286865498</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>7.794555400569994</v>
+        <v>7.79635865225318</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>3.7835687513896006</v>
+        <v>3.7844440709387941</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>6.3633605507045363</v>
+        <v>6.3648326988944044</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>6.7286780629680631</v>
+        <v>6.7302347264875468</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>7.1235898999906508</v>
+        <v>7.1252379254157496</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>9.626304320078555</v>
+        <v>9.6285313424776486</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>3.5094250608219122</v>
+        <v>3.5102369578863013</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>6.4698295054236032</v>
+        <v>6.471326284950595</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>6.9680799266033544</v>
+        <v>6.9696919751693702</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>7.5269377911197539</v>
+        <v>7.528679130111338</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>11.523002455171373</v>
+        <v>11.525668274131505</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18812,23 +18812,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>3.395346430571804</v>
+        <v>3.3961319358188997</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>6.5486870690330061</v>
+        <v>6.550202092068063</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>7.1543494834746229</v>
+        <v>7.1560046250555303</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>7.8564559935797336</v>
+        <v>7.8582735658165364</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>13.486952741889553</v>
+        <v>13.490072916034583</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>3.3478752162870911</v>
+        <v>3.3486497391827044</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>6.6070939103025523</v>
+        <v>6.6086224456201466</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>7.2992787972659086</v>
+        <v>7.3009674678956982</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>8.125658456616037</v>
+        <v>8.1275383081965149</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>15.520539772601582</v>
+        <v>15.524130412225087</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18876,23 +18876,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3281211555947037</v>
+        <v>3.3288911084357897</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>6.6503536681614541</v>
+        <v>6.6518922115201953</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>7.4120428277860961</v>
+        <v>7.4137575861036868</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>8.3455855063626014</v>
+        <v>8.3475162375381622</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>17.626232691331548</v>
+        <v>17.630310477957654</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.794555400569994</v>
+        <v>7.79635865225318</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>6.6298705240540334</v>
+        <v>6.6314043286865498</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>6.4209882113641292</v>
+        <v>6.4224736915749707</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>6.2196122810379961</v>
+        <v>6.2210511734107063</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.4423666604572514</v>
+        <v>4.4433943913214407</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>6.6298705240540334</v>
+        <v>6.6314043286865498</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>6.4209882113641292</v>
+        <v>6.4224736915749707</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>6.2196122810379961</v>
+        <v>6.2210511734107063</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4224894878368834</v>
+        <v>6.4239753153644337</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19510,7 +19510,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>7.794555400569994</v>
+        <v>7.79635865225318</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>4.4423666604572514</v>
+        <v>4.4433943913214407</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.31839626623399109</v>
+        <v>0.31685611828363341</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.9524227324638463E-2</v>
+        <v>6.9515075657243713E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3920866421045561</v>
+        <v>6.3935654360067202</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>6.3926140817074746</v>
+        <v>6.3940929976315246</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19862,11 +19862,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.5073177734455721</v>
+        <v>3.5081291829940846</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>3.8191037816760249</v>
+        <v>3.8199151912245375</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.40252628046064653</v>
+        <v>0.40253756226347903</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19887,11 +19887,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.0909354509469162</v>
+        <v>4.0918818790443012</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>4.4391274509469163</v>
+        <v>4.4400738790443013</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.30552764699613644</v>
+        <v>0.30554024612947839</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19933,11 +19933,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.1194737320452486</v>
+        <v>5.1206581100052357</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>5.529528504866235</v>
+        <v>5.5307128828262222</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.13501293302077577</v>
+        <v>0.13502776939983707</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19958,11 +19958,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.5570979441359754</v>
+        <v>5.5583835654070306</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>5.9927665179863672</v>
+        <v>5.9940521392574224</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>6.2471012437139817E-2</v>
+        <v>6.248677686152293E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20081,14 +20081,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="D8" s="352" t="s">
         <v>534</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.31839626623399109</v>
+        <v>0.31685611828363341</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>36261.006816000001</v>
+        <v>36351.659333039999</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20115,13 +20115,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="472" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0931602500000002</v>
+        <v>1.0934131500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>6.3920866421045561</v>
+        <v>6.3935654360067202</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>364</v>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>3.8191037816760249</v>
+        <v>3.8199151912245375</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>446</v>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>4.4391274509469163</v>
+        <v>4.4400738790443013</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>447</v>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>5.529528504866235</v>
+        <v>5.5307128828262222</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>449</v>
@@ -20285,7 +20285,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>5.9927665179863672</v>
+        <v>5.9940521392574224</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>448</v>
@@ -20306,22 +20306,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="472" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="470" t="s">
+      <c r="B30" s="475" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20511,10 +20511,10 @@
       <c r="B54" s="468" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20530,22 +20530,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>7.8104497800280309E-2</v>
+        <v>7.7927747719079829E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>6.0449999999999997E-2</v>
+        <v>6.0299251870324193E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>375</v>
@@ -20680,22 +20680,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
+      <c r="B74" s="475" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20703,13 +20703,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189839758400272</v>
+        <v>-0.10192197153370405</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8176998683420513</v>
+        <v>1.8181203888436921</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1647825163906788E-4</v>
+        <v>5.1659773764291728E-4</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>1.7163179490096876</v>
+        <v>1.7167150150476309</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20858,33 +20858,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
+      <c r="B97" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
+      <c r="B98" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20947,23 +20947,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="472" t="s">
         <v>541</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>1.2422086436922164</v>
+        <v>1.2424960256803463</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>6.0255316207492902</v>
+        <v>6.026925613027081</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21007,13 +21007,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21058,7 +21058,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>7.79 HKD</v>
+        <v>7.8 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>6.3920866421045561</v>
+        <v>6.3935654360067202</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21177,13 +21177,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21196,22 +21196,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21276,11 +21276,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>3.5073177734455721</v>
+        <v>3.5081291829940846</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>3.8191037816760249</v>
+        <v>3.8199151912245375</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21297,11 +21297,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>4.0909354509469162</v>
+        <v>4.0918818790443012</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>4.4391274509469163</v>
+        <v>4.4400738790443013</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21337,11 +21337,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>5.1194737320452486</v>
+        <v>5.1206581100052357</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>5.529528504866235</v>
+        <v>5.5307128828262222</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21358,11 +21358,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>5.5570979441359754</v>
+        <v>5.5583835654070306</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>5.9927665179863672</v>
+        <v>5.9940521392574224</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21380,13 +21380,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="473" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21394,13 +21394,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="474" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21437,22 +21437,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21476,15 +21476,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21499,12 +21496,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923E3A80-0189-40AD-831E-BA4AA255E9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD1ECC4-9EFB-45CF-B59B-78DC82AD5438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,32 +22,18 @@
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
     <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$9</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$91</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$101</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$E$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$E$16</definedName>
-    <definedName name="FV_adjustments" localSheetId="7">[1]DCF!$F$7</definedName>
     <definedName name="FV_adjustments">DCF!$F$7</definedName>
-    <definedName name="Holding_Period" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="Holding_Period">Thesis!$E$21</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$7</definedName>
     <definedName name="Market_currency">Thesis!$C$7</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$8</definedName>
     <definedName name="Market_Price">Thesis!$C$8</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$E$17</definedName>
     <definedName name="Reporting_currency">Thesis!$E$17</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$17</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -4992,65 +4978,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5132,93 +5118,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Thesis"/>
-      <sheetName val="Data"/>
-      <sheetName val="BS"/>
-      <sheetName val="Normalized_FCF"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="投资主题"/>
-      <sheetName val="Breakdown"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="7">
-          <cell r="C7" t="str">
-            <v>HKD</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>4.01</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>9065251704</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>1.0934131500000002</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="C17">
-            <v>0</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>CNY</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="C101">
-            <v>7.2499999999999995E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="C3">
-            <v>1000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="91">
-          <cell r="C91">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="7">
-          <cell r="F7">
-            <v>14232912.522995466</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5539,13 +5438,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5723,22 +5622,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="464" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5750,13 +5649,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5776,13 +5675,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5811,13 +5710,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5833,13 +5732,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5903,13 +5802,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5925,13 +5824,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="463"/>
-      <c r="D54" s="463"/>
-      <c r="E54" s="463"/>
-      <c r="F54" s="463"/>
+      <c r="C54" s="466"/>
+      <c r="D54" s="466"/>
+      <c r="E54" s="466"/>
+      <c r="F54" s="466"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5947,22 +5846,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6097,13 +5996,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6122,13 +6021,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6297,31 +6196,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="464" t="s">
         <v>488</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6371,22 +6270,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6420,13 +6319,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="462" t="s">
         <v>496</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6561,13 +6460,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="463" t="s">
         <v>358</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6583,13 +6482,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="464" t="s">
+      <c r="B127" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C127" s="464"/>
-      <c r="D127" s="464"/>
-      <c r="E127" s="464"/>
-      <c r="F127" s="464"/>
+      <c r="C127" s="467"/>
+      <c r="D127" s="467"/>
+      <c r="E127" s="467"/>
+      <c r="F127" s="467"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="202" t="s">
@@ -6602,22 +6501,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="465" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6793,13 +6692,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="469" t="s">
         <v>361</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6807,13 +6706,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="463" t="s">
+      <c r="B152" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="463"/>
-      <c r="D152" s="463"/>
-      <c r="E152" s="463"/>
-      <c r="F152" s="463"/>
+      <c r="C152" s="466"/>
+      <c r="D152" s="466"/>
+      <c r="E152" s="466"/>
+      <c r="F152" s="466"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6836,13 +6735,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="463" t="s">
         <v>443</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6850,22 +6749,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="468" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="468"/>
+      <c r="D161" s="468"/>
+      <c r="E161" s="468"/>
+      <c r="F161" s="468"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="468" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="468"/>
+      <c r="D162" s="468"/>
+      <c r="E162" s="468"/>
+      <c r="F162" s="468"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6889,6 +6788,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6905,18 +6816,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -18362,10 +18261,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="467" t="s">
+      <c r="J52" s="470" t="s">
         <v>425</v>
       </c>
-      <c r="K52" s="467"/>
+      <c r="K52" s="470"/>
       <c r="L52" s="324">
         <f>SUM(L21:L51)</f>
         <v>38779128.206817999</v>
@@ -19446,7 +19345,7 @@
       <c r="C4" s="457">
         <v>2</v>
       </c>
-      <c r="D4" s="468" t="str">
+      <c r="D4" s="471" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19456,16 +19355,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 6186.HK – 中国飞鹤: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="468"/>
-      <c r="F4" s="468"/>
-      <c r="G4" s="468"/>
+      <c r="E4" s="471"/>
+      <c r="F4" s="471"/>
+      <c r="G4" s="471"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="453"/>
-      <c r="D5" s="468"/>
-      <c r="E5" s="468"/>
-      <c r="F5" s="468"/>
-      <c r="G5" s="468"/>
+      <c r="D5" s="471"/>
+      <c r="E5" s="471"/>
+      <c r="F5" s="471"/>
+      <c r="G5" s="471"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19475,10 +19374,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000 CNY</v>
       </c>
-      <c r="D6" s="468"/>
-      <c r="E6" s="468"/>
-      <c r="F6" s="468"/>
-      <c r="G6" s="468"/>
+      <c r="D6" s="471"/>
+      <c r="E6" s="471"/>
+      <c r="F6" s="471"/>
+      <c r="G6" s="471"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19488,10 +19387,10 @@
         <f>Normalized_FCF!G8</f>
         <v>4902319</v>
       </c>
-      <c r="D7" s="468"/>
-      <c r="E7" s="468"/>
-      <c r="F7" s="468"/>
-      <c r="G7" s="468"/>
+      <c r="D7" s="471"/>
+      <c r="E7" s="471"/>
+      <c r="F7" s="471"/>
+      <c r="G7" s="471"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19501,10 +19400,10 @@
         <f>Normalized_FCF!G19</f>
         <v>2910551.9698010553</v>
       </c>
-      <c r="D8" s="468"/>
-      <c r="E8" s="468"/>
-      <c r="F8" s="468"/>
-      <c r="G8" s="468"/>
+      <c r="D8" s="471"/>
+      <c r="E8" s="471"/>
+      <c r="F8" s="471"/>
+      <c r="G8" s="471"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19514,27 +19413,27 @@
         <f>Normalized_FCF!C19</f>
         <v>2590789.1611465206</v>
       </c>
-      <c r="D9" s="468"/>
-      <c r="E9" s="468"/>
-      <c r="F9" s="468"/>
-      <c r="G9" s="468"/>
+      <c r="D9" s="471"/>
+      <c r="E9" s="471"/>
+      <c r="F9" s="471"/>
+      <c r="G9" s="471"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="456"/>
-      <c r="D10" s="468"/>
-      <c r="E10" s="468"/>
-      <c r="F10" s="468"/>
-      <c r="G10" s="468"/>
+      <c r="D10" s="471"/>
+      <c r="E10" s="471"/>
+      <c r="F10" s="471"/>
+      <c r="G10" s="471"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="456"/>
-      <c r="D11" s="468"/>
-      <c r="E11" s="468"/>
-      <c r="F11" s="468"/>
-      <c r="G11" s="468"/>
+      <c r="D11" s="471"/>
+      <c r="E11" s="471"/>
+      <c r="F11" s="471"/>
+      <c r="G11" s="471"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19544,10 +19443,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.328292424848343E-2</v>
       </c>
-      <c r="D12" s="468"/>
-      <c r="E12" s="468"/>
-      <c r="F12" s="468"/>
-      <c r="G12" s="468"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+      <c r="G12" s="471"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19557,10 +19456,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-8.6152390653333799E-2</v>
       </c>
-      <c r="D13" s="468"/>
-      <c r="E13" s="468"/>
-      <c r="F13" s="468"/>
-      <c r="G13" s="468"/>
+      <c r="D13" s="471"/>
+      <c r="E13" s="471"/>
+      <c r="F13" s="471"/>
+      <c r="G13" s="471"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19570,10 +19469,10 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15727112921242259</v>
       </c>
-      <c r="D14" s="468"/>
-      <c r="E14" s="468"/>
-      <c r="F14" s="468"/>
-      <c r="G14" s="468"/>
+      <c r="D14" s="471"/>
+      <c r="E14" s="471"/>
+      <c r="F14" s="471"/>
+      <c r="G14" s="471"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
@@ -20564,13 +20463,13 @@
       <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="474"/>
+      <c r="D30" s="474"/>
+      <c r="E30" s="474"/>
+      <c r="F30" s="474"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20582,13 +20481,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="469" t="s">
+      <c r="B33" s="472" t="s">
         <v>505</v>
       </c>
-      <c r="C33" s="469"/>
-      <c r="D33" s="469"/>
-      <c r="E33" s="469"/>
-      <c r="F33" s="469"/>
+      <c r="C33" s="472"/>
+      <c r="D33" s="472"/>
+      <c r="E33" s="472"/>
+      <c r="F33" s="472"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="379" t="s">
@@ -20608,13 +20507,13 @@
       <c r="C35" s="381"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="469" t="s">
+      <c r="B36" s="472" t="s">
         <v>506</v>
       </c>
-      <c r="C36" s="469"/>
-      <c r="D36" s="469"/>
-      <c r="E36" s="469"/>
-      <c r="F36" s="469"/>
+      <c r="C36" s="472"/>
+      <c r="D36" s="472"/>
+      <c r="E36" s="472"/>
+      <c r="F36" s="472"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="379" t="s">
@@ -20643,13 +20542,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="469" t="s">
+      <c r="B40" s="472" t="s">
         <v>507</v>
       </c>
-      <c r="C40" s="469"/>
-      <c r="D40" s="469"/>
-      <c r="E40" s="469"/>
-      <c r="F40" s="469"/>
+      <c r="C40" s="472"/>
+      <c r="D40" s="472"/>
+      <c r="E40" s="472"/>
+      <c r="F40" s="472"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="379" t="s">
@@ -20665,13 +20564,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="469" t="s">
+      <c r="B43" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C43" s="469"/>
-      <c r="D43" s="469"/>
-      <c r="E43" s="469"/>
-      <c r="F43" s="469"/>
+      <c r="C43" s="472"/>
+      <c r="D43" s="472"/>
+      <c r="E43" s="472"/>
+      <c r="F43" s="472"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="379" t="s">
@@ -20735,13 +20634,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="469" t="s">
+      <c r="B51" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C51" s="469"/>
-      <c r="D51" s="469"/>
-      <c r="E51" s="469"/>
-      <c r="F51" s="469"/>
+      <c r="C51" s="472"/>
+      <c r="D51" s="472"/>
+      <c r="E51" s="472"/>
+      <c r="F51" s="472"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="379" t="s">
@@ -20757,7 +20656,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="469" t="s">
+      <c r="B54" s="472" t="s">
         <v>511</v>
       </c>
       <c r="C54" s="475"/>
@@ -20938,13 +20837,13 @@
       <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="474" t="s">
         <v>484</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="474"/>
+      <c r="D74" s="474"/>
+      <c r="E74" s="474"/>
+      <c r="F74" s="474"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -21117,23 +21016,23 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="474"/>
+      <c r="D97" s="474"/>
+      <c r="E97" s="474"/>
+      <c r="F97" s="474"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="474"/>
+      <c r="D98" s="474"/>
+      <c r="E98" s="474"/>
+      <c r="F98" s="474"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21404,13 +21303,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="469" t="s">
+      <c r="B124" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C124" s="469"/>
-      <c r="D124" s="469"/>
-      <c r="E124" s="469"/>
-      <c r="F124" s="469"/>
+      <c r="C124" s="472"/>
+      <c r="D124" s="472"/>
+      <c r="E124" s="472"/>
+      <c r="F124" s="472"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="379" t="s">
@@ -21426,13 +21325,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="477"/>
+      <c r="D127" s="477"/>
+      <c r="E127" s="477"/>
+      <c r="F127" s="477"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21445,13 +21344,13 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="478" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="478"/>
+      <c r="D131" s="478"/>
+      <c r="E131" s="478"/>
+      <c r="F131" s="478"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
       <c r="B132" s="473" t="s">
@@ -21629,7 +21528,7 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="479" t="s">
         <v>527</v>
       </c>
       <c r="C149" s="473"/>
@@ -21672,13 +21571,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="469" t="s">
+      <c r="B158" s="472" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="469"/>
-      <c r="D158" s="469"/>
-      <c r="E158" s="469"/>
-      <c r="F158" s="469"/>
+      <c r="C158" s="472"/>
+      <c r="D158" s="472"/>
+      <c r="E158" s="472"/>
+      <c r="F158" s="472"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="350" t="s">
@@ -21686,22 +21585,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="476" t="s">
         <v>389</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="476"/>
+      <c r="D161" s="476"/>
+      <c r="E161" s="476"/>
+      <c r="F161" s="476"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="476" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="476"/>
+      <c r="D162" s="476"/>
+      <c r="E162" s="476"/>
+      <c r="F162" s="476"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21725,12 +21624,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21745,15 +21647,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21779,19 +21678,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="479" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="479" customWidth="1"/>
-    <col min="3" max="5" width="20.6640625" style="479" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="479"/>
+    <col min="1" max="1" width="2.6640625" style="461" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="461" customWidth="1"/>
+    <col min="3" max="5" width="20.6640625" style="461" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="461"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="477" t="s">
+      <c r="B2" s="459" t="s">
         <v>334</v>
       </c>
-      <c r="C2" s="478"/>
-      <c r="D2" s="478"/>
-      <c r="E2" s="478"/>
+      <c r="C2" s="460"/>
+      <c r="D2" s="460"/>
+      <c r="E2" s="460"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD1ECC4-9EFB-45CF-B59B-78DC82AD5438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69820599-CC2B-4B55-BDF2-F3062F4A1A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="555">
   <si>
     <t>Sales</t>
   </si>
@@ -1754,9 +1753,6 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>执行摘要</t>
@@ -3999,12 +3995,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="480">
+  <cellXfs count="477">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4978,11 +4973,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5038,9 +5028,8 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{E23C6B69-E688-450B-A241-7EFBAAC29699}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5346,7 +5335,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="436" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F3" s="437">
         <v>45930</v>
@@ -5354,13 +5343,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="429" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C4" s="428" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E4" s="438" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F4" s="439" t="s">
         <v>324</v>
@@ -5368,16 +5357,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E5" s="441" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F5" s="440" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5385,14 +5374,14 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C7" s="45" t="s">
         <v>308</v>
@@ -5402,7 +5391,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C8" s="47">
         <v>4.01</v>
@@ -5411,7 +5400,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C9" s="48">
         <v>9065251704</v>
@@ -5419,14 +5408,14 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>36351.659333039999</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
@@ -5438,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
-        <v>356</v>
-      </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="B12" s="459" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5458,10 +5447,10 @@
         <v>319</v>
       </c>
       <c r="C15" s="425" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E15" s="259" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5473,10 +5462,10 @@
         <v>320</v>
       </c>
       <c r="C16" s="425" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E16" s="424">
         <v>1.0934131499999999</v>
@@ -5484,7 +5473,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C17" s="423">
         <v>0</v>
@@ -5493,7 +5482,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="227" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5506,7 +5495,7 @@
         <v>6.3935654360067202</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E18" s="426">
         <v>6</v>
@@ -5521,7 +5510,7 @@
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5534,7 +5523,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="260" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5556,7 +5545,7 @@
         <v>3.8199151912245375</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5571,7 +5560,7 @@
         <v>4.4400738790443013</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E23" s="451">
         <v>0.25</v>
@@ -5586,7 +5575,7 @@
         <v>5.5307128828262222</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E24" s="451">
         <v>0.1174</v>
@@ -5601,7 +5590,7 @@
         <v>5.9940521392574224</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E25" s="452">
         <v>7.2499999999999995E-2</v>
@@ -5622,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
-        <v>357</v>
-      </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="B29" s="459" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5649,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5675,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5710,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5732,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5802,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5824,13 +5813,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="466"/>
-      <c r="D54" s="466"/>
-      <c r="E54" s="466"/>
-      <c r="F54" s="466"/>
+      <c r="C54" s="463"/>
+      <c r="D54" s="463"/>
+      <c r="E54" s="463"/>
+      <c r="F54" s="463"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5846,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5983,7 +5972,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="202" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5996,18 +5985,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
-        <v>483</v>
-      </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="B73" s="459" t="s">
+        <v>482</v>
+      </c>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6021,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6083,7 +6072,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6171,7 +6160,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
@@ -6184,7 +6173,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="202" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6196,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
-        <v>490</v>
-      </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="B96" s="459" t="s">
+        <v>489</v>
+      </c>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
-        <v>489</v>
-      </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="B97" s="461" t="s">
+        <v>488</v>
+      </c>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
-        <v>488</v>
-      </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="B98" s="461" t="s">
+        <v>487</v>
+      </c>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6229,7 +6218,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C101" s="214">
         <f>E25+C103</f>
@@ -6270,31 +6259,31 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
@@ -6319,17 +6308,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
-        <v>496</v>
-      </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="B114" s="459" t="s">
+        <v>495</v>
+      </c>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6460,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
-        <v>358</v>
-      </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="B124" s="460" t="s">
+        <v>357</v>
+      </c>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,17 +6471,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="467" t="s">
-        <v>359</v>
-      </c>
-      <c r="C127" s="467"/>
-      <c r="D127" s="467"/>
-      <c r="E127" s="467"/>
-      <c r="F127" s="467"/>
+      <c r="B127" s="464" t="s">
+        <v>358</v>
+      </c>
+      <c r="C127" s="464"/>
+      <c r="D127" s="464"/>
+      <c r="E127" s="464"/>
+      <c r="F127" s="464"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="202" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6501,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
-        <v>360</v>
-      </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="B132" s="459" t="s">
+        <v>359</v>
+      </c>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,28 +6536,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C138" s="217"/>
       <c r="D138" s="218"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="347" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="348" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6622,21 +6611,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="347" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="348" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6683,7 +6672,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="202" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6692,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="469" t="s">
-        <v>361</v>
-      </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="B149" s="466" t="s">
+        <v>360</v>
+      </c>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6706,13 +6695,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="466" t="s">
+      <c r="B152" s="463" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="466"/>
-      <c r="D152" s="466"/>
-      <c r="E152" s="466"/>
-      <c r="F152" s="466"/>
+      <c r="C152" s="463"/>
+      <c r="D152" s="463"/>
+      <c r="E152" s="463"/>
+      <c r="F152" s="463"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6735,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
-        <v>443</v>
-      </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="B158" s="460" t="s">
+        <v>442</v>
+      </c>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6749,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="468" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="468"/>
-      <c r="D161" s="468"/>
-      <c r="E161" s="468"/>
-      <c r="F161" s="468"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="468" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="468"/>
-      <c r="D162" s="468"/>
-      <c r="E162" s="468"/>
-      <c r="F162" s="468"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -7485,7 +7474,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9586,7 +9575,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10770,7 +10759,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10780,7 +10769,7 @@
       <c r="E3" s="241"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11069,7 +11058,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C9" s="307">
         <f>C61</f>
@@ -11460,7 +11449,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C16" s="273">
         <f>-C4*C82</f>
@@ -12163,7 +12152,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C35" s="283">
         <f>G35</f>
@@ -12231,7 +12220,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12304,7 +12293,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="238" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13872,7 +13861,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="239" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -16268,15 +16257,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C4" s="282">
         <f>Normalized_FCF!C19</f>
@@ -16287,7 +16276,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F4" s="282">
         <f>-BS!G31</f>
@@ -16298,7 +16287,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="315" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I4" s="312">
         <f>Normalized_FCF!C4</f>
@@ -16315,7 +16304,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F5" s="282">
         <f>BS!D66</f>
@@ -16326,7 +16315,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="315" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I5" s="312">
         <f>Normalized_FCF!C7</f>
@@ -16347,7 +16336,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F6" s="291">
         <f>BS!H42</f>
@@ -16358,7 +16347,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="315" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I6" s="312">
         <f>I7+I8</f>
@@ -16369,14 +16358,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="325" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C7" s="282">
         <f>F7</f>
         <v>14232912.522995466</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F7" s="290">
         <f>SUM(F4:F6)</f>
@@ -16387,7 +16376,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="319" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I7" s="320">
         <f>Normalized_FCF!C9</f>
@@ -16399,7 +16388,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C8" s="290">
         <f>C6+C7</f>
@@ -16410,7 +16399,7 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16460,7 +16449,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
@@ -16471,7 +16460,7 @@
         <v>HKD</v>
       </c>
       <c r="H10" s="315" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I10" s="313">
         <f>Normalized_FCF!C41</f>
@@ -16482,7 +16471,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16498,7 +16487,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16513,25 +16502,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C14" s="316" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F14" s="316" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16546,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16556,14 +16545,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
         <v>1.8613012126595999E-2</v>
       </c>
       <c r="E16" s="315" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F16" s="318">
         <f>Scenarios!C41</f>
@@ -16572,33 +16561,33 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="315" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C17" s="313">
         <f>Normalized_FCF!C32</f>
         <v>0.68269686315429268</v>
       </c>
       <c r="E17" s="315" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F17" s="318">
         <f>Scenarios!C40</f>
         <v>0.68269686315429268</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="315" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C18" s="313">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="315" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16621,41 +16610,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B20" s="121" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D20" s="121" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
+        <v>395</v>
+      </c>
+      <c r="F20" s="121" t="s">
         <v>396</v>
       </c>
-      <c r="F20" s="121" t="s">
-        <v>397</v>
-      </c>
       <c r="G20" s="121" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>422</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="K20" s="121" t="s">
+        <v>534</v>
+      </c>
+      <c r="L20" s="122" t="s">
         <v>423</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>534</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>535</v>
-      </c>
-      <c r="L20" s="122" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18210,7 +18199,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="322" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B51" s="323">
         <f>C15+1</f>
@@ -18261,10 +18250,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="470" t="s">
-        <v>425</v>
-      </c>
-      <c r="K52" s="470"/>
+      <c r="J52" s="467" t="s">
+        <v>424</v>
+      </c>
+      <c r="K52" s="467"/>
       <c r="L52" s="324">
         <f>SUM(L21:L51)</f>
         <v>38779128.206817999</v>
@@ -19053,7 +19042,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G81" s="330"/>
       <c r="H81" s="330"/>
@@ -19334,7 +19323,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19345,7 +19334,7 @@
       <c r="C4" s="457">
         <v>2</v>
       </c>
-      <c r="D4" s="471" t="str">
+      <c r="D4" s="468" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19355,16 +19344,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 6186.HK – 中国飞鹤: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="471"/>
-      <c r="F4" s="471"/>
-      <c r="G4" s="471"/>
+      <c r="E4" s="468"/>
+      <c r="F4" s="468"/>
+      <c r="G4" s="468"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="453"/>
-      <c r="D5" s="471"/>
-      <c r="E5" s="471"/>
-      <c r="F5" s="471"/>
-      <c r="G5" s="471"/>
+      <c r="D5" s="468"/>
+      <c r="E5" s="468"/>
+      <c r="F5" s="468"/>
+      <c r="G5" s="468"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19374,10 +19363,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000 CNY</v>
       </c>
-      <c r="D6" s="471"/>
-      <c r="E6" s="471"/>
-      <c r="F6" s="471"/>
-      <c r="G6" s="471"/>
+      <c r="D6" s="468"/>
+      <c r="E6" s="468"/>
+      <c r="F6" s="468"/>
+      <c r="G6" s="468"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19387,10 +19376,10 @@
         <f>Normalized_FCF!G8</f>
         <v>4902319</v>
       </c>
-      <c r="D7" s="471"/>
-      <c r="E7" s="471"/>
-      <c r="F7" s="471"/>
-      <c r="G7" s="471"/>
+      <c r="D7" s="468"/>
+      <c r="E7" s="468"/>
+      <c r="F7" s="468"/>
+      <c r="G7" s="468"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19400,10 +19389,10 @@
         <f>Normalized_FCF!G19</f>
         <v>2910551.9698010553</v>
       </c>
-      <c r="D8" s="471"/>
-      <c r="E8" s="471"/>
-      <c r="F8" s="471"/>
-      <c r="G8" s="471"/>
+      <c r="D8" s="468"/>
+      <c r="E8" s="468"/>
+      <c r="F8" s="468"/>
+      <c r="G8" s="468"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19413,27 +19402,27 @@
         <f>Normalized_FCF!C19</f>
         <v>2590789.1611465206</v>
       </c>
-      <c r="D9" s="471"/>
-      <c r="E9" s="471"/>
-      <c r="F9" s="471"/>
-      <c r="G9" s="471"/>
+      <c r="D9" s="468"/>
+      <c r="E9" s="468"/>
+      <c r="F9" s="468"/>
+      <c r="G9" s="468"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="456"/>
-      <c r="D10" s="471"/>
-      <c r="E10" s="471"/>
-      <c r="F10" s="471"/>
-      <c r="G10" s="471"/>
+      <c r="D10" s="468"/>
+      <c r="E10" s="468"/>
+      <c r="F10" s="468"/>
+      <c r="G10" s="468"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="456"/>
-      <c r="D11" s="471"/>
-      <c r="E11" s="471"/>
-      <c r="F11" s="471"/>
-      <c r="G11" s="471"/>
+      <c r="D11" s="468"/>
+      <c r="E11" s="468"/>
+      <c r="F11" s="468"/>
+      <c r="G11" s="468"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19443,10 +19432,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.328292424848343E-2</v>
       </c>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-      <c r="G12" s="471"/>
+      <c r="D12" s="468"/>
+      <c r="E12" s="468"/>
+      <c r="F12" s="468"/>
+      <c r="G12" s="468"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19456,10 +19445,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-8.6152390653333799E-2</v>
       </c>
-      <c r="D13" s="471"/>
-      <c r="E13" s="471"/>
-      <c r="F13" s="471"/>
-      <c r="G13" s="471"/>
+      <c r="D13" s="468"/>
+      <c r="E13" s="468"/>
+      <c r="F13" s="468"/>
+      <c r="G13" s="468"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19469,14 +19458,14 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15727112921242259</v>
       </c>
-      <c r="D14" s="471"/>
-      <c r="E14" s="471"/>
-      <c r="F14" s="471"/>
-      <c r="G14" s="471"/>
+      <c r="D14" s="468"/>
+      <c r="E14" s="468"/>
+      <c r="F14" s="468"/>
+      <c r="G14" s="468"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19500,7 +19489,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="458" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F18" s="326"/>
     </row>
@@ -19510,35 +19499,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E20" s="326"/>
       <c r="F20" s="326"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="309" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C22" s="331">
         <v>0.03</v>
@@ -19562,7 +19551,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="309" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C23" s="331">
         <v>0.02</v>
@@ -19585,7 +19574,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="309" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C24" s="331">
         <v>0.01</v>
@@ -19608,7 +19597,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19622,33 +19611,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="309" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C29" s="331">
         <v>0.08</v>
@@ -19671,7 +19660,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="322" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C30" s="331">
         <v>-0.1</v>
@@ -19698,12 +19687,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19714,7 +19703,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
@@ -19734,7 +19723,7 @@
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
@@ -19743,7 +19732,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
@@ -19754,7 +19743,7 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19763,7 +19752,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19774,15 +19763,15 @@
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F36" s="338" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19801,19 +19790,19 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C40" s="138">
         <f>DCF!C17</f>
         <v>0.68269686315429268</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C41" s="138">
         <f>DCF!C16</f>
@@ -19976,13 +19965,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E60" s="420"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -19995,10 +19984,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -20053,7 +20042,7 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -20066,10 +20055,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -20149,7 +20138,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="352" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="352"/>
       <c r="C2" s="352"/>
@@ -20163,7 +20152,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="443" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F3" s="444">
         <f>Thesis!F3</f>
@@ -20172,7 +20161,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="430" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C4" s="431" t="str">
         <f>Thesis!C4</f>
@@ -20180,7 +20169,7 @@
       </c>
       <c r="D4" s="356"/>
       <c r="E4" s="442" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F4" s="445" t="str">
         <f>Thesis!F4</f>
@@ -20189,14 +20178,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="350" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C5" s="362" t="str">
         <f>Thesis!C5</f>
         <v>6186.HK</v>
       </c>
       <c r="E5" s="446" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F5" s="447" t="str">
         <f>Thesis!F5</f>
@@ -20205,7 +20194,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="357" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C6" s="359" t="str">
         <f>Thesis!C6</f>
@@ -20215,7 +20204,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="350" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C7" s="359" t="str">
         <f>Market_currency</f>
@@ -20226,7 +20215,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="358" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
@@ -20235,7 +20224,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="358" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C9" s="360">
         <f>Common_Shares</f>
@@ -20244,14 +20233,14 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="358" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
         <v>36351.659333039999</v>
       </c>
       <c r="D10" s="350" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
@@ -20263,31 +20252,31 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
-        <v>502</v>
-      </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="B12" s="470" t="s">
+        <v>501</v>
+      </c>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C14" s="355"/>
       <c r="D14" s="356"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="350" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C15" s="365" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="358" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E15" s="351" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20296,14 +20285,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="350" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C16" s="365" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="358" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
@@ -20312,14 +20301,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="350" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C17" s="432">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="D17" s="358" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E17" s="351" t="str">
         <f>Reporting_currency</f>
@@ -20336,7 +20325,7 @@
         <v>6.3935654360067202</v>
       </c>
       <c r="D18" s="357" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E18" s="434">
         <f>Thesis!E18</f>
@@ -20345,14 +20334,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="357" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C19" s="359" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="350" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E19" s="435">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20365,14 +20354,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="354" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C21" s="368" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="369" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E21" s="370">
         <f>Holding_Period</f>
@@ -20381,14 +20370,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="350" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C22" s="371">
         <f>E140</f>
         <v>3.8199151912245375</v>
       </c>
       <c r="D22" s="372" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
@@ -20397,14 +20386,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="350" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C23" s="374">
         <f>E141</f>
         <v>4.4400738790443013</v>
       </c>
       <c r="D23" s="372" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
@@ -20413,14 +20402,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="350" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C24" s="374">
         <f>E144</f>
         <v>5.5307128828262222</v>
       </c>
       <c r="D24" s="372" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E24" s="375">
         <f>Thesis!E24</f>
@@ -20429,14 +20418,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="350" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C25" s="374">
         <f>E145</f>
         <v>5.9940521392574224</v>
       </c>
       <c r="D25" s="372" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E25" s="375">
         <f>Thesis!E25</f>
@@ -20445,7 +20434,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="352" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B27" s="352"/>
       <c r="C27" s="352"/>
@@ -20454,26 +20443,26 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
+        <v>502</v>
+      </c>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="471" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="474" t="s">
-        <v>504</v>
-      </c>
-      <c r="C30" s="474"/>
-      <c r="D30" s="474"/>
-      <c r="E30" s="474"/>
-      <c r="F30" s="474"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C32" s="377">
         <f>scaling_factor</f>
@@ -20481,13 +20470,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="472" t="s">
-        <v>505</v>
-      </c>
-      <c r="C33" s="472"/>
-      <c r="D33" s="472"/>
-      <c r="E33" s="472"/>
-      <c r="F33" s="472"/>
+      <c r="B33" s="469" t="s">
+        <v>504</v>
+      </c>
+      <c r="C33" s="469"/>
+      <c r="D33" s="469"/>
+      <c r="E33" s="469"/>
+      <c r="F33" s="469"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="379" t="s">
@@ -20507,13 +20496,13 @@
       <c r="C35" s="381"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="472" t="s">
-        <v>506</v>
-      </c>
-      <c r="C36" s="472"/>
-      <c r="D36" s="472"/>
-      <c r="E36" s="472"/>
-      <c r="F36" s="472"/>
+      <c r="B36" s="469" t="s">
+        <v>505</v>
+      </c>
+      <c r="C36" s="469"/>
+      <c r="D36" s="469"/>
+      <c r="E36" s="469"/>
+      <c r="F36" s="469"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="379" t="s">
@@ -20542,13 +20531,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="472" t="s">
-        <v>507</v>
-      </c>
-      <c r="C40" s="472"/>
-      <c r="D40" s="472"/>
-      <c r="E40" s="472"/>
-      <c r="F40" s="472"/>
+      <c r="B40" s="469" t="s">
+        <v>506</v>
+      </c>
+      <c r="C40" s="469"/>
+      <c r="D40" s="469"/>
+      <c r="E40" s="469"/>
+      <c r="F40" s="469"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="379" t="s">
@@ -20564,13 +20553,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="472" t="s">
-        <v>508</v>
-      </c>
-      <c r="C43" s="472"/>
-      <c r="D43" s="472"/>
-      <c r="E43" s="472"/>
-      <c r="F43" s="472"/>
+      <c r="B43" s="469" t="s">
+        <v>507</v>
+      </c>
+      <c r="C43" s="469"/>
+      <c r="D43" s="469"/>
+      <c r="E43" s="469"/>
+      <c r="F43" s="469"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="379" t="s">
@@ -20617,7 +20606,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="350" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20634,17 +20623,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="472" t="s">
-        <v>510</v>
-      </c>
-      <c r="C51" s="472"/>
-      <c r="D51" s="472"/>
-      <c r="E51" s="472"/>
-      <c r="F51" s="472"/>
+      <c r="B51" s="469" t="s">
+        <v>509</v>
+      </c>
+      <c r="C51" s="469"/>
+      <c r="D51" s="469"/>
+      <c r="E51" s="469"/>
+      <c r="F51" s="469"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="379" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C52" s="380">
         <f>Normalized_FCF!C12</f>
@@ -20656,13 +20645,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="472" t="s">
-        <v>511</v>
-      </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="B54" s="469" t="s">
+        <v>510</v>
+      </c>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20678,26 +20667,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
+        <v>511</v>
+      </c>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
-        <v>513</v>
-      </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C60" s="380">
         <f>Normalized_FCF!G19</f>
@@ -20740,7 +20729,7 @@
         <v>6.0299251870324193E-2</v>
       </c>
       <c r="E63" s="379" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F63" s="387">
         <f>Normalized_FCF!C90</f>
@@ -20749,13 +20738,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="376" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C65" s="388" t="s">
         <v>327</v>
       </c>
       <c r="D65" s="388" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -20815,7 +20804,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="352" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B71" s="352"/>
       <c r="C71" s="352"/>
@@ -20828,36 +20817,36 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
-        <v>514</v>
-      </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="B73" s="470" t="s">
+        <v>513</v>
+      </c>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="474" t="s">
-        <v>484</v>
-      </c>
-      <c r="C74" s="474"/>
-      <c r="D74" s="474"/>
-      <c r="E74" s="474"/>
-      <c r="F74" s="474"/>
+      <c r="B74" s="471" t="s">
+        <v>483</v>
+      </c>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
-        <v>515</v>
-      </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="B77" s="470" t="s">
+        <v>514</v>
+      </c>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20905,7 +20894,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="350" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20923,7 +20912,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="389" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C85" s="397">
         <f>BS!C66</f>
@@ -20949,7 +20938,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="350" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20980,7 +20969,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="379" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
@@ -20993,7 +20982,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="352" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B94" s="352"/>
       <c r="C94" s="352"/>
@@ -21006,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
-        <v>518</v>
-      </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="B96" s="470" t="s">
+        <v>517</v>
+      </c>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="474" t="s">
-        <v>519</v>
-      </c>
-      <c r="C97" s="474"/>
-      <c r="D97" s="474"/>
-      <c r="E97" s="474"/>
-      <c r="F97" s="474"/>
+      <c r="B97" s="471" t="s">
+        <v>518</v>
+      </c>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="474" t="s">
-        <v>520</v>
-      </c>
-      <c r="C98" s="474"/>
-      <c r="D98" s="474"/>
-      <c r="E98" s="474"/>
-      <c r="F98" s="474"/>
+      <c r="B98" s="471" t="s">
+        <v>519</v>
+      </c>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21040,7 +21029,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="392"/>
       <c r="B100" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -21076,7 +21065,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="392"/>
       <c r="B104" s="379" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C104" s="375">
         <v>0</v>
@@ -21089,29 +21078,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="392"/>
       <c r="B106" s="400" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C106" s="399"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
-        <v>521</v>
-      </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="B107" s="470" t="s">
+        <v>520</v>
+      </c>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
-        <v>540</v>
-      </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="B108" s="470" t="s">
+        <v>539</v>
+      </c>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21119,13 +21108,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="392"/>
       <c r="B110" s="376" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="392"/>
       <c r="B111" s="382" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
@@ -21139,7 +21128,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="392"/>
       <c r="B112" s="379" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
@@ -21155,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
-        <v>522</v>
-      </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="B114" s="470" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21169,25 +21158,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="392"/>
       <c r="B116" s="376" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="392"/>
       <c r="B117" s="349" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117" s="349" t="s">
         <v>379</v>
-      </c>
-      <c r="C117" s="349" t="s">
-        <v>380</v>
       </c>
       <c r="D117" s="349" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="349" t="s">
+        <v>380</v>
+      </c>
+      <c r="F117" s="349" t="s">
         <v>381</v>
-      </c>
-      <c r="F117" s="349" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21303,13 +21292,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="472" t="s">
-        <v>523</v>
-      </c>
-      <c r="C124" s="472"/>
-      <c r="D124" s="472"/>
-      <c r="E124" s="472"/>
-      <c r="F124" s="472"/>
+      <c r="B124" s="469" t="s">
+        <v>522</v>
+      </c>
+      <c r="C124" s="469"/>
+      <c r="D124" s="469"/>
+      <c r="E124" s="469"/>
+      <c r="F124" s="469"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="379" t="s">
@@ -21325,17 +21314,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="477" t="s">
-        <v>524</v>
-      </c>
-      <c r="C127" s="477"/>
-      <c r="D127" s="477"/>
-      <c r="E127" s="477"/>
-      <c r="F127" s="477"/>
+      <c r="B127" s="474" t="s">
+        <v>523</v>
+      </c>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B129" s="352"/>
       <c r="C129" s="352"/>
@@ -21344,31 +21333,31 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="478" t="s">
+      <c r="B131" s="475" t="s">
+        <v>524</v>
+      </c>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C131" s="478"/>
-      <c r="D131" s="478"/>
-      <c r="E131" s="478"/>
-      <c r="F131" s="478"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
-        <v>526</v>
-      </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="350" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C135" s="412">
         <f>E21</f>
@@ -21377,7 +21366,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="350" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C136" s="413">
         <f>Scenarios!C58</f>
@@ -21390,28 +21379,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="376" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C138" s="414"/>
       <c r="D138" s="414"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="347" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="348" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21458,21 +21447,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="347" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="348" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21519,7 +21508,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="352" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B147" s="352"/>
       <c r="C147" s="352"/>
@@ -21528,98 +21517,98 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="479" t="s">
-        <v>527</v>
-      </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="B149" s="476" t="s">
+        <v>526</v>
+      </c>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
-        <v>528</v>
-      </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="B152" s="472" t="s">
+        <v>527</v>
+      </c>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="419" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="419" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="350" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="472" t="s">
-        <v>444</v>
-      </c>
-      <c r="C158" s="472"/>
-      <c r="D158" s="472"/>
-      <c r="E158" s="472"/>
-      <c r="F158" s="472"/>
+      <c r="B158" s="469" t="s">
+        <v>443</v>
+      </c>
+      <c r="C158" s="469"/>
+      <c r="D158" s="469"/>
+      <c r="E158" s="469"/>
+      <c r="F158" s="469"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="350" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="476" t="s">
+      <c r="B161" s="473" t="s">
+        <v>388</v>
+      </c>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C161" s="476"/>
-      <c r="D161" s="476"/>
-      <c r="E161" s="476"/>
-      <c r="F161" s="476"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="476" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="476"/>
-      <c r="D162" s="476"/>
-      <c r="E162" s="476"/>
-      <c r="F162" s="476"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="419" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="419" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="419" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -21671,28 +21660,4 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C12B343-6327-45C8-9749-E2C760215AAE}">
-  <dimension ref="B2:E2"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" style="461" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="461" customWidth="1"/>
-    <col min="3" max="5" width="20.6640625" style="461" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="461"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="459" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="460"/>
-      <c r="D2" s="460"/>
-      <c r="E2" s="460"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69820599-CC2B-4B55-BDF2-F3062F4A1A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734249AF-74BA-460A-9E5B-81CB1BA5D247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.01</v>
+        <v>3.89</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>36351.659333039999</v>
+        <v>35263.829128559999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.31685611828363341</v>
+        <v>0.23344938128212497</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0934131499999999</v>
+        <v>1.0931321500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.3935654360067202</v>
+        <v>6.3919223316709823</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5533,7 +5533,7 @@
         <v>316</v>
       </c>
       <c r="E21" s="450">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>3.8199151912245375</v>
+        <v>4.0138896271444429</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E22" s="79">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.4400738790443013</v>
+        <v>4.6380901813259712</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
       </c>
       <c r="E23" s="451">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>5.5307128828262222</v>
+        <v>5.1648441984205515</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>5.9940521392574224</v>
+        <v>5.8129824439892515</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.7927747719079815E-2</v>
+        <v>8.031104380627542E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0299251870324193E-2</v>
+        <v>6.2159383033419016E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10192197153370404</v>
+        <v>-0.10189577825625812</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8181203888436919</v>
+        <v>1.8176531438418693</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1659773764291717E-4</v>
+        <v>5.1646497541641789E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>1.7167150150476305</v>
+        <v>1.7162738305610272</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>1.2424960256803461</v>
+        <v>1.2421767123602019</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.8 HKD</v>
+        <v>7.79 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3935654360067202</v>
+        <v>6.3919223316709823</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C135" s="204">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
         <v>475</v>
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="340">
         <f>Scenarios!C62</f>
-        <v>0.31178600823045277</v>
+        <v>0.49381397561910462</v>
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>3.5081291829940846</v>
+        <v>3.5200756515253384</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>3.8199151912245375</v>
+        <v>4.0138896271444429</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="340">
         <f>Scenarios!C63</f>
-        <v>0.34819199999999995</v>
+        <v>0.54305609086063367</v>
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>4.0918818790443012</v>
+        <v>4.0950340904653375</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.4400738790443013</v>
+        <v>4.6380901813259712</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
         <v>475</v>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="340">
         <f>Scenarios!C66</f>
-        <v>0.41005477282098601</v>
+        <v>0.58336743585196538</v>
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>5.1206581100052357</v>
+        <v>4.5814767625685864</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>5.5307128828262222</v>
+        <v>5.1648441984205515</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="340">
         <f>Scenarios!C67</f>
-        <v>0.43566857385039198</v>
+        <v>0.63167232993043521</v>
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.5583835654070306</v>
+        <v>5.1813101140588165</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>5.9940521392574224</v>
+        <v>5.8129824439892515</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -10173,11 +10173,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.089037603784476</v>
+        <v>3.0882437414034882</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2424960256803461</v>
+        <v>1.2421767123602019</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10583,11 +10583,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923948.32612094993</v>
+        <v>923710.87746795011</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10192197153370404</v>
+        <v>0.10189577825625812</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10600,11 +10600,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16481718.95304242</v>
+        <v>16477483.259493461</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8181203888436919</v>
+        <v>1.8176531438418693</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10617,11 +10617,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4683.0885214499995</v>
+        <v>4681.8849984500011</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1659773764291717E-4</v>
+        <v>5.1646497541641789E-4</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10634,11 +10634,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17410350.367684819</v>
+        <v>17405876.02195986</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>1.9205589581150389</v>
+        <v>1.9200653870735438</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -14222,28 +14222,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0299251870324193E-2</v>
+        <v>6.2159383033419016E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.1396508728179565E-2</v>
+        <v>8.3907455012853474E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.0648379052369079E-2</v>
+        <v>7.2827763496143949E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1122194513715722E-2</v>
+        <v>7.3316195372750637E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.117356608478803</v>
+        <v>0.12097686375321337</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.384039900249377E-2</v>
+        <v>7.6118251928020575E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15364,46 +15364,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31249026835351013</v>
+        <v>0.31240996040641139</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35105873520694875</v>
+        <v>0.35096851541711627</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.3153751548264534</v>
+        <v>0.31529410548247377</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49431528388283896</v>
+        <v>0.49418824810064543</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63013091576357727</v>
+        <v>0.62996897625578063</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54711909909974399</v>
+        <v>0.54697849308375923</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36517513689349623</v>
+        <v>0.36508128928112116</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21379101260410516</v>
+        <v>0.21373606971765671</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3907771188164471E-2</v>
+        <v>9.3883637507584661E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6295946573542596E-2</v>
+        <v>2.6289188687937178E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.7927747719079815E-2</v>
+        <v>8.031104380627542E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.7545819253603177E-2</v>
+        <v>9.0223268744759957E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8647170779664197E-2</v>
+        <v>8.1052469275700201E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12327064435981022</v>
+        <v>0.12704068074566721</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15713987924278736</v>
+        <v>0.16194575225084334</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13643867807973667</v>
+        <v>0.14061143781073501</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1066118926058912E-2</v>
+        <v>9.3851231177666111E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3314466983567371E-2</v>
+        <v>5.4945005068806348E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3418396805028548E-2</v>
+        <v>2.4134611184469065E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.5575926617313209E-3</v>
+        <v>6.7581461922717675E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15478,39 +15478,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10052140856961576</v>
+        <v>0.10362232605762449</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0514492608303063E-2</v>
+        <v>9.3306713459973087E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1361177478768533</v>
+        <v>0.14031675295274595</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19022229320120898</v>
+        <v>0.19609033309430543</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20457476044954157</v>
+        <v>0.2108855499749773</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10823651718214319</v>
+        <v>0.11157543287927872</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1682301197239067E-2</v>
+        <v>6.3585097121061362E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.191672735955333E-2</v>
+        <v>3.2901305067303051E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1172859986362402E-2</v>
+        <v>1.1517524047638365E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7167150150476305</v>
+        <v>1.7162738305610272</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0934131499999999</v>
+        <v>1.0931321500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>54635597.683374979</v>
+        <v>54621556.693517655</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3940929976315228</v>
+        <v>6.3924497577159132</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18717,23 +18717,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4433943913214398</v>
+        <v>4.4422524681390083</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.2210511734107046</v>
+        <v>6.2194524041076953</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.4224736915749698</v>
+        <v>6.4208231580073685</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>6.6314043286865489</v>
+        <v>6.6297001013170869</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.7963586522531783</v>
+        <v>7.7943550392718626</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>4.2618736801283132</v>
+        <v>4.2607784065767609</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2533599494721557</v>
+        <v>6.2517528770258437</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.4903541070304529</v>
+        <v>6.4886861286417954</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7383149898838699</v>
+        <v>6.7365832871764759</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>8.1577039451140436</v>
+        <v>8.1556074687651208</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>4.1095486077984171</v>
+        <v>4.1084924807902592</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2837859297258349</v>
+        <v>6.2821710380023799</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.554911704946158</v>
+        <v>6.5532271356787328</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>6.840989098073373</v>
+        <v>6.8392310087943509</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>8.5215761281347753</v>
+        <v>8.5193861390240695</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18811,23 +18811,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>3.9817233722768255</v>
+        <v>3.9807000955148721</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3124388342071516</v>
+        <v>6.3108165788753858</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>6.6163091407261287</v>
+        <v>6.6146087927208557</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>6.9395945353089799</v>
+        <v>6.9378111050800486</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>8.8879928718759285</v>
+        <v>8.8857087160680397</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>3.8744574403705951</v>
+        <v>3.8734617302488146</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.3394219890100691</v>
+        <v>6.3377927991846947</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6747011076217664</v>
+        <v>6.6729857532644132</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.0342925309758089</v>
+        <v>7.0324847639837964</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>9.2569719704684221</v>
+        <v>9.254592989454979</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.7844440709387932</v>
+        <v>3.7834714936619123</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.3648326988944035</v>
+        <v>6.3631969786834404</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>6.7302347264875451</v>
+        <v>6.7285051003547878</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.1252379254157487</v>
+        <v>7.1234067860545291</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>9.6285313424776469</v>
+        <v>9.6260568731453233</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>3.5102369578863004</v>
+        <v>3.5093348500369803</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.4713262849505941</v>
+        <v>6.4696631965872706</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>6.9696919751693684</v>
+        <v>6.9679008100960189</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.5286791301113363</v>
+        <v>7.5267443090095787</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.525668274131503</v>
+        <v>11.52270625306469</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3961319358188993</v>
+        <v>3.3952591522110156</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.5502020920680621</v>
+        <v>6.5485187331402228</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1560046250555294</v>
+        <v>7.1541655788545224</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>7.8582735658165346</v>
+        <v>7.8562540411089774</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>13.490072916034579</v>
+        <v>13.486606055873439</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>3.3486497391827035</v>
+        <v>3.3477891581875787</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.6086224456201448</v>
+        <v>6.6069240730450414</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.3009674678956973</v>
+        <v>7.2990911671959324</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.1275383081965131</v>
+        <v>8.1254495842182077</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>15.524130412225084</v>
+        <v>15.520140812643415</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>3.3288911084357893</v>
+        <v>3.3280356052790276</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>6.6518922115201944</v>
+        <v>6.6501827188993712</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.4137575861036851</v>
+        <v>7.4118522990841411</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.3475162375381604</v>
+        <v>8.345370980676428</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>17.63031047795765</v>
+        <v>17.625779603928649</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.7963586522531783</v>
+        <v>7.7943550392718626</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>6.6314043286865489</v>
+        <v>6.6297001013170869</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.4224736915749698</v>
+        <v>6.4208231580073685</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.2210511734107046</v>
+        <v>6.2194524041076953</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>4.4433943913214398</v>
+        <v>4.4422524681390083</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>6.6314043286865489</v>
+        <v>6.6297001013170869</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.4224736915749698</v>
+        <v>6.4208231580073685</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.2210511734107046</v>
+        <v>6.2194524041076953</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4239753153644328</v>
+        <v>6.4223243958893779</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.7963586522531783</v>
+        <v>7.7943550392718626</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>4.4433943913214398</v>
+        <v>4.4422524681390083</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.01</v>
+        <v>3.89</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.31685611828363341</v>
+        <v>0.23344938128212497</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.9515075657243935E-2</v>
+        <v>5.9252715164389458E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3935654360067202</v>
+        <v>6.3919223316709823</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3940929976315228</v>
+        <v>6.3924497577159132</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.30038934884423074</v>
+        <v>0.3003893488442308</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="C57" s="222">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" s="126"/>
     </row>
@@ -19996,23 +19996,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.31178600823045277</v>
+        <v>0.49381397561910462</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.5081291829940846</v>
+        <v>3.5200756515253384</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>3.8199151912245375</v>
+        <v>4.0138896271444429</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.40253756226347903</v>
+        <v>0.37203717146933357</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20021,23 +20021,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.34819199999999995</v>
+        <v>0.54305609086063367</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.0918818790443012</v>
+        <v>4.0950340904653375</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.4400738790443013</v>
+        <v>4.6380901813259712</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.30554024612947839</v>
+        <v>0.27438258153655048</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20067,15 +20067,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>0.41005477282098601</v>
+        <v>0.58336743585196538</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>5.1206581100052357</v>
+        <v>4.5814767625685864</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>5.5307128828262222</v>
+        <v>5.1648441984205515</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.13502776939983685</v>
+        <v>0.19203992300660611</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20092,15 +20092,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>0.43566857385039198</v>
+        <v>0.63167232993043521</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.5583835654070306</v>
+        <v>5.1813101140588165</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>5.9940521392574224</v>
+        <v>5.8129824439892515</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>6.248677686152293E-2</v>
+        <v>9.0573673715209857E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>4.01</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20237,14 +20237,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>36351.659333039999</v>
+        <v>35263.829128559999</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.31685611828363341</v>
+        <v>0.23344938128212497</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0934131499999999</v>
+        <v>1.0931321500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.3935654360067202</v>
+        <v>6.3919223316709823</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="E21" s="370">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -20374,14 +20374,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>3.8199151912245375</v>
+        <v>4.0138896271444429</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20390,14 +20390,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.4400738790443013</v>
+        <v>4.6380901813259712</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>5.5307128828262222</v>
+        <v>5.1648441984205515</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>5.9940521392574224</v>
+        <v>5.8129824439892515</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>7.7927747719079815E-2</v>
+        <v>8.031104380627542E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.0299251870324193E-2</v>
+        <v>6.2159383033419016E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10192197153370404</v>
+        <v>-0.10189577825625812</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8181203888436919</v>
+        <v>1.8176531438418693</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1659773764291717E-4</v>
+        <v>5.1646497541641789E-4</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>1.7167150150476305</v>
+        <v>1.7162738305610272</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>1.2424960256803461</v>
+        <v>1.2421767123602019</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>6.0269256130270792</v>
+        <v>6.0253767327184251</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21195,7 +21195,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.8 HKD</v>
+        <v>7.79 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.3935654360067202</v>
+        <v>6.3919223316709823</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C135" s="412">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
         <v>475</v>
@@ -21409,19 +21409,19 @@
       </c>
       <c r="C140" s="416">
         <f>Scenarios!C62</f>
-        <v>0.31178600823045277</v>
+        <v>0.49381397561910462</v>
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>3.5081291829940846</v>
+        <v>3.5200756515253384</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>3.8199151912245375</v>
+        <v>4.0138896271444429</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21430,19 +21430,19 @@
       </c>
       <c r="C141" s="416">
         <f>Scenarios!C63</f>
-        <v>0.34819199999999995</v>
+        <v>0.54305609086063367</v>
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>4.0918818790443012</v>
+        <v>4.0950340904653375</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.4400738790443013</v>
+        <v>4.6380901813259712</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
         <v>475</v>
@@ -21470,15 +21470,15 @@
       </c>
       <c r="C144" s="416">
         <f>Scenarios!C66</f>
-        <v>0.41005477282098601</v>
+        <v>0.58336743585196538</v>
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>5.1206581100052357</v>
+        <v>4.5814767625685864</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>5.5307128828262222</v>
+        <v>5.1648441984205515</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21491,15 +21491,15 @@
       </c>
       <c r="C145" s="416">
         <f>Scenarios!C67</f>
-        <v>0.43566857385039198</v>
+        <v>0.63167232993043521</v>
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.5583835654070306</v>
+        <v>5.1813101140588165</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>5.9940521392574224</v>
+        <v>5.8129824439892515</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734249AF-74BA-460A-9E5B-81CB1BA5D247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A4E534-1FAF-4DC7-9D31-138101331A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.23344938128212497</v>
+        <v>0.23321922687563271</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0931321500000002</v>
+        <v>1.0924664399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.3919223316709823</v>
+        <v>6.3880296947053443</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>4.0138896271444429</v>
+        <v>3.6591560894679178</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E22" s="79">
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.6380901813259712</v>
+        <v>4.3538511954983088</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
       </c>
       <c r="E23" s="451">
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>5.1648441984205515</v>
+        <v>5.1620541104191968</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>5.8129824439892515</v>
+        <v>5.8098270615809753</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.031104380627542E-2</v>
+        <v>8.0262134930095805E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189577825625812</v>
+        <v>-0.10183372442448399</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8176531438418693</v>
+        <v>1.8165462055138843</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1646497541641789E-4</v>
+        <v>5.161504517801086E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>1.7162738305610272</v>
+        <v>1.7152286315411802</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>1.2421767123602019</v>
+        <v>1.2414202352415062</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3919223316709823</v>
+        <v>6.3880296947053443</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="340">
         <f>Scenarios!C62</f>
-        <v>0.49381397561910462</v>
+        <v>0.46514124211524543</v>
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>3.5200756515253384</v>
+        <v>3.1940148473526722</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>4.0138896271444429</v>
+        <v>3.6591560894679178</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="340">
         <f>Scenarios!C63</f>
-        <v>0.54305609086063367</v>
+        <v>0.52103337867510235</v>
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>4.0950340904653375</v>
+        <v>3.8328178168232068</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.6380901813259712</v>
+        <v>4.3538511954983088</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>4.5814767625685864</v>
+        <v>4.5786866745672317</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>5.1648441984205515</v>
+        <v>5.1620541104191968</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.1813101140588165</v>
+        <v>5.1781547316505403</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>5.8129824439892515</v>
+        <v>5.8098270615809753</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10173,11 +10173,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0882437414034882</v>
+        <v>3.0863630220951315</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2421767123602019</v>
+        <v>1.2414202352415062</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10583,11 +10583,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923710.87746795011</v>
+        <v>923148.34386371996</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10189577825625812</v>
+        <v>0.10183372442448399</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10600,11 +10600,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16477483.259493461</v>
+        <v>16467448.584929474</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8176531438418693</v>
+        <v>1.8165462055138843</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10617,11 +10617,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4681.8849984500011</v>
+        <v>4679.03376252</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1646497541641789E-4</v>
+        <v>5.1615045178010871E-4</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10634,11 +10634,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17405876.02195986</v>
+        <v>17395275.96255571</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>1.9200653870735438</v>
+        <v>1.9188960803901485</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15364,46 +15364,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31240996040641139</v>
+        <v>0.31221970487807271</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35096851541711627</v>
+        <v>0.35075477799259863</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31529410548247377</v>
+        <v>0.31510209352951746</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49418824810064543</v>
+        <v>0.49388729083885125</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62996897625578063</v>
+        <v>0.62958532945956902</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54697849308375923</v>
+        <v>0.54664538692396791</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36508128928112116</v>
+        <v>0.36485895727388179</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21373606971765671</v>
+        <v>0.21360590591360815</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3883637507584661E-2</v>
+        <v>9.3826463014706388E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6289188687937178E-2</v>
+        <v>2.627317875190021E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.031104380627542E-2</v>
+        <v>8.0262134930095805E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.0223268744759957E-2</v>
+        <v>9.0168323391413521E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1052469275700201E-2</v>
+        <v>8.1003108876482641E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12704068074566721</v>
+        <v>0.12696331384032164</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16194575225084334</v>
+        <v>0.16184712839577609</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14061143781073501</v>
+        <v>0.1405258064071897</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.3851231177666111E-2</v>
+        <v>9.3794076420021022E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.4945005068806348E-2</v>
+        <v>5.4911543936660187E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.4134611184469065E-2</v>
+        <v>2.4119913371389815E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.7581461922717675E-3</v>
+        <v>6.7540305274807737E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7162738305610272</v>
+        <v>1.7152286315411802</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0931321500000002</v>
+        <v>1.0924664399999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>54621556.693517655</v>
+        <v>54588292.53921897</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3924497577159132</v>
+        <v>6.3885567995514219</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18717,23 +18717,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4422524681390083</v>
+        <v>4.4395471667803701</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.2194524041076953</v>
+        <v>6.2156648001478816</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.4208231580073685</v>
+        <v>6.4169129206362339</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>6.6297001013170869</v>
+        <v>6.6256626593166397</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.7943550392718626</v>
+        <v>7.7896083303829187</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>4.2607784065767609</v>
+        <v>4.2581836216799456</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2517528770258437</v>
+        <v>6.2479456022990263</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.4886861286417954</v>
+        <v>6.4847345631858717</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7365832871764759</v>
+        <v>6.7324807540471481</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>8.1556074687651208</v>
+        <v>8.1506407596183514</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>4.1084924807902592</v>
+        <v>4.1059904369802878</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2821710380023799</v>
+        <v>6.2783452388236531</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.5532271356787328</v>
+        <v>6.549236265191122</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>6.8392310087943509</v>
+        <v>6.8350659639048867</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>8.5193861390240695</v>
+        <v>8.5141978911561313</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18811,23 +18811,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>3.9807000955148721</v>
+        <v>3.978275876393162</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3108165788753858</v>
+        <v>6.3069733347582631</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>6.6146087927208557</v>
+        <v>6.6105805412240866</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>6.9378111050800486</v>
+        <v>6.933586025586445</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>8.8857087160680397</v>
+        <v>8.8802973802571081</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>3.8734617302488146</v>
+        <v>3.8711028185578127</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.3377927991846947</v>
+        <v>6.3339331267339789</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6729857532644132</v>
+        <v>6.6689219505980954</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.0324847639837964</v>
+        <v>7.0282020288796891</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>9.254592989454979</v>
+        <v>9.2489570056455079</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.7834714936619123</v>
+        <v>3.7811673854092671</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.3631969786834404</v>
+        <v>6.3593218352612286</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>6.7285051003547878</v>
+        <v>6.724407486785962</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.1234067860545291</v>
+        <v>7.1190686800610807</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>9.6260568731453233</v>
+        <v>9.6201946703722871</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>3.5093348500369803</v>
+        <v>3.5071976891246246</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.4696631965872706</v>
+        <v>6.4657232159668112</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>6.9679008100960189</v>
+        <v>6.9636574061779379</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.5267443090095787</v>
+        <v>7.5221605732243368</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.52270625306469</v>
+        <v>11.515689003796401</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3952591522110156</v>
+        <v>3.3931914626181157</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.5485187331402228</v>
+        <v>6.5445307300375415</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1541655788545224</v>
+        <v>7.1498087409667139</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>7.8562540411089774</v>
+        <v>7.8514696361514353</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>13.486606055873439</v>
+        <v>13.478392805062493</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>3.3477891581875787</v>
+        <v>3.3457503774962434</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.6069240730450414</v>
+        <v>6.6029005014899749</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.2990911671959324</v>
+        <v>7.294646070616424</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.1254495842182077</v>
+        <v>8.1205012410167807</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>15.520140812643415</v>
+        <v>15.5106891530793</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>3.3280356052790276</v>
+        <v>3.3260088543662572</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>6.6501827188993712</v>
+        <v>6.6461328031249609</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.4118522990841411</v>
+        <v>7.4073385317468388</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.345370980676428</v>
+        <v>8.3402887068492895</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>17.625779603928649</v>
+        <v>17.61504562474769</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.7943550392718626</v>
+        <v>7.7896083303829187</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>6.6297001013170869</v>
+        <v>6.6256626593166397</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.4208231580073685</v>
+        <v>6.4169129206362339</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.2194524041076953</v>
+        <v>6.2156648001478816</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>4.4422524681390083</v>
+        <v>4.4395471667803701</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>6.6297001013170869</v>
+        <v>6.6256626593166397</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.4208231580073685</v>
+        <v>6.4169129206362339</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.2194524041076953</v>
+        <v>6.2156648001478816</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4223243958893779</v>
+        <v>6.4184132442746442</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.7943550392718626</v>
+        <v>7.7896083303829187</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>4.4422524681390083</v>
+        <v>4.4395471667803701</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23344938128212497</v>
+        <v>0.23321922687563271</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.9252715164389458E-2</v>
+        <v>5.9276719164918328E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3919223316709823</v>
+        <v>6.3880296947053443</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3924497577159132</v>
+        <v>6.3885567995514219</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.3003893488442308</v>
+        <v>0.30038934884423074</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19996,23 +19996,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.49381397561910462</v>
+        <v>0.46514124211524543</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.5200756515253384</v>
+        <v>3.1940148473526722</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>4.0138896271444429</v>
+        <v>3.6591560894679178</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.37203717146933357</v>
+        <v>0.4271854915607588</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20021,23 +20021,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.54305609086063367</v>
+        <v>0.52103337867510235</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>4.0950340904653375</v>
+        <v>3.8328178168232068</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.6380901813259712</v>
+        <v>4.3538511954983088</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.27438258153655048</v>
+        <v>0.31843598048597743</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5814767625685864</v>
+        <v>4.5786866745672317</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>5.1648441984205515</v>
+        <v>5.1620541104191968</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19203992300660611</v>
+        <v>0.19198431314226483</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1813101140588165</v>
+        <v>5.1781547316505403</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>5.8129824439892515</v>
+        <v>5.8098270615809753</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>9.0573673715209857E-2</v>
+        <v>9.051345418816803E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.23344938128212497</v>
+        <v>0.23321922687563271</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20252,13 +20252,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0931321500000002</v>
+        <v>1.0924664399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.3919223316709823</v>
+        <v>6.3880296947053443</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20374,14 +20374,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>4.0138896271444429</v>
+        <v>3.6591560894679178</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20390,14 +20390,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.6380901813259712</v>
+        <v>4.3538511954983088</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>5.1648441984205515</v>
+        <v>5.1620541104191968</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>5.8129824439892515</v>
+        <v>5.8098270615809753</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20443,22 +20443,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20648,10 +20648,10 @@
       <c r="B54" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20667,22 +20667,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>8.031104380627542E-2</v>
+        <v>8.0262134930095805E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20817,22 +20817,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20840,13 +20840,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10189577825625812</v>
+        <v>-0.10183372442448399</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8176531438418693</v>
+        <v>1.8165462055138843</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1646497541641789E-4</v>
+        <v>5.161504517801086E-4</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>1.7162738305610272</v>
+        <v>1.7152286315411802</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20995,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21084,23 +21084,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>1.2421767123602019</v>
+        <v>1.2414202352415062</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>6.0253767327184251</v>
+        <v>6.0217073195145971</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21144,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.3919223316709823</v>
+        <v>6.3880296947053443</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21314,13 +21314,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21333,22 +21333,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21409,19 +21409,19 @@
       </c>
       <c r="C140" s="416">
         <f>Scenarios!C62</f>
-        <v>0.49381397561910462</v>
+        <v>0.46514124211524543</v>
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>3.5200756515253384</v>
+        <v>3.1940148473526722</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>4.0138896271444429</v>
+        <v>3.6591560894679178</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21430,19 +21430,19 @@
       </c>
       <c r="C141" s="416">
         <f>Scenarios!C63</f>
-        <v>0.54305609086063367</v>
+        <v>0.52103337867510235</v>
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>4.0950340904653375</v>
+        <v>3.8328178168232068</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.6380901813259712</v>
+        <v>4.3538511954983088</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21474,11 +21474,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>4.5814767625685864</v>
+        <v>4.5786866745672317</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>5.1648441984205515</v>
+        <v>5.1620541104191968</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21495,11 +21495,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.1813101140588165</v>
+        <v>5.1781547316505403</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>5.8129824439892515</v>
+        <v>5.8098270615809753</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21517,13 +21517,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21531,13 +21531,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21574,22 +21574,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21613,15 +21613,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21636,12 +21633,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A4E534-1FAF-4DC7-9D31-138101331A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E9C79B-77F9-4F65-8BE8-12B3A067F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>35263.829128559999</v>
+        <v>33178.821236639997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.23321922687563271</v>
+        <v>0.25981923397241607</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.0262134930095805E-2</v>
+        <v>8.5305930294555382E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2159383033419016E-2</v>
+        <v>6.6065573770491798E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14222,28 +14222,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2159383033419016E-2</v>
+        <v>6.6065573770491798E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.3907455012853474E-2</v>
+        <v>8.9180327868852466E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.2827763496143949E-2</v>
+        <v>7.7404371584699455E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.3316195372750637E-2</v>
+        <v>7.7923497267759559E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.12097686375321337</v>
+        <v>0.12857923497267759</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.6118251928020575E-2</v>
+        <v>8.0901639344262297E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0262134930095805E-2</v>
+        <v>8.5305930294555382E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.0168323391413521E-2</v>
+        <v>9.5834638795791974E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1003108876482641E-2</v>
+        <v>8.6093468177463786E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12696331384032164</v>
+        <v>0.13494188274285551</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16184712839577609</v>
+        <v>0.1720178495791172</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1405258064071897</v>
+        <v>0.1493566630939803</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.3794076420021022E-2</v>
+        <v>9.9688239692317424E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.4911543936660187E-2</v>
+        <v>5.8362269375302769E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.4119913371389815E-2</v>
+        <v>2.5635645632433438E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.7540305274807737E-3</v>
+        <v>7.1784641398634453E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15478,39 +15478,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10362232605762449</v>
+        <v>0.11013411157490689</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3306713459973087E-2</v>
+        <v>9.9170250098168114E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14031675295274595</v>
+        <v>0.1491344724005961</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19609033309430543</v>
+        <v>0.20841294965487653</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2108855499749773</v>
+        <v>0.22413792060182014</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11157543287927872</v>
+        <v>0.11858700379792192</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3585097121061362E-2</v>
+        <v>6.7580881912822036E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2901305067303051E-2</v>
+        <v>3.4968873418527009E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1517524047638365E-2</v>
+        <v>1.2241302881233124E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23321922687563271</v>
+        <v>0.25981923397241607</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20219,7 +20219,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20237,14 +20237,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>35263.829128559999</v>
+        <v>33178.821236639997</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.23321922687563271</v>
+        <v>0.25981923397241607</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20252,13 +20252,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20443,22 +20443,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20648,10 +20648,10 @@
       <c r="B54" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20667,22 +20667,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>8.0262134930095805E-2</v>
+        <v>8.5305930294555382E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.2159383033419016E-2</v>
+        <v>6.6065573770491798E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20817,22 +20817,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20840,13 +20840,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20995,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21084,23 +21084,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21144,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21314,13 +21314,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21333,22 +21333,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21517,13 +21517,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21531,13 +21531,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21574,22 +21574,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21613,12 +21613,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21633,15 +21636,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E9C79B-77F9-4F65-8BE8-12B3A067F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7A34EF-CCFB-43B8-81CE-72A77EC67FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>33178.821236639997</v>
+        <v>34991.871577440004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.25981923397241607</v>
+        <v>0.23693142690237817</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0924664399999999</v>
+        <v>1.0935255500000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.3880296947053443</v>
+        <v>6.3942226777410154</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>3.6591560894679178</v>
+        <v>3.6622525809857533</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.3538511954983088</v>
+        <v>4.3575669853197114</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>5.1620541104191968</v>
+        <v>5.1664929953737788</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>5.8098270615809753</v>
+        <v>5.8148471109454567</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.5305930294555382E-2</v>
+        <v>8.096435013791442E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.6065573770491798E-2</v>
+        <v>6.2642487046632125E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10183372442448399</v>
+        <v>-0.10193244884468242</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8165462055138843</v>
+        <v>1.8183072868444212</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.161504517801086E-4</v>
+        <v>5.1665084253351703E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>1.7152286315411802</v>
+        <v>1.7168914888422722</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>1.2414202352415062</v>
+        <v>1.2426237510084042</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.79 HKD</v>
+        <v>7.8 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3880296947053443</v>
+        <v>6.3942226777410154</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>3.1940148473526722</v>
+        <v>3.1971113388705077</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>3.6591560894679178</v>
+        <v>3.6622525809857533</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6591,11 +6591,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>3.8328178168232068</v>
+        <v>3.8365336066446094</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.3538511954983088</v>
+        <v>4.3575669853197114</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>4.5786866745672317</v>
+        <v>4.5831255595218137</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>5.1620541104191968</v>
+        <v>5.1664929953737788</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.1781547316505403</v>
+        <v>5.1831747810150217</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>5.8098270615809753</v>
+        <v>5.8148471109454567</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10173,11 +10173,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0863630220951315</v>
+        <v>3.089355148736872</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2414202352415062</v>
+        <v>1.2426237510084042</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10583,11 +10583,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923148.34386371996</v>
+        <v>924043.30558215</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10183372442448399</v>
+        <v>0.1019324488446824</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10600,11 +10600,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16467448.584929474</v>
+        <v>16483413.230462005</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8165462055138843</v>
+        <v>1.8183072868444212</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10617,11 +10617,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4679.03376252</v>
+        <v>4683.5699306500001</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1615045178010871E-4</v>
+        <v>5.1665084253351703E-4</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10634,11 +10634,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17395275.96255571</v>
+        <v>17412140.105974805</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>1.9188960803901485</v>
+        <v>1.9207563865316373</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -14222,28 +14222,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.6065573770491798E-2</v>
+        <v>6.2642487046632125E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.9180327868852466E-2</v>
+        <v>8.4559585492227987E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.7404371584699455E-2</v>
+        <v>7.339378238341969E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.7923497267759559E-2</v>
+        <v>7.3886010362694307E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.12857923497267759</v>
+        <v>0.12191709844559587</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>8.0901639344262297E-2</v>
+        <v>7.6709844559585502E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15364,46 +15364,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31221970487807271</v>
+        <v>0.31252239153234967</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35075477799259863</v>
+        <v>0.35109482312288176</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31510209352951746</v>
+        <v>0.31540757456404528</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49388729083885125</v>
+        <v>0.49436609819571647</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62958532945956902</v>
+        <v>0.63019569156669608</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54664538692396791</v>
+        <v>0.54717534150613811</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36485895727388179</v>
+        <v>0.36521267593844631</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21360590591360815</v>
+        <v>0.2138129897586846</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3826463014706388E-2</v>
+        <v>9.3917424660396404E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.627317875190021E-2</v>
+        <v>2.6298649727784767E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.5305930294555382E-2</v>
+        <v>8.096435013791442E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.5834638795791974E-2</v>
+        <v>9.0957208062922734E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.6093468177463786E-2</v>
+        <v>8.1711806881877014E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13494188274285551</v>
+        <v>0.12807411870355351</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.1720178495791172</v>
+        <v>0.16326313253023214</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1493566630939803</v>
+        <v>0.14175526982024303</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.9688239692317424E-2</v>
+        <v>9.4614682885607856E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.8362269375302769E-2</v>
+        <v>5.5391966258726583E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.5635645632433438E-2</v>
+        <v>2.4330939031190778E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>7.1784641398634453E-3</v>
+        <v>6.8131216911359498E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15478,39 +15478,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11013411157490689</v>
+        <v>0.1044276809233573</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9170250098168114E-2</v>
+        <v>9.4031895170801877E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1491344724005961</v>
+        <v>0.14140729766481391</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20841294965487653</v>
+        <v>0.1976143512271627</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22413792060182014</v>
+        <v>0.21252455684006777</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11858700379792192</v>
+        <v>0.11244259945606067</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7580881912822036E-2</v>
+        <v>6.4079281813712086E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4968873418527009E-2</v>
+        <v>3.3157014692178459E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2241302881233124E-2</v>
+        <v>1.160703848324177E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7152286315411802</v>
+        <v>1.7168914888422722</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0924664399999999</v>
+        <v>1.0935255500000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>54588292.53921897</v>
+        <v>54641214.07931792</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3885567995514219</v>
+        <v>6.3947502935977685</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18717,23 +18717,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4395471667803701</v>
+        <v>4.4438511605944129</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.2156648001478816</v>
+        <v>6.2216906811319097</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.4169129206362339</v>
+        <v>6.4231339050020111</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>6.6256626593166397</v>
+        <v>6.6320860196343352</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.7896083303829187</v>
+        <v>7.7971600974457065</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>4.2581836216799456</v>
+        <v>4.2623117895489351</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2479456022990263</v>
+        <v>6.2540027784506815</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.4847345631858717</v>
+        <v>6.4910212983859177</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7324807540471481</v>
+        <v>6.7390076709668296</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>8.1506407596183514</v>
+        <v>8.1585425356536128</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>4.1059904369802878</v>
+        <v>4.1099710586016807</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2783452388236531</v>
+        <v>6.2844318864152182</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.549236265191122</v>
+        <v>6.5555855326531294</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>6.8350659639048867</v>
+        <v>6.8416923337849838</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>8.5141978911561313</v>
+        <v>8.5224521237790594</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18811,23 +18811,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>3.978275876393162</v>
+        <v>3.9821326829816073</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3069733347582631</v>
+        <v>6.3130877363398596</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>6.6105805412240866</v>
+        <v>6.6169892799282399</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>6.933586025586445</v>
+        <v>6.9403079074005527</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>8.8802973802571081</v>
+        <v>8.8889065341990872</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>3.8711028185578127</v>
+        <v>3.8748557244193083</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.3339331267339789</v>
+        <v>6.3400736649402205</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6689219505980954</v>
+        <v>6.6753872493647091</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.0282020288796891</v>
+        <v>7.0350156377726156</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>9.2489570056455079</v>
+        <v>9.2579235628738008</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.7811673854092671</v>
+        <v>3.7848331018495465</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.3593218352612286</v>
+        <v>6.36548698697879</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>6.724407486785962</v>
+        <v>6.7309265769406501</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.1190686800610807</v>
+        <v>7.1259703811602373</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>9.6201946703722871</v>
+        <v>9.629521130210577</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>3.5071976891246246</v>
+        <v>3.5105978010260293</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.4657232159668112</v>
+        <v>6.4719915202959246</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>6.9636574061779379</v>
+        <v>6.9704084411987095</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.5221605732243368</v>
+        <v>7.5294530585520407</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.515689003796401</v>
+        <v>11.52685308255823</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3931914626181157</v>
+        <v>3.3964810492620532</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.5445307300375415</v>
+        <v>6.5508754356391989</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1498087409667139</v>
+        <v>7.1567402435359337</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>7.8514696361514353</v>
+        <v>7.8590813756995583</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>13.478392805062493</v>
+        <v>13.491459660099039</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>3.3457503774962434</v>
+        <v>3.3489939715807542</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.6029005014899749</v>
+        <v>6.6093017946501877</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.294646070616424</v>
+        <v>7.3017179881756045</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.1205012410167807</v>
+        <v>8.1283737977878392</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>15.5106891530793</v>
+        <v>15.525726252057755</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>3.3260088543662572</v>
+        <v>3.3292333096984943</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>6.6461328031249609</v>
+        <v>6.6525760085685244</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.4073385317468388</v>
+        <v>7.4145197009115043</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.3402887068492895</v>
+        <v>8.3483743402828559</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>17.61504562474769</v>
+        <v>17.632122827569255</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.7896083303829187</v>
+        <v>7.7971600974457065</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>6.6256626593166397</v>
+        <v>6.6320860196343352</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.4169129206362339</v>
+        <v>6.4231339050020111</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.2156648001478816</v>
+        <v>6.2216906811319097</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>4.4395471667803701</v>
+        <v>4.4438511605944129</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>6.6256626593166397</v>
+        <v>6.6320860196343352</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.4169129206362339</v>
+        <v>6.4231339050020111</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.2156648001478816</v>
+        <v>6.2216906811319097</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4184132442746442</v>
+        <v>6.424635683154456</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.7896083303829187</v>
+        <v>7.7971600974457065</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>4.4395471667803701</v>
+        <v>4.4438511605944129</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.25981923397241607</v>
+        <v>0.23693142690237817</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.9276719164918328E-2</v>
+        <v>5.9238543793282333E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3880296947053443</v>
+        <v>6.3942226777410154</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3885567995514219</v>
+        <v>6.3947502935977685</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.30038934884423074</v>
+        <v>0.3003893488442308</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20000,11 +20000,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.1940148473526722</v>
+        <v>3.1971113388705077</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>3.6591560894679178</v>
+        <v>3.6622525809857533</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.4271854915607588</v>
+        <v>0.42725601444340489</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20025,11 +20025,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8328178168232068</v>
+        <v>3.8365336066446094</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.3538511954983088</v>
+        <v>4.3575669853197114</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.31843598048597743</v>
+        <v>0.31851497751417446</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5786866745672317</v>
+        <v>4.5831255595218137</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>5.1620541104191968</v>
+        <v>5.1664929953737788</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19198431314226483</v>
+        <v>0.19207275371701127</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1781547316505403</v>
+        <v>5.1831747810150217</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>5.8098270615809753</v>
+        <v>5.8148471109454567</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>9.051345418816803E-2</v>
+        <v>9.060922585827802E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20237,14 +20237,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>33178.821236639997</v>
+        <v>34991.871577440004</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.25981923397241607</v>
+        <v>0.23693142690237817</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20252,13 +20252,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0924664399999999</v>
+        <v>1.0935255500000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.3880296947053443</v>
+        <v>6.3942226777410154</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>3.6591560894679178</v>
+        <v>3.6622525809857533</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.3538511954983088</v>
+        <v>4.3575669853197114</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>5.1620541104191968</v>
+        <v>5.1664929953737788</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>5.8098270615809753</v>
+        <v>5.8148471109454567</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20443,22 +20443,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20648,10 +20648,10 @@
       <c r="B54" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20667,22 +20667,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>8.5305930294555382E-2</v>
+        <v>8.096435013791442E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.6065573770491798E-2</v>
+        <v>6.2642487046632125E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20817,22 +20817,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20840,13 +20840,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10183372442448399</v>
+        <v>-0.10193244884468242</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8165462055138843</v>
+        <v>1.8183072868444212</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.161504517801086E-4</v>
+        <v>5.1665084253351703E-4</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>1.7152286315411802</v>
+        <v>1.7168914888422722</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20995,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21084,23 +21084,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>1.2414202352415062</v>
+        <v>1.2426237510084042</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>6.0217073195145971</v>
+        <v>6.0275451651505429</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21144,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21195,7 +21195,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.79 HKD</v>
+        <v>7.8 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.3880296947053443</v>
+        <v>6.3942226777410154</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21314,13 +21314,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21333,22 +21333,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21413,11 +21413,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>3.1940148473526722</v>
+        <v>3.1971113388705077</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>3.6591560894679178</v>
+        <v>3.6622525809857533</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21434,11 +21434,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>3.8328178168232068</v>
+        <v>3.8365336066446094</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.3538511954983088</v>
+        <v>4.3575669853197114</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21474,11 +21474,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>4.5786866745672317</v>
+        <v>4.5831255595218137</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>5.1620541104191968</v>
+        <v>5.1664929953737788</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21495,11 +21495,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.1781547316505403</v>
+        <v>5.1831747810150217</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>5.8098270615809753</v>
+        <v>5.8148471109454567</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21517,13 +21517,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21531,13 +21531,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21574,22 +21574,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21613,15 +21613,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21636,12 +21633,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7A34EF-CCFB-43B8-81CE-72A77EC67FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A000AD3-31D8-43D7-8DBC-9E5BB7C89B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.23693142690237817</v>
+        <v>0.23694116234606433</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0935255500000001</v>
+        <v>1.09355365</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.3942226777410154</v>
+        <v>6.3943869881745883</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>3.6622525809857533</v>
+        <v>3.3891802254695973</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E22" s="79">
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.3575669853197114</v>
+        <v>4.202256884081196</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
       </c>
       <c r="E23" s="451">
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>5.1664929953737788</v>
+        <v>5.1666107665847232</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>5.8148471109454567</v>
+        <v>5.8149803014423274</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.096435013791442E-2</v>
+        <v>8.0966430654678623E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10193244884468242</v>
+        <v>-0.10193506817242701</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8183072868444212</v>
+        <v>1.8183540113446035</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1665084253351703E-4</v>
+        <v>5.166641187561668E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>1.7168914888422722</v>
+        <v>1.7169356072909325</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>1.2426237510084042</v>
+        <v>1.2426556823404187</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3942226777410154</v>
+        <v>6.3943869881745883</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="340">
         <f>Scenarios!C62</f>
-        <v>0.46514124211524543</v>
+        <v>0.44245811110342687</v>
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>3.1971113388705077</v>
+        <v>2.9467221143661706</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>3.6622525809857533</v>
+        <v>3.3891802254695973</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="340">
         <f>Scenarios!C63</f>
-        <v>0.52103337867510235</v>
+        <v>0.50874815444966315</v>
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>3.8365336066446094</v>
+        <v>3.6935087296315325</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.3575669853197114</v>
+        <v>4.202256884081196</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>4.5831255595218137</v>
+        <v>4.583243330732758</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>5.1664929953737788</v>
+        <v>5.1666107665847232</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.1831747810150217</v>
+        <v>5.1833079715118924</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>5.8148471109454567</v>
+        <v>5.8149803014423274</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10173,11 +10173,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.089355148736872</v>
+        <v>3.0894345349749708</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2426237510084042</v>
+        <v>1.2426556823404187</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10583,11 +10583,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>924043.30558215</v>
+        <v>924067.05044745002</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.1019324488446824</v>
+        <v>0.10193506817242701</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10600,11 +10600,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16483413.230462005</v>
+        <v>16483836.799816903</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8183072868444212</v>
+        <v>1.8183540113446035</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10617,11 +10617,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4683.5699306500001</v>
+        <v>4683.6902829500004</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1665084253351703E-4</v>
+        <v>5.1666411875616691E-4</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10634,11 +10634,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17412140.105974805</v>
+        <v>17412587.5405473</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>1.9207563865316373</v>
+        <v>1.9208057436357866</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15364,46 +15364,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31252239153234967</v>
+        <v>0.31253042232705952</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35109482312288176</v>
+        <v>0.35110384510186504</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31540757456404528</v>
+        <v>0.31541567949844324</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49436609819571647</v>
+        <v>0.49437880177393584</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63019569156669608</v>
+        <v>0.63021188551747576</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54717534150613811</v>
+        <v>0.54718940210773659</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36521267593844631</v>
+        <v>0.36522206069968383</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.2138129897586846</v>
+        <v>0.21381848404732945</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3917424660396404E-2</v>
+        <v>9.3919838028454383E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6298649727784767E-2</v>
+        <v>2.6299325516345309E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.096435013791442E-2</v>
+        <v>8.0966430654678623E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.0957208062922734E-2</v>
+        <v>9.0959545363177477E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1711806881877014E-2</v>
+        <v>8.1713906605814318E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12807411870355351</v>
+        <v>0.12807740978599375</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16326313253023214</v>
+        <v>0.16326732785426834</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14175526982024303</v>
+        <v>0.1417589124631442</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.4614682885607856E-2</v>
+        <v>9.4617114170902544E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.5391966258726583E-2</v>
+        <v>5.5393389649567214E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.4330939031190778E-2</v>
+        <v>2.4331564256076264E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.8131216911359498E-3</v>
+        <v>6.8132967658925672E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7168914888422722</v>
+        <v>1.7169356072909325</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0935255500000001</v>
+        <v>1.09355365</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>54641214.07931792</v>
+        <v>54642618.178303652</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3947502935977685</v>
+        <v>6.3949146175893299</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18717,23 +18717,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4438511605944129</v>
+        <v>4.4439653529126559</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.2216906811319097</v>
+        <v>6.2218505580622105</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.4231339050020111</v>
+        <v>6.423298958358771</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>6.6320860196343352</v>
+        <v>6.6322564423712809</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.7971600974457065</v>
+        <v>7.7973604587438379</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>4.2623117895489351</v>
+        <v>4.2624213169040903</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2540027784506815</v>
+        <v>6.2541634856953126</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.4910212983859177</v>
+        <v>6.491188096224783</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7390076709668296</v>
+        <v>6.7391808412375687</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>8.1585425356536128</v>
+        <v>8.1587521832885059</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>4.1099710586016807</v>
+        <v>4.1100766713024965</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2844318864152182</v>
+        <v>6.2845933755875638</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.5555855326531294</v>
+        <v>6.5557539895798715</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>6.8416923337849838</v>
+        <v>6.8418681427128858</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>8.5224521237790594</v>
+        <v>8.5226711226901308</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18811,23 +18811,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>3.9821326829816073</v>
+        <v>3.9822350106578024</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3130877363398596</v>
+        <v>6.3132499618730362</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>6.6169892799282399</v>
+        <v>6.6171593147287666</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>6.9403079074005527</v>
+        <v>6.9404862504234464</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>8.8889065341990872</v>
+        <v>8.8891349497798764</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>3.8748557244193083</v>
+        <v>3.8749552954314863</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.3400736649402205</v>
+        <v>6.3402365839227572</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6753872493647091</v>
+        <v>6.6755587848004447</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.0350156377726156</v>
+        <v>7.0351964144718169</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>9.2579235628738008</v>
+        <v>9.2581614609751455</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.7848331018495465</v>
+        <v>3.7849303595772348</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.36548698697879</v>
+        <v>6.365650558999886</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>6.7309265769406501</v>
+        <v>6.7310995395539255</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.1259703811602373</v>
+        <v>7.1261534950963599</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>9.629521130210577</v>
+        <v>9.6297685771438104</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>3.5105978010260293</v>
+        <v>3.5106880118109616</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.4719915202959246</v>
+        <v>6.4721578291322572</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>6.9704084411987095</v>
+        <v>6.9705875577060441</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.5294530585520407</v>
+        <v>7.5296465406622168</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.52685308255823</v>
+        <v>11.52714928466491</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3964810492620532</v>
+        <v>3.3965683276228416</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.5508754356391989</v>
+        <v>6.5510437715319831</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1567402435359337</v>
+        <v>7.1569241481560342</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>7.8590813756995583</v>
+        <v>7.8592833281703145</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>13.491459660099039</v>
+        <v>13.491806346115153</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>3.3489939715807542</v>
+        <v>3.3490800296802665</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.6093017946501877</v>
+        <v>6.6094716319076987</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.3017179881756045</v>
+        <v>7.3019056182455806</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.1283737977878392</v>
+        <v>8.1285826701856685</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>15.525726252057755</v>
+        <v>15.526125212015922</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>3.3292333096984943</v>
+        <v>3.3293188600141708</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>6.6525760085685244</v>
+        <v>6.6527469578306073</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.4145197009115043</v>
+        <v>7.4147102296134584</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.3483743402828559</v>
+        <v>8.3485888659690293</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>17.632122827569255</v>
+        <v>17.632575914972154</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.7971600974457065</v>
+        <v>7.7973604587438379</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>6.6320860196343352</v>
+        <v>6.6322564423712809</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.4231339050020111</v>
+        <v>6.423298958358771</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.2216906811319097</v>
+        <v>6.2218505580622105</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>4.4438511605944129</v>
+        <v>4.4439653529126559</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>6.6320860196343352</v>
+        <v>6.6322564423712809</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.4231339050020111</v>
+        <v>6.423298958358771</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.2216906811319097</v>
+        <v>6.2218505580622105</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.424635683154456</v>
+        <v>6.4248007751019607</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.7971600974457065</v>
+        <v>7.7973604587438379</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>4.4438511605944129</v>
+        <v>4.4439653529126559</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23693142690237817</v>
+        <v>0.23694116234606433</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.9238543793282333E-2</v>
+        <v>5.923753194283414E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3942226777410154</v>
+        <v>6.3943869881745883</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3947502935977685</v>
+        <v>6.3949146175893299</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19996,23 +19996,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.46514124211524543</v>
+        <v>0.44245811110342687</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.1971113388705077</v>
+        <v>2.9467221143661706</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>3.6622525809857533</v>
+        <v>3.3891802254695973</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.42725601444340489</v>
+        <v>0.46997574095259598</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20021,23 +20021,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.52103337867510235</v>
+        <v>0.50874815444966315</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8365336066446094</v>
+        <v>3.6935087296315325</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.3575669853197114</v>
+        <v>4.202256884081196</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.31851497751417446</v>
+        <v>0.34282099412303191</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5831255595218137</v>
+        <v>4.583243330732758</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>5.1664929953737788</v>
+        <v>5.1666107665847232</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19207275371701127</v>
+        <v>0.19207509786387678</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1831747810150217</v>
+        <v>5.1833079715118924</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>5.8148471109454567</v>
+        <v>5.8149803014423274</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>9.060922585827802E-2</v>
+        <v>9.0611764318265786E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.23693142690237817</v>
+        <v>0.23694116234606433</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20252,13 +20252,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0935255500000001</v>
+        <v>1.09355365</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.3942226777410154</v>
+        <v>6.3943869881745883</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20374,14 +20374,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>3.6622525809857533</v>
+        <v>3.3891802254695973</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20390,14 +20390,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.3575669853197114</v>
+        <v>4.202256884081196</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>5.1664929953737788</v>
+        <v>5.1666107665847232</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>5.8148471109454567</v>
+        <v>5.8149803014423274</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20443,22 +20443,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20648,10 +20648,10 @@
       <c r="B54" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20667,22 +20667,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>8.096435013791442E-2</v>
+        <v>8.0966430654678623E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20817,22 +20817,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20840,13 +20840,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10193244884468242</v>
+        <v>-0.10193506817242701</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8183072868444212</v>
+        <v>1.8183540113446035</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1665084253351703E-4</v>
+        <v>5.166641187561668E-4</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>1.7168914888422722</v>
+        <v>1.7169356072909325</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20995,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21084,23 +21084,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>1.2426237510084042</v>
+        <v>1.2426556823404187</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>6.0275451651505429</v>
+        <v>6.027700053181408</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21144,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.3942226777410154</v>
+        <v>6.3943869881745883</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21314,13 +21314,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21333,22 +21333,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21409,19 +21409,19 @@
       </c>
       <c r="C140" s="416">
         <f>Scenarios!C62</f>
-        <v>0.46514124211524543</v>
+        <v>0.44245811110342687</v>
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>3.1971113388705077</v>
+        <v>2.9467221143661706</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>3.6622525809857533</v>
+        <v>3.3891802254695973</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21430,19 +21430,19 @@
       </c>
       <c r="C141" s="416">
         <f>Scenarios!C63</f>
-        <v>0.52103337867510235</v>
+        <v>0.50874815444966315</v>
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>3.8365336066446094</v>
+        <v>3.6935087296315325</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.3575669853197114</v>
+        <v>4.202256884081196</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21474,11 +21474,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>4.5831255595218137</v>
+        <v>4.583243330732758</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>5.1664929953737788</v>
+        <v>5.1666107665847232</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21495,11 +21495,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.1831747810150217</v>
+        <v>5.1833079715118924</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>5.8148471109454567</v>
+        <v>5.8149803014423274</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21517,13 +21517,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21531,13 +21531,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21574,22 +21574,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21613,12 +21613,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21633,15 +21636,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A000AD3-31D8-43D7-8DBC-9E5BB7C89B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F803F30-66DB-4E7F-8183-817AC24AABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>34991.871577440004</v>
+        <v>34901.219060399999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.23694116234606433</v>
+        <v>0.2378091647390099</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.09355365</v>
+        <v>1.0928174399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.3943869881745883</v>
+        <v>6.3900821132884182</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>3.3891802254695973</v>
+        <v>3.3871964121579978</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.202256884081196</v>
+        <v>4.1997703137498341</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>5.1666107665847232</v>
+        <v>5.1635252027694323</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>5.8149803014423274</v>
+        <v>5.811490757823039</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.0966430654678623E-2</v>
+        <v>8.1122082691842776E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2642487046632125E-2</v>
+        <v>6.2805194805194794E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10193506817242701</v>
+        <v>-0.10186644271766378</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8183540113446035</v>
+        <v>1.817129846067763</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.166641187561668E-4</v>
+        <v>5.1631628644737294E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>1.7169356072909325</v>
+        <v>1.7157797196365463</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>1.2426556823404187</v>
+        <v>1.2418190928051032</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.8 HKD</v>
+        <v>7.79 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3943869881745883</v>
+        <v>6.3900821132884182</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>2.9467221143661706</v>
+        <v>2.9447383010545711</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>3.3891802254695973</v>
+        <v>3.3871964121579978</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6591,11 +6591,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>3.6935087296315325</v>
+        <v>3.6910221593001711</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.202256884081196</v>
+        <v>4.1997703137498341</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>4.583243330732758</v>
+        <v>4.5801577669174671</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>5.1666107665847232</v>
+        <v>5.1635252027694323</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.1833079715118924</v>
+        <v>5.179818427892604</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>5.8149803014423274</v>
+        <v>5.811490757823039</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10173,11 +10173,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0894345349749708</v>
+        <v>3.0873546437881103</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2426556823404187</v>
+        <v>1.2418190928051032</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10583,11 +10583,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>924067.05044745002</v>
+        <v>923444.94342671998</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10193506817242701</v>
+        <v>0.10186644271766379</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10600,11 +10600,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16483836.799816903</v>
+        <v>16472739.433455046</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.8183540113446035</v>
+        <v>1.817129846067763</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10617,11 +10617,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4683.6902829500004</v>
+        <v>4680.5370955199996</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1666411875616691E-4</v>
+        <v>5.1631628644737294E-4</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10634,11 +10634,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17412587.5405473</v>
+        <v>17400864.913977288</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>1.9208057436357866</v>
+        <v>1.9195126050718743</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -14222,28 +14222,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2642487046632125E-2</v>
+        <v>6.2805194805194794E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.4559585492227987E-2</v>
+        <v>8.4779220779220787E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.339378238341969E-2</v>
+        <v>7.3584415584415586E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.3886010362694307E-2</v>
+        <v>7.4077922077922076E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.12191709844559587</v>
+        <v>0.12223376623376624</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.6709844559585502E-2</v>
+        <v>7.6909090909090913E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15364,46 +15364,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31253042232705952</v>
+        <v>0.31232001836359469</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35110384510186504</v>
+        <v>0.35086747246317235</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31541567949844324</v>
+        <v>0.31520333310153476</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49437880177393584</v>
+        <v>0.49404597254543475</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63021188551747576</v>
+        <v>0.6297876097700198</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54718940210773659</v>
+        <v>0.54682101934962879</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36522206069968383</v>
+        <v>0.36497618329503362</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21381848404732945</v>
+        <v>0.2136745356400972</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3919838028454383E-2</v>
+        <v>9.3856608644185088E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6299325516345309E-2</v>
+        <v>2.6281620096553247E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0966430654678623E-2</v>
+        <v>8.1122082691842776E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.0959545363177477E-2</v>
+        <v>9.1134408431992817E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1713906605814318E-2</v>
+        <v>8.1870995610788241E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12807740978599375</v>
+        <v>0.12832362923258045</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16326732785426834</v>
+        <v>0.16358119734286228</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1417589124631442</v>
+        <v>0.14203143359730619</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.4617114170902544E-2</v>
+        <v>9.4799008648060679E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.5393389649567214E-2</v>
+        <v>5.549987938703823E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.4331564256076264E-2</v>
+        <v>2.4378339907580541E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.8132967658925672E-3</v>
+        <v>6.8263948302735708E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15478,39 +15478,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1044276809233573</v>
+        <v>0.10469892165302837</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4031895170801877E-2</v>
+        <v>9.4276133859557215E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14140729766481391</v>
+        <v>0.14177458934706019</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1976143512271627</v>
+        <v>0.19812763525632415</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21252455684006777</v>
+        <v>0.21307656867601601</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11244259945606067</v>
+        <v>0.11273465815594655</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4079281813712086E-2</v>
+        <v>6.4245721506734715E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3157014692178459E-2</v>
+        <v>3.324313680826204E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.160703848324177E-2</v>
+        <v>1.1637186635146294E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7169356072909325</v>
+        <v>1.7157797196365463</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09355365</v>
+        <v>1.0928174399999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>54642618.178303652</v>
+        <v>54605831.284556784</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3949146175893299</v>
+        <v>6.3906093874887162</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18717,23 +18717,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4439653529126559</v>
+        <v>4.4409735548125191</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.2218505580622105</v>
+        <v>6.2176618393840268</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.423298958358771</v>
+        <v>6.4189746191495018</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>6.6322564423712809</v>
+        <v>6.6277914273119478</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.7973604587438379</v>
+        <v>7.7921110640357387</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>4.2624213169040903</v>
+        <v>4.2595517391767261</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2541634856953126</v>
+        <v>6.2499530130771612</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.491188096224783</v>
+        <v>6.4868180522051579</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7391808412375687</v>
+        <v>6.7346438417706214</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>8.1587521832885059</v>
+        <v>8.1532594898620232</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>4.1100766713024965</v>
+        <v>4.107309656125711</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2845933755875638</v>
+        <v>6.2803624167415641</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.5557539895798715</v>
+        <v>6.5513404780482984</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>6.8418681427128858</v>
+        <v>6.8372620113672973</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>8.5226711226901308</v>
+        <v>8.5169334291556282</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18811,23 +18811,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>3.9822350106578024</v>
+        <v>3.979554061957026</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3132499618730362</v>
+        <v>6.3089997106353106</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>6.6171593147287666</v>
+        <v>6.6127044634655512</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>6.9404862504234464</v>
+        <v>6.9358137266909115</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>8.8891349497798764</v>
+        <v>8.8831505428498829</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>3.8749552954314863</v>
+        <v>3.872346570346942</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.3402365839227572</v>
+        <v>6.3359681645585582</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6755587848004447</v>
+        <v>6.6710646174288124</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.0351964144718169</v>
+        <v>7.0304601292860838</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>9.2581614609751455</v>
+        <v>9.2519286153811624</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.7849303595772348</v>
+        <v>3.7823822417230946</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.365650558999886</v>
+        <v>6.3613650302578426</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>6.7310995395539255</v>
+        <v>6.7265679806386265</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.1261534950963599</v>
+        <v>7.121355975135061</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>9.6297685771438104</v>
+        <v>9.6232855555525223</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>3.5106880118109616</v>
+        <v>3.5083245213492216</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.4721578291322572</v>
+        <v>6.4678005968049854</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>6.9705875577060441</v>
+        <v>6.9658947689563933</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.5296465406622168</v>
+        <v>7.5245773782304495</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.52714928466491</v>
+        <v>11.51938889487986</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3965683276228416</v>
+        <v>3.3942816656300994</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.5510437715319831</v>
+        <v>6.5466334310470504</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1569241481560342</v>
+        <v>7.1521059125558741</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>7.8592833281703145</v>
+        <v>7.8539922453057169</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>13.491806346115153</v>
+        <v>13.482723295868761</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>3.3490800296802665</v>
+        <v>3.3468253380986956</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.6094716319076987</v>
+        <v>6.6050219562012273</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.3019056182455806</v>
+        <v>7.296989777184459</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.1285826701856685</v>
+        <v>8.1231102876943133</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>15.526125212015922</v>
+        <v>15.515672603090572</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>3.3293188600141708</v>
+        <v>3.3270774721884049</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>6.6527469578306073</v>
+        <v>6.6482681480000831</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.4147102296134584</v>
+        <v>7.4097184454260576</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.3485888659690293</v>
+        <v>8.3429683693349439</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>17.632575914972154</v>
+        <v>17.620705186257229</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.7973604587438379</v>
+        <v>7.7921110640357387</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>6.6322564423712809</v>
+        <v>6.6277914273119478</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.423298958358771</v>
+        <v>6.4189746191495018</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.2218505580622105</v>
+        <v>6.2176618393840268</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>4.4439653529126559</v>
+        <v>4.4409735548125191</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>6.6322564423712809</v>
+        <v>6.6277914273119478</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.423298958358771</v>
+        <v>6.4189746191495018</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.2218505580622105</v>
+        <v>6.2176618393840268</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4248007751019607</v>
+        <v>6.4204754248288962</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.7973604587438379</v>
+        <v>7.7921110640357387</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>4.4439653529126559</v>
+        <v>4.4409735548125191</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23694116234606433</v>
+        <v>0.2378091647390099</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.923753194283414E-2</v>
+        <v>5.926405925039515E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3943869881745883</v>
+        <v>6.3900821132884182</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3949146175893299</v>
+        <v>6.3906093874887162</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20000,11 +20000,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9467221143661706</v>
+        <v>2.9447383010545711</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>3.3891802254695973</v>
+        <v>3.3871964121579978</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.46997574095259598</v>
+        <v>0.4699291257753645</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20025,11 +20025,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6935087296315325</v>
+        <v>3.6910221593001711</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.202256884081196</v>
+        <v>4.1997703137498341</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.34282099412303191</v>
+        <v>0.34276739495784381</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.583243330732758</v>
+        <v>4.5801577669174671</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>5.1666107665847232</v>
+        <v>5.1635252027694323</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19207509786387678</v>
+        <v>0.19201364225477791</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1833079715118924</v>
+        <v>5.179818427892604</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>5.8149803014423274</v>
+        <v>5.811490757823039</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>9.0611764318265786E-2</v>
+        <v>9.0545214475754032E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20237,14 +20237,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>34991.871577440004</v>
+        <v>34901.219060399999</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.23694116234606433</v>
+        <v>0.2378091647390099</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20252,13 +20252,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.09355365</v>
+        <v>1.0928174399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.3943869881745883</v>
+        <v>6.3900821132884182</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>3.3891802254695973</v>
+        <v>3.3871964121579978</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.202256884081196</v>
+        <v>4.1997703137498341</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>5.1666107665847232</v>
+        <v>5.1635252027694323</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>5.8149803014423274</v>
+        <v>5.811490757823039</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20443,22 +20443,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20648,10 +20648,10 @@
       <c r="B54" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20667,22 +20667,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>8.0966430654678623E-2</v>
+        <v>8.1122082691842776E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.2642487046632125E-2</v>
+        <v>6.2805194805194794E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20817,22 +20817,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20840,13 +20840,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10193506817242701</v>
+        <v>-0.10186644271766378</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8183540113446035</v>
+        <v>1.817129846067763</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.166641187561668E-4</v>
+        <v>5.1631628644737294E-4</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>1.7169356072909325</v>
+        <v>1.7157797196365463</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20995,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21084,23 +21084,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>1.2426556823404187</v>
+        <v>1.2418190928051032</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>6.027700053181408</v>
+        <v>6.0236420418930248</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21144,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21195,7 +21195,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>7.8 HKD</v>
+        <v>7.79 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.3943869881745883</v>
+        <v>6.3900821132884182</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21314,13 +21314,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21333,22 +21333,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21413,11 +21413,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>2.9467221143661706</v>
+        <v>2.9447383010545711</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>3.3891802254695973</v>
+        <v>3.3871964121579978</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21434,11 +21434,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>3.6935087296315325</v>
+        <v>3.6910221593001711</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.202256884081196</v>
+        <v>4.1997703137498341</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21474,11 +21474,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>4.583243330732758</v>
+        <v>4.5801577669174671</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>5.1666107665847232</v>
+        <v>5.1635252027694323</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21495,11 +21495,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.1833079715118924</v>
+        <v>5.179818427892604</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>5.8149803014423274</v>
+        <v>5.811490757823039</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21517,13 +21517,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21531,13 +21531,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21574,22 +21574,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21613,15 +21613,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21636,12 +21633,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F803F30-66DB-4E7F-8183-817AC24AABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE398E1-A122-4DC4-9AC3-9A512253E393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>34901.219060399999</v>
+        <v>35807.744230800003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.2378091647390099</v>
+        <v>0.22659565455699582</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0928174399999999</v>
+        <v>1.09235412</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>6.3900821132884182</v>
+        <v>6.3873729207587608</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>3.3871964121579978</v>
+        <v>3.3859479363378795</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>4.1997703137498341</v>
+        <v>4.1982054371984079</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>5.1635252027694323</v>
+        <v>5.1615833608671222</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>5.811490757823039</v>
+        <v>5.8092946787835151</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.1122082691842776E-2</v>
+        <v>7.903483659815333E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2805194805194794E-2</v>
+        <v>6.1215189873417716E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10186644271766378</v>
+        <v>-0.10182325457066646</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.817129846067763</v>
+        <v>1.8163594405366434</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1631628644737294E-4</v>
+        <v>5.160973846865841E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>1.7157797196365463</v>
+        <v>1.7150522833506632</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>1.2418190928051032</v>
+        <v>1.2412926008211553</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>6.63 HKD</v>
+        <v>6.62 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3900821132884182</v>
+        <v>6.3873729207587608</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>2.9447383010545711</v>
+        <v>2.9434898252344528</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>3.3871964121579978</v>
+        <v>3.3859479363378795</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6591,11 +6591,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>3.6910221593001711</v>
+        <v>3.6894572827487444</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>4.1997703137498341</v>
+        <v>4.1982054371984079</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>4.5801577669174671</v>
+        <v>4.5782159250151571</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>5.1635252027694323</v>
+        <v>5.1615833608671222</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>5.179818427892604</v>
+        <v>5.1776223488530801</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>5.811490757823039</v>
+        <v>5.8092946787835151</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10173,11 +10173,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0873546437881103</v>
+        <v>3.0860457031533781</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2418190928051032</v>
+        <v>1.2412926008211553</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10583,11 +10583,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923444.94342671998</v>
+        <v>923053.43200356001</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10186644271766379</v>
+        <v>0.10182325457066647</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10600,11 +10600,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16472739.433455046</v>
+        <v>16465755.513401292</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.817129846067763</v>
+        <v>1.8163594405366434</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10617,11 +10617,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4680.5370955199996</v>
+        <v>4678.5526959600002</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1631628644737294E-4</v>
+        <v>5.160973846865841E-4</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10634,11 +10634,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17400864.913977288</v>
+        <v>17393487.498100813</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>1.9195126050718743</v>
+        <v>1.9186987924919965</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -14222,28 +14222,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2805194805194794E-2</v>
+        <v>6.1215189873417716E-2</v>
       </c>
       <c r="E92" s="241"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.4779220779220787E-2</v>
+        <v>8.263291139240507E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.3584415584415586E-2</v>
+        <v>7.1721518987341762E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4077922077922076E-2</v>
+        <v>7.2202531645569626E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.12223376623376624</v>
+        <v>0.11913924050632911</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.6909090909090913E-2</v>
+        <v>7.4962025316455697E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15364,46 +15364,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31232001836359469</v>
+        <v>0.31218760456270567</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35086747246317235</v>
+        <v>0.35071871576201502</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31520333310153476</v>
+        <v>0.31506969686647196</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49404597254543475</v>
+        <v>0.49383651269274453</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.6297876097700198</v>
+        <v>0.62952059976022479</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54682101934962879</v>
+        <v>0.5465891845477564</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36497618329503362</v>
+        <v>0.36482144494711322</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.2136745356400972</v>
+        <v>0.21358394440113165</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3856608644185088E-2</v>
+        <v>9.3816816413273205E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6281620096553247E-2</v>
+        <v>2.6270477521611241E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15421,46 +15421,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1122082691842776E-2</v>
+        <v>7.903483659815333E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.1134408431992817E-2</v>
+        <v>8.8789548294181009E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1870995610788241E-2</v>
+        <v>7.9764480219359987E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12832362923258045</v>
+        <v>0.12502190194753027</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16358119734286228</v>
+        <v>0.15937230373676575</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14203143359730619</v>
+        <v>0.13837700874626743</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.4799008648060679E-2</v>
+        <v>9.2359859480281817E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.549987938703823E-2</v>
+        <v>5.4071884658514341E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.4378339907580541E-2</v>
+        <v>2.3751092762853976E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.8263948302735708E-3</v>
+        <v>6.650753802939554E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15478,39 +15478,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10469892165302837</v>
+        <v>0.10204831604155928</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4276133859557215E-2</v>
+        <v>9.1889396293492465E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14177458934706019</v>
+        <v>0.13818535923700803</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19812763525632415</v>
+        <v>0.19311174575616405</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21307656867601601</v>
+        <v>0.2076822251652308</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11273465815594655</v>
+        <v>0.10988061617731498</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4245721506734715E-2</v>
+        <v>6.2619247544538903E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.324313680826204E-2</v>
+        <v>3.2401538408052877E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1637186635146294E-2</v>
+        <v>1.1342574315269173E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.7157797196365463</v>
+        <v>1.7150522833506632</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0928174399999999</v>
+        <v>1.09235412</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>54605831.284556784</v>
+        <v>54582680.140710875</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3906093874887162</v>
+        <v>6.3878999714114881</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18685,23 +18685,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18717,23 +18717,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>4.4409735548125191</v>
+        <v>4.4390907226100831</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>6.2176618393840268</v>
+        <v>6.215025747592315</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.4189746191495018</v>
+        <v>6.4162531771119884</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>6.6277914273119478</v>
+        <v>6.6249814535581413</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>7.7921110640357387</v>
+        <v>7.788807455614017</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18748,23 +18748,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>4.2595517391767261</v>
+        <v>4.2577458240809758</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2499530130771612</v>
+        <v>6.2473032308500231</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.4868180522051579</v>
+        <v>6.484067846699701</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>6.7346438417706214</v>
+        <v>6.7317885659756369</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>8.1532594898620232</v>
+        <v>8.1498027659403753</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18780,23 +18780,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>4.107309656125711</v>
+        <v>4.1055682868537522</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>6.2803624167415641</v>
+        <v>6.2776997418899221</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.5513404780482984</v>
+        <v>6.5485629170768256</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>6.8372620113672973</v>
+        <v>6.8343632287169163</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>8.5169334291556282</v>
+        <v>8.5133225189962918</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18811,23 +18811,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>3.979554061957026</v>
+        <v>3.9778668570127258</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>6.3089997106353106</v>
+        <v>6.3063248944776085</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>6.6127044634655512</v>
+        <v>6.6099008861068178</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>6.9358137266909115</v>
+        <v>6.9328731612330152</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>8.8831505428498829</v>
+        <v>8.8793843682274201</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>3.872346570346942</v>
+        <v>3.8707048179852914</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.3359681645585582</v>
+        <v>6.3332819146301143</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6710646174288124</v>
+        <v>6.6682362972122657</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.0304601292860838</v>
+        <v>7.0274794367496431</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>9.2519286153811624</v>
+        <v>9.2480060905300974</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.7823822417230946</v>
+        <v>3.7807786313888427</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>6.3613650302578426</v>
+        <v>6.3586680128623119</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>6.7265679806386265</v>
+        <v>6.72371612875311</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>7.121355975135061</v>
+        <v>7.1183367456374071</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>9.6232855555525223</v>
+        <v>9.619205587114612</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>3.5083245213492216</v>
+        <v>3.5068371028127538</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>6.4678005968049854</v>
+        <v>6.4650584540985951</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>6.9658947689563933</v>
+        <v>6.9629414500888318</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>7.5245773782304495</v>
+        <v>7.5213871956223821</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.51938889487986</v>
+        <v>11.514505038649697</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3942816656300994</v>
+        <v>3.3928425976542811</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>6.5466334310470504</v>
+        <v>6.5438578657144983</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>7.1521059125558741</v>
+        <v>7.1490736460581825</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>7.8539922453057169</v>
+        <v>7.850662401222066</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>13.482723295868761</v>
+        <v>13.477007048004488</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>3.3468253380986956</v>
+        <v>3.345406390103459</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>6.6050219562012273</v>
+        <v>6.6022216359823744</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>7.296989777184459</v>
+        <v>7.2938960845146523</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>8.1231102876943133</v>
+        <v>8.1196663460799723</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>15.515672603090572</v>
+        <v>15.509094449075695</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>3.3270774721884049</v>
+        <v>3.3256668966631699</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>6.6482681480000831</v>
+        <v>6.6454494927649224</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>7.4097184454260576</v>
+        <v>7.4065769593694899</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>8.3429683693349439</v>
+        <v>8.3394312148538816</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>17.620705186257229</v>
+        <v>17.613234565064641</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>7.7921110640357387</v>
+        <v>7.788807455614017</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>6.6277914273119478</v>
+        <v>6.6249814535581413</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.4189746191495018</v>
+        <v>6.4162531771119884</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>6.2176618393840268</v>
+        <v>6.215025747592315</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>4.4409735548125191</v>
+        <v>4.4390907226100831</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>6.6277914273119478</v>
+        <v>6.6249814535581413</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>6.4189746191495018</v>
+        <v>6.4162531771119884</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>6.2176618393840268</v>
+        <v>6.215025747592315</v>
       </c>
       <c r="F24" s="334">
         <v>0.2</v>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4204754248288962</v>
+        <v>6.4177533464972845</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>7.7921110640357387</v>
+        <v>7.788807455614017</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>4.4409735548125191</v>
+        <v>4.4390907226100831</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2378091647390099</v>
+        <v>0.22659565455699582</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>5.926405925039515E-2</v>
+        <v>5.9280772056685284E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3900821132884182</v>
+        <v>6.3873729207587608</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3906093874887162</v>
+        <v>6.3878999714114881</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.3003893488442308</v>
+        <v>0.30038934884423074</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20000,11 +20000,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9447383010545711</v>
+        <v>2.9434898252344528</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>3.3871964121579978</v>
+        <v>3.3859479363378795</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.4699291257753645</v>
+        <v>0.46989975717032972</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20025,11 +20025,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6910221593001711</v>
+        <v>3.6894572827487444</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>4.1997703137498341</v>
+        <v>4.1982054371984079</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.34276739495784381</v>
+        <v>0.34273362628407489</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5801577669174671</v>
+        <v>4.5782159250151571</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>5.1635252027694323</v>
+        <v>5.1615833608671222</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19201364225477791</v>
+        <v>0.19197492384549586</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.179818427892604</v>
+        <v>5.1776223488530801</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>5.811490757823039</v>
+        <v>5.8092946787835151</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>9.0545214475754032E-2</v>
+        <v>9.0503286585398746E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20237,14 +20237,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>34901.219060399999</v>
+        <v>35807.744230800003</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.2378091647390099</v>
+        <v>0.22659565455699582</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20252,13 +20252,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0928174399999999</v>
+        <v>1.09235412</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>6.3900821132884182</v>
+        <v>6.3873729207587608</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>3.3871964121579978</v>
+        <v>3.3859479363378795</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>444</v>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>4.1997703137498341</v>
+        <v>4.1982054371984079</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>445</v>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>5.1635252027694323</v>
+        <v>5.1615833608671222</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>447</v>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>5.811490757823039</v>
+        <v>5.8092946787835151</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>446</v>
@@ -20443,22 +20443,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20648,10 +20648,10 @@
       <c r="B54" s="469" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20667,22 +20667,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>8.1122082691842776E-2</v>
+        <v>7.903483659815333E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
-        <v>6.2805194805194794E-2</v>
+        <v>6.1215189873417716E-2</v>
       </c>
       <c r="E63" s="379" t="s">
         <v>373</v>
@@ -20817,22 +20817,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20840,13 +20840,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10186644271766378</v>
+        <v>-0.10182325457066646</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.817129846067763</v>
+        <v>1.8163594405366434</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20960,7 +20960,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1631628644737294E-4</v>
+        <v>5.160973846865841E-4</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>1.7157797196365463</v>
+        <v>1.7150522833506632</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20995,33 +20995,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21084,23 +21084,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>1.2418190928051032</v>
+        <v>1.2412926008211553</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>6.0236420418930248</v>
+        <v>6.0210882083535004</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21144,13 +21144,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21218,7 +21218,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>6.63 HKD</v>
+        <v>6.62 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>6.3900821132884182</v>
+        <v>6.3873729207587608</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21314,13 +21314,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21333,22 +21333,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21413,11 +21413,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>2.9447383010545711</v>
+        <v>2.9434898252344528</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>3.3871964121579978</v>
+        <v>3.3859479363378795</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21434,11 +21434,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>3.6910221593001711</v>
+        <v>3.6894572827487444</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>4.1997703137498341</v>
+        <v>4.1982054371984079</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21474,11 +21474,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>4.5801577669174671</v>
+        <v>4.5782159250151571</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>5.1635252027694323</v>
+        <v>5.1615833608671222</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21495,11 +21495,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>5.179818427892604</v>
+        <v>5.1776223488530801</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>5.811490757823039</v>
+        <v>5.8092946787835151</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21517,13 +21517,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21531,13 +21531,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21574,22 +21574,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21613,12 +21613,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21633,15 +21636,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBB8800-2936-4314-A6BD-FDB0BED73E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4120ABBF-B251-48B7-BA06-B7D13019234C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3243,6 +3243,9 @@
     <t>accepts 5-10, 15, 20, 25, or 30</t>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
@@ -3256,9 +3259,6 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
-  </si>
-  <si>
-    <t>Implied Return</t>
   </si>
 </sst>
 </file>
@@ -5342,7 +5342,7 @@
         <v>536</v>
       </c>
       <c r="C4" s="425" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E4" s="435" t="s">
         <v>540</v>
@@ -5356,13 +5356,13 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E5" s="438" t="s">
         <v>542</v>
       </c>
       <c r="F5" s="437" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>35807.744230800003</v>
+        <v>34901.219060399999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.20967048786502251</v>
+        <v>0.22027668345247436</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,7 +5443,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="422" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5458,13 +5458,13 @@
         <v>320</v>
       </c>
       <c r="C16" s="422" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.09235412</v>
+        <v>1.09146385</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.1038256936984379</v>
+        <v>6.0988510679787797</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.2552810114252879</v>
+        <v>3.252988557176598</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>409</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.034423645394611</v>
+        <v>4.0315502153760354</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>410</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>4.9583479389611078</v>
+        <v>4.9547823242751843</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>411</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.5794505037218762</v>
+        <v>5.5754180582043196</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>412</v>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10871307104352078</v>
+        <v>0.11144588455082099</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1215189873417716E-2</v>
+        <v>6.2805194805194794E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10182325457066646</v>
+        <v>-0.10174026848841813</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7594639313829044</v>
+        <v>1.7580299660363992</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.160973846865841E-4</v>
+        <v>5.1567676466030086E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6581567741969243</v>
+        <v>1.6568053743126412</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2412926008211553</v>
+        <v>1.2402809457694648</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,7 +6331,7 @@
         <v>124</v>
       </c>
       <c r="F117" s="346" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E82,C$18)</f>
-        <v>-9.1188638213080694E-2</v>
+        <v>-9.1163725549836608E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E83,C$18)</f>
-        <v>-5.8081198189490701E-2</v>
+        <v>-5.805452864625979E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E84,C$18)</f>
-        <v>2.3112547017982255E-2</v>
+        <v>2.3143856897623844E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E85,C$18)</f>
-        <v>0.14579424753803166</v>
+        <v>0.14583350700743808</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E86,C$18)</f>
-        <v>0.32713236945852026</v>
+        <v>0.32718559814657738</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.1038256936984379</v>
+        <v>6.0988510679787797</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.8128229003218612</v>
+        <v>2.8105304460731713</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.2552810114252879</v>
+        <v>3.252988557176598</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.5256754909449475</v>
+        <v>3.5228020609263724</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.034423645394611</v>
+        <v>4.0315502153760354</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.3749805031091427</v>
+        <v>4.3714148884232191</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>4.9583479389611078</v>
+        <v>4.9547823242751843</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>4.9477781737914412</v>
+        <v>4.9437457282738846</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.5794505037218762</v>
+        <v>5.5754180582043196</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -7470,7 +7470,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0860457031533781</v>
+        <v>3.0835305719721582</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2412926008211553</v>
+        <v>1.2402809457694648</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923053.43200356001</v>
+        <v>922301.14228004997</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10182325457066647</v>
+        <v>0.10174026848841812</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15949983.402095413</v>
+        <v>15936984.14529453</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7594639313829044</v>
+        <v>1.7580299660363994</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4678.5526959600002</v>
+        <v>4674.7396695500001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.160973846865841E-4</v>
+        <v>5.1567676466030086E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16877715.386794932</v>
+        <v>16863960.027244132</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8618032833382574</v>
+        <v>1.8602859112894778</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="236" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1215189873417716E-2</v>
+        <v>6.2805194805194794E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.263291139240507E-2</v>
+        <v>8.4779220779220787E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1721518987341762E-2</v>
+        <v>7.3584415584415586E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.2202531645569626E-2</v>
+        <v>7.4077922077922076E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11913924050632911</v>
+        <v>0.12223376623376624</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4962025316455697E-2</v>
+        <v>7.6909090909090913E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.4294166306219071</v>
+        <v>0.42906665552066081</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35172142392550931</v>
+        <v>0.35143477051674277</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31603397243438891</v>
+        <v>0.31577640434407112</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49383651269274453</v>
+        <v>0.49343403530550772</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62952059976022479</v>
+        <v>0.62900753966909928</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.5465891845477564</v>
+        <v>0.54614371366572478</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36482144494711322</v>
+        <v>0.36452411500451815</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21358394440113165</v>
+        <v>0.21340987321423305</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3816816413273205E-2</v>
+        <v>9.3740355588327315E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6270477521611241E-2</v>
+        <v>2.6249067048949533E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10871307104352078</v>
+        <v>0.11144588455082099</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.9043398462154255E-2</v>
+        <v>9.1281758575777333E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0008600616300982E-2</v>
+        <v>8.2019845284174317E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12502190194753027</v>
+        <v>0.12816468449493706</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15937230373676575</v>
+        <v>0.16337858173223357</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13837700874626743</v>
+        <v>0.14185551004304539</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.2359859480281817E-2</v>
+        <v>9.4681588312861859E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.4071884658514341E-2</v>
+        <v>5.5431135899800789E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3751092762853976E-2</v>
+        <v>2.4348144308656446E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.650753802939554E-3</v>
+        <v>6.8179394932336443E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10204831604155928</v>
+        <v>0.10469892165302837</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1889396293492465E-2</v>
+        <v>9.4276133859557215E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13818535923700803</v>
+        <v>0.14177458934706019</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19311174575616405</v>
+        <v>0.19812763525632415</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2076822251652308</v>
+        <v>0.21307656867601601</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10988061617731498</v>
+        <v>0.11273465815594655</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2619247544538903E-2</v>
+        <v>6.4245721506734715E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2401538408052877E-2</v>
+        <v>3.324313680826204E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1342574315269173E-2</v>
+        <v>1.1637186635146294E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6581567741969243</v>
+        <v>1.6568053743126412</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09235412</v>
+        <v>1.09146385</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68724985.660321355</v>
+        <v>68668974.709418535</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0837602332754823</v>
+        <v>8.0771719583826496</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18681,23 +18681,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="G69" s="300"/>
       <c r="H69" s="300"/>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.0342456151865718</v>
+        <v>3.0317727011430633</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>4.6136787442629803</v>
+        <v>4.6099185902062949</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>6.3925527395807</v>
+        <v>6.3873428009506652</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>8.1226105665840098</v>
+        <v>8.1159906286200165</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>9.0126439390127988</v>
+        <v>9.005298622715932</v>
       </c>
       <c r="G70" s="300"/>
       <c r="H70" s="300"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>2.8220693351891972</v>
+        <v>2.8197693450843047</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>4.3336057311692615</v>
+        <v>4.330073836975199</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>6.2297456147203913</v>
+        <v>6.2246683641046143</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>8.2155320705761952</v>
+        <v>8.2088364014680195</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>9.281179543384475</v>
+        <v>9.2736153702277999</v>
       </c>
       <c r="G71" s="300"/>
       <c r="H71" s="300"/>
@@ -18776,23 +18776,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>2.6835859822771573</v>
+        <v>2.6813988562813842</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>4.1116364434026762</v>
+        <v>4.1082854544610425</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>6.0855341754501895</v>
+        <v>6.0805744573412142</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>8.3039049694778502</v>
+        <v>8.29713727634444</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>9.5440815336784297</v>
+        <v>9.5363030950645964</v>
       </c>
       <c r="G72" s="300"/>
       <c r="H72" s="300"/>
@@ -18807,23 +18807,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>2.5932005771131217</v>
+        <v>2.591087115337753</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>3.9357167281564318</v>
+        <v>3.9325091140069324</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>5.9577944390336928</v>
+        <v>5.9529388289727008</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>8.3879519222794219</v>
+        <v>8.3811157307723612</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>9.8014680976025748</v>
+        <v>9.7934798886111061</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18839,23 +18839,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>2.5342077718778544</v>
+        <v>2.5321423893139383</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>3.7962931776116231</v>
+        <v>3.7931991938335128</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.84464502216127</v>
+        <v>5.8398816290192377</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>8.4678846885802201</v>
+        <v>8.4609833517667496</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>10.053454943402439</v>
+        <v>10.045261364810488</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18871,23 +18871,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.4957043092534366</v>
+        <v>2.4936703070606323</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>3.6857943263639896</v>
+        <v>3.682790399290476</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>5.7444194314584269</v>
+        <v>5.7397377223005543</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>8.543904662125037</v>
+        <v>8.5369413689362421</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>10.300155351877832</v>
+        <v>10.291760712138553</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18903,23 +18903,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>2.4319186989932486</v>
+        <v>2.4299366821541009</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>3.3956580680863784</v>
+        <v>3.3928906024331384</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>5.3909955737918436</v>
+        <v>5.3866019055284058</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>8.8716977013991887</v>
+        <v>8.8644672564656126</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>11.458162068846017</v>
+        <v>11.448823652156536</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18935,23 +18935,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>2.4243638391683096</v>
+        <v>2.4223879795495473</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>3.3049365873248635</v>
+        <v>3.3022430597940682</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>5.1982753083732893</v>
+        <v>5.1940387073717886</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>9.1267410968177707</v>
+        <v>9.1193027911918776</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>12.499690356008477</v>
+        <v>12.489503092437536</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18967,23 +18967,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>2.4234690306567712</v>
+        <v>2.4214939003080862</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>3.2765692708080612</v>
+        <v>3.273898862676381</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>5.0931859096320284</v>
+        <v>5.0890349566244382</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>9.3251807393760107</v>
+        <v>9.3175807051885222</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>13.436456228834906</v>
+        <v>13.425505499883707</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18999,23 +18999,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>2.4233630482440098</v>
+        <v>2.4213880042711264</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>3.2676992144596655</v>
+        <v>3.2650360354352146</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>5.0358811850675709</v>
+        <v>5.0317769354835349</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>9.4795791376329515</v>
+        <v>9.4718532685541028</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>14.27899724409912</v>
+        <v>14.267359843146666</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>9.0126439390127988</v>
+        <v>9.005298622715932</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -19090,7 +19090,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>8.1226105665840098</v>
+        <v>8.1159906286200165</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.3925527395807</v>
+        <v>6.3873428009506652</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>4.6136787442629803</v>
+        <v>4.6099185902062949</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>3.0342456151865718</v>
+        <v>3.0317727011430633</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E83</f>
-        <v>8.1226105665840098</v>
+        <v>8.1159906286200165</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E84</f>
-        <v>6.3925527395807</v>
+        <v>6.3873428009506652</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E85</f>
-        <v>4.6136787442629803</v>
+        <v>4.6099185902062949</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.293845806151932</v>
+        <v>6.2887163137984432</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E82</f>
-        <v>9.0126439390127988</v>
+        <v>9.005298622715932</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E86</f>
-        <v>3.0342456151865718</v>
+        <v>3.0317727011430633</v>
       </c>
       <c r="F30" s="331">
         <v>0.1</v>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20967048786502251</v>
+        <v>0.22027668345247436</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19743,7 +19743,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-3.5416746028471155E-2</v>
+        <v>-3.538882915572962E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.1038256936984379</v>
+        <v>6.0988510679787797</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>8.0837602332754823</v>
+        <v>8.0771719583826496</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.30502235430156116</v>
+        <v>0.3050223543015611</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19996,11 +19996,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.8128229003218612</v>
+        <v>2.8105304460731713</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.2552810114252879</v>
+        <v>3.252988557176598</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46668185253290806</v>
+        <v>0.46662272599900179</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20021,11 +20021,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.5256754909449475</v>
+        <v>3.5228020609263724</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.034423645394611</v>
+        <v>4.0315502153760354</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33903360812551842</v>
+        <v>0.33896562312479428</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20067,19 +20067,19 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.3749805031091427</v>
+        <v>4.3714148884232191</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>4.9583479389611078</v>
+        <v>4.9547823242751843</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
         <v>0.1174</v>
       </c>
       <c r="G66" s="445">
-        <f>(1-E66/C47)</f>
-        <v>0.38662852486014165</v>
+        <f>(1-E66/C36)</f>
+        <v>0.18758758509621243</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20092,11 +20092,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>4.9477781737914412</v>
+        <v>4.9437457282738846</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.5794505037218762</v>
+        <v>5.5754180582043196</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20104,7 +20104,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.5909266792779548E-2</v>
+        <v>8.5824855196526606E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20233,14 +20233,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>35807.744230800003</v>
+        <v>34901.219060399999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.20967048786502251</v>
+        <v>0.22027668345247436</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.09235412</v>
+        <v>1.09146385</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.1038256936984379</v>
+        <v>6.0988510679787797</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.2552810114252879</v>
+        <v>3.252988557176598</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>444</v>
@@ -20386,7 +20386,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.034423645394611</v>
+        <v>4.0315502153760354</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>445</v>
@@ -20402,7 +20402,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>4.9583479389611078</v>
+        <v>4.9547823242751843</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>447</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.5794505037218762</v>
+        <v>5.5754180582043196</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>446</v>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10871307104352078</v>
+        <v>0.11144588455082099</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1215189873417716E-2</v>
+        <v>6.2805194805194794E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -20863,7 +20863,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10182325457066646</v>
+        <v>-0.10174026848841813</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7594639313829044</v>
+        <v>1.7580299660363992</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -20956,7 +20956,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.160973846865841E-4</v>
+        <v>5.1567676466030086E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6581567741969243</v>
+        <v>1.6568053743126412</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2412926008211553</v>
+        <v>1.2402809457694648</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5811447827749525</v>
+        <v>7.5749661401148591</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.1038256936984379</v>
+        <v>6.0988510679787797</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21409,11 +21409,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.8128229003218612</v>
+        <v>2.8105304460731713</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.2552810114252879</v>
+        <v>3.252988557176598</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21430,11 +21430,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.5256754909449475</v>
+        <v>3.5228020609263724</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.034423645394611</v>
+        <v>4.0315502153760354</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21470,11 +21470,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.3749805031091427</v>
+        <v>4.3714148884232191</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>4.9583479389611078</v>
+        <v>4.9547823242751843</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21491,11 +21491,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>4.9477781737914412</v>
+        <v>4.9437457282738846</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.5794505037218762</v>
+        <v>5.5754180582043196</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4120ABBF-B251-48B7-BA06-B7D13019234C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB81A6A-11CE-4EEB-9C79-BABAF287E5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$89:$M$89</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
@@ -2086,9 +2086,6 @@
     <t>Try obtain this number by reverse engineering.</t>
   </si>
   <si>
-    <t>CNS_01</t>
-  </si>
-  <si>
     <t>Assets held for sale</t>
   </si>
   <si>
@@ -3231,34 +3228,37 @@
     <t>更新日期:</t>
   </si>
   <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>Prompt for fundamental Analysis</t>
+  </si>
+  <si>
+    <t>accepts 5-10, 15, 20, 25, or 30</t>
+  </si>
+  <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
+    <t>中国飞鹤</t>
+  </si>
+  <si>
+    <t>6186.HK</t>
+  </si>
+  <si>
+    <t>CNS_01</t>
+  </si>
+  <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>EBIT</t>
-  </si>
-  <si>
-    <t>Prompt for fundamental Analysis</t>
-  </si>
-  <si>
-    <t>accepts 5-10, 15, 20, 25, or 30</t>
-  </si>
-  <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>中国飞鹤</t>
-  </si>
-  <si>
-    <t>6186.HK</t>
-  </si>
-  <si>
-    <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5032,14 +5032,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="433" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F3" s="434">
         <v>45930</v>
@@ -5339,13 +5339,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="426" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C4" s="425" t="s">
         <v>552</v>
       </c>
       <c r="E4" s="435" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F4" s="436" t="s">
         <v>324</v>
@@ -5359,10 +5359,10 @@
         <v>553</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F5" s="437" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5370,7 +5370,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>404</v>
+        <v>554</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>34901.219060399999</v>
+        <v>35626.439196719999</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22027668345247436</v>
+        <v>0.21151245374364994</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5443,7 +5443,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="422" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5458,18 +5458,18 @@
         <v>320</v>
       </c>
       <c r="C16" s="422" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.09146385</v>
+        <v>1.0914415199999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C17" s="420">
         <v>0</v>
@@ -5478,7 +5478,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.0988510679787797</v>
+        <v>6.0987262930314925</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5519,7 +5519,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C21" s="257" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5538,10 +5538,10 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.252988557176598</v>
+        <v>3.2529310572008892</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E22" s="79">
         <v>0.29465259038036606</v>
@@ -5553,10 +5553,10 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.0315502153760354</v>
+        <v>4.0314781432043176</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E23" s="448">
         <v>0.20075184365903009</v>
@@ -5568,10 +5568,10 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>4.9547823242751843</v>
+        <v>4.9546928905349281</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E24" s="448">
         <v>0.1174</v>
@@ -5583,10 +5583,10 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.5754180582043196</v>
+        <v>5.5753169152831736</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E25" s="449">
         <v>7.2499999999999995E-2</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11144588455082099</v>
+        <v>0.10917503240400375</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.2805194805194794E-2</v>
+        <v>6.1526717557251906E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5968,7 +5968,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5981,18 +5981,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
-        <v>482</v>
-      </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="B73" s="456" t="s">
+        <v>481</v>
+      </c>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10174026848841813</v>
+        <v>-0.10173818700839903</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6068,7 +6068,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7580299660363992</v>
+        <v>1.7579939989183475</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1567676466030086E-4</v>
+        <v>5.1566621455169685E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6156,11 +6156,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6568053743126412</v>
+        <v>1.6567714781245002</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
-        <v>489</v>
-      </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="B96" s="456" t="s">
+        <v>488</v>
+      </c>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
-        <v>488</v>
-      </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="B97" s="458" t="s">
+        <v>487</v>
+      </c>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
-        <v>487</v>
-      </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="B98" s="458" t="s">
+        <v>486</v>
+      </c>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6255,35 +6255,35 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2402809457694648</v>
+        <v>1.2402555711558032</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5749661401148591</v>
+        <v>7.5748111656794634</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,17 +6304,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
-        <v>495</v>
-      </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="B114" s="456" t="s">
+        <v>494</v>
+      </c>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6331,127 +6331,127 @@
         <v>124</v>
       </c>
       <c r="F117" s="346" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
-        <f>DCF!B82&amp;" ("&amp;DCF!D82&amp;"yrs)"</f>
+        <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
       </c>
       <c r="C118" s="206">
-        <f>DCF!C82</f>
+        <f>DCF!C90</f>
         <v>0.05</v>
       </c>
       <c r="D118" s="207" t="str">
-        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
         <v>9.01 HKD</v>
       </c>
       <c r="E118" s="208">
-        <f>DCF!F82</f>
+        <f>DCF!F90</f>
         <v>0.05</v>
       </c>
       <c r="F118" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E82,C$18)</f>
-        <v>-9.1163725549836608E-2</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
+        <v>-9.1163100162497374E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
-        <f>DCF!B83&amp;" ("&amp;DCF!D83&amp;"yrs)"</f>
+        <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
       </c>
       <c r="C119" s="198">
-        <f>DCF!C83</f>
+        <f>DCF!C91</f>
         <v>0.02</v>
       </c>
       <c r="D119" s="207" t="str">
-        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
         <v>8.12 HKD</v>
       </c>
       <c r="E119" s="199">
-        <f>DCF!F83</f>
+        <f>DCF!F91</f>
         <v>0.16999999999999996</v>
       </c>
       <c r="F119" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E83,C$18)</f>
-        <v>-5.805452864625979E-2</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
+        <v>-5.8053859155239369E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
-        <f>DCF!B84&amp;" ("&amp;DCF!D84&amp;"yrs)"</f>
+        <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
       </c>
       <c r="C120" s="198">
-        <f>DCF!C84</f>
+        <f>DCF!C92</f>
         <v>-0.05</v>
       </c>
       <c r="D120" s="207" t="str">
-        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
         <v>6.39 HKD</v>
       </c>
       <c r="E120" s="199">
-        <f>DCF!F84</f>
+        <f>DCF!F92</f>
         <v>0.46750000000000003</v>
       </c>
       <c r="F120" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E84,C$18)</f>
-        <v>2.3143856897623844E-2</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
+        <v>2.3144642877135413E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
-        <f>DCF!B85&amp;" ("&amp;DCF!D85&amp;"yrs)"</f>
+        <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
       </c>
       <c r="C121" s="198">
-        <f>DCF!C85</f>
+        <f>DCF!C93</f>
         <v>-0.15</v>
       </c>
       <c r="D121" s="207" t="str">
-        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
         <v>4.61 HKD</v>
       </c>
       <c r="E121" s="199">
-        <f>DCF!F85</f>
+        <f>DCF!F93</f>
         <v>0.21249999999999999</v>
       </c>
       <c r="F121" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E85,C$18)</f>
-        <v>0.14583350700743808</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
+        <v>0.14583449254984052</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
-        <f>DCF!B86&amp;" ("&amp;DCF!D86&amp;"yrs)"</f>
+        <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
       </c>
       <c r="C122" s="198">
-        <f>DCF!C86</f>
+        <f>DCF!C94</f>
         <v>-0.3</v>
       </c>
       <c r="D122" s="207" t="str">
-        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
         <v>3.03 HKD</v>
       </c>
       <c r="E122" s="199">
-        <f>DCF!F86</f>
+        <f>DCF!F94</f>
         <v>0.1</v>
       </c>
       <c r="F122" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E86,C$18)</f>
-        <v>0.32718559814657738</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
+        <v>0.32718693436786978</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.0988510679787797</v>
+        <v>6.0987262930314925</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6532,28 +6532,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="344" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C139" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E139" s="345" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.8105304460731713</v>
+        <v>2.8104729460974625</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.252988557176598</v>
+        <v>3.2529310572008892</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.5228020609263724</v>
+        <v>3.5227299887546542</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.0315502153760354</v>
+        <v>4.0314781432043176</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6607,21 +6607,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="344" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C143" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E143" s="345" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.3714148884232191</v>
+        <v>4.371325454682963</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>4.9547823242751843</v>
+        <v>4.9546928905349281</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>4.9437457282738846</v>
+        <v>4.9436445853527387</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.5754180582043196</v>
+        <v>5.5753169152831736</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
-        <v>442</v>
-      </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="B158" s="457" t="s">
+        <v>441</v>
+      </c>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7470,7 +7470,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9571,7 +9571,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0835305719721582</v>
+        <v>3.083467486751633</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2402809457694648</v>
+        <v>1.2402555711558032</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>922301.14228004997</v>
+        <v>922282.2731397599</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10174026848841812</v>
+        <v>0.10173818700839903</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15936984.14529453</v>
+        <v>15936658.094316324</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7580299660363994</v>
+        <v>1.7579939989183475</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4674.7396695500001</v>
+        <v>4674.6440301599996</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1567676466030086E-4</v>
+        <v>5.1566621455169685E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16863960.027244132</v>
+        <v>16863615.011486247</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8602859112894778</v>
+        <v>1.8602478521412984</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10765,7 +10765,7 @@
       <c r="E3" s="238"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11054,7 +11054,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C9" s="304">
         <f>C61</f>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="235" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="236" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.2805194805194794E-2</v>
+        <v>6.1526717557251906E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.4779220779220787E-2</v>
+        <v>8.3053435114503818E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.3584415584415586E-2</v>
+        <v>7.2086513994910936E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4077922077922076E-2</v>
+        <v>7.2569974554707373E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.12223376623376624</v>
+        <v>0.11974554707379134</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.6909090909090913E-2</v>
+        <v>7.5343511450381678E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42906665552066081</v>
+        <v>0.42905787734773476</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35143477051674277</v>
+        <v>0.35142758059613688</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31577640434407112</v>
+        <v>0.31576994394952018</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49343403530550772</v>
+        <v>0.4934239402556273</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62900753966909928</v>
+        <v>0.6289946709530525</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54614371366572478</v>
+        <v>0.54613254024103808</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36452411500451815</v>
+        <v>0.3645166572921183</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21340987321423305</v>
+        <v>0.21340550711226006</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3740355588327315E-2</v>
+        <v>9.3738437776628547E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6249067048949533E-2</v>
+        <v>2.6248530025513337E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11144588455082099</v>
+        <v>0.10917503240400375</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.1281758575777333E-2</v>
+        <v>8.9421776233113703E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2019845284174317E-2</v>
+        <v>8.0348586246697246E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12816468449493706</v>
+        <v>0.12555316545944714</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16337858173223357</v>
+        <v>0.16004953459365204</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14185551004304539</v>
+        <v>0.1389650229620962</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.4681588312861859E-2</v>
+        <v>9.275233009977564E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.5431135899800789E-2</v>
+        <v>5.4301655753755736E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.4348144308656446E-2</v>
+        <v>2.3852019790490724E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.8179394932336443E-3</v>
+        <v>6.6790152736675157E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10469892165302837</v>
+        <v>0.1025676458941881</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4276133859557215E-2</v>
+        <v>9.2357026808980974E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14177458934706019</v>
+        <v>0.13888859261734904</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19812763525632415</v>
+        <v>0.19409450273202239</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21307656867601601</v>
+        <v>0.20873913216352713</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11273465815594655</v>
+        <v>0.11043980506371354</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4245721506734715E-2</v>
+        <v>6.2937920560032737E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.324313680826204E-2</v>
+        <v>3.2566431733284697E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1637186635146294E-2</v>
+        <v>1.140029733977436E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16219,7 +16219,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U110"/>
+  <dimension ref="A2:U118"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -16253,10 +16253,10 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -16272,7 +16272,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F4" s="279">
         <f>-BS!G31</f>
@@ -16300,7 +16300,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
@@ -16332,7 +16332,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F6" s="288">
         <f>BS!H42</f>
@@ -16343,7 +16343,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="312" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
@@ -16354,14 +16354,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="322" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" s="279">
         <f>F7</f>
         <v>13760746.8563288</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
@@ -16372,7 +16372,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="316" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I7" s="317">
         <f>Normalized_FCF!C9</f>
@@ -16384,7 +16384,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
@@ -16395,11 +16395,11 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6568053743126412</v>
+        <v>1.6567714781245002</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09146385</v>
+        <v>1.0914415199999998</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16445,11 +16445,11 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68668974.709418535</v>
+        <v>68667569.827153981</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16467,11 +16467,11 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5749661401148591</v>
+        <v>7.5748111656794634</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16483,7 +16483,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16501,7 +16501,7 @@
         <v>400</v>
       </c>
       <c r="C14" s="313" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E14" s="106" t="s">
         <v>400</v>
@@ -16511,12 +16511,12 @@
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16531,7 +16531,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16541,7 +16541,7 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
@@ -16571,19 +16571,19 @@
         <v>0.68269686315429268</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="312" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C18" s="310">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="312" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0771719583826496</v>
+        <v>8.0770067094375442</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16624,23 +16624,23 @@
         <v>396</v>
       </c>
       <c r="G20" s="121" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>421</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>532</v>
+      </c>
+      <c r="K20" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="L20" s="122" t="s">
         <v>422</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>533</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>534</v>
-      </c>
-      <c r="L20" s="122" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18195,7 +18195,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="319" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B51" s="320">
         <f>C15+1</f>
@@ -18247,7 +18247,7 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="464" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K52" s="464"/>
       <c r="L52" s="321">
@@ -18279,23 +18279,23 @@
         <v>53324935.238620415</v>
       </c>
       <c r="B55" s="123">
-        <f>C86</f>
+        <f>C94</f>
         <v>-0.3</v>
       </c>
       <c r="C55" s="123">
-        <f>C85</f>
+        <f>C93</f>
         <v>-0.15</v>
       </c>
       <c r="D55" s="123">
-        <f>C84</f>
+        <f>C92</f>
         <v>-0.05</v>
       </c>
       <c r="E55" s="123">
-        <f>C83</f>
+        <f>C91</f>
         <v>0.02</v>
       </c>
       <c r="F55" s="123">
-        <f>C82</f>
+        <f>C90</f>
         <v>0.05</v>
       </c>
       <c r="G55" s="123"/>
@@ -18307,23 +18307,23 @@
     </row>
     <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B56" s="118">
-        <f t="dataTable" ref="B56:F65" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11419915.467190061</v>
+        <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
+        <v>34287291.4709865</v>
       </c>
       <c r="C56" s="118">
-        <v>24527348.85583692</v>
+        <v>41720555.436503738</v>
       </c>
       <c r="D56" s="118">
-        <v>39289906.365351558</v>
+        <v>46676064.746848568</v>
       </c>
       <c r="E56" s="118">
-        <v>53647347.214533597</v>
+        <v>50144921.264089949</v>
       </c>
       <c r="F56" s="118">
-        <v>61033575.176970296</v>
+        <v>51631574.057193398</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18334,22 +18334,22 @@
     </row>
     <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>9659102.4226120021</v>
+        <v>24584196.317863755</v>
       </c>
       <c r="C57" s="118">
-        <v>22203072.952348541</v>
+        <v>35829390.522107795</v>
       </c>
       <c r="D57" s="118">
-        <v>37938799.119961888</v>
+        <v>44481317.033642232</v>
       </c>
       <c r="E57" s="118">
-        <v>54418486.176689364</v>
+        <v>51087507.650393307</v>
       </c>
       <c r="F57" s="118">
-        <v>63262104.1865144</v>
+        <v>54057347.845474087</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18360,22 +18360,22 @@
     </row>
     <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>8509853.8154281881</v>
+        <v>18251173.840301126</v>
       </c>
       <c r="C58" s="118">
-        <v>20360989.485714391</v>
+        <v>31160402.011863917</v>
       </c>
       <c r="D58" s="118">
-        <v>36742014.147355668</v>
+        <v>42537251.46017275</v>
       </c>
       <c r="E58" s="118">
-        <v>55151877.077760585</v>
+        <v>51983953.444360137</v>
       </c>
       <c r="F58" s="118">
-        <v>65443880.839214943</v>
+        <v>56432231.274560057</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18386,22 +18386,22 @@
     </row>
     <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>7759761.484399124</v>
+        <v>14117732.596204303</v>
       </c>
       <c r="C59" s="118">
-        <v>18901063.195141871</v>
+        <v>27460038.157591373</v>
       </c>
       <c r="D59" s="118">
-        <v>35681924.894231275</v>
+        <v>40815235.334488817</v>
       </c>
       <c r="E59" s="118">
-        <v>55849367.7249332</v>
+        <v>52836517.276384525</v>
       </c>
       <c r="F59" s="118">
-        <v>67579885.953746915</v>
+        <v>58757291.974364527</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18412,22 +18412,22 @@
     </row>
     <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>7270190.7322123228</v>
+        <v>11419915.467190061</v>
       </c>
       <c r="C60" s="118">
-        <v>17744012.055760387</v>
+        <v>24527348.85583692</v>
       </c>
       <c r="D60" s="118">
-        <v>34742918.096591942</v>
+        <v>39289906.365351558</v>
       </c>
       <c r="E60" s="118">
-        <v>56512715.473293178</v>
+        <v>53647347.214533597</v>
       </c>
       <c r="F60" s="118">
-        <v>69671079.772169828</v>
+        <v>61033575.176970296</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18438,22 +18438,22 @@
     </row>
     <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>6950657.3741416829</v>
+        <v>9659102.4226120021</v>
       </c>
       <c r="C61" s="118">
-        <v>16827001.828744762</v>
+        <v>22203072.952348541</v>
       </c>
       <c r="D61" s="118">
-        <v>33911163.823624715</v>
+        <v>37938799.119961888</v>
       </c>
       <c r="E61" s="118">
-        <v>57143591.653551623</v>
+        <v>54418486.176689364</v>
       </c>
       <c r="F61" s="118">
-        <v>71718402.391604856</v>
+        <v>63262104.1865144</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18464,22 +18464,22 @@
     </row>
     <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>6421311.9892386161</v>
-      </c>
-      <c r="C62" s="281">
-        <v>14419212.851170991</v>
+        <v>8509853.8154281881</v>
+      </c>
+      <c r="C62" s="118">
+        <v>20360989.485714391</v>
       </c>
       <c r="D62" s="118">
-        <v>30978162.364403542</v>
+        <v>36742014.147355668</v>
       </c>
       <c r="E62" s="118">
-        <v>59863887.52961728</v>
+        <v>55151877.077760585</v>
       </c>
       <c r="F62" s="118">
-        <v>81328493.269679546</v>
+        <v>65443880.839214943</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18487,34 +18487,25 @@
       <c r="J62" s="299"/>
       <c r="K62" s="299"/>
       <c r="L62" s="299"/>
-      <c r="M62" s="279"/>
-      <c r="N62" s="279"/>
-      <c r="O62" s="279"/>
-      <c r="P62" s="279"/>
-      <c r="Q62" s="279"/>
-      <c r="R62" s="279"/>
-      <c r="S62" s="279"/>
-      <c r="T62" s="279"/>
-      <c r="U62" s="279"/>
     </row>
     <row r="63" spans="1:21" ht="13.15">
-      <c r="A63" s="132">
-        <v>20</v>
+      <c r="A63" s="131">
+        <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>6358615.5571498051</v>
-      </c>
-      <c r="C63" s="281">
-        <v>13666331.488794912</v>
+        <v>7759761.484399124</v>
+      </c>
+      <c r="C63" s="118">
+        <v>18901063.195141871</v>
       </c>
       <c r="D63" s="118">
-        <v>29378811.309197303</v>
+        <v>35681924.894231275</v>
       </c>
       <c r="E63" s="118">
-        <v>61980447.107304662</v>
+        <v>55849367.7249332</v>
       </c>
       <c r="F63" s="118">
-        <v>89971950.466475472</v>
+        <v>67579885.953746915</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18522,34 +18513,25 @@
       <c r="J63" s="299"/>
       <c r="K63" s="299"/>
       <c r="L63" s="299"/>
-      <c r="M63" s="279"/>
-      <c r="N63" s="279"/>
-      <c r="O63" s="279"/>
-      <c r="P63" s="279"/>
-      <c r="Q63" s="279"/>
-      <c r="R63" s="279"/>
-      <c r="S63" s="279"/>
-      <c r="T63" s="279"/>
-      <c r="U63" s="279"/>
     </row>
     <row r="64" spans="1:21" ht="13.15">
-      <c r="A64" s="132">
-        <v>25</v>
+      <c r="A64" s="131">
+        <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>6351189.7011609282</v>
-      </c>
-      <c r="C64" s="281">
-        <v>13430916.196552634</v>
+        <v>7270190.7322123228</v>
+      </c>
+      <c r="C64" s="118">
+        <v>17744012.055760387</v>
       </c>
       <c r="D64" s="118">
-        <v>28506693.162188768</v>
+        <v>34742918.096591942</v>
       </c>
       <c r="E64" s="118">
-        <v>63627262.251684964</v>
+        <v>56512715.473293178</v>
       </c>
       <c r="F64" s="118">
-        <v>97746003.101429433</v>
+        <v>69671079.772169828</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18557,34 +18539,25 @@
       <c r="J64" s="299"/>
       <c r="K64" s="299"/>
       <c r="L64" s="299"/>
-      <c r="M64" s="279"/>
-      <c r="N64" s="279"/>
-      <c r="O64" s="279"/>
-      <c r="P64" s="279"/>
-      <c r="Q64" s="279"/>
-      <c r="R64" s="279"/>
-      <c r="S64" s="279"/>
-      <c r="T64" s="279"/>
-      <c r="U64" s="279"/>
     </row>
     <row r="65" spans="1:21" ht="13.15">
-      <c r="A65" s="132">
-        <v>30</v>
+      <c r="A65" s="131">
+        <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>6350310.1720500933</v>
-      </c>
-      <c r="C65" s="281">
-        <v>13357305.183462057</v>
+        <v>6950657.3741416829</v>
+      </c>
+      <c r="C65" s="118">
+        <v>16827001.828744762</v>
       </c>
       <c r="D65" s="118">
-        <v>28031131.489930686</v>
+        <v>33911163.823624715</v>
       </c>
       <c r="E65" s="118">
-        <v>64908586.977126196</v>
+        <v>57143591.653551623</v>
       </c>
       <c r="F65" s="118">
-        <v>104738100.47578071</v>
+        <v>71718402.391604856</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18592,27 +18565,32 @@
       <c r="J65" s="299"/>
       <c r="K65" s="299"/>
       <c r="L65" s="299"/>
-      <c r="M65" s="279"/>
-      <c r="N65" s="279"/>
-      <c r="O65" s="279"/>
-      <c r="P65" s="279"/>
-      <c r="Q65" s="279"/>
-      <c r="R65" s="279"/>
-      <c r="S65" s="279"/>
-      <c r="T65" s="279"/>
-      <c r="U65" s="279"/>
-    </row>
-    <row r="66" spans="1:21">
-      <c r="C66" s="279"/>
-      <c r="D66" s="111"/>
-      <c r="E66" s="111"/>
-      <c r="F66" s="111"/>
-      <c r="G66" s="111"/>
-      <c r="H66" s="111"/>
-      <c r="I66" s="111"/>
-      <c r="J66" s="111"/>
-      <c r="K66" s="111"/>
-      <c r="L66" s="111"/>
+    </row>
+    <row r="66" spans="1:21" ht="13.15">
+      <c r="A66" s="131">
+        <v>15</v>
+      </c>
+      <c r="B66" s="118">
+        <v>6421311.9892386161</v>
+      </c>
+      <c r="C66" s="281">
+        <v>14419212.851170991</v>
+      </c>
+      <c r="D66" s="118">
+        <v>30978162.364403542</v>
+      </c>
+      <c r="E66" s="118">
+        <v>59863887.52961728</v>
+      </c>
+      <c r="F66" s="118">
+        <v>81328493.269679546</v>
+      </c>
+      <c r="G66" s="299"/>
+      <c r="H66" s="299"/>
+      <c r="I66" s="299"/>
+      <c r="J66" s="299"/>
+      <c r="K66" s="299"/>
+      <c r="L66" s="299"/>
       <c r="M66" s="279"/>
       <c r="N66" s="279"/>
       <c r="O66" s="279"/>
@@ -18624,19 +18602,30 @@
       <c r="U66" s="279"/>
     </row>
     <row r="67" spans="1:21" ht="13.15">
-      <c r="B67" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67" s="279"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="111"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="111"/>
-      <c r="I67" s="111"/>
-      <c r="J67" s="111"/>
-      <c r="K67" s="111"/>
-      <c r="L67" s="111"/>
+      <c r="A67" s="132">
+        <v>20</v>
+      </c>
+      <c r="B67" s="118">
+        <v>6358615.5571498051</v>
+      </c>
+      <c r="C67" s="281">
+        <v>13666331.488794912</v>
+      </c>
+      <c r="D67" s="118">
+        <v>29378811.309197303</v>
+      </c>
+      <c r="E67" s="118">
+        <v>61980447.107304662</v>
+      </c>
+      <c r="F67" s="118">
+        <v>89971950.466475472</v>
+      </c>
+      <c r="G67" s="299"/>
+      <c r="H67" s="299"/>
+      <c r="I67" s="299"/>
+      <c r="J67" s="299"/>
+      <c r="K67" s="299"/>
+      <c r="L67" s="299"/>
       <c r="M67" s="279"/>
       <c r="N67" s="279"/>
       <c r="O67" s="279"/>
@@ -18648,182 +18637,171 @@
       <c r="U67" s="279"/>
     </row>
     <row r="68" spans="1:21" ht="13.15">
-      <c r="B68" s="124">
+      <c r="A68" s="132">
+        <v>25</v>
+      </c>
+      <c r="B68" s="118">
+        <v>6351189.7011609282</v>
+      </c>
+      <c r="C68" s="281">
+        <v>13430916.196552634</v>
+      </c>
+      <c r="D68" s="118">
+        <v>28506693.162188768</v>
+      </c>
+      <c r="E68" s="118">
+        <v>63627262.251684964</v>
+      </c>
+      <c r="F68" s="118">
+        <v>97746003.101429433</v>
+      </c>
+      <c r="G68" s="299"/>
+      <c r="H68" s="299"/>
+      <c r="I68" s="299"/>
+      <c r="J68" s="299"/>
+      <c r="K68" s="299"/>
+      <c r="L68" s="299"/>
+      <c r="M68" s="279"/>
+      <c r="N68" s="279"/>
+      <c r="O68" s="279"/>
+      <c r="P68" s="279"/>
+      <c r="Q68" s="279"/>
+      <c r="R68" s="279"/>
+      <c r="S68" s="279"/>
+      <c r="T68" s="279"/>
+      <c r="U68" s="279"/>
+    </row>
+    <row r="69" spans="1:21" ht="13.15">
+      <c r="A69" s="132">
+        <v>30</v>
+      </c>
+      <c r="B69" s="118">
+        <v>6350310.1720500933</v>
+      </c>
+      <c r="C69" s="281">
+        <v>13357305.183462057</v>
+      </c>
+      <c r="D69" s="118">
+        <v>28031131.489930686</v>
+      </c>
+      <c r="E69" s="118">
+        <v>64908586.977126196</v>
+      </c>
+      <c r="F69" s="118">
+        <v>104738100.47578071</v>
+      </c>
+      <c r="G69" s="299"/>
+      <c r="H69" s="299"/>
+      <c r="I69" s="299"/>
+      <c r="J69" s="299"/>
+      <c r="K69" s="299"/>
+      <c r="L69" s="299"/>
+      <c r="M69" s="279"/>
+      <c r="N69" s="279"/>
+      <c r="O69" s="279"/>
+      <c r="P69" s="279"/>
+      <c r="Q69" s="279"/>
+      <c r="R69" s="279"/>
+      <c r="S69" s="279"/>
+      <c r="T69" s="279"/>
+      <c r="U69" s="279"/>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="C70" s="279"/>
+      <c r="D70" s="111"/>
+      <c r="E70" s="111"/>
+      <c r="F70" s="111"/>
+      <c r="G70" s="111"/>
+      <c r="H70" s="111"/>
+      <c r="I70" s="111"/>
+      <c r="J70" s="111"/>
+      <c r="K70" s="111"/>
+      <c r="L70" s="111"/>
+      <c r="M70" s="279"/>
+      <c r="N70" s="279"/>
+      <c r="O70" s="279"/>
+      <c r="P70" s="279"/>
+      <c r="Q70" s="279"/>
+      <c r="R70" s="279"/>
+      <c r="S70" s="279"/>
+      <c r="T70" s="279"/>
+      <c r="U70" s="279"/>
+    </row>
+    <row r="71" spans="1:21" ht="13.15">
+      <c r="B71" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="279"/>
+      <c r="D71" s="111"/>
+      <c r="E71" s="111"/>
+      <c r="F71" s="111"/>
+      <c r="G71" s="111"/>
+      <c r="H71" s="111"/>
+      <c r="I71" s="111"/>
+      <c r="J71" s="111"/>
+      <c r="K71" s="111"/>
+      <c r="L71" s="111"/>
+      <c r="M71" s="279"/>
+      <c r="N71" s="279"/>
+      <c r="O71" s="279"/>
+      <c r="P71" s="279"/>
+      <c r="Q71" s="279"/>
+      <c r="R71" s="279"/>
+      <c r="S71" s="279"/>
+      <c r="T71" s="279"/>
+      <c r="U71" s="279"/>
+    </row>
+    <row r="72" spans="1:21" ht="13.15">
+      <c r="B72" s="124">
         <f>B55</f>
         <v>-0.3</v>
       </c>
-      <c r="C68" s="124">
+      <c r="C72" s="124">
         <f>C55</f>
         <v>-0.15</v>
       </c>
-      <c r="D68" s="124">
+      <c r="D72" s="124">
         <f>D55</f>
         <v>-0.05</v>
       </c>
-      <c r="E68" s="124">
+      <c r="E72" s="124">
         <f>E55</f>
         <v>0.02</v>
       </c>
-      <c r="F68" s="124">
+      <c r="F72" s="124">
         <f>F55</f>
         <v>0.05</v>
       </c>
-      <c r="G68" s="124"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="124"/>
-      <c r="L68" s="124"/>
-    </row>
-    <row r="69" spans="1:21" ht="13.15">
-      <c r="A69" s="131">
-        <v>0</v>
-      </c>
-      <c r="B69" s="119">
-        <f>C11</f>
-        <v>7.5749661401148591</v>
-      </c>
-      <c r="C69" s="119">
-        <f>C11</f>
-        <v>7.5749661401148591</v>
-      </c>
-      <c r="D69" s="119">
-        <f>C11</f>
-        <v>7.5749661401148591</v>
-      </c>
-      <c r="E69" s="119">
-        <f>C11</f>
-        <v>7.5749661401148591</v>
-      </c>
-      <c r="F69" s="119">
-        <f>C11</f>
-        <v>7.5749661401148591</v>
-      </c>
-      <c r="G69" s="300"/>
-      <c r="H69" s="300"/>
-      <c r="I69" s="300"/>
-      <c r="J69" s="300"/>
-      <c r="K69" s="300"/>
-      <c r="L69" s="300"/>
-    </row>
-    <row r="70" spans="1:21" ht="13.15">
-      <c r="A70" s="131">
-        <f>A56</f>
-        <v>5</v>
-      </c>
-      <c r="B70" s="119">
-        <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>3.0317727011430633</v>
-      </c>
-      <c r="C70" s="119">
-        <f t="shared" si="11"/>
-        <v>4.6099185902062949</v>
-      </c>
-      <c r="D70" s="119">
-        <f t="shared" si="11"/>
-        <v>6.3873428009506652</v>
-      </c>
-      <c r="E70" s="119">
-        <f t="shared" si="11"/>
-        <v>8.1159906286200165</v>
-      </c>
-      <c r="F70" s="119">
-        <f t="shared" si="11"/>
-        <v>9.005298622715932</v>
-      </c>
-      <c r="G70" s="300"/>
-      <c r="H70" s="300"/>
-      <c r="I70" s="300"/>
-      <c r="J70" s="300"/>
-      <c r="K70" s="300"/>
-      <c r="L70" s="300"/>
-    </row>
-    <row r="71" spans="1:21" ht="13.15">
-      <c r="A71" s="131">
-        <v>6</v>
-      </c>
-      <c r="B71" s="119">
-        <f t="shared" si="11"/>
-        <v>2.8197693450843047</v>
-      </c>
-      <c r="C71" s="119">
-        <f t="shared" si="11"/>
-        <v>4.330073836975199</v>
-      </c>
-      <c r="D71" s="119">
-        <f t="shared" si="11"/>
-        <v>6.2246683641046143</v>
-      </c>
-      <c r="E71" s="119">
-        <f t="shared" si="11"/>
-        <v>8.2088364014680195</v>
-      </c>
-      <c r="F71" s="119">
-        <f t="shared" si="11"/>
-        <v>9.2736153702277999</v>
-      </c>
-      <c r="G71" s="300"/>
-      <c r="H71" s="300"/>
-      <c r="I71" s="300"/>
-      <c r="J71" s="300"/>
-      <c r="K71" s="300"/>
-      <c r="L71" s="300"/>
-    </row>
-    <row r="72" spans="1:21" ht="13.15">
-      <c r="A72" s="131">
-        <f t="shared" ref="A72" si="12">A58</f>
-        <v>7</v>
-      </c>
-      <c r="B72" s="119">
-        <f t="shared" si="11"/>
-        <v>2.6813988562813842</v>
-      </c>
-      <c r="C72" s="119">
-        <f t="shared" si="11"/>
-        <v>4.1082854544610425</v>
-      </c>
-      <c r="D72" s="119">
-        <f t="shared" si="11"/>
-        <v>6.0805744573412142</v>
-      </c>
-      <c r="E72" s="119">
-        <f t="shared" si="11"/>
-        <v>8.29713727634444</v>
-      </c>
-      <c r="F72" s="119">
-        <f t="shared" si="11"/>
-        <v>9.5363030950645964</v>
-      </c>
-      <c r="G72" s="300"/>
-      <c r="H72" s="300"/>
-      <c r="I72" s="300"/>
-      <c r="J72" s="300"/>
-      <c r="K72" s="300"/>
-      <c r="L72" s="300"/>
+      <c r="G72" s="124"/>
+      <c r="H72" s="124"/>
+      <c r="I72" s="124"/>
+      <c r="J72" s="124"/>
+      <c r="K72" s="124"/>
+      <c r="L72" s="124"/>
     </row>
     <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B73" s="119">
-        <f t="shared" si="11"/>
-        <v>2.591087115337753</v>
+        <f>C11</f>
+        <v>7.5748111656794634</v>
       </c>
       <c r="C73" s="119">
-        <f t="shared" si="11"/>
-        <v>3.9325091140069324</v>
+        <f>C11</f>
+        <v>7.5748111656794634</v>
       </c>
       <c r="D73" s="119">
-        <f t="shared" si="11"/>
-        <v>5.9529388289727008</v>
+        <f>C11</f>
+        <v>7.5748111656794634</v>
       </c>
       <c r="E73" s="119">
-        <f t="shared" si="11"/>
-        <v>8.3811157307723612</v>
+        <f>C11</f>
+        <v>7.5748111656794634</v>
       </c>
       <c r="F73" s="119">
-        <f t="shared" si="11"/>
-        <v>9.7934798886111061</v>
+        <f>C11</f>
+        <v>7.5748111656794634</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18834,28 +18812,27 @@
     </row>
     <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
-        <f t="shared" ref="A74" si="13">A60</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B74" s="119">
-        <f t="shared" si="11"/>
-        <v>2.5321423893139383</v>
+        <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
+        <v>5.7849054496571384</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>3.7931991938335128</v>
+        <v>6.6798583076683018</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8398816290192377</v>
+        <v>7.2764935463424099</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>8.4609833517667496</v>
+        <v>7.6941382134142868</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>10.045261364810488</v>
+        <v>7.8731287850165188</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18866,28 +18843,27 @@
     </row>
     <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
-        <f t="shared" ref="A75:A79" si="14">A61</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B75" s="119">
-        <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.4936703070606323</v>
+        <f t="shared" si="11"/>
+        <v>4.6166686186868553</v>
       </c>
       <c r="C75" s="119">
-        <f t="shared" si="15"/>
-        <v>3.682790399290476</v>
+        <f t="shared" si="11"/>
+        <v>5.970571660293488</v>
       </c>
       <c r="D75" s="119">
-        <f t="shared" si="15"/>
-        <v>5.7397377223005543</v>
+        <f t="shared" si="11"/>
+        <v>7.0122495012419881</v>
       </c>
       <c r="E75" s="119">
-        <f t="shared" si="15"/>
-        <v>8.5369413689362421</v>
+        <f t="shared" si="11"/>
+        <v>7.8076240769942569</v>
       </c>
       <c r="F75" s="119">
-        <f t="shared" si="15"/>
-        <v>10.291760712138553</v>
+        <f t="shared" si="11"/>
+        <v>8.1651879927590887</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18898,28 +18874,27 @@
     </row>
     <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
-        <f t="shared" si="14"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B76" s="119">
-        <f t="shared" si="15"/>
-        <v>2.4299366821541009</v>
+        <f t="shared" si="11"/>
+        <v>3.8541830413635938</v>
       </c>
       <c r="C76" s="119">
-        <f t="shared" si="15"/>
-        <v>3.3928906024331384</v>
+        <f t="shared" si="11"/>
+        <v>5.4084330586444507</v>
       </c>
       <c r="D76" s="119">
-        <f t="shared" si="15"/>
-        <v>5.3866019055284058</v>
+        <f t="shared" si="11"/>
+        <v>6.7781871769106132</v>
       </c>
       <c r="E76" s="119">
-        <f t="shared" si="15"/>
-        <v>8.8644672564656126</v>
+        <f t="shared" si="11"/>
+        <v>7.9155546885108734</v>
       </c>
       <c r="F76" s="119">
-        <f t="shared" si="15"/>
-        <v>11.448823652156536</v>
+        <f t="shared" si="11"/>
+        <v>8.4511200842553098</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18929,29 +18904,28 @@
       <c r="L76" s="300"/>
     </row>
     <row r="77" spans="1:21" ht="13.15">
-      <c r="A77" s="132">
-        <f t="shared" si="14"/>
-        <v>20</v>
+      <c r="A77" s="131">
+        <v>4</v>
       </c>
       <c r="B77" s="119">
-        <f t="shared" si="15"/>
-        <v>2.4223879795495473</v>
+        <f t="shared" si="11"/>
+        <v>3.3565234570966629</v>
       </c>
       <c r="C77" s="119">
-        <f t="shared" si="15"/>
-        <v>3.3022430597940682</v>
+        <f t="shared" si="11"/>
+        <v>4.9629152857757486</v>
       </c>
       <c r="D77" s="119">
-        <f t="shared" si="15"/>
-        <v>5.1940387073717886</v>
+        <f t="shared" si="11"/>
+        <v>6.5708592439364333</v>
       </c>
       <c r="E77" s="119">
-        <f t="shared" si="15"/>
-        <v>9.1193027911918776</v>
+        <f t="shared" si="11"/>
+        <v>8.0182019833798215</v>
       </c>
       <c r="F77" s="119">
-        <f t="shared" si="15"/>
-        <v>12.489503092437536</v>
+        <f t="shared" si="11"/>
+        <v>8.7310536004054615</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18961,29 +18935,28 @@
       <c r="L77" s="300"/>
     </row>
     <row r="78" spans="1:21" ht="13.15">
-      <c r="A78" s="132">
-        <f t="shared" si="14"/>
-        <v>25</v>
+      <c r="A78" s="131">
+        <v>5</v>
       </c>
       <c r="B78" s="119">
-        <f t="shared" si="15"/>
-        <v>2.4214939003080862</v>
+        <f t="shared" si="11"/>
+        <v>3.0317106748245397</v>
       </c>
       <c r="C78" s="119">
-        <f t="shared" si="15"/>
-        <v>3.273898862676381</v>
+        <f t="shared" si="11"/>
+        <v>4.6098242769753801</v>
       </c>
       <c r="D78" s="119">
-        <f t="shared" si="15"/>
-        <v>5.0890349566244382</v>
+        <f t="shared" si="11"/>
+        <v>6.387212123819447</v>
       </c>
       <c r="E78" s="119">
-        <f t="shared" si="15"/>
-        <v>9.3175807051885222</v>
+        <f t="shared" si="11"/>
+        <v>8.1158245854929465</v>
       </c>
       <c r="F78" s="119">
-        <f t="shared" si="15"/>
-        <v>13.425505499883707</v>
+        <f t="shared" si="11"/>
+        <v>9.0051143854475644</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18993,29 +18966,28 @@
       <c r="L78" s="300"/>
     </row>
     <row r="79" spans="1:21" ht="13.15">
-      <c r="A79" s="132">
-        <f t="shared" si="14"/>
-        <v>30</v>
+      <c r="A79" s="131">
+        <v>6</v>
       </c>
       <c r="B79" s="119">
-        <f t="shared" si="15"/>
-        <v>2.4213880042711264</v>
+        <f t="shared" si="11"/>
+        <v>2.8197116560921529</v>
       </c>
       <c r="C79" s="119">
-        <f t="shared" si="15"/>
-        <v>3.2650360354352146</v>
+        <f t="shared" si="11"/>
+        <v>4.3299852490217088</v>
       </c>
       <c r="D79" s="119">
-        <f t="shared" si="15"/>
-        <v>5.0317769354835349</v>
+        <f t="shared" si="11"/>
+        <v>6.2245410150911118</v>
       </c>
       <c r="E79" s="119">
-        <f t="shared" si="15"/>
-        <v>9.4718532685541028</v>
+        <f t="shared" si="11"/>
+        <v>8.2086684588313066</v>
       </c>
       <c r="F79" s="119">
-        <f t="shared" si="15"/>
-        <v>14.267359843146666</v>
+        <f t="shared" si="11"/>
+        <v>9.2734256435307412</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19024,269 +18996,524 @@
       <c r="K79" s="300"/>
       <c r="L79" s="300"/>
     </row>
-    <row r="81" spans="2:12" ht="13.15">
-      <c r="B81" s="153" t="s">
+    <row r="80" spans="1:21" ht="13.15">
+      <c r="A80" s="131">
+        <f t="shared" ref="A80" si="12">A62</f>
+        <v>7</v>
+      </c>
+      <c r="B80" s="119">
+        <f t="shared" si="11"/>
+        <v>2.6813439981782401</v>
+      </c>
+      <c r="C80" s="119">
+        <f t="shared" si="11"/>
+        <v>4.1082014040234593</v>
+      </c>
+      <c r="D80" s="119">
+        <f t="shared" si="11"/>
+        <v>6.0804500563107693</v>
+      </c>
+      <c r="E80" s="119">
+        <f t="shared" si="11"/>
+        <v>8.2969675271810743</v>
+      </c>
+      <c r="F80" s="119">
+        <f t="shared" si="11"/>
+        <v>9.5361079941016875</v>
+      </c>
+      <c r="G80" s="300"/>
+      <c r="H80" s="300"/>
+      <c r="I80" s="300"/>
+      <c r="J80" s="300"/>
+      <c r="K80" s="300"/>
+      <c r="L80" s="300"/>
+    </row>
+    <row r="81" spans="1:12" ht="13.15">
+      <c r="A81" s="131">
+        <v>8</v>
+      </c>
+      <c r="B81" s="119">
+        <f t="shared" si="11"/>
+        <v>2.5910341049010941</v>
+      </c>
+      <c r="C81" s="119">
+        <f t="shared" si="11"/>
+        <v>3.9324286597358022</v>
+      </c>
+      <c r="D81" s="119">
+        <f t="shared" si="11"/>
+        <v>5.9528170392093003</v>
+      </c>
+      <c r="E81" s="119">
+        <f t="shared" si="11"/>
+        <v>8.3809442635137152</v>
+      </c>
+      <c r="F81" s="119">
+        <f t="shared" si="11"/>
+        <v>9.7932795261291847</v>
+      </c>
+      <c r="G81" s="300"/>
+      <c r="H81" s="300"/>
+      <c r="I81" s="300"/>
+      <c r="J81" s="300"/>
+      <c r="K81" s="300"/>
+      <c r="L81" s="300"/>
+    </row>
+    <row r="82" spans="1:12" ht="13.15">
+      <c r="A82" s="131">
+        <f t="shared" ref="A82" si="13">A64</f>
+        <v>9</v>
+      </c>
+      <c r="B82" s="119">
+        <f t="shared" si="11"/>
+        <v>2.5320905848134467</v>
+      </c>
+      <c r="C82" s="119">
+        <f t="shared" si="11"/>
+        <v>3.7931215896709936</v>
+      </c>
+      <c r="D82" s="119">
+        <f t="shared" si="11"/>
+        <v>5.8397621522662719</v>
+      </c>
+      <c r="E82" s="119">
+        <f t="shared" si="11"/>
+        <v>8.4608102505153937</v>
+      </c>
+      <c r="F82" s="119">
+        <f t="shared" si="11"/>
+        <v>10.045055851191067</v>
+      </c>
+      <c r="G82" s="300"/>
+      <c r="H82" s="300"/>
+      <c r="I82" s="300"/>
+      <c r="J82" s="300"/>
+      <c r="K82" s="300"/>
+      <c r="L82" s="300"/>
+    </row>
+    <row r="83" spans="1:12" ht="13.15">
+      <c r="A83" s="131">
+        <f t="shared" ref="A83:A87" si="14">A65</f>
+        <v>10</v>
+      </c>
+      <c r="B83" s="119">
+        <f t="shared" si="11"/>
+        <v>2.4936192896513454</v>
+      </c>
+      <c r="C83" s="119">
+        <f t="shared" si="11"/>
+        <v>3.6827150539552944</v>
+      </c>
+      <c r="D83" s="119">
+        <f t="shared" si="11"/>
+        <v>5.739620294368021</v>
+      </c>
+      <c r="E83" s="119">
+        <f t="shared" si="11"/>
+        <v>8.536766713677828</v>
+      </c>
+      <c r="F83" s="119">
+        <f t="shared" si="11"/>
+        <v>10.29155015544746</v>
+      </c>
+      <c r="G83" s="300"/>
+      <c r="H83" s="300"/>
+      <c r="I83" s="300"/>
+      <c r="J83" s="300"/>
+      <c r="K83" s="300"/>
+      <c r="L83" s="300"/>
+    </row>
+    <row r="84" spans="1:12" ht="13.15">
+      <c r="A84" s="131">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="B84" s="119">
+        <f t="shared" si="11"/>
+        <v>2.4298869686559277</v>
+      </c>
+      <c r="C84" s="119">
+        <f t="shared" si="11"/>
+        <v>3.3928211880891337</v>
+      </c>
+      <c r="D84" s="119">
+        <f t="shared" si="11"/>
+        <v>5.3864917023177803</v>
+      </c>
+      <c r="E84" s="119">
+        <f t="shared" si="11"/>
+        <v>8.8642859004327601</v>
+      </c>
+      <c r="F84" s="119">
+        <f t="shared" si="11"/>
+        <v>11.448589423389221</v>
+      </c>
+      <c r="G84" s="300"/>
+      <c r="H84" s="300"/>
+      <c r="I84" s="300"/>
+      <c r="J84" s="300"/>
+      <c r="K84" s="300"/>
+      <c r="L84" s="300"/>
+    </row>
+    <row r="85" spans="1:12" ht="13.15">
+      <c r="A85" s="132">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="B85" s="119">
+        <f t="shared" si="11"/>
+        <v>2.4223384204884906</v>
+      </c>
+      <c r="C85" s="119">
+        <f t="shared" si="11"/>
+        <v>3.3021754999866357</v>
+      </c>
+      <c r="D85" s="119">
+        <f t="shared" si="11"/>
+        <v>5.1939324437659566</v>
+      </c>
+      <c r="E85" s="119">
+        <f t="shared" si="11"/>
+        <v>9.1191162215392705</v>
+      </c>
+      <c r="F85" s="119">
+        <f t="shared" si="11"/>
+        <v>12.489247572656414</v>
+      </c>
+      <c r="G85" s="300"/>
+      <c r="H85" s="300"/>
+      <c r="I85" s="300"/>
+      <c r="J85" s="300"/>
+      <c r="K85" s="300"/>
+      <c r="L85" s="300"/>
+    </row>
+    <row r="86" spans="1:12" ht="13.15">
+      <c r="A86" s="132">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="B86" s="119">
+        <f t="shared" si="11"/>
+        <v>2.4214443595387842</v>
+      </c>
+      <c r="C86" s="119">
+        <f t="shared" si="11"/>
+        <v>3.2738318827561534</v>
+      </c>
+      <c r="D86" s="119">
+        <f t="shared" si="11"/>
+        <v>5.0889308412654346</v>
+      </c>
+      <c r="E86" s="119">
+        <f t="shared" si="11"/>
+        <v>9.3173900790151052</v>
+      </c>
+      <c r="F86" s="119">
+        <f t="shared" si="11"/>
+        <v>13.42523083065136</v>
+      </c>
+      <c r="G86" s="300"/>
+      <c r="H86" s="300"/>
+      <c r="I86" s="300"/>
+      <c r="J86" s="300"/>
+      <c r="K86" s="300"/>
+      <c r="L86" s="300"/>
+    </row>
+    <row r="87" spans="1:12" ht="13.15">
+      <c r="A87" s="132">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="B87" s="119">
+        <f t="shared" si="11"/>
+        <v>2.4213384656683266</v>
+      </c>
+      <c r="C87" s="119">
+        <f t="shared" si="11"/>
+        <v>3.2649692368374672</v>
+      </c>
+      <c r="D87" s="119">
+        <f t="shared" si="11"/>
+        <v>5.031673991552803</v>
+      </c>
+      <c r="E87" s="119">
+        <f t="shared" si="11"/>
+        <v>9.4716594861549073</v>
+      </c>
+      <c r="F87" s="119">
+        <f t="shared" si="11"/>
+        <v>14.267067950616006</v>
+      </c>
+      <c r="G87" s="300"/>
+      <c r="H87" s="300"/>
+      <c r="I87" s="300"/>
+      <c r="J87" s="300"/>
+      <c r="K87" s="300"/>
+      <c r="L87" s="300"/>
+    </row>
+    <row r="89" spans="1:12" ht="13.15">
+      <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="C81" s="153" t="s">
+      <c r="C89" s="153" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="153" t="s">
+      <c r="D89" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="E81" s="154" t="s">
+      <c r="E89" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="F81" s="154" t="s">
-        <v>461</v>
-      </c>
-      <c r="G81" s="327"/>
-      <c r="H81" s="327"/>
-      <c r="I81" s="327"/>
-      <c r="J81" s="327"/>
-      <c r="K81" s="327"/>
-      <c r="L81" s="327"/>
-    </row>
-    <row r="82" spans="2:12">
-      <c r="B82" s="120" t="str">
+      <c r="F89" s="154" t="s">
+        <v>460</v>
+      </c>
+      <c r="G89" s="327"/>
+      <c r="H89" s="327"/>
+      <c r="I89" s="327"/>
+      <c r="J89" s="327"/>
+      <c r="K89" s="327"/>
+      <c r="L89" s="327"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C82" s="130">
+      <c r="C90" s="130">
         <f>Scenarios!C29</f>
         <v>0.05</v>
       </c>
-      <c r="D82" s="133">
+      <c r="D90" s="133">
         <f>Scenarios!D29</f>
         <v>5</v>
       </c>
-      <c r="E82" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>9.005298622715932</v>
-      </c>
-      <c r="F82" s="130">
+      <c r="E90" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
+        <v>9.0051143854475644</v>
+      </c>
+      <c r="F90" s="130">
         <f>Scenarios!F29</f>
         <v>0.05</v>
       </c>
-      <c r="G82" s="301"/>
-      <c r="H82" s="301"/>
-      <c r="I82" s="301"/>
-      <c r="J82" s="301"/>
-      <c r="K82" s="301"/>
-      <c r="L82" s="301"/>
-    </row>
-    <row r="83" spans="2:12">
-      <c r="B83" s="120" t="str">
+      <c r="G90" s="301"/>
+      <c r="H90" s="301"/>
+      <c r="I90" s="301"/>
+      <c r="J90" s="301"/>
+      <c r="K90" s="301"/>
+      <c r="L90" s="301"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
       </c>
-      <c r="C83" s="130">
+      <c r="C91" s="130">
         <f>Scenarios!C22</f>
         <v>0.02</v>
       </c>
-      <c r="D83" s="133">
+      <c r="D91" s="133">
         <f>Scenarios!D22</f>
         <v>5</v>
       </c>
-      <c r="E83" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>8.1159906286200165</v>
-      </c>
-      <c r="F83" s="130">
-        <f>Scenarios!F22*(1-F$82-F$86)</f>
+      <c r="E91" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
+        <v>8.1158245854929465</v>
+      </c>
+      <c r="F91" s="130">
+        <f>Scenarios!F22*(1-F$90-F$94)</f>
         <v>0.16999999999999996</v>
       </c>
-      <c r="G83" s="301"/>
-      <c r="H83" s="301"/>
-      <c r="I83" s="301"/>
-      <c r="J83" s="301"/>
-      <c r="K83" s="301"/>
-      <c r="L83" s="301"/>
-    </row>
-    <row r="84" spans="2:12">
-      <c r="B84" s="120" t="str">
+      <c r="G91" s="301"/>
+      <c r="H91" s="301"/>
+      <c r="I91" s="301"/>
+      <c r="J91" s="301"/>
+      <c r="K91" s="301"/>
+      <c r="L91" s="301"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
       </c>
-      <c r="C84" s="130">
+      <c r="C92" s="130">
         <f>Scenarios!C23</f>
         <v>-0.05</v>
       </c>
-      <c r="D84" s="133">
+      <c r="D92" s="133">
         <f>Scenarios!D23</f>
         <v>5</v>
       </c>
-      <c r="E84" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>6.3873428009506652</v>
-      </c>
-      <c r="F84" s="130">
-        <f>Scenarios!F23*(1-F$82-F$86)</f>
+      <c r="E92" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
+        <v>6.387212123819447</v>
+      </c>
+      <c r="F92" s="130">
+        <f>Scenarios!F23*(1-F$90-F$94)</f>
         <v>0.46750000000000003</v>
       </c>
-      <c r="G84" s="301"/>
-      <c r="H84" s="301"/>
-      <c r="I84" s="301"/>
-      <c r="J84" s="301"/>
-      <c r="K84" s="301"/>
-      <c r="L84" s="301"/>
-    </row>
-    <row r="85" spans="2:12">
-      <c r="B85" s="120" t="str">
+      <c r="G92" s="301"/>
+      <c r="H92" s="301"/>
+      <c r="I92" s="301"/>
+      <c r="J92" s="301"/>
+      <c r="K92" s="301"/>
+      <c r="L92" s="301"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C85" s="130">
+      <c r="C93" s="130">
         <f>Scenarios!C24</f>
         <v>-0.15</v>
       </c>
-      <c r="D85" s="133">
+      <c r="D93" s="133">
         <f>Scenarios!D24</f>
         <v>5</v>
       </c>
-      <c r="E85" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>4.6099185902062949</v>
-      </c>
-      <c r="F85" s="130">
-        <f>Scenarios!F24*(1-F$82-F$86)</f>
+      <c r="E93" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
+        <v>4.6098242769753801</v>
+      </c>
+      <c r="F93" s="130">
+        <f>Scenarios!F24*(1-F$90-F$94)</f>
         <v>0.21249999999999999</v>
       </c>
-      <c r="G85" s="301"/>
-      <c r="H85" s="301"/>
-      <c r="I85" s="301"/>
-      <c r="J85" s="301"/>
-      <c r="K85" s="301"/>
-      <c r="L85" s="301"/>
-    </row>
-    <row r="86" spans="2:12">
-      <c r="B86" s="120" t="str">
+      <c r="G93" s="301"/>
+      <c r="H93" s="301"/>
+      <c r="I93" s="301"/>
+      <c r="J93" s="301"/>
+      <c r="K93" s="301"/>
+      <c r="L93" s="301"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C86" s="130">
+      <c r="C94" s="130">
         <f>Scenarios!C30</f>
         <v>-0.3</v>
       </c>
-      <c r="D86" s="133">
+      <c r="D94" s="133">
         <f>Scenarios!D30</f>
         <v>5</v>
       </c>
-      <c r="E86" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>3.0317727011430633</v>
-      </c>
-      <c r="F86" s="130">
+      <c r="E94" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
+        <v>3.0317106748245397</v>
+      </c>
+      <c r="F94" s="130">
         <f>Scenarios!F30</f>
         <v>0.1</v>
       </c>
-      <c r="G86" s="301"/>
-      <c r="H86" s="301"/>
-      <c r="I86" s="301"/>
-      <c r="J86" s="301"/>
-      <c r="K86" s="301"/>
-      <c r="L86" s="301"/>
-    </row>
-    <row r="87" spans="2:12">
-      <c r="B87" s="141"/>
-      <c r="C87" s="141"/>
-      <c r="D87" s="141"/>
-      <c r="E87" s="141"/>
-      <c r="F87" s="142"/>
-      <c r="G87" s="142"/>
-      <c r="H87" s="142"/>
-      <c r="I87" s="142"/>
-      <c r="J87" s="142"/>
-      <c r="K87" s="142"/>
-      <c r="L87" s="142"/>
-    </row>
-    <row r="97" spans="3:21">
-      <c r="C97" s="112"/>
-    </row>
-    <row r="98" spans="3:21">
-      <c r="C98" s="112"/>
-    </row>
-    <row r="99" spans="3:21">
-      <c r="C99" s="112"/>
-    </row>
-    <row r="106" spans="3:21">
-      <c r="C106" s="279"/>
-      <c r="M106" s="279"/>
-      <c r="N106" s="279"/>
-      <c r="O106" s="279"/>
-      <c r="P106" s="279"/>
-      <c r="Q106" s="279"/>
-      <c r="R106" s="279"/>
-      <c r="S106" s="279"/>
-      <c r="T106" s="279"/>
-      <c r="U106" s="279"/>
-    </row>
-    <row r="107" spans="3:21">
-      <c r="C107" s="279"/>
-      <c r="M107" s="279"/>
-      <c r="N107" s="279"/>
-      <c r="O107" s="279"/>
-      <c r="P107" s="279"/>
-      <c r="Q107" s="279"/>
-      <c r="R107" s="279"/>
-      <c r="S107" s="279"/>
-      <c r="T107" s="279"/>
-      <c r="U107" s="279"/>
-    </row>
-    <row r="108" spans="3:21">
-      <c r="C108" s="279"/>
-      <c r="M108" s="279"/>
-      <c r="N108" s="279"/>
-      <c r="O108" s="279"/>
-      <c r="P108" s="279"/>
-      <c r="Q108" s="279"/>
-      <c r="R108" s="279"/>
-      <c r="S108" s="279"/>
-      <c r="T108" s="279"/>
-      <c r="U108" s="279"/>
-    </row>
-    <row r="109" spans="3:21">
-      <c r="C109" s="279"/>
-      <c r="M109" s="279"/>
-      <c r="N109" s="279"/>
-      <c r="O109" s="279"/>
-      <c r="P109" s="279"/>
-      <c r="Q109" s="279"/>
-      <c r="R109" s="279"/>
-      <c r="S109" s="279"/>
-      <c r="T109" s="279"/>
-      <c r="U109" s="279"/>
-    </row>
-    <row r="110" spans="3:21">
-      <c r="C110" s="279"/>
-      <c r="M110" s="279"/>
-      <c r="N110" s="279"/>
-      <c r="O110" s="279"/>
-      <c r="P110" s="279"/>
-      <c r="Q110" s="279"/>
-      <c r="R110" s="279"/>
-      <c r="S110" s="279"/>
-      <c r="T110" s="279"/>
-      <c r="U110" s="279"/>
+      <c r="G94" s="301"/>
+      <c r="H94" s="301"/>
+      <c r="I94" s="301"/>
+      <c r="J94" s="301"/>
+      <c r="K94" s="301"/>
+      <c r="L94" s="301"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="B95" s="141"/>
+      <c r="C95" s="141"/>
+      <c r="D95" s="141"/>
+      <c r="E95" s="141"/>
+      <c r="F95" s="142"/>
+      <c r="G95" s="142"/>
+      <c r="H95" s="142"/>
+      <c r="I95" s="142"/>
+      <c r="J95" s="142"/>
+      <c r="K95" s="142"/>
+      <c r="L95" s="142"/>
+    </row>
+    <row r="105" spans="3:3">
+      <c r="C105" s="112"/>
+    </row>
+    <row r="106" spans="3:3">
+      <c r="C106" s="112"/>
+    </row>
+    <row r="107" spans="3:3">
+      <c r="C107" s="112"/>
+    </row>
+    <row r="114" spans="3:21">
+      <c r="C114" s="279"/>
+      <c r="M114" s="279"/>
+      <c r="N114" s="279"/>
+      <c r="O114" s="279"/>
+      <c r="P114" s="279"/>
+      <c r="Q114" s="279"/>
+      <c r="R114" s="279"/>
+      <c r="S114" s="279"/>
+      <c r="T114" s="279"/>
+      <c r="U114" s="279"/>
+    </row>
+    <row r="115" spans="3:21">
+      <c r="C115" s="279"/>
+      <c r="M115" s="279"/>
+      <c r="N115" s="279"/>
+      <c r="O115" s="279"/>
+      <c r="P115" s="279"/>
+      <c r="Q115" s="279"/>
+      <c r="R115" s="279"/>
+      <c r="S115" s="279"/>
+      <c r="T115" s="279"/>
+      <c r="U115" s="279"/>
+    </row>
+    <row r="116" spans="3:21">
+      <c r="C116" s="279"/>
+      <c r="M116" s="279"/>
+      <c r="N116" s="279"/>
+      <c r="O116" s="279"/>
+      <c r="P116" s="279"/>
+      <c r="Q116" s="279"/>
+      <c r="R116" s="279"/>
+      <c r="S116" s="279"/>
+      <c r="T116" s="279"/>
+      <c r="U116" s="279"/>
+    </row>
+    <row r="117" spans="3:21">
+      <c r="C117" s="279"/>
+      <c r="M117" s="279"/>
+      <c r="N117" s="279"/>
+      <c r="O117" s="279"/>
+      <c r="P117" s="279"/>
+      <c r="Q117" s="279"/>
+      <c r="R117" s="279"/>
+      <c r="S117" s="279"/>
+      <c r="T117" s="279"/>
+      <c r="U117" s="279"/>
+    </row>
+    <row r="118" spans="3:21">
+      <c r="C118" s="279"/>
+      <c r="M118" s="279"/>
+      <c r="N118" s="279"/>
+      <c r="O118" s="279"/>
+      <c r="P118" s="279"/>
+      <c r="Q118" s="279"/>
+      <c r="R118" s="279"/>
+      <c r="S118" s="279"/>
+      <c r="T118" s="279"/>
+      <c r="U118" s="279"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J52:K52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C21:L50">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>0</formula>
+  <conditionalFormatting sqref="B74:L87">
+    <cfRule type="expression" dxfId="1" priority="21">
+      <formula>ISNUMBER(MATCH(B74, $E$90:$E$94, 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70:L79">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>ISNUMBER(MATCH(C70, $E$82:$E$86, 0))</formula>
+  <conditionalFormatting sqref="C21:L50">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
-      <formula1>$A$56:$A$65</formula1>
+      <formula1>$A$56:$A$69</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19319,7 +19546,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19461,7 +19688,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19485,7 +19712,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="455" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F18" s="323"/>
     </row>
@@ -19495,35 +19722,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E20" s="323"/>
       <c r="F20" s="323"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C21" s="153" t="s">
         <v>379</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="306" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C22" s="328">
         <v>0.02</v>
@@ -19533,8 +19760,8 @@
         <v>5</v>
       </c>
       <c r="E22" s="330">
-        <f>DCF!E83</f>
-        <v>8.1159906286200165</v>
+        <f>DCF!E91</f>
+        <v>8.1158245854929465</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19547,7 +19774,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="306" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="328">
         <v>-0.05</v>
@@ -19557,8 +19784,8 @@
         <v>5</v>
       </c>
       <c r="E23" s="330">
-        <f>DCF!E84</f>
-        <v>6.3873428009506652</v>
+        <f>DCF!E92</f>
+        <v>6.387212123819447</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19570,7 +19797,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="306" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C24" s="328">
         <v>-0.15</v>
@@ -19580,8 +19807,8 @@
         <v>5</v>
       </c>
       <c r="E24" s="330">
-        <f>DCF!E85</f>
-        <v>4.6099185902062949</v>
+        <f>DCF!E93</f>
+        <v>4.6098242769753801</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19593,11 +19820,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.2887163137984432</v>
+        <v>6.2885876544431305</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19607,33 +19834,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C28" s="153" t="s">
         <v>379</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="306" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C29" s="328">
         <v>0.05</v>
@@ -19643,8 +19870,8 @@
         <v>5</v>
       </c>
       <c r="E29" s="330">
-        <f>DCF!E82</f>
-        <v>9.005298622715932</v>
+        <f>DCF!E90</f>
+        <v>9.0051143854475644</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19656,7 +19883,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="319" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C30" s="328">
         <v>-0.3</v>
@@ -19666,8 +19893,8 @@
         <v>5</v>
       </c>
       <c r="E30" s="330">
-        <f>DCF!E86</f>
-        <v>3.0317727011430633</v>
+        <f>DCF!E94</f>
+        <v>3.0317106748245397</v>
       </c>
       <c r="F30" s="331">
         <v>0.1</v>
@@ -19683,12 +19910,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19699,7 +19926,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19712,62 +19939,62 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22027668345247436</v>
+        <v>0.21151245374364994</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5749661401148591</v>
+        <v>7.5748111656794634</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-3.538882915572962E-2</v>
+        <v>-3.5388128352455681E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.0988510679787797</v>
+        <v>6.0987262930314925</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F36" s="335" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19855,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>8.0771719583826496</v>
+        <v>8.0770067094375442</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19961,13 +20188,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E60" s="417"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -19980,10 +20207,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -19996,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.8105304460731713</v>
+        <v>2.8104729460974625</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.252988557176598</v>
+        <v>3.2529310572008892</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20008,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46662272599900179</v>
+        <v>0.466621241730795</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20021,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.5228020609263724</v>
+        <v>3.5227299887546542</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.0315502153760354</v>
+        <v>4.0314781432043176</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20033,12 +20260,12 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33896562312479428</v>
+        <v>0.33896391648027346</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -20051,10 +20278,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -20067,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.3714148884232191</v>
+        <v>4.371325454682963</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>4.9547823242751843</v>
+        <v>4.9546928905349281</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20079,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18758758509621243</v>
+        <v>0.18758562813414925</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20092,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>4.9437457282738846</v>
+        <v>4.9436445853527387</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.5754180582043196</v>
+        <v>5.5753169152831736</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20104,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.5824855196526606E-2</v>
+        <v>8.582273619105929E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20148,7 +20375,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="440" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F3" s="441">
         <f>Thesis!F3</f>
@@ -20157,7 +20384,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="427" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C4" s="428" t="str">
         <f>Thesis!C4</f>
@@ -20165,7 +20392,7 @@
       </c>
       <c r="D4" s="353"/>
       <c r="E4" s="439" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F4" s="442" t="str">
         <f>Thesis!F4</f>
@@ -20181,7 +20408,7 @@
         <v>6186.HK</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F5" s="444" t="str">
         <f>Thesis!F5</f>
@@ -20215,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20233,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>34901.219060399999</v>
+        <v>35626.439196719999</v>
       </c>
       <c r="D10" s="347" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22027668345247436</v>
+        <v>0.21151245374364994</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20248,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
-        <v>501</v>
-      </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="B12" s="467" t="s">
+        <v>500</v>
+      </c>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20292,12 +20519,12 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.09146385</v>
+        <v>1.0914415199999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="347" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C17" s="429">
         <f>Terminal_Growth</f>
@@ -20318,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.0988510679787797</v>
+        <v>6.0987262930314925</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20350,7 +20577,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="351" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C21" s="365" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -20370,10 +20597,10 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.252988557176598</v>
+        <v>3.2529310572008892</v>
       </c>
       <c r="D22" s="369" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
@@ -20386,10 +20613,10 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.0315502153760354</v>
+        <v>4.0314781432043176</v>
       </c>
       <c r="D23" s="369" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
@@ -20402,10 +20629,10 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>4.9547823242751843</v>
+        <v>4.9546928905349281</v>
       </c>
       <c r="D24" s="369" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E24" s="372">
         <f>Thesis!E24</f>
@@ -20418,10 +20645,10 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.5754180582043196</v>
+        <v>5.5753169152831736</v>
       </c>
       <c r="D25" s="369" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E25" s="372">
         <f>Thesis!E25</f>
@@ -20439,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
+        <v>501</v>
+      </c>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
-        <v>503</v>
-      </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20467,7 +20694,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="466" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C33" s="466"/>
       <c r="D33" s="466"/>
@@ -20493,7 +20720,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="466" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C36" s="466"/>
       <c r="D36" s="466"/>
@@ -20528,7 +20755,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="466" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C40" s="466"/>
       <c r="D40" s="466"/>
@@ -20550,7 +20777,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="466" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C43" s="466"/>
       <c r="D43" s="466"/>
@@ -20602,7 +20829,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="347" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20620,7 +20847,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="466" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C51" s="466"/>
       <c r="D51" s="466"/>
@@ -20629,7 +20856,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="376" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
@@ -20642,12 +20869,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="466" t="s">
-        <v>510</v>
-      </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+        <v>509</v>
+      </c>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20663,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
+        <v>510</v>
+      </c>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
-        <v>512</v>
-      </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20712,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.11144588455082099</v>
+        <v>0.10917503240400375</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20722,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.2805194805194794E-2</v>
+        <v>6.1526717557251906E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -20800,7 +21027,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="349" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B71" s="349"/>
       <c r="C71" s="349"/>
@@ -20813,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
-        <v>513</v>
-      </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="B73" s="467" t="s">
+        <v>512</v>
+      </c>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
-        <v>483</v>
-      </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="B74" s="468" t="s">
+        <v>482</v>
+      </c>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20836,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
-        <v>514</v>
-      </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="B77" s="467" t="s">
+        <v>513</v>
+      </c>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20863,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10174026848841813</v>
+        <v>-0.10173818700839903</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -20890,7 +21117,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="347" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20908,7 +21135,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C85" s="394">
         <f>BS!C66</f>
@@ -20925,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7580299660363992</v>
+        <v>1.7579939989183475</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -20934,7 +21161,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="347" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20956,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1567676466030086E-4</v>
+        <v>5.1566621455169685E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -20965,11 +21192,11 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="376" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6568053743126412</v>
+        <v>1.6567714781245002</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -20978,7 +21205,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="349" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B94" s="349"/>
       <c r="C94" s="349"/>
@@ -20991,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
-        <v>517</v>
-      </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="B96" s="467" t="s">
+        <v>516</v>
+      </c>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
-        <v>518</v>
-      </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="B97" s="468" t="s">
+        <v>517</v>
+      </c>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
-        <v>519</v>
-      </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="B98" s="468" t="s">
+        <v>518</v>
+      </c>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21061,7 +21288,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="389"/>
       <c r="B104" s="376" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C104" s="372">
         <v>0</v>
@@ -21080,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
-        <v>520</v>
-      </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="B107" s="467" t="s">
+        <v>519</v>
+      </c>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
-        <v>539</v>
-      </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="B108" s="467" t="s">
+        <v>538</v>
+      </c>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21104,17 +21331,17 @@
     <row r="110" spans="1:6">
       <c r="A110" s="389"/>
       <c r="B110" s="373" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="389"/>
       <c r="B111" s="379" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2402809457694648</v>
+        <v>1.2402555711558032</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5749661401148591</v>
+        <v>7.5748111656794634</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21140,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
-        <v>521</v>
-      </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="B114" s="467" t="s">
+        <v>520</v>
+      </c>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21154,7 +21381,7 @@
     <row r="116" spans="1:6">
       <c r="A116" s="389"/>
       <c r="B116" s="373" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -21178,118 +21405,118 @@
     <row r="118" spans="1:6">
       <c r="A118" s="389"/>
       <c r="B118" s="399" t="str">
-        <f>DCF!B82</f>
+        <f>DCF!B90</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C118" s="400">
-        <f>DCF!C82</f>
+        <f>DCF!C90</f>
         <v>0.05</v>
       </c>
       <c r="D118" s="401">
-        <f>DCF!D82</f>
+        <f>DCF!D90</f>
         <v>5</v>
       </c>
       <c r="E118" s="402" t="str">
-        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
         <v>9.01 HKD</v>
       </c>
       <c r="F118" s="403">
-        <f>DCF!F82</f>
+        <f>DCF!F90</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="389"/>
       <c r="B119" s="404" t="str">
-        <f>DCF!B83</f>
+        <f>DCF!B91</f>
         <v>Optimistic</v>
       </c>
       <c r="C119" s="405">
-        <f>DCF!C83</f>
+        <f>DCF!C91</f>
         <v>0.02</v>
       </c>
       <c r="D119" s="406">
-        <f>DCF!D83</f>
+        <f>DCF!D91</f>
         <v>5</v>
       </c>
       <c r="E119" s="402" t="str">
-        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
         <v>8.12 HKD</v>
       </c>
       <c r="F119" s="407">
-        <f>DCF!F83</f>
+        <f>DCF!F91</f>
         <v>0.16999999999999996</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="B120" s="404" t="str">
-        <f>DCF!B84</f>
+        <f>DCF!B92</f>
         <v>Base</v>
       </c>
       <c r="C120" s="405">
-        <f>DCF!C84</f>
+        <f>DCF!C92</f>
         <v>-0.05</v>
       </c>
       <c r="D120" s="406">
-        <f>DCF!D84</f>
+        <f>DCF!D92</f>
         <v>5</v>
       </c>
       <c r="E120" s="402" t="str">
-        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
         <v>6.39 HKD</v>
       </c>
       <c r="F120" s="407">
-        <f>DCF!F84</f>
+        <f>DCF!F92</f>
         <v>0.46750000000000003</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="404" t="str">
-        <f>DCF!B85</f>
+        <f>DCF!B93</f>
         <v>Pessimistic</v>
       </c>
       <c r="C121" s="405">
-        <f>DCF!C85</f>
+        <f>DCF!C93</f>
         <v>-0.15</v>
       </c>
       <c r="D121" s="406">
-        <f>DCF!D85</f>
+        <f>DCF!D93</f>
         <v>5</v>
       </c>
       <c r="E121" s="402" t="str">
-        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
         <v>4.61 HKD</v>
       </c>
       <c r="F121" s="407">
-        <f>DCF!F85</f>
+        <f>DCF!F93</f>
         <v>0.21249999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="404" t="str">
-        <f>DCF!B86</f>
+        <f>DCF!B94</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C122" s="405">
-        <f>DCF!C86</f>
+        <f>DCF!C94</f>
         <v>-0.3</v>
       </c>
       <c r="D122" s="406">
-        <f>DCF!D86</f>
+        <f>DCF!D94</f>
         <v>5</v>
       </c>
       <c r="E122" s="402" t="str">
-        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
         <v>3.03 HKD</v>
       </c>
       <c r="F122" s="407">
-        <f>DCF!F86</f>
+        <f>DCF!F94</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="466" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C124" s="466"/>
       <c r="D124" s="466"/>
@@ -21302,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.0988510679787797</v>
+        <v>6.0987262930314925</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21310,17 +21537,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
-        <v>523</v>
-      </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="B127" s="471" t="s">
+        <v>522</v>
+      </c>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B129" s="349"/>
       <c r="C129" s="349"/>
@@ -21329,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
+        <v>523</v>
+      </c>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
-        <v>525</v>
-      </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21375,28 +21602,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="373" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C138" s="411"/>
       <c r="D138" s="411"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="344" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C139" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E139" s="345" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="345" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21409,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.8105304460731713</v>
+        <v>2.8104729460974625</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.252988557176598</v>
+        <v>3.2529310572008892</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21430,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.5228020609263724</v>
+        <v>3.5227299887546542</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.0315502153760354</v>
+        <v>4.0314781432043176</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21443,21 +21670,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="344" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C143" s="344" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E143" s="345" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="345" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21470,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.3714148884232191</v>
+        <v>4.371325454682963</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>4.9547823242751843</v>
+        <v>4.9546928905349281</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21491,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>4.9437457282738846</v>
+        <v>4.9436445853527387</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.5754180582043196</v>
+        <v>5.5753169152831736</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21504,7 +21731,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="349" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="349"/>
       <c r="C147" s="349"/>
@@ -21513,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
-        <v>526</v>
-      </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="B149" s="473" t="s">
+        <v>525</v>
+      </c>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21527,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
-        <v>527</v>
-      </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="B152" s="469" t="s">
+        <v>526</v>
+      </c>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21552,12 +21779,12 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="347" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="466" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C158" s="466"/>
       <c r="D158" s="466"/>
@@ -21566,30 +21793,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="347" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21609,12 +21836,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21629,15 +21859,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB81A6A-11CE-4EEB-9C79-BABAF287E5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF296DA2-F323-4FFC-8BFC-605C877BCFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.21151245374364994</v>
+        <v>0.22545855615291369</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.0987262930314925</v>
+        <v>6.3312611801486041</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.2529310572008892</v>
+        <v>3.3600899913562405</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.0314781432043176</v>
+        <v>4.1657943234885693</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>4.9546928905349281</v>
+        <v>5.1213646876146415</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.5753169152831736</v>
+        <v>5.7638103449548144</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6337,7 +6337,7 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (5yrs)</v>
+        <v>Snowball Scenario (3yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>9.01 HKD</v>
+        <v>8.45 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,13 +6353,13 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.1163100162497374E-2</v>
+        <v>-6.0246887493633453E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (5yrs)</v>
+        <v>Optimistic (3yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
@@ -6367,21 +6367,21 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>8.12 HKD</v>
+        <v>7.92 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
-        <v>0.16999999999999996</v>
+        <v>0.15999999999999995</v>
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-5.8053859155239369E-2</v>
+        <v>-3.8827847485508639E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (5yrs)</v>
+        <v>Base (3yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
@@ -6389,21 +6389,21 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.39 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
-        <v>0.46750000000000003</v>
+        <v>0.44</v>
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.3144642877135413E-2</v>
+        <v>1.3999452867582288E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (5yrs)</v>
+        <v>Pessimistic (3yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
@@ -6411,21 +6411,21 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>4.61 HKD</v>
+        <v>5.41 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
-        <v>0.21249999999999999</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.14583449254984052</v>
+        <v>9.6435164014073704E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (5yrs)</v>
+        <v>Devil's advocate (3yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6433,25 +6433,25 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.03 HKD</v>
+        <v>3.85 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.32718693436786978</v>
+        <v>0.23384033458224196</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.0987262930314925</v>
+        <v>6.3312611801486041</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.8104729460974625</v>
+        <v>2.9176318802528138</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.2529310572008892</v>
+        <v>3.3600899913562405</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.5227299887546542</v>
+        <v>3.6570461690389062</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.0314781432043176</v>
+        <v>4.1657943234885693</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.371325454682963</v>
+        <v>4.5379972517626763</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>4.9546928905349281</v>
+        <v>5.1213646876146415</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>4.9436445853527387</v>
+        <v>5.1321380150243794</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.5753169152831736</v>
+        <v>5.7638103449548144</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="312" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="F15" s="314">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>432</v>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>8.0770067094375442</v>
+        <v>7.8915077316668718</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16801,30 +16801,30 @@
     <row r="24" spans="1:21">
       <c r="A24" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B24" s="117">
         <v>4</v>
       </c>
       <c r="C24" s="281">
         <f t="shared" si="5"/>
-        <v>22336989.010079876</v>
+        <v>0</v>
       </c>
       <c r="D24" s="303">
         <f t="shared" si="1"/>
-        <v>1.8613012126595999E-2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="303">
         <f t="shared" si="6"/>
-        <v>0.68269686315429268</v>
+        <v>0</v>
       </c>
       <c r="F24" s="281">
         <f t="shared" si="7"/>
-        <v>-1809972.6718289186</v>
+        <v>0</v>
       </c>
       <c r="G24" s="281">
         <f t="shared" si="8"/>
-        <v>5238834.2176195439</v>
+        <v>0</v>
       </c>
       <c r="H24" s="303">
         <f t="shared" si="2"/>
@@ -16832,19 +16832,19 @@
       </c>
       <c r="I24" s="281">
         <f t="shared" si="9"/>
-        <v>3838700.2893017023</v>
+        <v>0</v>
       </c>
       <c r="J24" s="303">
         <f t="shared" si="10"/>
-        <v>1.8756720358476642E-2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
-        <v>0.75580680282513402</v>
+        <v>0</v>
       </c>
       <c r="L24" s="281">
         <f t="shared" si="4"/>
-        <v>2901315.7926610368</v>
+        <v>0</v>
       </c>
       <c r="N24" s="279"/>
       <c r="O24" s="279"/>
@@ -16858,30 +16858,30 @@
     <row r="25" spans="1:21">
       <c r="A25" s="306" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B25" s="117">
         <v>5</v>
       </c>
       <c r="C25" s="281">
         <f t="shared" si="5"/>
-        <v>22752747.657396134</v>
+        <v>0</v>
       </c>
       <c r="D25" s="303">
         <f t="shared" si="1"/>
-        <v>1.8613012126595999E-2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="303">
         <f t="shared" si="6"/>
-        <v>0.68269686315429268</v>
+        <v>0</v>
       </c>
       <c r="F25" s="281">
         <f t="shared" si="7"/>
-        <v>-1843661.7151184776</v>
+        <v>0</v>
       </c>
       <c r="G25" s="281">
         <f t="shared" si="8"/>
-        <v>5337066.6972941626</v>
+        <v>0</v>
       </c>
       <c r="H25" s="303">
         <f t="shared" si="2"/>
@@ -16889,19 +16889,19 @@
       </c>
       <c r="I25" s="281">
         <f t="shared" si="9"/>
-        <v>3910691.5604764721</v>
+        <v>0</v>
       </c>
       <c r="J25" s="303">
         <f t="shared" si="10"/>
-        <v>1.8754074491151629E-2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
-        <v>0.70471496766912267</v>
+        <v>0</v>
       </c>
       <c r="L25" s="281">
         <f t="shared" si="4"/>
-        <v>2755922.8766050879</v>
+        <v>0</v>
       </c>
       <c r="N25" s="279"/>
       <c r="O25" s="279"/>
@@ -18199,11 +18199,11 @@
       </c>
       <c r="B51" s="320">
         <f>C15+1</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51" s="281">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>22752747.657396134</v>
+        <v>21928827.47830417</v>
       </c>
       <c r="D51" s="305">
         <f>Terminal_Growth</f>
@@ -18215,11 +18215,11 @@
       </c>
       <c r="F51" s="281">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-1843661.7151184776</v>
+        <v>-1776899.2250061403</v>
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>5337066.6972941626</v>
+        <v>5142396.7300701421</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>53940573.247951344</v>
+        <v>51972751.825022414</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18235,11 +18235,11 @@
       </c>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.70471496766912267</v>
+        <v>0.81060279602995633</v>
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>38012729.332483977</v>
+        <v>42129257.946734183</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18252,7 +18252,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>53324935.238620415</v>
+        <v>51784225.183604501</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18276,7 +18276,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>53324935.238620415</v>
+        <v>51784225.183604501</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -19285,11 +19285,11 @@
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>9.0051143854475644</v>
+        <v>8.4511200842553098</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19313,15 +19313,15 @@
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>8.1158245854929465</v>
+        <v>7.9155546885108734</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
-        <v>0.16999999999999996</v>
+        <v>0.15999999999999995</v>
       </c>
       <c r="G91" s="301"/>
       <c r="H91" s="301"/>
@@ -19341,15 +19341,15 @@
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.387212123819447</v>
+        <v>6.7781871769106132</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
-        <v>0.46750000000000003</v>
+        <v>0.44</v>
       </c>
       <c r="G92" s="301"/>
       <c r="H92" s="301"/>
@@ -19369,15 +19369,15 @@
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>4.6098242769753801</v>
+        <v>5.4084330586444507</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
-        <v>0.21249999999999999</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="G93" s="301"/>
       <c r="H93" s="301"/>
@@ -19397,15 +19397,15 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.0317106748245397</v>
+        <v>3.8541830413635938</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G94" s="301"/>
       <c r="H94" s="301"/>
@@ -19709,7 +19709,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="455" t="s">
         <v>547</v>
@@ -19757,11 +19757,11 @@
       </c>
       <c r="D22" s="329">
         <f>C18</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>8.1158245854929465</v>
+        <v>7.9155546885108734</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19769,7 +19769,7 @@
       </c>
       <c r="G22" s="332">
         <f>F22*(1-F$29-F$30)</f>
-        <v>0.16999999999999996</v>
+        <v>0.15999999999999995</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -19781,18 +19781,18 @@
       </c>
       <c r="D23" s="329">
         <f>C18</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.387212123819447</v>
+        <v>6.7781871769106132</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
       </c>
       <c r="G23" s="332">
         <f t="shared" ref="G23:G24" si="0">F23*(1-F$29-F$30)</f>
-        <v>0.46750000000000003</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -19804,18 +19804,18 @@
       </c>
       <c r="D24" s="329">
         <f>C18</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>4.6098242769753801</v>
+        <v>5.4084330586444507</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
       </c>
       <c r="G24" s="332">
         <f t="shared" si="0"/>
-        <v>0.21249999999999999</v>
+        <v>0.19999999999999998</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.2885876544431305</v>
+        <v>6.663222149664124</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19867,11 +19867,11 @@
       </c>
       <c r="D29" s="329">
         <f>C18</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>9.0051143854475644</v>
+        <v>8.4511200842553098</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19890,18 +19890,18 @@
       </c>
       <c r="D30" s="329">
         <f>C18</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.0317106748245397</v>
+        <v>3.8541830413635938</v>
       </c>
       <c r="F30" s="331">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G30" s="332">
         <f>F30</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21151245374364994</v>
+        <v>0.22545855615291369</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-3.5388128352455681E-2</v>
+        <v>-2.4144218546244385E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.0987262930314925</v>
+        <v>6.3312611801486041</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20057,7 +20057,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>8.0770067094375442</v>
+        <v>7.8915077316668718</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.3050223543015611</v>
+        <v>0.29381947754327764</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.8104729460974625</v>
+        <v>2.9176318802528138</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.2529310572008892</v>
+        <v>3.3600899913562405</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.466621241730795</v>
+        <v>0.46928583488363151</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.5227299887546542</v>
+        <v>3.6570461690389062</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.0314781432043176</v>
+        <v>4.1657943234885693</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.33896391648027346</v>
+        <v>0.34202772481567534</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.371325454682963</v>
+        <v>4.5379972517626763</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>4.9546928905349281</v>
+        <v>5.1213646876146415</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.18758562813414925</v>
+        <v>0.19109881240210735</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>4.9436445853527387</v>
+        <v>5.1321380150243794</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.5753169152831736</v>
+        <v>5.7638103449548144</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.582273619105929E-2</v>
+        <v>8.9626824584808973E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.21151245374364994</v>
+        <v>0.22545855615291369</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.0987262930314925</v>
+        <v>6.3312611801486041</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.2529310572008892</v>
+        <v>3.3600899913562405</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.0314781432043176</v>
+        <v>4.1657943234885693</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>4.9546928905349281</v>
+        <v>5.1213646876146415</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.5753169152831736</v>
+        <v>5.7638103449548144</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21414,11 +21414,11 @@
       </c>
       <c r="D118" s="401">
         <f>DCF!D90</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>9.01 HKD</v>
+        <v>8.45 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21437,15 +21437,15 @@
       </c>
       <c r="D119" s="406">
         <f>DCF!D91</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>8.12 HKD</v>
+        <v>7.92 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
-        <v>0.16999999999999996</v>
+        <v>0.15999999999999995</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -21459,15 +21459,15 @@
       </c>
       <c r="D120" s="406">
         <f>DCF!D92</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.39 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
-        <v>0.46750000000000003</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -21481,15 +21481,15 @@
       </c>
       <c r="D121" s="406">
         <f>DCF!D93</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>4.61 HKD</v>
+        <v>5.41 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
-        <v>0.21249999999999999</v>
+        <v>0.19999999999999998</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -21503,15 +21503,15 @@
       </c>
       <c r="D122" s="406">
         <f>DCF!D94</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.03 HKD</v>
+        <v>3.85 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.0987262930314925</v>
+        <v>6.3312611801486041</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.8104729460974625</v>
+        <v>2.9176318802528138</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.2529310572008892</v>
+        <v>3.3600899913562405</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.5227299887546542</v>
+        <v>3.6570461690389062</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.0314781432043176</v>
+        <v>4.1657943234885693</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.371325454682963</v>
+        <v>4.5379972517626763</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>4.9546928905349281</v>
+        <v>5.1213646876146415</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>4.9436445853527387</v>
+        <v>5.1321380150243794</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.5753169152831736</v>
+        <v>5.7638103449548144</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,15 +21836,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21859,12 +21856,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF296DA2-F323-4FFC-8BFC-605C877BCFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D86A20-B3D7-4EEB-A909-A181F109C25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>35626.439196719999</v>
+        <v>35989.049264880006</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22545855615291369</v>
+        <v>0.22071966109380317</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0914415199999998</v>
+        <v>1.0902572700000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3312611801486041</v>
+        <v>6.3243915532238484</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3600899913562405</v>
+        <v>3.3569242646628044</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1657943234885693</v>
+        <v>4.161826307936364</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1213646876146415</v>
+        <v>5.1164408111201887</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7638103449548144</v>
+        <v>5.7582418061619247</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10917503240400375</v>
+        <v>0.10795776710784652</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1526717557251906E-2</v>
+        <v>6.0906801007556667E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10173818700839903</v>
+        <v>-0.10162779772435872</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7579939989183475</v>
+        <v>1.7560865175232669</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1566621455169685E-4</v>
+        <v>5.151066997234698E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6567714781245002</v>
+        <v>1.6549738264986318</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2402555711558032</v>
+        <v>1.2389098530085398</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.45 HKD</v>
+        <v>8.44 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0246887493633453E-2</v>
+        <v>-6.0212711598195849E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.92 HKD</v>
+        <v>7.91 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8827847485508639E-2</v>
+        <v>-3.8792158599914361E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>6.77 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3999452867582288E-2</v>
+        <v>1.403905588829775E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.41 HKD</v>
+        <v>5.4 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6435164014073704E-2</v>
+        <v>9.6481410845161236E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23384033458224196</v>
+        <v>0.23389918463113599</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3312611801486041</v>
+        <v>6.3243915532238484</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9176318802528138</v>
+        <v>2.9144661535593777</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3600899913562405</v>
+        <v>3.3569242646628044</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6570461690389062</v>
+        <v>3.653078153486701</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1657943234885693</v>
+        <v>4.161826307936364</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5379972517626763</v>
+        <v>4.5330733752682235</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1213646876146415</v>
+        <v>5.1164408111201887</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1321380150243794</v>
+        <v>5.1265694762314897</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7638103449548144</v>
+        <v>5.7582418061619247</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.083467486751633</v>
+        <v>3.0801218229627159</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2402555711558032</v>
+        <v>1.2389098530085398</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>922282.2731397599</v>
+        <v>921281.56649451016</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10173818700839903</v>
+        <v>0.10162779772435872</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15936658.094316324</v>
+        <v>15919366.295349222</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7579939989183475</v>
+        <v>1.7560865175232669</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4674.6440301599996</v>
+        <v>4669.5718874100003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1566621455169685E-4</v>
+        <v>5.1510669972346969E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16863615.011486247</v>
+        <v>16845317.433731142</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8602478521412984</v>
+        <v>1.8582294219473492</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1526717557251906E-2</v>
+        <v>6.0906801007556667E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.3053435114503818E-2</v>
+        <v>8.2216624685138545E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.2086513994910936E-2</v>
+        <v>7.1360201511335014E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.2569974554707373E-2</v>
+        <v>7.1838790931989929E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11974554707379134</v>
+        <v>0.11853904282115869</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.5343511450381678E-2</v>
+        <v>7.4584382871536528E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42905787734773476</v>
+        <v>0.42859233541815073</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35142758059613688</v>
+        <v>0.35104627009557898</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31576994394952018</v>
+        <v>0.31542732315924449</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.4934239402556273</v>
+        <v>0.49288855902764578</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.6289946709530525</v>
+        <v>0.62831219101672398</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54613254024103808</v>
+        <v>0.54553996844591313</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.3645166572921183</v>
+        <v>0.36412114471220652</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21340550711226006</v>
+        <v>0.21317395510771692</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3738437776628547E-2</v>
+        <v>9.3636728484007045E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6248530025513337E-2</v>
+        <v>2.6220049505839959E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10917503240400375</v>
+        <v>0.10795776710784652</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.9421776233113703E-2</v>
+        <v>8.8424753172689913E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0348586246697246E-2</v>
+        <v>7.9452726236585516E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12555316545944714</v>
+        <v>0.12415328942761858</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.16004953459365204</v>
+        <v>0.15826503552058538</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1389650229620962</v>
+        <v>0.13741560918033074</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.275233009977564E-2</v>
+        <v>9.1718172471588547E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.4301655753755736E-2</v>
+        <v>5.3696210354588644E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3852019790490724E-2</v>
+        <v>2.3586077703780111E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.6790152736675157E-3</v>
+        <v>6.6045464750226594E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1025676458941881</v>
+        <v>0.10153421873152624</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2357026808980974E-2</v>
+        <v>9.1426477420477381E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13888859261734904</v>
+        <v>0.13748921133153191</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19409450273202239</v>
+        <v>0.19213889061381559</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20873913216352713</v>
+        <v>0.20663596710394497</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11043980506371354</v>
+        <v>0.10932706143586754</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2937920560032737E-2</v>
+        <v>6.2303785340284294E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2566431733284697E-2</v>
+        <v>3.223830647652616E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.140029733977436E-2</v>
+        <v>1.1285432882950435E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6567714781245002</v>
+        <v>1.6549738264986318</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0914415199999998</v>
+        <v>1.0902572700000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68667569.827153981</v>
+        <v>68593063.252062559</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8915077316668718</v>
+        <v>7.8829451858410327</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.7849054496571384</v>
+        <v>5.7786286366962809</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6798583076683018</v>
+        <v>6.6726104413778069</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2764935463424099</v>
+        <v>7.2685983111654906</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.6941382134142868</v>
+        <v>7.6857898200168711</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8731287850165188</v>
+        <v>7.8645861809531761</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6166686186868553</v>
+        <v>4.6116593811679474</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.970571660293488</v>
+        <v>5.9640933933784623</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0122495012419881</v>
+        <v>7.0046409795578919</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8076240769942569</v>
+        <v>7.7991525476967656</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1651879927590887</v>
+        <v>8.1563284948352575</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8541830413635938</v>
+        <v>3.8500011258114593</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4084330586444507</v>
+        <v>5.4025647306283986</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7781871769106132</v>
+        <v>6.7708326205581537</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9155546885108734</v>
+        <v>7.9069660509447797</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4511200842553098</v>
+        <v>8.4419503405939391</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3565234570966629</v>
+        <v>3.3528815185857788</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9629152857757486</v>
+        <v>4.957530359218091</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5708592439364333</v>
+        <v>6.5637296452203895</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0182019833798215</v>
+        <v>8.0095019701177144</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7310536004054615</v>
+        <v>8.7215801196583858</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0317106748245397</v>
+        <v>3.0284211688813722</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6098242769753801</v>
+        <v>4.6048224657926733</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.387212123819447</v>
+        <v>6.3802817882778493</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1158245854929465</v>
+        <v>8.1070186484919731</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0051143854475644</v>
+        <v>8.9953435397214783</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8197116560921529</v>
+        <v>2.8166521760673082</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3299852490217088</v>
+        <v>4.3252870724018999</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2245410150911118</v>
+        <v>6.217787183060679</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2086684588313066</v>
+        <v>8.1997617831695919</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2734256435307412</v>
+        <v>9.2633636712517795</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6813439981782401</v>
+        <v>2.6784346516199</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1082014040234593</v>
+        <v>4.1037438701807725</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0804500563107693</v>
+        <v>6.0738525677168003</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.2969675271810743</v>
+        <v>8.2879650441217336</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5361079941016875</v>
+        <v>9.5257610028199089</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5910341049010941</v>
+        <v>2.5882227475516615</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9324286597358022</v>
+        <v>3.9281618451104152</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9528170392093003</v>
+        <v>5.9463580366429678</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3809442635137152</v>
+        <v>8.3718506629293596</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.7932795261291847</v>
+        <v>9.7826534952642277</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5320905848134467</v>
+        <v>2.5293431831248392</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.7931215896709936</v>
+        <v>3.7890059278052379</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8397621522662719</v>
+        <v>5.8334258179761678</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4608102505153937</v>
+        <v>8.4516299927044471</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.045055851191067</v>
+        <v>10.034156634720203</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.4936192896513454</v>
+        <v>2.490913630585188</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6827150539552944</v>
+        <v>3.6787191868174518</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.739620294368021</v>
+        <v>5.7333926172922913</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.536766713677828</v>
+        <v>8.5275040406024356</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.29155015544746</v>
+        <v>10.280383484537245</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4298869686559277</v>
+        <v>2.4272504612573176</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.3928211880891337</v>
+        <v>3.3891398653445184</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.3864917023177803</v>
+        <v>5.380647181396065</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8642859004327601</v>
+        <v>8.8546678582516414</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.448589423389221</v>
+        <v>11.436167326761776</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4223384204884906</v>
+        <v>2.4197101035132826</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3021754999866357</v>
+        <v>3.298592530799374</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1939324437659566</v>
+        <v>5.1882968559824461</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1191162215392705</v>
+        <v>9.1092216800659394</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.489247572656414</v>
+        <v>12.475696327658959</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4214443595387842</v>
+        <v>2.4188170126491562</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2738318827561534</v>
+        <v>3.2702796673271926</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0889308412654346</v>
+        <v>5.0834091836792661</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3173900790151052</v>
+        <v>9.3072804038755059</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.42523083065136</v>
+        <v>13.410664012988793</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4213384656683266</v>
+        <v>2.418711233677036</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2649692368374672</v>
+        <v>3.2614266376712528</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.031673991552803</v>
+        <v>5.0262144595345468</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4716594861549073</v>
+        <v>9.4613824236271089</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.267067950616006</v>
+        <v>14.251587711949155</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4511200842553098</v>
+        <v>8.4419503405939391</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9155546885108734</v>
+        <v>7.9069660509447797</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7781871769106132</v>
+        <v>6.7708326205581537</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4084330586444507</v>
+        <v>5.4025647306283986</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8541830413635938</v>
+        <v>3.8500011258114593</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9155546885108734</v>
+        <v>7.9069660509447797</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7781871769106132</v>
+        <v>6.7708326205581537</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4084330586444507</v>
+        <v>5.4025647306283986</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.663222149664124</v>
+        <v>6.6559923341530398</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4511200842553098</v>
+        <v>8.4419503405939391</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8541830413635938</v>
+        <v>3.8500011258114593</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22545855615291369</v>
+        <v>0.22071966109380317</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4144218546244385E-2</v>
+        <v>-2.4107467971085331E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3312611801486041</v>
+        <v>6.3243915532238484</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8915077316668718</v>
+        <v>7.8829451858410327</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9176318802528138</v>
+        <v>2.9144661535593777</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3600899913562405</v>
+        <v>3.3569242646628044</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46928583488363151</v>
+        <v>0.46920992534821515</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6570461690389062</v>
+        <v>3.653078153486701</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1657943234885693</v>
+        <v>4.161826307936364</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34202772481567534</v>
+        <v>0.34194044234739396</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5379972517626763</v>
+        <v>4.5330733752682235</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1213646876146415</v>
+        <v>5.1164408111201887</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19109881240210735</v>
+        <v>0.19099872801011331</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1321380150243794</v>
+        <v>5.1265694762314897</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7638103449548144</v>
+        <v>5.7582418061619247</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9626824584808973E-2</v>
+        <v>8.9518452849955188E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>35626.439196719999</v>
+        <v>35989.049264880006</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22545855615291369</v>
+        <v>0.22071966109380317</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0914415199999998</v>
+        <v>1.0902572700000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3312611801486041</v>
+        <v>6.3243915532238484</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3600899913562405</v>
+        <v>3.3569242646628044</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1657943234885693</v>
+        <v>4.161826307936364</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1213646876146415</v>
+        <v>5.1164408111201887</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7638103449548144</v>
+        <v>5.7582418061619247</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10917503240400375</v>
+        <v>0.10795776710784652</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.1526717557251906E-2</v>
+        <v>6.0906801007556667E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10173818700839903</v>
+        <v>-0.10162779772435872</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7579939989183475</v>
+        <v>1.7560865175232669</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1566621455169685E-4</v>
+        <v>5.151066997234698E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6567714781245002</v>
+        <v>1.6549738264986318</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2402555711558032</v>
+        <v>1.2389098530085398</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5748111656794634</v>
+        <v>7.5665922460593338</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.45 HKD</v>
+        <v>8.44 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.92 HKD</v>
+        <v>7.91 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>6.77 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.41 HKD</v>
+        <v>5.4 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3312611801486041</v>
+        <v>6.3243915532238484</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9176318802528138</v>
+        <v>2.9144661535593777</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3600899913562405</v>
+        <v>3.3569242646628044</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6570461690389062</v>
+        <v>3.653078153486701</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1657943234885693</v>
+        <v>4.161826307936364</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5379972517626763</v>
+        <v>4.5330733752682235</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1213646876146415</v>
+        <v>5.1164408111201887</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1321380150243794</v>
+        <v>5.1265694762314897</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7638103449548144</v>
+        <v>5.7582418061619247</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,12 +21836,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21856,15 +21859,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D86A20-B3D7-4EEB-A909-A181F109C25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9102A1D-97AD-4026-A493-FB51A2452935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>35989.049264880006</v>
+        <v>36079.701781919997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22071966109380317</v>
+        <v>0.21978250753226489</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0902572700000002</v>
+        <v>1.09065528</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3243915532238484</v>
+        <v>6.3267003395547077</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3569242646628044</v>
+        <v>3.357988221497302</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.161826307936364</v>
+        <v>4.1631599029289186</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1164408111201887</v>
+        <v>5.1180956577180829</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7582418061619247</v>
+        <v>5.7601133148171551</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10795776710784652</v>
+        <v>0.10772582854367654</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0906801007556667E-2</v>
+        <v>6.0753768844221102E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10162779772435872</v>
+        <v>-0.10166489803167632</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7560865175232669</v>
+        <v>1.7567275955642685</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.151066997234698E-4</v>
+        <v>5.1529474489702494E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6549738264986318</v>
+        <v>1.6555779922774891</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2389098530085398</v>
+        <v>1.2393621302133464</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.44 HKD</v>
+        <v>8.45 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0212711598195849E-2</v>
+        <v>-6.0224205905314736E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8792158599914361E-2</v>
+        <v>-3.8804161771677469E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.403905588829775E-2</v>
+        <v>1.4025736272410093E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6481410845161236E-2</v>
+        <v>9.6465856707051781E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23389918463113599</v>
+        <v>0.23387939162077337</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3243915532238484</v>
+        <v>6.3267003395547077</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9144661535593777</v>
+        <v>2.9155301103938753</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3569242646628044</v>
+        <v>3.357988221497302</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.653078153486701</v>
+        <v>3.6544117484792551</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.161826307936364</v>
+        <v>4.1631599029289186</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5330733752682235</v>
+        <v>4.5347282218661178</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1164408111201887</v>
+        <v>5.1180956577180829</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1265694762314897</v>
+        <v>5.1284409848867201</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7582418061619247</v>
+        <v>5.7601133148171551</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0801218229627159</v>
+        <v>3.0812462541593608</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2389098530085398</v>
+        <v>1.2393621302133464</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>921281.56649451016</v>
+        <v>921617.89011864003</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10162779772435872</v>
+        <v>0.10166489803167633</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15919366.295349222</v>
+        <v>15925177.829152808</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7560865175232669</v>
+        <v>1.7567275955642685</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4669.5718874100003</v>
+        <v>4671.27656424</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1510669972346969E-4</v>
+        <v>5.1529474489702494E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16845317.433731142</v>
+        <v>16851466.995835688</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8582294219473492</v>
+        <v>1.8589077883408418</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0906801007556667E-2</v>
+        <v>6.0753768844221102E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2216624685138545E-2</v>
+        <v>8.2010050251256295E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1360201511335014E-2</v>
+        <v>7.1180904522613067E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1838790931989929E-2</v>
+        <v>7.165829145728643E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11853904282115869</v>
+        <v>0.11824120603015076</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4584382871536528E-2</v>
+        <v>7.4396984924623127E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42859233541815073</v>
+        <v>0.42874879760383255</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35104627009557898</v>
+        <v>0.35117442326621612</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31542732315924449</v>
+        <v>0.31554247325486418</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49288855902764578</v>
+        <v>0.49306849323288021</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62831219101672398</v>
+        <v>0.62854156305764275</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54553996844591313</v>
+        <v>0.54573912360755783</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36412114471220652</v>
+        <v>0.36425407100473822</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21317395510771692</v>
+        <v>0.21325177652492461</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3636728484007045E-2</v>
+        <v>9.3670911566596265E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6220049505839959E-2</v>
+        <v>2.6229621413490539E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10795776710784652</v>
+        <v>0.10772582854367654</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8424753172689913E-2</v>
+        <v>8.8234779715129677E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9452726236585516E-2</v>
+        <v>7.9282028455996023E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12415328942761858</v>
+        <v>0.12388655608866338</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15826503552058538</v>
+        <v>0.15792501584362884</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13741560918033074</v>
+        <v>0.13712038281596931</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1718172471588547E-2</v>
+        <v>9.1521123368024676E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3696210354588644E-2</v>
+        <v>5.3580848373096637E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3586077703780111E-2</v>
+        <v>2.3535404916230216E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.6045464750226594E-3</v>
+        <v>6.5903571390679748E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10153421873152624</v>
+        <v>0.10127910762918574</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1426477420477381E-2</v>
+        <v>9.1196762653089264E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13748921133153191</v>
+        <v>0.13714376105180445</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19213889061381559</v>
+        <v>0.19165612958212264</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20663596710394497</v>
+        <v>0.20611678125695018</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10932706143586754</v>
+        <v>0.10905237032673222</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2303785340284294E-2</v>
+        <v>6.2147243166062481E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.223830647652616E-2</v>
+        <v>3.2157305706484639E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1285432882950435E-2</v>
+        <v>1.1257077523948049E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6549738264986318</v>
+        <v>1.6555779922774891</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0902572700000002</v>
+        <v>1.09065528</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68593063.252062559</v>
+        <v>68618103.878579021</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8829451858410327</v>
+        <v>7.8858229387345453</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.7786286366962809</v>
+        <v>5.7807381864759311</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6726104413778069</v>
+        <v>6.6750463487134875</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2685983111654906</v>
+        <v>7.2712517902051914</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.6857898200168711</v>
+        <v>7.6885955992493846</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8645861809531761</v>
+        <v>7.8674572316968963</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6116593811679474</v>
+        <v>4.6133429164222433</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9640933933784623</v>
+        <v>5.9662706490380355</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0046409795578919</v>
+        <v>7.0071980981692379</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.7991525476967656</v>
+        <v>7.8019997111974577</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1563284948352575</v>
+        <v>8.1593060492103167</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8500011258114593</v>
+        <v>3.8514066096272961</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4025647306283986</v>
+        <v>5.404536994283597</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7708326205581537</v>
+        <v>6.7733043849439181</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9069660509447797</v>
+        <v>7.9098525729103111</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4419503405939391</v>
+        <v>8.4450321642584196</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3528815185857788</v>
+        <v>3.3541055236072834</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.957530359218091</v>
+        <v>4.9593401583476773</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5637296452203895</v>
+        <v>6.5661258044646136</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0095019701177144</v>
+        <v>8.0124259239099462</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7215801196583858</v>
+        <v>8.7247640251446796</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0284211688813722</v>
+        <v>3.0295267262049439</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6048224657926733</v>
+        <v>4.606503505158372</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.3802817882778493</v>
+        <v>6.3826109779328304</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1070186484919731</v>
+        <v>8.1099782017837239</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>8.9953435397214783</v>
+        <v>8.9986273854529024</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8166521760673082</v>
+        <v>2.8176804248700851</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3252870724018999</v>
+        <v>4.3268660644022798</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.217787183060679</v>
+        <v>6.2200570523335799</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.1997617831695919</v>
+        <v>8.2027551933280201</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2633636712517795</v>
+        <v>9.2667453605798347</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6784346516199</v>
+        <v>2.6794124426468664</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1037438701807725</v>
+        <v>4.1052419854813653</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0738525677168003</v>
+        <v>6.0760698921291159</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.2879650441217336</v>
+        <v>8.2909906538176994</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5257610028199089</v>
+        <v>9.5292384830817287</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5882227475516615</v>
+        <v>2.5891676057645792</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9281618451104152</v>
+        <v>3.9295958623272615</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9463580366429678</v>
+        <v>5.9485288178221323</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3718506629293596</v>
+        <v>8.3749068959617254</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.7826534952642277</v>
+        <v>9.786224756859804</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5293431831248392</v>
+        <v>2.530266546727189</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.7890059278052379</v>
+        <v>3.790389144675991</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8334258179761678</v>
+        <v>5.8355553720490443</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4516299927044471</v>
+        <v>8.4547153500287742</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.034156634720203</v>
+        <v>10.037819710208968</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.490913630585188</v>
+        <v>2.491822965071083</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6787191868174518</v>
+        <v>3.6800621423416504</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7333926172922913</v>
+        <v>5.7354856531824421</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5275040406024356</v>
+        <v>8.5306170965540815</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.280383484537245</v>
+        <v>10.284136447753605</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4272504612573176</v>
+        <v>2.4281365548268519</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.3891398653445184</v>
+        <v>3.3903771068607389</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.380647181396065</v>
+        <v>5.3826114438170505</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8546678582516414</v>
+        <v>8.8579003488309169</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.436167326761776</v>
+        <v>11.440342221149523</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4197101035132826</v>
+        <v>2.4205934443951085</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.298592530799374</v>
+        <v>3.2997967170490861</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1882968559824461</v>
+        <v>5.1901908988734871</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1092216800659394</v>
+        <v>9.112547098222409</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.475696327658959</v>
+        <v>12.480250713153099</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4188170126491562</v>
+        <v>2.4197000274986733</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2702796673271926</v>
+        <v>3.2714735176652803</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0834091836792661</v>
+        <v>5.0852649362111393</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3072804038755059</v>
+        <v>9.3106781254734052</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.410664012988793</v>
+        <v>13.415559718370154</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.418711233677036</v>
+        <v>2.4195942099108154</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2614266376712528</v>
+        <v>3.2626172561168048</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0262144595345468</v>
+        <v>5.0280493325246978</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4613824236271089</v>
+        <v>9.464836401804595</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.251587711949155</v>
+        <v>14.256790405461329</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4419503405939391</v>
+        <v>8.4450321642584196</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9069660509447797</v>
+        <v>7.9098525729103111</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7708326205581537</v>
+        <v>6.7733043849439181</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4025647306283986</v>
+        <v>5.404536994283597</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8500011258114593</v>
+        <v>3.8514066096272961</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9069660509447797</v>
+        <v>7.9098525729103111</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7708326205581537</v>
+        <v>6.7733043849439181</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4025647306283986</v>
+        <v>5.404536994283597</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6559923341530398</v>
+        <v>6.6584221748721166</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4419503405939391</v>
+        <v>8.4450321642584196</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8500011258114593</v>
+        <v>3.8514066096272961</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22071966109380317</v>
+        <v>0.21978250753226489</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4107467971085331E-2</v>
+        <v>-2.4119828221539803E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3243915532238484</v>
+        <v>6.3267003395547077</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8829451858410327</v>
+        <v>7.8858229387345453</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.29381947754327764</v>
+        <v>0.2938194775432777</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9144661535593777</v>
+        <v>2.9155301103938753</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3569242646628044</v>
+        <v>3.357988221497302</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46920992534821515</v>
+        <v>0.46923545588162829</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.653078153486701</v>
+        <v>3.6544117484792551</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.161826307936364</v>
+        <v>4.1631599029289186</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34194044234739396</v>
+        <v>0.34196979792124393</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5330733752682235</v>
+        <v>4.5347282218661178</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1164408111201887</v>
+        <v>5.1180956577180829</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19099872801011331</v>
+        <v>0.19103238923462118</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1265694762314897</v>
+        <v>5.1284409848867201</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7582418061619247</v>
+        <v>5.7601133148171551</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9518452849955188E-2</v>
+        <v>8.9554901343317117E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>35989.049264880006</v>
+        <v>36079.701781919997</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22071966109380317</v>
+        <v>0.21978250753226489</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0902572700000002</v>
+        <v>1.09065528</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3243915532238484</v>
+        <v>6.3267003395547077</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3569242646628044</v>
+        <v>3.357988221497302</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.161826307936364</v>
+        <v>4.1631599029289186</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1164408111201887</v>
+        <v>5.1180956577180829</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7582418061619247</v>
+        <v>5.7601133148171551</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10795776710784652</v>
+        <v>0.10772582854367654</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.0906801007556667E-2</v>
+        <v>6.0753768844221102E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10162779772435872</v>
+        <v>-0.10166489803167632</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7560865175232669</v>
+        <v>1.7567275955642685</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.151066997234698E-4</v>
+        <v>5.1529474489702494E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6549738264986318</v>
+        <v>1.6555779922774891</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2389098530085398</v>
+        <v>1.2393621302133464</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5665922460593338</v>
+        <v>7.5693545109510421</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.44 HKD</v>
+        <v>8.45 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3243915532238484</v>
+        <v>6.3267003395547077</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9144661535593777</v>
+        <v>2.9155301103938753</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3569242646628044</v>
+        <v>3.357988221497302</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.653078153486701</v>
+        <v>3.6544117484792551</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.161826307936364</v>
+        <v>4.1631599029289186</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5330733752682235</v>
+        <v>4.5347282218661178</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1164408111201887</v>
+        <v>5.1180956577180829</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1265694762314897</v>
+        <v>5.1284409848867201</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7582418061619247</v>
+        <v>5.7601133148171551</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,15 +21836,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21859,12 +21856,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9102A1D-97AD-4026-A493-FB51A2452935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6C8E1A-4130-4566-93B5-93553D948F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.21978250753226489</v>
+        <v>0.2201207182523266</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.09065528</v>
+        <v>1.0916428500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3267003395547077</v>
+        <v>6.3324290602320019</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.357988221497302</v>
+        <v>3.3606281849430597</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1631599029289186</v>
+        <v>4.1664689112623732</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1180956577180829</v>
+        <v>5.1222017778022115</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7601133148171551</v>
+        <v>5.7647570318158445</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10772582854367654</v>
+        <v>0.10782337246836637</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10166489803167632</v>
+        <v>-0.10175695388579474</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7567275955642685</v>
+        <v>1.7583182828358246</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1529474489702494E-4</v>
+        <v>5.1576133561597132E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6555779922774891</v>
+        <v>1.657077090285646</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2393621302133464</v>
+        <v>1.2404843517634361</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0224205905314736E-2</v>
+        <v>-6.025269025329584E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.91 HKD</v>
+        <v>7.92 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8804161771677469E-2</v>
+        <v>-3.8833907133871699E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.77 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.4025736272410093E-2</v>
+        <v>1.3992728644319063E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.4 HKD</v>
+        <v>5.41 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6465856707051781E-2</v>
+        <v>9.6427311752418851E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23387939162077337</v>
+        <v>0.23383034245960019</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3267003395547077</v>
+        <v>6.3324290602320019</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9155301103938753</v>
+        <v>2.918170073839633</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.357988221497302</v>
+        <v>3.3606281849430597</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6544117484792551</v>
+        <v>3.6577207568127101</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1631599029289186</v>
+        <v>4.1664689112623732</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5347282218661178</v>
+        <v>4.5388343419502464</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1180956577180829</v>
+        <v>5.1222017778022115</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1284409848867201</v>
+        <v>5.1330847018854096</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7601133148171551</v>
+        <v>5.7647570318158445</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0812462541593608</v>
+        <v>3.0840362707842477</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2393621302133464</v>
+        <v>1.2404843517634361</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>921617.89011864003</v>
+        <v>922452.39960705012</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10166489803167633</v>
+        <v>0.10175695388579473</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15925177.829152808</v>
+        <v>15939597.809651814</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7567275955642685</v>
+        <v>1.7583182828358246</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4671.27656424</v>
+        <v>4675.5063265500003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1529474489702494E-4</v>
+        <v>5.1576133561597132E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16851466.995835688</v>
+        <v>16866725.715585414</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8589077883408418</v>
+        <v>1.8605909980572353</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42874879760383255</v>
+        <v>0.42913702242409812</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35117442326621612</v>
+        <v>0.35149240579611785</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31554247325486418</v>
+        <v>0.3158281916537265</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49306849323288021</v>
+        <v>0.49351495845501908</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62854156305764275</v>
+        <v>0.62911069686445753</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54573912360755783</v>
+        <v>0.54623328119903913</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36425407100473822</v>
+        <v>0.36458389693553295</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21325177652492461</v>
+        <v>0.21344487241947963</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3670911566596265E-2</v>
+        <v>9.3755729000511615E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6229621413490539E-2</v>
+        <v>2.6253371894228435E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10772582854367654</v>
+        <v>0.10782337246836637</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8234779715129677E-2</v>
+        <v>8.8314674823145187E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9282028455996023E-2</v>
+        <v>7.935381699842374E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12388655608866338</v>
+        <v>0.12399873328015555</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15792501584362884</v>
+        <v>0.15806801428755216</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13712038281596931</v>
+        <v>0.13724454301483396</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1521123368024676E-2</v>
+        <v>9.1603994204907779E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3580848373096637E-2</v>
+        <v>5.3629364929517497E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3535404916230216E-2</v>
+        <v>2.3556715829274277E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.5903571390679748E-3</v>
+        <v>6.5963245965398078E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6555779922774891</v>
+        <v>1.657077090285646</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09065528</v>
+        <v>1.0916428500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68618103.878579021</v>
+        <v>68680236.416778803</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8858229387345453</v>
+        <v>7.8929634186849178</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.7807381864759311</v>
+        <v>5.7859725476123103</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6750463487134875</v>
+        <v>6.6810904908393107</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2712517902051914</v>
+        <v>7.277835786323978</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.6885955992493846</v>
+        <v>7.6955574931632453</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8674572316968963</v>
+        <v>7.8745810818086452</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6133429164222433</v>
+        <v>4.617520220789185</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9662706490380355</v>
+        <v>5.9716730066967001</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0071980981692379</v>
+        <v>7.0135429981139854</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8019997111974577</v>
+        <v>7.809064290626063</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1593060492103167</v>
+        <v>8.1666941635144266</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8514066096272961</v>
+        <v>3.8548939934920408</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.404536994283597</v>
+        <v>5.4094307115720195</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7733043849439181</v>
+        <v>6.7794374980678382</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9098525729103111</v>
+        <v>7.9170148112900032</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4450321642584196</v>
+        <v>8.4526789987508533</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3541055236072834</v>
+        <v>3.3571426097083559</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9593401583476773</v>
+        <v>4.96383075739395</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5661258044646136</v>
+        <v>6.5720713208707835</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0124259239099462</v>
+        <v>8.01968104073263</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7247640251446796</v>
+        <v>8.7326641521291783</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0295267262049439</v>
+        <v>3.0322699116677225</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.606503505158372</v>
+        <v>4.6106746165535233</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.3826109779328304</v>
+        <v>6.3883903247521827</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1099782017837239</v>
+        <v>8.1173216505521903</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>8.9986273854529024</v>
+        <v>9.0067754911009619</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8176804248700851</v>
+        <v>2.8202317870724385</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3268660644022798</v>
+        <v>4.330783968801204</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2200570523335799</v>
+        <v>6.2256892093091309</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2027551933280201</v>
+        <v>8.2101826501008652</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2667453605798347</v>
+        <v>9.2751362425418673</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6794124426468664</v>
+        <v>2.6818386055184065</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1052419854813653</v>
+        <v>4.1089592130068242</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0760698921291159</v>
+        <v>6.0815716711544479</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.2909906538176994</v>
+        <v>8.2984980063149898</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5292384830817287</v>
+        <v>9.537867048148355</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5891676057645792</v>
+        <v>2.5915120534551686</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9295958623272615</v>
+        <v>3.9331540452443781</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9485288178221323</v>
+        <v>5.9539151105512316</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3749068959617254</v>
+        <v>8.3824902332039439</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.786224756859804</v>
+        <v>9.7950860186721833</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.530266546727189</v>
+        <v>2.5325576605001419</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.790389144675991</v>
+        <v>3.7938212782531631</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8355553720490443</v>
+        <v>5.840839369224371</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4547153500287742</v>
+        <v>8.4623709524829511</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.037819710208968</v>
+        <v>10.046908787017189</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.491822965071083</v>
+        <v>2.4940792688278628</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6800621423416504</v>
+        <v>3.6833943766750443</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7354856531824421</v>
+        <v>5.7406790389115372</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5306170965540815</v>
+        <v>8.5383414267622886</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.284136447753605</v>
+        <v>10.293448560222092</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4281365548268519</v>
+        <v>2.4303351916110159</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.3903771068607389</v>
+        <v>3.3934470362699862</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.3826114438170505</v>
+        <v>5.3874853078885385</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8579003488309169</v>
+        <v>8.8659210285157908</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.440342221149523</v>
+        <v>11.450701258486546</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4205934443951085</v>
+        <v>2.4227852510197292</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.2997967170490861</v>
+        <v>3.3027846274398529</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1901908988734871</v>
+        <v>5.1948905293800216</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.112547098222409</v>
+        <v>9.1207983562530792</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.480250713153099</v>
+        <v>12.491551370127675</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4197000274986733</v>
+        <v>2.4218910251493311</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2714735176652803</v>
+        <v>3.2744357818756926</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0852649362111393</v>
+        <v>5.0898695580244171</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3106781254734052</v>
+        <v>9.319108787814649</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.415559718370154</v>
+        <v>13.427707281907438</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4195942099108154</v>
+        <v>2.4217851117454279</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2626172561168048</v>
+        <v>3.2655715011314381</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0280493325246978</v>
+        <v>5.0326021465717927</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.464836401804595</v>
+        <v>9.4734066518705298</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.256790405461329</v>
+        <v>14.26969968922762</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4450321642584196</v>
+        <v>8.4526789987508533</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9098525729103111</v>
+        <v>7.9170148112900032</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7733043849439181</v>
+        <v>6.7794374980678382</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.404536994283597</v>
+        <v>5.4094307115720195</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8514066096272961</v>
+        <v>3.8548939934920408</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9098525729103111</v>
+        <v>7.9170148112900032</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7733043849439181</v>
+        <v>6.7794374980678382</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.404536994283597</v>
+        <v>5.4094307115720195</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6584221748721166</v>
+        <v>6.6644512640883171</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4450321642584196</v>
+        <v>8.4526789987508533</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8514066096272961</v>
+        <v>3.8548939934920408</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21978250753226489</v>
+        <v>0.2201207182523266</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4119828221539803E-2</v>
+        <v>-2.4150458457392169E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3267003395547077</v>
+        <v>6.3324290602320019</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8858229387345453</v>
+        <v>7.8929634186849178</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.2938194775432777</v>
+        <v>0.29381947754327764</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9155301103938753</v>
+        <v>2.918170073839633</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.357988221497302</v>
+        <v>3.3606281849430597</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46923545588162829</v>
+        <v>0.46929872360545066</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6544117484792551</v>
+        <v>3.6577207568127101</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1631599029289186</v>
+        <v>4.1664689112623732</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34196979792124393</v>
+        <v>0.34204254455402838</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5347282218661178</v>
+        <v>4.5388343419502464</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1180956577180829</v>
+        <v>5.1222017778022115</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19103238923462118</v>
+        <v>0.19111580578613718</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1284409848867201</v>
+        <v>5.1330847018854096</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7601133148171551</v>
+        <v>5.7647570318158445</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9554901343317117E-2</v>
+        <v>8.9645225081346536E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.21978250753226489</v>
+        <v>0.2201207182523266</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.09065528</v>
+        <v>1.0916428500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3267003395547077</v>
+        <v>6.3324290602320019</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.357988221497302</v>
+        <v>3.3606281849430597</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1631599029289186</v>
+        <v>4.1664689112623732</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1180956577180829</v>
+        <v>5.1222017778022115</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7601133148171551</v>
+        <v>5.7647570318158445</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10772582854367654</v>
+        <v>0.10782337246836637</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10166489803167632</v>
+        <v>-0.10175695388579474</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7567275955642685</v>
+        <v>1.7583182828358246</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1529474489702494E-4</v>
+        <v>5.1576133561597132E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6555779922774891</v>
+        <v>1.657077090285646</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2393621302133464</v>
+        <v>1.2404843517634361</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5693545109510421</v>
+        <v>7.5762084340663112</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.91 HKD</v>
+        <v>7.92 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.77 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.4 HKD</v>
+        <v>5.41 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3267003395547077</v>
+        <v>6.3324290602320019</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9155301103938753</v>
+        <v>2.918170073839633</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.357988221497302</v>
+        <v>3.3606281849430597</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6544117484792551</v>
+        <v>3.6577207568127101</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1631599029289186</v>
+        <v>4.1664689112623732</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5347282218661178</v>
+        <v>4.5388343419502464</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1180956577180829</v>
+        <v>5.1222017778022115</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1284409848867201</v>
+        <v>5.1330847018854096</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7601133148171551</v>
+        <v>5.7647570318158445</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,12 +21836,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21856,15 +21859,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6C8E1A-4130-4566-93B5-93553D948F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677950B8-DA2A-42C7-BD68-A2083480D400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>36079.701781919997</v>
+        <v>38164.70967384</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.2201207182523266</v>
+        <v>0.19741662370587493</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0916428500000002</v>
+        <v>1.0946661899999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3324290602320019</v>
+        <v>6.3499669262794551</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3606281849430597</v>
+        <v>3.3687101508635449</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1664689112623732</v>
+        <v>4.1765990865966423</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1222017778022115</v>
+        <v>5.1347722255630259</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7647570318158445</v>
+        <v>5.7789732750703093</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10782337246836637</v>
+        <v>0.10221509055023491</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0753768844221102E-2</v>
+        <v>5.7434679334916861E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10175695388579474</v>
+        <v>-0.10203877304392053</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7583182828358246</v>
+        <v>1.7631880018993704</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1576133561597132E-4</v>
+        <v>5.1718975323114741E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.657077090285646</v>
+        <v>1.6616664186086809</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2404843517634361</v>
+        <v>1.2439199130919969</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.45 HKD</v>
+        <v>8.48 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.025269025329584E-2</v>
+        <v>-6.0339573200743415E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.92 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8833907133871699E-2</v>
+        <v>-3.8924636278625704E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3992728644319063E-2</v>
+        <v>1.3892049371140979E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.41 HKD</v>
+        <v>5.42 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6427311752418851E-2</v>
+        <v>9.6309743429008221E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.85 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23383034245960019</v>
+        <v>0.23368073645802717</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3324290602320019</v>
+        <v>6.3499669262794551</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.918170073839633</v>
+        <v>2.9262520397601182</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3606281849430597</v>
+        <v>3.3687101508635449</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6577207568127101</v>
+        <v>3.6678509321469792</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1664689112623732</v>
+        <v>4.1765990865966423</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5388343419502464</v>
+        <v>4.5514047897110608</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1222017778022115</v>
+        <v>5.1347722255630259</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1330847018854096</v>
+        <v>5.1473009451398744</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7647570318158445</v>
+        <v>5.7789732750703093</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0840362707842477</v>
+        <v>3.0925776084744196</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2404843517634361</v>
+        <v>1.2439199130919969</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>922452.39960705012</v>
+        <v>925007.1612104699</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10175695388579473</v>
+        <v>0.10203877304392055</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15939597.809651814</v>
+        <v>15983743.038690623</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7583182828358246</v>
+        <v>1.7631880018993704</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4675.5063265500003</v>
+        <v>4688.4552917699993</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1576133561597132E-4</v>
+        <v>5.1718975323114741E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16866725.715585414</v>
+        <v>16913438.655192863</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8605909980572353</v>
+        <v>1.8657439646965222</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0753768844221102E-2</v>
+        <v>5.7434679334916861E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2010050251256295E-2</v>
+        <v>7.7529691211401436E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1180904522613067E-2</v>
+        <v>6.7292161520190019E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>7.165829145728643E-2</v>
+        <v>6.7743467933491688E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11824120603015076</v>
+        <v>0.11178147268408552</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.4396984924623127E-2</v>
+        <v>7.0332541567695972E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42913702242409812</v>
+        <v>0.43032553121648892</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35149240579611785</v>
+        <v>0.35246587532430607</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.3158281916537265</v>
+        <v>0.31670288799324298</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49351495845501908</v>
+        <v>0.49488176401280315</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62911069686445753</v>
+        <v>0.63085303918297131</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54623328119903913</v>
+        <v>0.54774609184803491</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36458389693553295</v>
+        <v>0.36559362376969029</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21344487241947963</v>
+        <v>0.21403601486188251</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3755729000511615E-2</v>
+        <v>9.4015388508853909E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6253371894228435E-2</v>
+        <v>2.6326081452471489E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10782337246836637</v>
+        <v>0.10221509055023491</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8314674823145187E-2</v>
+        <v>8.3721110528338735E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.935381699842374E-2</v>
+        <v>7.522633919079405E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12399873328015555</v>
+        <v>0.11754911259211476</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15806801428755216</v>
+        <v>0.1498463275969053</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13724454301483396</v>
+        <v>0.13010596005891567</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.1603994204907779E-2</v>
+        <v>8.6839340562871806E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.3629364929517497E-2</v>
+        <v>5.0839908518261881E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3556715829274277E-2</v>
+        <v>2.2331446201628007E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.5963245965398078E-3</v>
+        <v>6.2532259982117549E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10127910762918574</v>
+        <v>9.574604474208058E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1196762653089264E-2</v>
+        <v>8.6214516712421682E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13714376105180445</v>
+        <v>0.12965134655253724</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19165612958212264</v>
+        <v>0.18118560468808745</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20611678125695018</v>
+        <v>0.19485624451369637</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10905237032673222</v>
+        <v>0.1030946398813288</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2147243166062481E-2</v>
+        <v>5.8752025605921306E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2157305706484639E-2</v>
+        <v>3.0400493280714695E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1257077523948049E-2</v>
+        <v>1.0642082789860627E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.657077090285646</v>
+        <v>1.6616664186086809</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0916428500000002</v>
+        <v>1.0946661899999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68680236.416778803</v>
+        <v>68870448.541530296</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8929634186849178</v>
+        <v>7.9148232348530394</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.7859725476123103</v>
+        <v>5.8019969847641653</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6810904908393107</v>
+        <v>6.6995939859380718</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.277835786323978</v>
+        <v>7.2979919867206755</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.6955574931632453</v>
+        <v>7.7168705872684997</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8745810818086452</v>
+        <v>7.896389987503281</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.617520220789185</v>
+        <v>4.6303085916234004</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9716730066967001</v>
+        <v>5.9882117472454652</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0135429981139854</v>
+        <v>7.0329672311293123</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.809064290626063</v>
+        <v>7.8306917454593172</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1666941635144266</v>
+        <v>8.1893120857884707</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8548939934920408</v>
+        <v>3.8655702464499408</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4094307115720195</v>
+        <v>5.4244123039925833</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7794374980678382</v>
+        <v>6.7982133683677315</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9170148112900032</v>
+        <v>7.9389412385638716</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4526789987508533</v>
+        <v>8.4760889652285165</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3571426097083559</v>
+        <v>3.3664403241922045</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.96383075739395</v>
+        <v>4.9775782464028859</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5720713208707835</v>
+        <v>6.5902728838702931</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.01968104073263</v>
+        <v>8.0418918054325363</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7326641521291783</v>
+        <v>8.7568495464984952</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0322699116677225</v>
+        <v>3.0406678807605818</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6106746165535233</v>
+        <v>4.6234440282665297</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.3883903247521827</v>
+        <v>6.406083177322448</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1173216505521903</v>
+        <v>8.139802834062877</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0067754911009619</v>
+        <v>9.0317200456439259</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8202317870724385</v>
+        <v>2.8280425097562603</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.330783968801204</v>
+        <v>4.3427782143589289</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2256892093091309</v>
+        <v>6.2429314559047739</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2101826501008652</v>
+        <v>8.2329210151378867</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2751362425418673</v>
+        <v>9.3008240308212713</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6818386055184065</v>
+        <v>2.6892660438326934</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1089592130068242</v>
+        <v>4.1203391077654903</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0815716711544479</v>
+        <v>6.098414779590752</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.2984980063149898</v>
+        <v>8.3214809635728599</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.537867048148355</v>
+        <v>9.564282477848046</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5915120534551686</v>
+        <v>2.5986893294769851</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9331540452443781</v>
+        <v>3.9440470419338616</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9539151105512316</v>
+        <v>5.9704046700352071</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3824902332039439</v>
+        <v>8.4057058096368884</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.7950860186721833</v>
+        <v>9.822213824587541</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5325576605001419</v>
+        <v>2.5395716604336327</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.7938212782531631</v>
+        <v>3.8043283883610091</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.840839369224371</v>
+        <v>5.8570157618041874</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4623709524829511</v>
+        <v>8.4858077611383447</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.046908787017189</v>
+        <v>10.074734024192642</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.4940792688278628</v>
+        <v>2.5009867016174581</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6833943766750443</v>
+        <v>3.6935956559256486</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7406790389115372</v>
+        <v>5.7565780342335895</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5383414267622886</v>
+        <v>8.5619886380907797</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.293448560222092</v>
+        <v>10.321956597232603</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4303351916110159</v>
+        <v>2.4370660831275996</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.3934470362699862</v>
+        <v>3.4028452970314023</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.3874853078885385</v>
+        <v>5.4024061218074415</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8659210285157908</v>
+        <v>8.8904754820922047</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.450701258486546</v>
+        <v>11.482414344083022</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4227852510197292</v>
+        <v>2.4294952327329034</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3027846274398529</v>
+        <v>3.3119317957426757</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1948905293800216</v>
+        <v>5.2092779458625227</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1207983562530792</v>
+        <v>9.1460587007901157</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.491551370127675</v>
+        <v>12.526147123600854</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4218910251493311</v>
+        <v>2.4285985302751825</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2744357818756926</v>
+        <v>3.2835044371385154</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0898695580244171</v>
+        <v>5.1039661155473803</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.319108787814649</v>
+        <v>9.3449183594731355</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.427707281907438</v>
+        <v>13.464895749301951</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4217851117454279</v>
+        <v>2.4284923235406994</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2655715011314381</v>
+        <v>3.2746156064835046</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0326021465717927</v>
+        <v>5.0465401001559842</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4734066518705298</v>
+        <v>9.4996435564285218</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.26969968922762</v>
+        <v>14.309220081687871</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4526789987508533</v>
+        <v>8.4760889652285165</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9170148112900032</v>
+        <v>7.9389412385638716</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7794374980678382</v>
+        <v>6.7982133683677315</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4094307115720195</v>
+        <v>5.4244123039925833</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8548939934920408</v>
+        <v>3.8655702464499408</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9170148112900032</v>
+        <v>7.9389412385638716</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7794374980678382</v>
+        <v>6.7982133683677315</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4094307115720195</v>
+        <v>5.4244123039925833</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6644512640883171</v>
+        <v>6.682908676313172</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4526789987508533</v>
+        <v>8.4760889652285165</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8548939934920408</v>
+        <v>3.8655702464499408</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2201207182523266</v>
+        <v>0.19741662370587493</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4150458457392169E-2</v>
+        <v>-2.4243886533072509E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3324290602320019</v>
+        <v>6.3499669262794551</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8929634186849178</v>
+        <v>7.9148232348530394</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.918170073839633</v>
+        <v>2.9262520397601182</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3606281849430597</v>
+        <v>3.3687101508635449</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46929872360545066</v>
+        <v>0.4694917012997224</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6577207568127101</v>
+        <v>3.6678509321469792</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1664689112623732</v>
+        <v>4.1765990865966423</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34204254455402838</v>
+        <v>0.34226443458914568</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5388343419502464</v>
+        <v>4.5514047897110608</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1222017778022115</v>
+        <v>5.1347722255630259</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19111580578613718</v>
+        <v>0.1913702409515432</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1330847018854096</v>
+        <v>5.1473009451398744</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7647570318158445</v>
+        <v>5.7789732750703093</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9645225081346536E-2</v>
+        <v>8.9920728381446824E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>36079.701781919997</v>
+        <v>38164.70967384</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.2201207182523266</v>
+        <v>0.19741662370587493</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0916428500000002</v>
+        <v>1.0946661899999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3324290602320019</v>
+        <v>6.3499669262794551</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3606281849430597</v>
+        <v>3.3687101508635449</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1664689112623732</v>
+        <v>4.1765990865966423</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1222017778022115</v>
+        <v>5.1347722255630259</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7647570318158445</v>
+        <v>5.7789732750703093</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10782337246836637</v>
+        <v>0.10221509055023491</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>6.0753768844221102E-2</v>
+        <v>5.7434679334916861E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10175695388579474</v>
+        <v>-0.10203877304392053</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7583182828358246</v>
+        <v>1.7631880018993704</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1576133561597132E-4</v>
+        <v>5.1718975323114741E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.657077090285646</v>
+        <v>1.6616664186086809</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2404843517634361</v>
+        <v>1.2439199130919969</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5762084340663112</v>
+        <v>7.5971909871119765</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.45 HKD</v>
+        <v>8.48 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.92 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.41 HKD</v>
+        <v>5.42 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.85 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3324290602320019</v>
+        <v>6.3499669262794551</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.918170073839633</v>
+        <v>2.9262520397601182</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3606281849430597</v>
+        <v>3.3687101508635449</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6577207568127101</v>
+        <v>3.6678509321469792</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1664689112623732</v>
+        <v>4.1765990865966423</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5388343419502464</v>
+        <v>4.5514047897110608</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1222017778022115</v>
+        <v>5.1347722255630259</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1330847018854096</v>
+        <v>5.1473009451398744</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7647570318158445</v>
+        <v>5.7789732750703093</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,15 +21836,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21859,12 +21856,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677950B8-DA2A-42C7-BD68-A2083480D400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DCEFA5-52C2-48D5-A4B3-66C9B96C17EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>38164.70967384</v>
+        <v>38255.362190879998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.19741662370587493</v>
+        <v>0.19533826835250381</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3499669262794551</v>
+        <v>6.3311797365665701</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3687101508635449</v>
+        <v>3.3600524597516164</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1765990865966423</v>
+        <v>4.1657472802642896</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1347722255630259</v>
+        <v>5.1213063120807742</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7789732750703093</v>
+        <v>5.7637443265594994</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10221509055023491</v>
+        <v>0.10167117489729709</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7434679334916861E-2</v>
+        <v>5.7298578199052132E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10203877304392053</v>
+        <v>-0.10173687827667183</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7631880018993704</v>
+        <v>1.7579713845727392</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1718975323114741E-4</v>
+        <v>5.1565958116500633E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6616664186086809</v>
+        <v>1.6567501658772323</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2439199130919969</v>
+        <v>1.2402396168532595</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.48 HKD</v>
+        <v>8.45 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0339573200743415E-2</v>
+        <v>-6.0246482751229229E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.92 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8924636278625704E-2</v>
+        <v>-3.8827424825084021E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.8 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3892049371140979E-2</v>
+        <v>1.3999921882205443E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.42 HKD</v>
+        <v>5.41 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6309743429008221E-2</v>
+        <v>9.6435711709584496E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.85 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23368073645802717</v>
+        <v>0.23384103153358995</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3499669262794551</v>
+        <v>6.3311797365665701</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9262520397601182</v>
+        <v>2.9175943486481897</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3687101508635449</v>
+        <v>3.3600524597516164</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6678509321469792</v>
+        <v>3.6569991258146266</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1765990865966423</v>
+        <v>4.1657472802642896</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5514047897110608</v>
+        <v>4.5379388762288091</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1347722255630259</v>
+        <v>5.1213063120807742</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1473009451398744</v>
+        <v>5.1320719966290644</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7789732750703093</v>
+        <v>5.7637443265594994</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0925776084744196</v>
+        <v>3.0834278218839137</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2439199130919969</v>
+        <v>1.2402396168532595</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>925007.1612104699</v>
+        <v>922270.40915723995</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10203877304392055</v>
+        <v>0.10173687827667183</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15983743.038690623</v>
+        <v>15936453.089581262</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7631880018993704</v>
+        <v>1.7579713845727392</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4688.4552917699993</v>
+        <v>4674.5838968399994</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1718975323114741E-4</v>
+        <v>5.1565958116500633E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16913438.655192863</v>
+        <v>16863398.082635343</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8657439646965222</v>
+        <v>1.8602239224305761</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7434679334916861E-2</v>
+        <v>5.7298578199052132E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.7529691211401436E-2</v>
+        <v>7.7345971563981056E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7292161520190019E-2</v>
+        <v>6.7132701421800944E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7743467933491688E-2</v>
+        <v>6.7582938388625599E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11178147268408552</v>
+        <v>0.11151658767772513</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.0332541567695972E-2</v>
+        <v>7.0165876777251196E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.43032553121648892</v>
+        <v>0.4290523580665937</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35246587532430607</v>
+        <v>0.35142305992953116</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31670288799324298</v>
+        <v>0.31576588197282995</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49488176401280315</v>
+        <v>0.49341759298736398</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63085303918297131</v>
+        <v>0.62898657974063454</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54774609184803491</v>
+        <v>0.54612551494401163</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36559362376969029</v>
+        <v>0.36451196825127224</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21403601486188251</v>
+        <v>0.21340276192320051</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.4015388508853909E-2</v>
+        <v>9.373723195144941E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6326081452471489E-2</v>
+        <v>2.6248192371727219E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10221509055023491</v>
+        <v>0.10167117489729709</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3721110528338735E-2</v>
+        <v>8.3275606618372314E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.522633919079405E-2</v>
+        <v>7.4826038382187196E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11754911259211476</v>
+        <v>0.11692360023397251</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.1498463275969053</v>
+        <v>0.14904895254517408</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13010596005891567</v>
+        <v>0.12941362913365206</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.6839340562871806E-2</v>
+        <v>8.6377243661438924E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.0839908518261881E-2</v>
+        <v>5.0569374863317661E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.2331446201628007E-2</v>
+        <v>2.22126142065046E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.2532259982117549E-3</v>
+        <v>6.2199507989874926E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.574604474208058E-2</v>
+        <v>9.5519158380132529E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6214516712421682E-2</v>
+        <v>8.6010216909785608E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12965134655253724</v>
+        <v>0.12934411587350278</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18118560468808745</v>
+        <v>0.18075625491394504</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19485624451369637</v>
+        <v>0.19439449985845064</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1030946398813288</v>
+        <v>0.10285033978682329</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8752025605921306E-2</v>
+        <v>5.8612802796428602E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0400493280714695E-2</v>
+        <v>3.0328454197111106E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0642082789860627E-2</v>
+        <v>1.0616864584197449E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6616664186086809</v>
+        <v>1.6567501658772323</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68870448.541530296</v>
+        <v>68666686.506643713</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9148232348530394</v>
+        <v>7.8914062175073685</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.8019969847641653</v>
+        <v>5.7848310342431892</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6995939859380718</v>
+        <v>6.6797723798298225</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2979919867206755</v>
+        <v>7.276399943554245</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.7168705872684997</v>
+        <v>7.6940392381613423</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.896389987503281</v>
+        <v>7.8730275072786684</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6303085916234004</v>
+        <v>4.6166092311464162</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9882117472454652</v>
+        <v>5.9704948565210687</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0329672311293123</v>
+        <v>7.0121592976156899</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8306917454593172</v>
+        <v>7.807523641890743</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1893120857884707</v>
+        <v>8.1650829580528619</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8655702464499408</v>
+        <v>3.8541334622254459</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4244123039925833</v>
+        <v>5.4083634860665786</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7982133683677315</v>
+        <v>6.7780999841969223</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9389412385638716</v>
+        <v>7.9154528650180067</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4760889652285165</v>
+        <v>8.4510113713982236</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3664403241922045</v>
+        <v>3.3564802797129238</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9775782464028859</v>
+        <v>4.9628514442145333</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5902728838702931</v>
+        <v>6.5707747182315801</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0418918054325363</v>
+        <v>8.0180988394607162</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7568495464984952</v>
+        <v>8.730941286561519</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0406678807605818</v>
+        <v>3.0316716757420474</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6234440282665297</v>
+        <v>4.6097649774786484</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.406083177322448</v>
+        <v>6.3871299605000429</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.139802834062877</v>
+        <v>8.1157201857838537</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0317200456439259</v>
+        <v>9.0049985461619446</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8280425097562603</v>
+        <v>2.8196753841060449</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3427782143589289</v>
+        <v>4.3299295492963621</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2429314559047739</v>
+        <v>6.2244609443275847</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2329210151378867</v>
+        <v>8.2085628648044615</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.3008240308212713</v>
+        <v>9.2733063527637611</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6892660438326934</v>
+        <v>2.6813095061151802</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1203391077654903</v>
+        <v>4.108148557263779</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.098414779590752</v>
+        <v>6.0803718390932397</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3214809635728599</v>
+        <v>8.2968607972995851</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.564282477848046</v>
+        <v>9.5359853242620467</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5986893294769851</v>
+        <v>2.5910007745593711</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9440470419338616</v>
+        <v>3.9323780740677932</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9704046700352071</v>
+        <v>5.9527404638273866</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.4057058096368884</v>
+        <v>8.3808364533788602</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.822213824587541</v>
+        <v>9.7931535481065168</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5395716604336327</v>
+        <v>2.532058012704764</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.8043283883610091</v>
+        <v>3.7930727960103687</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8570157618041874</v>
+        <v>5.839687031190965</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4858077611383447</v>
+        <v>8.4607014130067046</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.074734024192642</v>
+        <v>10.044926634387817</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.5009867016174581</v>
+        <v>2.4935872124266982</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6935956559256486</v>
+        <v>3.6826676805336227</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7565780342335895</v>
+        <v>5.7395464614897076</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5619886380907797</v>
+        <v>8.5366568990863332</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.321956597232603</v>
+        <v>10.291417767810071</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4370660831275996</v>
+        <v>2.4298557112661228</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.4028452970314023</v>
+        <v>3.392777543781484</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.4024061218074415</v>
+        <v>5.38642241198741</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8904754820922047</v>
+        <v>8.8641718727255849</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.482414344083022</v>
+        <v>11.448442151920656</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4294952327329034</v>
+        <v>2.4223072602011086</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3119317957426757</v>
+        <v>3.3021330217198939</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2092779458625227</v>
+        <v>5.1938656304643054</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1460587007901157</v>
+        <v>9.1189989157657543</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.526147123600854</v>
+        <v>12.489086914450997</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4285985302751825</v>
+        <v>2.4214132107523541</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2835044371385154</v>
+        <v>3.2737897690938169</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.1039661155473803</v>
+        <v>5.0888653786751794</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3449183594731355</v>
+        <v>9.3172702227018611</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.464895749301951</v>
+        <v>13.425058132217767</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4284923235406994</v>
+        <v>2.4213073182440854</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2746156064835046</v>
+        <v>3.264927237181741</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0465401001559842</v>
+        <v>5.0316092654987301</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4996435564285218</v>
+        <v>9.4715376453629379</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.309220081687871</v>
+        <v>14.26688442302396</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4760889652285165</v>
+        <v>8.4510113713982236</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9389412385638716</v>
+        <v>7.9154528650180067</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7982133683677315</v>
+        <v>6.7780999841969223</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4244123039925833</v>
+        <v>5.4083634860665786</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8655702464499408</v>
+        <v>3.8541334622254459</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9389412385638716</v>
+        <v>7.9154528650180067</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7982133683677315</v>
+        <v>6.7780999841969223</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4244123039925833</v>
+        <v>5.4083634860665786</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.682908676313172</v>
+        <v>6.6631364358285534</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4760889652285165</v>
+        <v>8.4510113713982236</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8655702464499408</v>
+        <v>3.8541334622254459</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19741662370587493</v>
+        <v>0.19533826835250381</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4243886533072509E-2</v>
+        <v>-2.4143783312465427E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3499669262794551</v>
+        <v>6.3311797365665701</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.9148232348530394</v>
+        <v>7.8914062175073685</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.29381947754327764</v>
+        <v>0.2938194775432777</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9262520397601182</v>
+        <v>2.9175943486481897</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3687101508635449</v>
+        <v>3.3600524597516164</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.4694917012997224</v>
+        <v>0.4692849358950929</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6678509321469792</v>
+        <v>3.6569991258146266</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1765990865966423</v>
+        <v>4.1657472802642896</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34226443458914568</v>
+        <v>0.34202669113870476</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5514047897110608</v>
+        <v>4.5379388762288091</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1347722255630259</v>
+        <v>5.1213063120807742</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.1913702409515432</v>
+        <v>0.19109762711331835</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1473009451398744</v>
+        <v>5.1320719966290644</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7789732750703093</v>
+        <v>5.7637443265594994</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9920728381446824E-2</v>
+        <v>8.9625541149901622E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>38164.70967384</v>
+        <v>38255.362190879998</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.19741662370587493</v>
+        <v>0.19533826835250381</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3499669262794551</v>
+        <v>6.3311797365665701</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3687101508635449</v>
+        <v>3.3600524597516164</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1765990865966423</v>
+        <v>4.1657472802642896</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1347722255630259</v>
+        <v>5.1213063120807742</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7789732750703093</v>
+        <v>5.7637443265594994</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10221509055023491</v>
+        <v>0.10167117489729709</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.7434679334916861E-2</v>
+        <v>5.7298578199052132E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10203877304392053</v>
+        <v>-0.10173687827667183</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7631880018993704</v>
+        <v>1.7579713845727392</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1718975323114741E-4</v>
+        <v>5.1565958116500633E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6616664186086809</v>
+        <v>1.6567501658772323</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2439199130919969</v>
+        <v>1.2402396168532595</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5971909871119765</v>
+        <v>7.5747137254164558</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.48 HKD</v>
+        <v>8.45 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.92 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.8 HKD</v>
+        <v>6.78 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.42 HKD</v>
+        <v>5.41 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.85 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3499669262794551</v>
+        <v>6.3311797365665701</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9262520397601182</v>
+        <v>2.9175943486481897</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3687101508635449</v>
+        <v>3.3600524597516164</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6678509321469792</v>
+        <v>3.6569991258146266</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1765990865966423</v>
+        <v>4.1657472802642896</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5514047897110608</v>
+        <v>4.5379388762288091</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1347722255630259</v>
+        <v>5.1213063120807742</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1473009451398744</v>
+        <v>5.1320719966290644</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7789732750703093</v>
+        <v>5.7637443265594994</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,12 +21836,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21856,15 +21859,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DCEFA5-52C2-48D5-A4B3-66C9B96C17EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB33E43-0216-40DA-868C-C8EF3F181411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.22</v>
+        <v>4.41</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>38255.362190879998</v>
+        <v>39977.76001464</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.19533826835250381</v>
+        <v>0.17744503402744635</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3311797365665701</v>
+        <v>6.3370746508781428</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3600524597516164</v>
+        <v>3.3627690101256129</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1657472802642896</v>
+        <v>4.169152284920794</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1213063120807742</v>
+        <v>5.1255315531795258</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7637443265594994</v>
+        <v>5.7685227605828171</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10167117489729709</v>
+        <v>9.7381370866784847E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7298578199052132E-2</v>
+        <v>5.4829931972789112E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10173687827667183</v>
+        <v>-0.10183160472651563</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7579713845727392</v>
+        <v>1.7596082186392876</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1565958116500633E-4</v>
+        <v>5.1613970796149464E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6567501658772323</v>
+        <v>1.6582927536207335</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2402396168532595</v>
+        <v>1.2413943947258479</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.45 HKD</v>
+        <v>8.46 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0246482751229229E-2</v>
+        <v>-6.0275751326631238E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8827424825084021E-2</v>
+        <v>-3.8857989113218888E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3999921882205443E-2</v>
+        <v>1.3966005569312101E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6435711709584496E-2</v>
+        <v>9.6396105736473253E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.85 HKD</v>
+        <v>3.86 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23384103153358995</v>
+        <v>0.23379063245115386</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3311797365665701</v>
+        <v>6.3370746508781428</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9175943486481897</v>
+        <v>2.9203108990221862</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3600524597516164</v>
+        <v>3.3627690101256129</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6569991258146266</v>
+        <v>3.660404130471131</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1657472802642896</v>
+        <v>4.169152284920794</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5379388762288091</v>
+        <v>4.5421641173275606</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1213063120807742</v>
+        <v>5.1255315531795258</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1320719966290644</v>
+        <v>5.1368504306523821</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7637443265594994</v>
+        <v>5.7685227605828171</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0834278218839137</v>
+        <v>3.086298778570066</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2402396168532595</v>
+        <v>1.2413943947258479</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>922270.40915723995</v>
+        <v>923129.1282681002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10173687827667183</v>
+        <v>0.10183160472651563</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15936453.089581262</v>
+        <v>15951291.402392207</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7579713845727392</v>
+        <v>1.7596082186392876</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4674.5838968399994</v>
+        <v>4678.936367100001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1565958116500633E-4</v>
+        <v>5.1613970796149464E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16863398.082635343</v>
+        <v>16879099.467027403</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8602239224305761</v>
+        <v>1.8619559630737648</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7298578199052132E-2</v>
+        <v>5.4829931972789112E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.7345971563981056E-2</v>
+        <v>7.4013605442176875E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7132701421800944E-2</v>
+        <v>6.4240362811791379E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7582938388625599E-2</v>
+        <v>6.4671201814058957E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11151658767772513</v>
+        <v>0.10671201814058957</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.0165876777251196E-2</v>
+        <v>6.7142857142857143E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.4290523580665937</v>
+        <v>0.42945184552252119</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35142305992953116</v>
+        <v>0.35175026732398096</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31576588197282995</v>
+        <v>0.316059889234383</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49341759298736398</v>
+        <v>0.49387701043427101</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62898657974063454</v>
+        <v>0.62957222446167849</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54612551494401163</v>
+        <v>0.54663400834459619</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36451196825127224</v>
+        <v>0.36485136263080215</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21340276192320051</v>
+        <v>0.21360145964585789</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.373723195144941E-2</v>
+        <v>9.3824509990164118E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6248192371727219E-2</v>
+        <v>2.6272631868203892E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10167117489729709</v>
+        <v>9.7381370866784847E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.3275606618372314E-2</v>
+        <v>7.9761965379587518E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.4826038382187196E-2</v>
+        <v>7.1668909123442856E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11692360023397251</v>
+        <v>0.11199025179915442</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.14904895254517408</v>
+        <v>0.14276014160128764</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12941362913365206</v>
+        <v>0.12395328987405808</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.6377243661438924E-2</v>
+        <v>8.273273529043132E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.0569374863317661E-2</v>
+        <v>4.8435705135115165E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.22126142065046E-2</v>
+        <v>2.1275399090740162E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.2199507989874926E-3</v>
+        <v>5.9575128952843292E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5519158380132529E-2</v>
+        <v>9.1403820490739057E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6010216909785608E-2</v>
+        <v>8.2304561305962642E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12934411587350278</v>
+        <v>0.12377146689029064</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18075625491394504</v>
+        <v>0.17296857046187031</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19439449985845064</v>
+        <v>0.18601922662191875</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10285033978682329</v>
+        <v>9.8419146009159686E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8612802796428602E-2</v>
+        <v>5.6087534648736663E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0328454197111106E-2</v>
+        <v>2.9021786102450989E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0616864584197449E-2</v>
+        <v>1.0159448649730892E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6567501658772323</v>
+        <v>1.6582927536207335</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68666686.506643713</v>
+        <v>68730621.547166795</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8914062175073685</v>
+        <v>7.8987538470781002</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.7848310342431892</v>
+        <v>5.79021724734607</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6797723798298225</v>
+        <v>6.6859918661559625</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.276399943554245</v>
+        <v>7.2831749453625569</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.6940392381613423</v>
+        <v>7.7012031008071746</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8730275072786684</v>
+        <v>7.8803580245691531</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6166092311464162</v>
+        <v>4.6209077216268621</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9704948565210687</v>
+        <v>5.9760539398264445</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0121592976156899</v>
+        <v>7.0186882669260697</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.807523641890743</v>
+        <v>7.8147931690198975</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1650829580528619</v>
+        <v>8.1726854059989531</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8541334622254459</v>
+        <v>3.8577220171947455</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4083634860665786</v>
+        <v>5.4133991730384805</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7780999841969223</v>
+        <v>6.7844110226233534</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9154528650180067</v>
+        <v>7.922822884243188</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4510113713982236</v>
+        <v>8.4588800451609956</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3564802797129238</v>
+        <v>3.3596054735094474</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9628514442145333</v>
+        <v>4.9674723182414926</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5707747182315801</v>
+        <v>6.5768927176465883</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0180988394607162</v>
+        <v>8.0255644315884123</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.730941286561519</v>
+        <v>8.7390706009839789</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0316716757420474</v>
+        <v>3.034494442665896</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6097649774786484</v>
+        <v>4.6140570953254656</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.3871299605000429</v>
+        <v>6.3930769696485221</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1157201857838537</v>
+        <v>8.1232766724202357</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0049985461619446</v>
+        <v>9.0133830332582239</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8196753841060449</v>
+        <v>2.8223007628612482</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3299295492963621</v>
+        <v>4.3339611144596173</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2244609443275847</v>
+        <v>6.2302564935663183</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2085628648044615</v>
+        <v>8.2162057965679853</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2733063527637611</v>
+        <v>9.2819406592609806</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6813095061151802</v>
+        <v>2.6838060534316406</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.108148557263779</v>
+        <v>4.1119736237967057</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0803718390932397</v>
+        <v>6.086033228038958</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.2968607972995851</v>
+        <v>8.3045859426106006</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5359853242620467</v>
+        <v>9.5448642091937543</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5910007745593711</v>
+        <v>2.5934132360883071</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9323780740677932</v>
+        <v>3.9360394820125797</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9527404638273866</v>
+        <v>5.9582830161499221</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3808364533788602</v>
+        <v>8.3886397877979775</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.7931535481065168</v>
+        <v>9.8022718804566065</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.532058012704764</v>
+        <v>2.5344155930670174</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.7930727960103687</v>
+        <v>3.7966044978480054</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.839687031190965</v>
+        <v>5.8451243203041532</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4607014130067046</v>
+        <v>8.4685791090950673</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.044926634387817</v>
+        <v>10.054279390783872</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.4935872124266982</v>
+        <v>2.4959089729132611</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6826676805336227</v>
+        <v>3.6860965849903007</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7395464614897076</v>
+        <v>5.7448905104640815</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5366568990863332</v>
+        <v>8.5446053167622313</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.291417767810071</v>
+        <v>10.301000030265115</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4298557112661228</v>
+        <v>2.4321181318264919</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.392777543781484</v>
+        <v>3.3959365336903167</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.38642241198741</v>
+        <v>5.3914376697886084</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8641718727255849</v>
+        <v>8.872425237154804</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.448442151920656</v>
+        <v>11.459101711164692</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4223072602011086</v>
+        <v>2.4245626524548958</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3021330217198939</v>
+        <v>3.3052076131891623</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1938656304643054</v>
+        <v>5.1987016000799802</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1189989157657543</v>
+        <v>9.1274895477573388</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.489086914450997</v>
+        <v>12.500715410284919</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4214132107523541</v>
+        <v>2.4236677705633562</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2737897690938169</v>
+        <v>3.2768379703716053</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0888653786751794</v>
+        <v>5.0936035833382318</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3172702227018611</v>
+        <v>9.3259454636310313</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.425058132217767</v>
+        <v>13.437558103883431</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4213073182440854</v>
+        <v>2.4235617794593618</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.264927237181741</v>
+        <v>3.2679671866220557</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0316092654987301</v>
+        <v>5.036294159421125</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4715376453629379</v>
+        <v>9.4803565235406939</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.26688442302396</v>
+        <v>14.280168212880863</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4510113713982236</v>
+        <v>8.4588800451609956</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9154528650180067</v>
+        <v>7.922822884243188</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7780999841969223</v>
+        <v>6.7844110226233534</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4083634860665786</v>
+        <v>5.4133991730384805</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8541334622254459</v>
+        <v>3.8577220171947455</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9154528650180067</v>
+        <v>7.922822884243188</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7780999841969223</v>
+        <v>6.7844110226233534</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4083634860665786</v>
+        <v>5.4133991730384805</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6631364358285534</v>
+        <v>6.6693404325511025</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4510113713982236</v>
+        <v>8.4588800451609956</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8541334622254459</v>
+        <v>3.8577220171947455</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.22</v>
+        <v>4.41</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19533826835250381</v>
+        <v>0.17744503402744635</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4143783312465427E-2</v>
+        <v>-2.4175256821875095E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3311797365665701</v>
+        <v>6.3370746508781428</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8914062175073685</v>
+        <v>7.8987538470781002</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9175943486481897</v>
+        <v>2.9203108990221862</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3600524597516164</v>
+        <v>3.3627690101256129</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.4692849358950929</v>
+        <v>0.46934994530013519</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6569991258146266</v>
+        <v>3.660404130471131</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1657472802642896</v>
+        <v>4.169152284920794</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34202669113870476</v>
+        <v>0.34210144039520429</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5379388762288091</v>
+        <v>4.5421641173275606</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1213063120807742</v>
+        <v>5.1255315531795258</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19109762711331835</v>
+        <v>0.19118334001805248</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1320719966290644</v>
+        <v>5.1368504306523821</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7637443265594994</v>
+        <v>5.7685227605828171</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9625541149901622E-2</v>
+        <v>8.971835138734563E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.22</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>38255.362190879998</v>
+        <v>39977.76001464</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.19533826835250381</v>
+        <v>0.17744503402744635</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3311797365665701</v>
+        <v>6.3370746508781428</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3600524597516164</v>
+        <v>3.3627690101256129</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1657472802642896</v>
+        <v>4.169152284920794</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1213063120807742</v>
+        <v>5.1255315531795258</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7637443265594994</v>
+        <v>5.7685227605828171</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10167117489729709</v>
+        <v>9.7381370866784847E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.7298578199052132E-2</v>
+        <v>5.4829931972789112E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10173687827667183</v>
+        <v>-0.10183160472651563</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7579713845727392</v>
+        <v>1.7596082186392876</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1565958116500633E-4</v>
+        <v>5.1613970796149464E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6567501658772323</v>
+        <v>1.6582927536207335</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2402396168532595</v>
+        <v>1.2413943947258479</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5747137254164558</v>
+        <v>7.5817664849658533</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.45 HKD</v>
+        <v>8.46 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.85 HKD</v>
+        <v>3.86 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3311797365665701</v>
+        <v>6.3370746508781428</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9175943486481897</v>
+        <v>2.9203108990221862</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3600524597516164</v>
+        <v>3.3627690101256129</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6569991258146266</v>
+        <v>3.660404130471131</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1657472802642896</v>
+        <v>4.169152284920794</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5379388762288091</v>
+        <v>4.5421641173275606</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1213063120807742</v>
+        <v>5.1255315531795258</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1320719966290644</v>
+        <v>5.1368504306523821</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7637443265594994</v>
+        <v>5.7685227605828171</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,15 +21836,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21859,12 +21856,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB33E43-0216-40DA-868C-C8EF3F181411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B2F3F4-071C-4CED-8BE5-B1E5FADFFDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>39977.76001464</v>
+        <v>38799.277293120002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.17744503402744635</v>
+        <v>0.190816596048551</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3370746508781428</v>
+        <v>6.3547161196588675</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3627690101256129</v>
+        <v>3.3708987192411541</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.169152284920794</v>
+        <v>4.1793423029890828</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1255315531795258</v>
+        <v>5.1381762592761566</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7685227605828171</v>
+        <v>5.7828229845025474</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.7381370866784847E-2</v>
+        <v>0.10061854562635701</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.4829931972789112E-2</v>
+        <v>5.6495327102803729E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10183160472651563</v>
+        <v>-0.10211508869579866</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7596082186392876</v>
+        <v>1.764506704954441</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1613970796149464E-4</v>
+        <v>5.175765637737002E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6582927536207335</v>
+        <v>1.6629091928224158</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2413943947258479</v>
+        <v>1.2448502511999526</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.46 HKD</v>
+        <v>8.48 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0275751326631238E-2</v>
+        <v>-6.0363018460194331E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.92 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8857989113218888E-2</v>
+        <v>-3.8949119391683037E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3966005569312101E-2</v>
+        <v>1.3864881339780043E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.41 HKD</v>
+        <v>5.43 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6396105736473253E-2</v>
+        <v>9.6278018140195515E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.86 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23379063245115386</v>
+        <v>0.23364036642040975</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3370746508781428</v>
+        <v>6.3547161196588675</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9203108990221862</v>
+        <v>2.9284406081377274</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3627690101256129</v>
+        <v>3.3708987192411541</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.660404130471131</v>
+        <v>3.6705941485394193</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.169152284920794</v>
+        <v>4.1793423029890828</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5421641173275606</v>
+        <v>4.5548088234241915</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1255315531795258</v>
+        <v>5.1381762592761566</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1368504306523821</v>
+        <v>5.1511506545721124</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7685227605828171</v>
+        <v>5.7828229845025474</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.086298778570066</v>
+        <v>3.0948905731361256</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2413943947258479</v>
+        <v>1.2448502511999526</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>923129.1282681002</v>
+        <v>925698.98180369998</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10183160472651563</v>
+        <v>0.10211508869579866</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15951291.402392207</v>
+        <v>15995697.41380767</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7596082186392876</v>
+        <v>1.764506704954441</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4678.936367100001</v>
+        <v>4691.9618266999996</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1613970796149464E-4</v>
+        <v>5.1757656377370009E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16879099.467027403</v>
+        <v>16926088.357438069</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8619559630737648</v>
+        <v>1.8671393702140133</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4829931972789112E-2</v>
+        <v>5.6495327102803729E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.4013605442176875E-2</v>
+        <v>7.6261682242990653E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.4240362811791379E-2</v>
+        <v>6.6191588785046718E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.4671201814058957E-2</v>
+        <v>6.6635514018691583E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.10671201814058957</v>
+        <v>0.10995327102803738</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>6.7142857142857143E-2</v>
+        <v>6.9182242990654202E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42945184552252119</v>
+        <v>0.43064737528080804</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35175026732398096</v>
+        <v>0.35272948750071464</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.316059889234383</v>
+        <v>0.31693975273228181</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49387701043427101</v>
+        <v>0.49525189022362087</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62957222446167849</v>
+        <v>0.63132485944784089</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54663400834459619</v>
+        <v>0.54815575573183217</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36485136263080215</v>
+        <v>0.36586705429897021</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21360145964585789</v>
+        <v>0.21419609418773397</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3824509990164118E-2</v>
+        <v>9.4085703404325469E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6272631868203892E-2</v>
+        <v>2.6345770948998239E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.7381370866784847E-2</v>
+        <v>0.10061854562635701</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.9761965379587518E-2</v>
+        <v>8.2413431659045466E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.1668909123442856E-2</v>
+        <v>7.405134409632752E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11199025179915442</v>
+        <v>0.11571305846346282</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.14276014160128764</v>
+        <v>0.1475058082822058</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12395328987405808</v>
+        <v>0.1280737747036991</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.273273529043132E-2</v>
+        <v>8.5482956611908925E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>4.8435705135115165E-2</v>
+        <v>5.0045816399003261E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.1275399090740162E-2</v>
+        <v>2.1982640982319033E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>5.9575128952843292E-3</v>
+        <v>6.155553960046317E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1403820490739057E-2</v>
+        <v>9.4180104757981123E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2304561305962642E-2</v>
+        <v>8.4804466205442811E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12377146689029064</v>
+        <v>0.12753088060424805</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17296857046187031</v>
+        <v>0.17822228872356261</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18601922662191875</v>
+        <v>0.1916693433183789</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8419146009159686E-2</v>
+        <v>0.10140851259355005</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6087534648736663E-2</v>
+        <v>5.7791127990871181E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9021786102450989E-2</v>
+        <v>2.9903288951357208E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0159448649730892E-2</v>
+        <v>1.046803003395169E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6582927536207335</v>
+        <v>1.6629091928224158</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68730621.547166795</v>
+        <v>68921957.32607168</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.8987538470781002</v>
+        <v>7.9207427973551088</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.79021724734607</v>
+        <v>5.8063363468407418</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6859918661559625</v>
+        <v>6.7046046683199112</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2831749453625569</v>
+        <v>7.3034502159726902</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.7012031008071746</v>
+        <v>7.7226420993296365</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8803580245691531</v>
+        <v>7.90229576362547</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6209077216268621</v>
+        <v>4.6337716381499847</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9760539398264445</v>
+        <v>5.9926903809005232</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0186882669260697</v>
+        <v>7.0382272461497806</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8147931690198975</v>
+        <v>7.8365483853167381</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1726854059989531</v>
+        <v>8.1954369407981584</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8577220171947455</v>
+        <v>3.8684613387714015</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4133991730384805</v>
+        <v>5.4284692673280475</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7844110226233534</v>
+        <v>6.8032978090106067</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.922822884243188</v>
+        <v>7.944878839122655</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4588800451609956</v>
+        <v>8.4824283030651255</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3596054735094474</v>
+        <v>3.3689581130697617</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9674723182414926</v>
+        <v>4.9813010188090683</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5768927176465883</v>
+        <v>6.5952018040854634</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0255644315884123</v>
+        <v>8.0479064035814272</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7390706009839789</v>
+        <v>8.7633988675222998</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.034494442665896</v>
+        <v>3.0429420217027241</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6140570953254656</v>
+        <v>4.6269019407287599</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.3930769696485221</v>
+        <v>6.4108743405154085</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1232766724202357</v>
+        <v>8.1458906606890711</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0133830332582239</v>
+        <v>9.0384749446132364</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8223007628612482</v>
+        <v>2.8301576264048918</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3339611144596173</v>
+        <v>4.3460262145112658</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2302564935663183</v>
+        <v>6.2476005965605799</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2162057965679853</v>
+        <v>8.239078485630607</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2819406592609806</v>
+        <v>9.3077801949120555</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6838060534316406</v>
+        <v>2.6912773684016438</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1119736237967057</v>
+        <v>4.1234207438493815</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.086033228038958</v>
+        <v>6.1029758350155108</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3045859426106006</v>
+        <v>8.3277046687917888</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5448642091937543</v>
+        <v>9.5714356847150999</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5934132360883071</v>
+        <v>2.6006329109636264</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9360394820125797</v>
+        <v>3.9469968277070953</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9582830161499221</v>
+        <v>5.9748699856282697</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3886397877979775</v>
+        <v>8.4119925073226991</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.8022718804566065</v>
+        <v>9.8295599404663268</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5344155930670174</v>
+        <v>2.5414710273210983</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.7966044978480054</v>
+        <v>3.8071736773845384</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8451243203041532</v>
+        <v>5.861396272884325</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4685791090950673</v>
+        <v>8.4921543677437086</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.054279390783872</v>
+        <v>10.082269002040956</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.4959089729132611</v>
+        <v>2.5028572104914755</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6860965849903007</v>
+        <v>3.6963581270123487</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7448905104640815</v>
+        <v>5.7608834270971503</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5446053167622313</v>
+        <v>8.5683922210112424</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.301000030265115</v>
+        <v>10.329676474911222</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4321181318264919</v>
+        <v>2.4388887852363745</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.3959365336903167</v>
+        <v>3.4053903134926609</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.3914376697886084</v>
+        <v>5.4064466265351747</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.872425237154804</v>
+        <v>8.8971247430709735</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.459101711164692</v>
+        <v>11.491002137817334</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4245626524548958</v>
+        <v>2.4313122725393406</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3052076131891623</v>
+        <v>3.3144088172358606</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.1987016000799802</v>
+        <v>5.2131740084120182</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1274895477573388</v>
+        <v>9.1528991145960124</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.500715410284919</v>
+        <v>12.535515533811427</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4236677705633562</v>
+        <v>2.4304148994303514</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2768379703716053</v>
+        <v>3.2859601975724151</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0936035833382318</v>
+        <v>5.107783414498086</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3259454636310313</v>
+        <v>9.3519075020811524</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.437558103883431</v>
+        <v>13.474966257461988</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4235617794593618</v>
+        <v>2.4303086132629628</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2679671866220557</v>
+        <v>3.2770647188866056</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.036294159421125</v>
+        <v>5.0503144497094308</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4803565235406939</v>
+        <v>9.5067484193055645</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.280168212880863</v>
+        <v>14.319922067078576</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4588800451609956</v>
+        <v>8.4824283030651255</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.922822884243188</v>
+        <v>7.944878839122655</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7844110226233534</v>
+        <v>6.8032978090106067</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4133991730384805</v>
+        <v>5.4284692673280475</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8577220171947455</v>
+        <v>3.8684613387714015</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.922822884243188</v>
+        <v>7.944878839122655</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7844110226233534</v>
+        <v>6.8032978090106067</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4133991730384805</v>
+        <v>5.4284692673280475</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6693404325511025</v>
+        <v>6.6879068796123766</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4588800451609956</v>
+        <v>8.4824283030651255</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8577220171947455</v>
+        <v>3.8684613387714015</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17744503402744635</v>
+        <v>0.190816596048551</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4175256821875095E-2</v>
+        <v>-2.4269097920927997E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3370746508781428</v>
+        <v>6.3547161196588675</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.8987538470781002</v>
+        <v>7.9207427973551088</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9203108990221862</v>
+        <v>2.9284406081377274</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3627690101256129</v>
+        <v>3.3708987192411541</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46934994530013519</v>
+        <v>0.46954377571438866</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.660404130471131</v>
+        <v>3.6705941485394193</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.169152284920794</v>
+        <v>4.1793423029890828</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34210144039520429</v>
+        <v>0.3423243109066787</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5421641173275606</v>
+        <v>4.5548088234241915</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1255315531795258</v>
+        <v>5.1381762592761566</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19118334001805248</v>
+        <v>0.19143889946857562</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1368504306523821</v>
+        <v>5.1511506545721124</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7685227605828171</v>
+        <v>5.7828229845025474</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.971835138734563E-2</v>
+        <v>8.9995072067360904E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>39977.76001464</v>
+        <v>38799.277293120002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.17744503402744635</v>
+        <v>0.190816596048551</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3370746508781428</v>
+        <v>6.3547161196588675</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3627690101256129</v>
+        <v>3.3708987192411541</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.169152284920794</v>
+        <v>4.1793423029890828</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1255315531795258</v>
+        <v>5.1381762592761566</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7685227605828171</v>
+        <v>5.7828229845025474</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.7381370866784847E-2</v>
+        <v>0.10061854562635701</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.4829931972789112E-2</v>
+        <v>5.6495327102803729E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10183160472651563</v>
+        <v>-0.10211508869579866</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7596082186392876</v>
+        <v>1.764506704954441</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1613970796149464E-4</v>
+        <v>5.175765637737002E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6582927536207335</v>
+        <v>1.6629091928224158</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2413943947258479</v>
+        <v>1.2448502511999526</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5817664849658533</v>
+        <v>7.6028729897990805</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.46 HKD</v>
+        <v>8.48 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.92 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.78 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.41 HKD</v>
+        <v>5.43 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.86 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3370746508781428</v>
+        <v>6.3547161196588675</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9203108990221862</v>
+        <v>2.9284406081377274</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3627690101256129</v>
+        <v>3.3708987192411541</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.660404130471131</v>
+        <v>3.6705941485394193</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.169152284920794</v>
+        <v>4.1793423029890828</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5421641173275606</v>
+        <v>4.5548088234241915</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1255315531795258</v>
+        <v>5.1381762592761566</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1368504306523821</v>
+        <v>5.1511506545721124</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7685227605828171</v>
+        <v>5.7828229845025474</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,12 +21836,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21856,15 +21859,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B2F3F4-071C-4CED-8BE5-B1E5FADFFDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C07DAE4-1F57-4AC3-B56B-3D22B296D912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>38799.277293120002</v>
+        <v>38617.972259039998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.190816596048551</v>
+        <v>0.19212406523521777</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3547161196588675</v>
+        <v>6.3435947781007966</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3708987192411541</v>
+        <v>3.3657736770484949</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1793423029890828</v>
+        <v>4.1729184233887535</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1381762592761566</v>
+        <v>5.130204922130142</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7828229845025474</v>
+        <v>5.7738079939399709</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10061854562635701</v>
+        <v>0.10091401467201033</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6495327102803729E-2</v>
+        <v>5.6760563380281688E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10211508869579866</v>
+        <v>-0.1019363778362993</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.764506704954441</v>
+        <v>1.7614186548546737</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.175765637737002E-4</v>
+        <v>5.1667075686749186E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6629091928224158</v>
+        <v>1.6599989477752417</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2448502511999526</v>
+        <v>1.2426716480064259</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.48 HKD</v>
+        <v>8.47 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0363018460194331E-2</v>
+        <v>-6.0308060895368665E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.93 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8949119391683037E-2</v>
+        <v>-3.8891728989395351E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.8 HKD</v>
+        <v>6.79 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3864881339780043E-2</v>
+        <v>1.3928565480441156E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.43 HKD</v>
+        <v>5.42 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6278018140195515E-2</v>
+        <v>9.6352385012812264E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.86 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23364036642040975</v>
+        <v>0.23373499766474543</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3547161196588675</v>
+        <v>6.3435947781007966</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9284406081377274</v>
+        <v>2.9233155659450683</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3708987192411541</v>
+        <v>3.3657736770484949</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6705941485394193</v>
+        <v>3.66417026893909</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1793423029890828</v>
+        <v>4.1729184233887535</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5548088234241915</v>
+        <v>4.5468374862781769</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1381762592761566</v>
+        <v>5.130204922130142</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1511506545721124</v>
+        <v>5.1421356640095359</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7828229845025474</v>
+        <v>5.7738079939399709</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0948905731361256</v>
+        <v>3.0894742280940206</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2448502511999526</v>
+        <v>1.2426716480064259</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>925698.98180369998</v>
+        <v>924078.92288010009</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10211508869579866</v>
+        <v>0.1019363778362993</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15995697.41380767</v>
+        <v>15967703.462378718</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.764506704954441</v>
+        <v>1.7614186548546735</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4691.9618266999996</v>
+        <v>4683.7504591000006</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1757656377370009E-4</v>
+        <v>5.1667075686749186E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16926088.357438069</v>
+        <v>16896466.135717917</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8671393702140133</v>
+        <v>1.8638717034478405</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6495327102803729E-2</v>
+        <v>5.6760563380281688E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.6261682242990653E-2</v>
+        <v>7.6619718309859169E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6191588785046718E-2</v>
+        <v>6.6502347417840377E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6635514018691583E-2</v>
+        <v>6.6948356807511739E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.10995327102803738</v>
+        <v>0.11046948356807512</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>6.9182242990654202E-2</v>
+        <v>6.950704225352114E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.43064737528080804</v>
+        <v>0.42989370250276399</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35272948750071464</v>
+        <v>0.35211217824028002</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31693975273228181</v>
+        <v>0.31638507882126915</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49525189022362087</v>
+        <v>0.49438515356304558</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63132485944784089</v>
+        <v>0.63021998249286559</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54815575573183217</v>
+        <v>0.54719643240853588</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36586705429897021</v>
+        <v>0.36522675308030261</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21419609418773397</v>
+        <v>0.21382123119165189</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.4085703404325469E-2</v>
+        <v>9.3921044712483387E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6345770948998239E-2</v>
+        <v>2.6299663410625583E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10061854562635701</v>
+        <v>0.10091401467201033</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2413431659045466E-2</v>
+        <v>8.2655440901474184E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.405134409632752E-2</v>
+        <v>7.4268797845368342E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11571305846346282</v>
+        <v>0.11605285294907174</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.1475058082822058</v>
+        <v>0.14793896302649429</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1280737747036991</v>
+        <v>0.12844986676256712</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.5482956611908925E-2</v>
+        <v>8.5733979596315166E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.0045816399003261E-2</v>
+        <v>5.0192777275035655E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.1982640982319033E-2</v>
+        <v>2.204719359447967E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.155553960046317E-3</v>
+        <v>6.1736299085975548E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4180104757981123E-2</v>
+        <v>9.4622264874215781E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4804466205442811E-2</v>
+        <v>8.5202609239271185E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12753088060424805</v>
+        <v>0.12812961713290652</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17822228872356261</v>
+        <v>0.17905901308376715</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1916693433183789</v>
+        <v>0.19256919939029615</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10140851259355005</v>
+        <v>0.10188460889680614</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7791127990871181E-2</v>
+        <v>5.8062447840593584E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9903288951357208E-2</v>
+        <v>3.0043679979297855E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.046803003395169E-2</v>
+        <v>1.0517175714862262E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6629091928224158</v>
+        <v>1.6599989477752417</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68921957.32607168</v>
+        <v>68801337.519641176</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9207427973551088</v>
+        <v>7.9068807641211603</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.8063363468407418</v>
+        <v>5.7961747206566088</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.7046046683199112</v>
+        <v>6.6928709894074023</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.3034502159726902</v>
+        <v>7.2906685019079305</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.7226420993296365</v>
+        <v>7.7091267606583012</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.90229576362547</v>
+        <v>7.8884660144084595</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6337716381499847</v>
+        <v>4.625662108767461</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9926903809005232</v>
+        <v>5.9822026179032779</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0382272461497806</v>
+        <v>7.0259096968377666</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8365483853167381</v>
+        <v>7.8228337000989612</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1954369407981584</v>
+        <v>8.1810941673807456</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8684613387714015</v>
+        <v>3.8616911732687167</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4284692673280475</v>
+        <v>5.418968943517724</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.8032978090106067</v>
+        <v>6.7913914079644275</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.944878839122655</v>
+        <v>7.9309745655809891</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4824283030651255</v>
+        <v>8.4675832681927723</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3689581130697617</v>
+        <v>3.363062124458347</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9813010188090683</v>
+        <v>4.9725832808345327</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5952018040854634</v>
+        <v>6.5836595903143822</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0479064035814272</v>
+        <v>8.0338218222631959</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7633988675222998</v>
+        <v>8.7480621081486074</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0429420217027241</v>
+        <v>3.0376165914352615</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6269019407287599</v>
+        <v>4.6188044339527519</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4108743405154085</v>
+        <v>6.3996547168714537</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1458906606890711</v>
+        <v>8.1316345978490698</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0384749446132364</v>
+        <v>9.0226567766368362</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8301576264048918</v>
+        <v>2.8252045885297523</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3460262145112658</v>
+        <v>4.3384202662608971</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2476005965605799</v>
+        <v>6.2366667170851757</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.239078485630607</v>
+        <v>8.2246593354692052</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.3077801949120555</v>
+        <v>9.2914907178141206</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6912773684016438</v>
+        <v>2.6865673838361794</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1234207438493815</v>
+        <v>4.1162043757825026</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.1029758350155108</v>
+        <v>6.0922950622628322</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3277046687917888</v>
+        <v>8.3131304146044371</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5714356847150999</v>
+        <v>9.5546847860995783</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.6006329109636264</v>
+        <v>2.5960815625909568</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9469968277070953</v>
+        <v>3.9400892178275986</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9748699856282697</v>
+        <v>5.9644134099726447</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.4119925073226991</v>
+        <v>8.3972707416141645</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.8295599404663268</v>
+        <v>9.8123573005049192</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5414710273210983</v>
+        <v>2.5370232177222807</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.8071736773845384</v>
+        <v>3.8005107709635726</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.861396272884325</v>
+        <v>5.8511382867319162</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4921543677437086</v>
+        <v>8.4772923113576848</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.082269002040956</v>
+        <v>10.064624097824831</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.5028572104914755</v>
+        <v>2.4984769786471532</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6963581270123487</v>
+        <v>3.6898891580643447</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7608834270971503</v>
+        <v>5.7508013477308078</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5683922210112424</v>
+        <v>8.5533967413235512</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.329676474911222</v>
+        <v>10.31159858471146</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4388887852363745</v>
+        <v>2.4346205040587385</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.4053903134926609</v>
+        <v>3.3994305651574463</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.4064466265351747</v>
+        <v>5.3969848443851953</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8971247430709735</v>
+        <v>8.8815539510341193</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.491002137817334</v>
+        <v>11.470891820186646</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4313122725393406</v>
+        <v>2.4270572509603925</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3144088172358606</v>
+        <v>3.3086082949425784</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2131740084120182</v>
+        <v>5.2040504712378164</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1528991145960124</v>
+        <v>9.1368806937282283</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.535515533811427</v>
+        <v>12.513577221031925</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4304148994303514</v>
+        <v>2.4261614483374268</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2859601975724151</v>
+        <v>3.2802094629974472</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.107783414498086</v>
+        <v>5.0988443206207767</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3519075020811524</v>
+        <v>9.3355407981101646</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.474966257461988</v>
+        <v>13.451383818937455</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4303086132629628</v>
+        <v>2.4260553481806717</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2770647188866056</v>
+        <v>3.2713295522229218</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0503144497094308</v>
+        <v>5.0414759318412408</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.5067484193055645</v>
+        <v>9.4901107293935514</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.319922067078576</v>
+        <v>14.294860877657342</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4824283030651255</v>
+        <v>8.4675832681927723</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.944878839122655</v>
+        <v>7.9309745655809891</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.8032978090106067</v>
+        <v>6.7913914079644275</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4284692673280475</v>
+        <v>5.418968943517724</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8684613387714015</v>
+        <v>3.8616911732687167</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.944878839122655</v>
+        <v>7.9309745655809891</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.8032978090106067</v>
+        <v>6.7913914079644275</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4284692673280475</v>
+        <v>5.418968943517724</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6879068796123766</v>
+        <v>6.676202423376064</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4824283030651255</v>
+        <v>8.4675832681927723</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8684613387714015</v>
+        <v>3.8616911732687167</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.190816596048551</v>
+        <v>0.19212406523521777</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4269097920927997E-2</v>
+        <v>-2.4210000365147522E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3547161196588675</v>
+        <v>6.3435947781007966</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.9207427973551088</v>
+        <v>7.9068807641211603</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.2938194775432777</v>
+        <v>0.29381947754327764</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9284406081377274</v>
+        <v>2.9233155659450683</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3708987192411541</v>
+        <v>3.3657736770484949</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46954377571438866</v>
+        <v>0.46942170886013446</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6705941485394193</v>
+        <v>3.66417026893909</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1793423029890828</v>
+        <v>4.1729184233887535</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.3423243109066787</v>
+        <v>0.34218395572895022</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5548088234241915</v>
+        <v>4.5468374862781769</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1381762592761566</v>
+        <v>5.130204922130142</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19143889946857562</v>
+        <v>0.19127795806874193</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1511506545721124</v>
+        <v>5.1421356640095359</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7828229845025474</v>
+        <v>5.7738079939399709</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9995072067360904E-2</v>
+        <v>8.9820804148434852E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>38799.277293120002</v>
+        <v>38617.972259039998</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.190816596048551</v>
+        <v>0.19212406523521777</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3547161196588675</v>
+        <v>6.3435947781007966</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3708987192411541</v>
+        <v>3.3657736770484949</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1793423029890828</v>
+        <v>4.1729184233887535</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1381762592761566</v>
+        <v>5.130204922130142</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7828229845025474</v>
+        <v>5.7738079939399709</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10061854562635701</v>
+        <v>0.10091401467201033</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6495327102803729E-2</v>
+        <v>5.6760563380281688E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10211508869579866</v>
+        <v>-0.1019363778362993</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.764506704954441</v>
+        <v>1.7614186548546737</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.175765637737002E-4</v>
+        <v>5.1667075686749186E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6629091928224158</v>
+        <v>1.6599989477752417</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2448502511999526</v>
+        <v>1.2426716480064259</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.6028729897990805</v>
+        <v>7.5895672581581941</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.48 HKD</v>
+        <v>8.47 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.93 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.8 HKD</v>
+        <v>6.79 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.43 HKD</v>
+        <v>5.42 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.86 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3547161196588675</v>
+        <v>6.3435947781007966</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9284406081377274</v>
+        <v>2.9233155659450683</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3708987192411541</v>
+        <v>3.3657736770484949</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6705941485394193</v>
+        <v>3.66417026893909</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1793423029890828</v>
+        <v>4.1729184233887535</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5548088234241915</v>
+        <v>4.5468374862781769</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1381762592761566</v>
+        <v>5.130204922130142</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1511506545721124</v>
+        <v>5.1421356640095359</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7828229845025474</v>
+        <v>5.7738079939399709</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,15 +21836,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21859,12 +21856,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C07DAE4-1F57-4AC3-B56B-3D22B296D912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5364B7-38C4-4313-AFCC-DBA155D54DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.26</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>38617.972259039998</v>
+        <v>37530.142054559998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.19212406523521777</v>
+        <v>0.20452742481236513</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3435947781007966</v>
+        <v>6.3513189245461659</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3657736770484949</v>
+        <v>3.3693331915394484</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1729184233887535</v>
+        <v>4.1773800242236234</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.130204922130142</v>
+        <v>5.1357412843720285</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7738079939399709</v>
+        <v>5.7800692086455321</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10091401467201033</v>
+        <v>0.10396549604881608</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6760563380281688E-2</v>
+        <v>5.8405797101449275E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.1019363778362993</v>
+        <v>-0.10206049854987898</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7614186548546737</v>
+        <v>1.7635634097007229</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1667075686749186E-4</v>
+        <v>5.1729987028499157E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6599989477752417</v>
+        <v>1.6620202110211286</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2426716480064259</v>
+        <v>1.2441847613323032</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.47 HKD</v>
+        <v>8.48 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0308060895368665E-2</v>
+        <v>-6.0346251149301956E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.93 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.8891728989395351E-2</v>
+        <v>-3.893160984224097E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.79 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3928565480441156E-2</v>
+        <v>1.3884311053355478E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.42 HKD</v>
+        <v>5.43 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6352385012812264E-2</v>
+        <v>9.6300707050652301E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.86 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23373499766474543</v>
+        <v>0.23366923775772797</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3435947781007966</v>
+        <v>6.3513189245461659</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9233155659450683</v>
+        <v>2.9268750804360217</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3657736770484949</v>
+        <v>3.3693331915394484</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.66417026893909</v>
+        <v>3.6686318697739599</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1729184233887535</v>
+        <v>4.1773800242236234</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5468374862781769</v>
+        <v>4.5523738485200633</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.130204922130142</v>
+        <v>5.1357412843720285</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1421356640095359</v>
+        <v>5.1483968787150971</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7738079939399709</v>
+        <v>5.7800692086455321</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0894742280940206</v>
+        <v>3.0932360622293555</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2426716480064259</v>
+        <v>1.2441847613323032</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>924078.92288010009</v>
+        <v>925204.10839037981</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.1019363778362993</v>
+        <v>0.10206049854987896</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15967703.462378718</v>
+        <v>15987146.204901528</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7614186548546735</v>
+        <v>1.7635634097007229</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4683.7504591000006</v>
+        <v>4689.4535305799991</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1667075686749186E-4</v>
+        <v>5.1729987028499157E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16896466.135717917</v>
+        <v>16917039.766822487</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8638717034478405</v>
+        <v>1.8661412081208868</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6760563380281688E-2</v>
+        <v>5.8405797101449275E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.6619718309859169E-2</v>
+        <v>7.8840579710144937E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6502347417840377E-2</v>
+        <v>6.8429951690821264E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.6948356807511739E-2</v>
+        <v>6.8888888888888902E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11046948356807512</v>
+        <v>0.11367149758454108</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>6.950704225352114E-2</v>
+        <v>7.1521739130434789E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42989370250276399</v>
+        <v>0.43041715364209854</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35211217824028002</v>
+        <v>0.35254092032186995</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31638507882126915</v>
+        <v>0.31677031854218918</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49438515356304558</v>
+        <v>0.49498713137848238</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63021998249286559</v>
+        <v>0.63098735676689366</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.54719643240853588</v>
+        <v>0.5478627147809374</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36522675308030261</v>
+        <v>0.36567146385159871</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21382123119165189</v>
+        <v>0.21408158617342896</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.3921044712483387E-2</v>
+        <v>9.4035405722137672E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6299663410625583E-2</v>
+        <v>2.6331686649617596E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10091401467201033</v>
+        <v>0.10396549604881608</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.2655440901474184E-2</v>
+        <v>8.5154811671949271E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.4268797845368342E-2</v>
+        <v>7.6514569696180965E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11605285294907174</v>
+        <v>0.11956210902861894</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.14793896302649429</v>
+        <v>0.15241240501615791</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12844986676256712</v>
+        <v>0.13233398907752111</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.5733979596315166E-2</v>
+        <v>8.8326440543864432E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.0192777275035655E-2</v>
+        <v>5.1710528061214726E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.204719359447967E-2</v>
+        <v>2.2713866116458377E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.1736299085975548E-3</v>
+        <v>6.3603107849317872E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4622264874215781E-2</v>
+        <v>9.7364939218395952E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5202609239271185E-2</v>
+        <v>8.7672250086786307E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12812961713290652</v>
+        <v>0.13184351907878786</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17905901308376715</v>
+        <v>0.18424912940503577</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19256919939029615</v>
+        <v>0.19815091531465259</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10188460889680614</v>
+        <v>0.1048377859662788</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8062447840593584E-2</v>
+        <v>5.974541734321949E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0043679979297855E-2</v>
+        <v>3.091451128304562E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0517175714862262E-2</v>
+        <v>1.0822021387756821E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6599989477752417</v>
+        <v>1.6620202110211286</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68801337.519641176</v>
+        <v>68885112.039488122</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9068807641211603</v>
+        <v>7.9165084132829557</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.7961747206566088</v>
+        <v>5.8032323124371965</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.6928709894074023</v>
+        <v>6.7010204247781182</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2906685019079305</v>
+        <v>7.2995458330053999</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.7091267606583012</v>
+        <v>7.718513618764498</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8884660144084595</v>
+        <v>7.8980712412326817</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.625662108767461</v>
+        <v>4.6312944501739866</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9822026179032779</v>
+        <v>5.9894867226897421</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0259096968377666</v>
+        <v>7.0344646498744359</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8228337000989612</v>
+        <v>7.8323590110986379</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1810941673807456</v>
+        <v>8.1910557067984833</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8616911732687167</v>
+        <v>3.8663932813308661</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.418968943517724</v>
+        <v>5.4255672385171358</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7913914079644275</v>
+        <v>6.7996608046768454</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9309745655809891</v>
+        <v>7.9406315520597799</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4675832681927723</v>
+        <v>8.4778936451146514</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.363062124458347</v>
+        <v>3.3671570872141436</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9725832808345327</v>
+        <v>4.9786380436017819</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5836595903143822</v>
+        <v>6.5916760466929647</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0338218222631959</v>
+        <v>8.0436040385682759</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7480621081486074</v>
+        <v>8.7587140043053111</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0376165914352615</v>
+        <v>3.0413152821962366</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6188044339527519</v>
+        <v>4.6244284252539511</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.3996547168714537</v>
+        <v>6.4074471235370822</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1316345978490698</v>
+        <v>8.1415359138490846</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0226567766368362</v>
+        <v>9.0336430272891697</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8252045885297523</v>
+        <v>2.828644640226508</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3384202662608971</v>
+        <v>4.3437028536029896</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2366667170851757</v>
+        <v>6.2442606647976033</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2246593354692052</v>
+        <v>8.234673921109156</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.2914907178141206</v>
+        <v>9.3028043085321066</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6865673838361794</v>
+        <v>2.6898386268196912</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1162043757825026</v>
+        <v>4.1212163865602678</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0922950622628322</v>
+        <v>6.0997132188279028</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3131304146044371</v>
+        <v>8.3232527252166353</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5546847860995783</v>
+        <v>9.5663188496091145</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5960815625909568</v>
+        <v>2.5992426273933309</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9400892178275986</v>
+        <v>3.9448867856406284</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9644134099726447</v>
+        <v>5.9716758540994972</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.3972707416141645</v>
+        <v>8.4074955039482209</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.8123573005049192</v>
+        <v>9.8243051136005839</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5370232177222807</v>
+        <v>2.5401123713574778</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.8005107709635726</v>
+        <v>3.8051383839793766</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8511382867319162</v>
+        <v>5.8582628037573174</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4772923113576848</v>
+        <v>8.4876145102943479</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.064624097824831</v>
+        <v>10.076879078347478</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.4984769786471532</v>
+        <v>2.5015191972548232</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6898891580643447</v>
+        <v>3.6943820749704592</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7508013477308078</v>
+        <v>5.7578036915661119</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5533967413235512</v>
+        <v>8.5638116072389163</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.31159858471146</v>
+        <v>10.324154288589193</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4346205040587385</v>
+        <v>2.4375849691562204</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.3994305651574463</v>
+        <v>3.4035698111898043</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.3969848443851953</v>
+        <v>5.4035563709028382</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8815539510341193</v>
+        <v>8.8923683907611117</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.470891820186646</v>
+        <v>11.484859113397743</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4270572509603925</v>
+        <v>2.4300125068198035</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3086082949425784</v>
+        <v>3.3126369531236977</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2040504712378164</v>
+        <v>5.2103870752226262</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1368806937282283</v>
+        <v>9.1480060267611432</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.513577221031925</v>
+        <v>12.528814118468118</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4261614483374268</v>
+        <v>2.4291156134413772</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2802094629974472</v>
+        <v>3.2842035419306015</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.0988443206207767</v>
+        <v>5.1050528225210838</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3355407981101646</v>
+        <v>9.3469080254936436</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.451383818937455</v>
+        <v>13.467762617102343</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4260553481806717</v>
+        <v>2.4290093840939697</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2713295522229218</v>
+        <v>3.2753128187171288</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0414759318412408</v>
+        <v>5.047614580314308</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.4901107293935514</v>
+        <v>9.5016661656439343</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.294860877657342</v>
+        <v>14.312266718146459</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4675832681927723</v>
+        <v>8.4778936451146514</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9309745655809891</v>
+        <v>7.9406315520597799</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7913914079644275</v>
+        <v>6.7996608046768454</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.418968943517724</v>
+        <v>5.4255672385171358</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8616911732687167</v>
+        <v>3.8663932813308661</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9309745655809891</v>
+        <v>7.9406315520597799</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7913914079644275</v>
+        <v>6.7996608046768454</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.418968943517724</v>
+        <v>5.4255672385171358</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.676202423376064</v>
+        <v>6.6843315626135054</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4675832681927723</v>
+        <v>8.4778936451146514</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8616911732687167</v>
+        <v>3.8663932813308661</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.26</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19212406523521777</v>
+        <v>0.20452742481236513</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4210000365147522E-2</v>
+        <v>-2.4251067533528303E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3435947781007966</v>
+        <v>6.3513189245461659</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.9068807641211603</v>
+        <v>7.9165084132829557</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.29381947754327764</v>
+        <v>0.2938194775432777</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9233155659450683</v>
+        <v>2.9268750804360217</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3657736770484949</v>
+        <v>3.3693331915394484</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46942170886013446</v>
+        <v>0.46950653375035734</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.66417026893909</v>
+        <v>3.6686318697739599</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1729184233887535</v>
+        <v>4.1773800242236234</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34218395572895022</v>
+        <v>0.342281489270023</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5468374862781769</v>
+        <v>4.5523738485200633</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.130204922130142</v>
+        <v>5.1357412843720285</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19127795806874193</v>
+        <v>0.19138979708234327</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1421356640095359</v>
+        <v>5.1483968787150971</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7738079939399709</v>
+        <v>5.7800692086455321</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9820804148434852E-2</v>
+        <v>8.9941903829282577E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.26</v>
+        <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>38617.972259039998</v>
+        <v>37530.142054559998</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.19212406523521777</v>
+        <v>0.20452742481236513</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3435947781007966</v>
+        <v>6.3513189245461659</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3657736770484949</v>
+        <v>3.3693331915394484</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1729184233887535</v>
+        <v>4.1773800242236234</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.130204922130142</v>
+        <v>5.1357412843720285</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7738079939399709</v>
+        <v>5.7800692086455321</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10091401467201033</v>
+        <v>0.10396549604881608</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6760563380281688E-2</v>
+        <v>5.8405797101449275E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.1019363778362993</v>
+        <v>-0.10206049854987898</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7614186548546737</v>
+        <v>1.7635634097007229</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1667075686749186E-4</v>
+        <v>5.1729987028499157E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6599989477752417</v>
+        <v>1.6620202110211286</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2426716480064259</v>
+        <v>1.2441847613323032</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5895672581581941</v>
+        <v>7.5988085371190408</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.47 HKD</v>
+        <v>8.48 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.93 HKD</v>
+        <v>7.94 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.79 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.42 HKD</v>
+        <v>5.43 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.86 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3435947781007966</v>
+        <v>6.3513189245461659</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9233155659450683</v>
+        <v>2.9268750804360217</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3657736770484949</v>
+        <v>3.3693331915394484</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.66417026893909</v>
+        <v>3.6686318697739599</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1729184233887535</v>
+        <v>4.1773800242236234</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5468374862781769</v>
+        <v>4.5523738485200633</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.130204922130142</v>
+        <v>5.1357412843720285</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1421356640095359</v>
+        <v>5.1483968787150971</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7738079939399709</v>
+        <v>5.7800692086455321</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5364B7-38C4-4313-AFCC-DBA155D54DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9638299E-BCDB-422F-BFAE-9997056B4DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.1399999999999997</v>
+        <v>4.12</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>37530.142054559998</v>
+        <v>37348.837020480001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.20452742481236513</v>
+        <v>0.20873319918927694</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3513189245461659</v>
+        <v>6.3885807555246439</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3693331915394484</v>
+        <v>3.3865045422207749</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1773800242236234</v>
+        <v>4.1989031034891706</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1357412843720285</v>
+        <v>5.1624490889886134</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.7800692086455321</v>
+        <v>5.8102737530218826</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10396549604881608</v>
+        <v>0.10508308716282604</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8405797101449275E-2</v>
+        <v>5.8689320388349508E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10206049854987898</v>
+        <v>-0.10265926568655152</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7635634097007229</v>
+        <v>1.7739098593866502</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1729987028499157E-4</v>
+        <v>5.2033475808715382E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6620202110211286</v>
+        <v>1.6717709284581856</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2441847613323032</v>
+        <v>1.251484127469247</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.48 HKD</v>
+        <v>8.53 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0346251149301956E-2</v>
+        <v>-6.0529189063881973E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.99 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.893160984224097E-2</v>
+        <v>-3.9122645421219571E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.8 HKD</v>
+        <v>6.84 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3884311053355478E-2</v>
+        <v>1.3672327049110099E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.43 HKD</v>
+        <v>5.46 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6300707050652301E-2</v>
+        <v>9.6053166668089204E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.89 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23366923775772797</v>
+        <v>0.23335425150290859</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3513189245461659</v>
+        <v>6.3885807555246439</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9268750804360217</v>
+        <v>2.9440464311173482</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3693331915394484</v>
+        <v>3.3865045422207749</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6686318697739599</v>
+        <v>3.6901549490395071</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1773800242236234</v>
+        <v>4.1989031034891706</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5523738485200633</v>
+        <v>4.5790816531366483</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1357412843720285</v>
+        <v>5.1624490889886134</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1483968787150971</v>
+        <v>5.1786014230914477</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.7800692086455321</v>
+        <v>5.8102737530218826</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.0932360622293555</v>
+        <v>3.1113834172427959</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2441847613323032</v>
+        <v>1.251484127469247</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>925204.10839037981</v>
+        <v>930632.08319639997</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10206049854987896</v>
+        <v>0.10265926568655152</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>15987146.204901528</v>
+        <v>16080939.37554723</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7635634097007229</v>
+        <v>1.77390985938665</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4689.4535305799991</v>
+        <v>4716.9655524</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.1729987028499157E-4</v>
+        <v>5.2033475808715393E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>16917039.766822487</v>
+        <v>17016288.424296033</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8661412081208868</v>
+        <v>1.8770894598312886</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8405797101449275E-2</v>
+        <v>5.8689320388349508E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.8840579710144937E-2</v>
+        <v>7.9223300970873795E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.8429951690821264E-2</v>
+        <v>6.8762135922330089E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.8888888888888902E-2</v>
+        <v>6.9223300970873786E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11367149758454108</v>
+        <v>0.11422330097087378</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.1521739130434789E-2</v>
+        <v>7.186893203883496E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.43041715364209854</v>
+        <v>0.4329423191108433</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35254092032186995</v>
+        <v>0.35460920257034306</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31677031854218918</v>
+        <v>0.31862874231349442</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49498713137848238</v>
+        <v>0.49789111510927331</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63098735676689366</v>
+        <v>0.63468922475946721</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.5478627147809374</v>
+        <v>0.55107690826107913</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36567146385159871</v>
+        <v>0.36781678019322206</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21408158617342896</v>
+        <v>0.21533755709448746</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.4035405722137672E-2</v>
+        <v>9.4587091353994249E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6331686649617596E-2</v>
+        <v>2.6486169028627778E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10396549604881608</v>
+        <v>0.10508308716282604</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.5154811671949271E-2</v>
+        <v>8.6070194798626959E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.6514569696180965E-2</v>
+        <v>7.7337073377061749E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11956210902861894</v>
+        <v>0.12084735803623138</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15241240501615791</v>
+        <v>0.15405078270860853</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13233398907752111</v>
+        <v>0.13375653113132988</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.8326440543864432E-2</v>
+        <v>8.9275917522626716E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.1710528061214726E-2</v>
+        <v>5.2266397353030937E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.2713866116458377E-2</v>
+        <v>2.295803188203744E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.3603107849317872E-3</v>
+        <v>6.4286818030649942E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7364939218395952E-2</v>
+        <v>9.7837584554407567E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7672250086786307E-2</v>
+        <v>8.8097843533809519E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13184351907878786</v>
+        <v>0.13248353616169459</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18424912940503577</v>
+        <v>0.18514354265457475</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19815091531465259</v>
+        <v>0.19911281296181108</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1048377859662788</v>
+        <v>0.10534670725737723</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.974541734321949E-2</v>
+        <v>6.0035443641002099E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.091451128304562E-2</v>
+        <v>3.1064581726167197E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0822021387756821E-2</v>
+        <v>1.0874555472163405E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6620202110211286</v>
+        <v>1.6717709284581856</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>68885112.039488122</v>
+        <v>69289246.272431299</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9165084132829557</v>
+        <v>7.9629528765416682</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.8032323124371965</v>
+        <v>5.8372786363777509</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.7010204247781182</v>
+        <v>6.7403338797341297</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.2995458330053999</v>
+        <v>7.3423707086383825</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.718513618764498</v>
+        <v>7.7637964888713604</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.8980712412326817</v>
+        <v>7.9444075375426353</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6312944501739866</v>
+        <v>4.6584652650966962</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9894867226897421</v>
+        <v>6.0246257614563472</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0344646498744359</v>
+        <v>7.0757343508486201</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8323590110986379</v>
+        <v>7.8783097877958053</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.1910557067984833</v>
+        <v>8.2391108803628992</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8663932813308661</v>
+        <v>3.8890765845402964</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4255672385171358</v>
+        <v>5.4573978821685936</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.7996608046768454</v>
+        <v>6.8395529616642152</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9406315520597799</v>
+        <v>7.9872175406190555</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.4778936451146514</v>
+        <v>8.5276316355715469</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3671570872141436</v>
+        <v>3.3869114783496386</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>4.9786380436017819</v>
+        <v>5.0078466491666438</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.5916760466929647</v>
+        <v>6.6303480015474916</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0436040385682759</v>
+        <v>8.0907941447027039</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.7587140043053111</v>
+        <v>8.8100995078037929</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0413152821962366</v>
+        <v>3.0591580290876714</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6244284252539511</v>
+        <v>4.6515589586755883</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4074471235370822</v>
+        <v>6.4450382466655478</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1415359138490846</v>
+        <v>8.1893005653696704</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0336430272891697</v>
+        <v>9.086641480618578</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.828644640226508</v>
+        <v>2.8452396939050359</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3437028536029896</v>
+        <v>4.3691864300812799</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2442606647976033</v>
+        <v>6.2808944078423785</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.234673921109156</v>
+        <v>8.2829849934165782</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.3028043085321066</v>
+        <v>9.3573818735841012</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.6898386268196912</v>
+        <v>2.7056193352776745</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1212163865602678</v>
+        <v>4.1453946824773968</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.0997132188279028</v>
+        <v>6.1354989328941185</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3232527252166353</v>
+        <v>8.3720834704402094</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.5663188496091145</v>
+        <v>9.6224423981657363</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.5992426273933309</v>
+        <v>2.6144918284812615</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9448867856406284</v>
+        <v>3.968030593467327</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9716758540994972</v>
+        <v>6.0067104003059155</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.4074955039482209</v>
+        <v>8.4568204835535887</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.8243051136005839</v>
+        <v>9.8819422124414569</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5401123713574778</v>
+        <v>2.555014667868218</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.8051383839793766</v>
+        <v>3.8274623177950113</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8582628037573174</v>
+        <v>5.8926319798315143</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.4876145102943479</v>
+        <v>8.537409530990093</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.076879078347478</v>
+        <v>10.135997974669436</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.5015191972548232</v>
+        <v>2.5161950758597045</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.6943820749704592</v>
+        <v>3.7160562251875815</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7578036915661119</v>
+        <v>5.7915834954952183</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.5638116072389163</v>
+        <v>8.6140536600206161</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.324154288589193</v>
+        <v>10.384723895731796</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4375849691562204</v>
+        <v>2.4518857593063332</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.4035698111898043</v>
+        <v>3.4235378279961823</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.4035563709028382</v>
+        <v>5.4352578814972921</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.8923683907611117</v>
+        <v>8.9445380159856196</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.484859113397743</v>
+        <v>11.552238327727723</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4300125068198035</v>
+        <v>2.444268870951475</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3126369531236977</v>
+        <v>3.3320714862823633</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2103870752226262</v>
+        <v>5.2409553028358005</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.1480060267611432</v>
+        <v>9.2016754233713307</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.528814118468118</v>
+        <v>12.602317993740209</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4291156134413772</v>
+        <v>2.4433667156912455</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.2842035419306015</v>
+        <v>3.3034712623414575</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.1050528225210838</v>
+        <v>5.1350030765815147</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.3469080254936436</v>
+        <v>9.4017443376289531</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.467762617102343</v>
+        <v>13.54677510258111</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4290093840939697</v>
+        <v>2.4432598631189562</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2753128187171288</v>
+        <v>3.2945283791546638</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.047614580314308</v>
+        <v>5.0772278564811337</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.5016661656439343</v>
+        <v>9.5574104107187399</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.312266718146459</v>
+        <v>14.396233728732149</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.4778936451146514</v>
+        <v>8.5276316355715469</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9406315520597799</v>
+        <v>7.9872175406190555</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.7996608046768454</v>
+        <v>6.8395529616642152</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4255672385171358</v>
+        <v>5.4573978821685936</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8663932813308661</v>
+        <v>3.8890765845402964</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9406315520597799</v>
+        <v>7.9872175406190555</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.7996608046768454</v>
+        <v>6.8395529616642152</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4255672385171358</v>
+        <v>5.4573978821685936</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.6843315626135054</v>
+        <v>6.723547107581278</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.4778936451146514</v>
+        <v>8.5276316355715469</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8663932813308661</v>
+        <v>3.8890765845402964</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.1399999999999997</v>
+        <v>4.12</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20452742481236513</v>
+        <v>0.20873319918927694</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4251067533528303E-2</v>
+        <v>-2.4447785323366562E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3513189245461659</v>
+        <v>6.3885807555246439</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.9165084132829557</v>
+        <v>7.9629528765416682</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.2938194775432777</v>
+        <v>0.29381947754327759</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9268750804360217</v>
+        <v>2.9440464311173482</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3693331915394484</v>
+        <v>3.3865045422207749</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46950653375035734</v>
+        <v>0.46991285360332458</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6686318697739599</v>
+        <v>3.6901549490395071</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1773800242236234</v>
+        <v>4.1989031034891706</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.342281489270023</v>
+        <v>0.34274868485334697</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5523738485200633</v>
+        <v>4.5790816531366483</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1357412843720285</v>
+        <v>5.1624490889886134</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19138979708234327</v>
+        <v>0.19192551733430152</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1483968787150971</v>
+        <v>5.1786014230914477</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.7800692086455321</v>
+        <v>5.8102737530218826</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>8.9941903829282577E-2</v>
+        <v>9.0521983619391455E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.1399999999999997</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>37530.142054559998</v>
+        <v>37348.837020480001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.20452742481236513</v>
+        <v>0.20873319918927694</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3513189245461659</v>
+        <v>6.3885807555246439</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3693331915394484</v>
+        <v>3.3865045422207749</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1773800242236234</v>
+        <v>4.1989031034891706</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1357412843720285</v>
+        <v>5.1624490889886134</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.7800692086455321</v>
+        <v>5.8102737530218826</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10396549604881608</v>
+        <v>0.10508308716282604</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.8405797101449275E-2</v>
+        <v>5.8689320388349508E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10206049854987898</v>
+        <v>-0.10265926568655152</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7635634097007229</v>
+        <v>1.7739098593866502</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.1729987028499157E-4</v>
+        <v>5.2033475808715382E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6620202110211286</v>
+        <v>1.6717709284581856</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.2441847613323032</v>
+        <v>1.251484127469247</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.5988085371190408</v>
+        <v>7.6433891230905093</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.48 HKD</v>
+        <v>8.53 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.94 HKD</v>
+        <v>7.99 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.8 HKD</v>
+        <v>6.84 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.43 HKD</v>
+        <v>5.46 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.89 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3513189245461659</v>
+        <v>6.3885807555246439</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9268750804360217</v>
+        <v>2.9440464311173482</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3693331915394484</v>
+        <v>3.3865045422207749</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6686318697739599</v>
+        <v>3.6901549490395071</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1773800242236234</v>
+        <v>4.1989031034891706</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5523738485200633</v>
+        <v>4.5790816531366483</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1357412843720285</v>
+        <v>5.1624490889886134</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1483968787150971</v>
+        <v>5.1786014230914477</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.7800692086455321</v>
+        <v>5.8102737530218826</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,12 +21836,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21856,15 +21859,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9638299E-BCDB-422F-BFAE-9997056B4DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AD302B-ED7D-4561-9795-30C3103F1B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>37348.837020480001</v>
+        <v>37076.879469359999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.20873319918927694</v>
+        <v>0.21221443999201767</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3885807555246439</v>
+        <v>6.3953088514136374</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.3865045422207749</v>
+        <v>3.389605047238744</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.1989031034891706</v>
+        <v>4.2027893682625965</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1624490889886134</v>
+        <v>5.1672715216422498</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.8102737530218826</v>
+        <v>5.815727566361458</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10508308716282604</v>
+        <v>0.10596534712555475</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8689320388349508E-2</v>
+        <v>5.9119804400977992E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10265926568655152</v>
+        <v>-0.10276738068264599</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7739098593866502</v>
+        <v>1.7757780420220599</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.2033475808715382E-4</v>
+        <v>5.2088274554802443E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6717709284581856</v>
+        <v>1.6735315440849619</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.251484127469247</v>
+        <v>1.2528021205471123</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.53 HKD</v>
+        <v>8.54 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0529189063881973E-2</v>
+        <v>-6.0561994090042481E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.99 HKD</v>
+        <v>8 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.9122645421219571E-2</v>
+        <v>-3.9156902442716877E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.84 HKD</v>
+        <v>6.85 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3672327049110099E-2</v>
+        <v>1.3634313793748026E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6053166668089204E-2</v>
+        <v>9.6008777962922412E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23335425150290859</v>
+        <v>0.23329776977115066</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3885807555246439</v>
+        <v>6.3953088514136374</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9440464311173482</v>
+        <v>2.9471469361353173</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.3865045422207749</v>
+        <v>3.389605047238744</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.6901549490395071</v>
+        <v>3.694041213812933</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.1989031034891706</v>
+        <v>4.2027893682625965</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5790816531366483</v>
+        <v>4.5839040857902846</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1624490889886134</v>
+        <v>5.1672715216422498</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1786014230914477</v>
+        <v>5.1840552364310231</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.8102737530218826</v>
+        <v>5.815727566361458</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.1113834172427959</v>
+        <v>3.1146601522141011</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.251484127469247</v>
+        <v>1.2528021205471123</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10579,11 +10579,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>930632.08319639997</v>
+        <v>931612.17284897331</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10265926568655152</v>
+        <v>0.10276738068264599</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16080939.37554723</v>
+        <v>16097874.921366261</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.77390985938665</v>
+        <v>1.7757780420220597</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4716.9655524</v>
+        <v>4721.9331966634272</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.2033475808715393E-4</v>
+        <v>5.2088274554802443E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17016288.424296033</v>
+        <v>17034209.027411897</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8770894598312886</v>
+        <v>1.8790663054502537</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8689320388349508E-2</v>
+        <v>5.9119804400977992E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.9223300970873795E-2</v>
+        <v>7.9804400977995113E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.8762135922330089E-2</v>
+        <v>6.926650366748166E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.9223300970873786E-2</v>
+        <v>6.9731051344743278E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11422330097087378</v>
+        <v>0.11506112469437654</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.186893203883496E-2</v>
+        <v>7.2396088019559907E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.4329423191108433</v>
+        <v>0.43339826974351892</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35460920257034306</v>
+        <v>0.35498265714645522</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31862874231349442</v>
+        <v>0.31896430428152944</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49789111510927331</v>
+        <v>0.49841546618080607</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63468922475946721</v>
+        <v>0.63535764394790739</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.55107690826107913</v>
+        <v>0.55165727163486666</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36781678019322206</v>
+        <v>0.36820414425128467</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21533755709448746</v>
+        <v>0.21556433856412457</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.4587091353994249E-2</v>
+        <v>9.4686705187620804E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6486169028627778E-2</v>
+        <v>2.6514062780272473E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10508308716282604</v>
+        <v>0.10596534712555475</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.6070194798626959E-2</v>
+        <v>8.6792825708179769E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7337073377061749E-2</v>
+        <v>7.7986382464921622E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12084735803623138</v>
+        <v>0.12186197217134623</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15405078270860853</v>
+        <v>0.15534416722442723</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13375653113132988</v>
+        <v>0.13487952851708232</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.9275917522626716E-2</v>
+        <v>9.0025463142123396E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.2266397353030937E-2</v>
+        <v>5.2705217252842197E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.295803188203744E-2</v>
+        <v>2.3150783664454964E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.4286818030649942E-3</v>
+        <v>6.4826559364969377E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7837584554407567E-2</v>
+        <v>9.855521964893868E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8097843533809519E-2</v>
+        <v>8.8744037985157773E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13248353616169459</v>
+        <v>0.13345529804063122</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18514354265457475</v>
+        <v>0.18650156374984059</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19911281296181108</v>
+        <v>0.20057329814246005</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10534670725737723</v>
+        <v>0.10611942149153893</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0035443641002099E-2</v>
+        <v>6.0475801418319965E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1064581726167197E-2</v>
+        <v>3.1292439293840797E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0874555472163405E-2</v>
+        <v>1.0954319937729396E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6717709284581856</v>
+        <v>1.6735315440849619</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>69289246.272431299</v>
+        <v>69362217.830722049</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9629528765416682</v>
+        <v>7.9713390130817086</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.8372786363777509</v>
+        <v>5.843426131713449</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.7403338797341297</v>
+        <v>6.7474324223372681</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.3423707086383825</v>
+        <v>7.3501032827531469</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.7637964888713604</v>
+        <v>7.7719728850442635</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.9444075375426353</v>
+        <v>7.9527741431690266</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6584652650966962</v>
+        <v>4.6633713001299091</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>6.0246257614563472</v>
+        <v>6.0309705603044055</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0757343508486201</v>
+        <v>7.0831861184663936</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8783097877958053</v>
+        <v>7.8866067829695217</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.2391108803628992</v>
+        <v>8.2477878510649116</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8890765845402964</v>
+        <v>3.8931723424530063</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4573978821685936</v>
+        <v>5.4631453083436279</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.8395529616642152</v>
+        <v>6.8467559962543518</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9872175406190555</v>
+        <v>7.9956292313459922</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.5276316355715469</v>
+        <v>8.5366124601937479</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3869114783496386</v>
+        <v>3.3904783840624861</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.0078466491666438</v>
+        <v>5.0131206331299563</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.6303480015474916</v>
+        <v>6.6373307131760848</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0907941447027039</v>
+        <v>8.0993149165152207</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.8100995078037929</v>
+        <v>8.8193778117884172</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.0591580290876714</v>
+        <v>3.062379763201541</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6515589586755883</v>
+        <v>4.6564577203732025</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4450382466655478</v>
+        <v>6.4518258004261062</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1893005653696704</v>
+        <v>8.1979250786342082</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.086641480618578</v>
+        <v>9.0962110231398388</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8452396939050359</v>
+        <v>2.8482361411943979</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3691864300812799</v>
+        <v>4.3737878128270564</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2808944078423785</v>
+        <v>6.2875090944937231</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2829849934165782</v>
+        <v>8.2917081698802395</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.3573818735841012</v>
+        <v>9.3672365447426298</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.7056193352776745</v>
+        <v>2.7084687422153766</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1453946824773968</v>
+        <v>4.1497603802730012</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.1354989328941185</v>
+        <v>6.14196049716434</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3720834704402094</v>
+        <v>8.3809004804359066</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.6224423981657363</v>
+        <v>9.6325762162418691</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.6144918284812615</v>
+        <v>2.6172452650262716</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.968030593467327</v>
+        <v>3.9722095013257306</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.0067104003059155</v>
+        <v>6.0130363316977542</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.4568204835535887</v>
+        <v>8.4657267338315005</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.8819422124414569</v>
+        <v>9.8923493212061544</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.555014667868218</v>
+        <v>2.5577054663946881</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.8274623177950113</v>
+        <v>3.8314931870085474</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8926319798315143</v>
+        <v>5.8988377702121984</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.537409530990093</v>
+        <v>8.5464006531447971</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.135997974669436</v>
+        <v>10.146672640751609</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.5161950758597045</v>
+        <v>2.5188449917633511</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.7160562251875815</v>
+        <v>3.7199697677361878</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7915834954952183</v>
+        <v>5.7976828672646219</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.6140536600206161</v>
+        <v>8.6231254994847166</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.384723895731796</v>
+        <v>10.395660506040867</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4518857593063332</v>
+        <v>2.4544679482351035</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.4235378279961823</v>
+        <v>3.4271433065316823</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.4352578814972921</v>
+        <v>5.4409819910620802</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.9445380159856196</v>
+        <v>8.9539579030868754</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.552238327727723</v>
+        <v>11.564404498928461</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.444268870951475</v>
+        <v>2.4468430381995012</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3320714862823633</v>
+        <v>3.3355806375831905</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2409553028358005</v>
+        <v>5.2464747837935883</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.2016754233713307</v>
+        <v>9.2113661132063616</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.602317993740209</v>
+        <v>12.615590050106116</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4433667156912455</v>
+        <v>2.4459399328398166</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.3034712623414575</v>
+        <v>3.3069502934862616</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.1350030765815147</v>
+        <v>5.1404109745813384</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.4017443376289531</v>
+        <v>9.4116457288530793</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.54677510258111</v>
+        <v>13.561041808343258</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4432598631189562</v>
+        <v>2.4458329677363748</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2945283791546638</v>
+        <v>3.2979979921551403</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0772278564811337</v>
+        <v>5.0825749088509626</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.5574104107187399</v>
+        <v>9.5674757407434345</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.396233728732149</v>
+        <v>14.411395036802569</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.5276316355715469</v>
+        <v>8.5366124601937479</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9872175406190555</v>
+        <v>7.9956292313459922</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.8395529616642152</v>
+        <v>6.8467559962543518</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4573978821685936</v>
+        <v>5.4631453083436279</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8890765845402964</v>
+        <v>3.8931723424530063</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9872175406190555</v>
+        <v>7.9956292313459922</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.8395529616642152</v>
+        <v>6.8467559962543518</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4573978821685936</v>
+        <v>5.4631453083436279</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.723547107581278</v>
+        <v>6.7306279712949983</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.5276316355715469</v>
+        <v>8.5366124601937479</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8890765845402964</v>
+        <v>3.8931723424530063</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20873319918927694</v>
+        <v>0.21221443999201767</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4447785323366562E-2</v>
+        <v>-2.4483061219574633E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3885807555246439</v>
+        <v>6.3953088514136374</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.9629528765416682</v>
+        <v>7.9713390130817086</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20223,11 +20223,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9440464311173482</v>
+        <v>2.9471469361353173</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.3865045422207749</v>
+        <v>3.389605047238744</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46991285360332458</v>
+        <v>0.46998571515596221</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20248,11 +20248,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6901549490395071</v>
+        <v>3.694041213812933</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.1989031034891706</v>
+        <v>4.2027893682625965</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34274868485334697</v>
+        <v>0.34283246268339329</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5790816531366483</v>
+        <v>4.5839040857902846</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1624490889886134</v>
+        <v>5.1672715216422498</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19192551733430152</v>
+        <v>0.19202158305457584</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1786014230914477</v>
+        <v>5.1840552364310231</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.8102737530218826</v>
+        <v>5.815727566361458</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.0521983619391455E-2</v>
+        <v>9.0626003922244847E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>37348.837020480001</v>
+        <v>37076.879469359999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.20873319918927694</v>
+        <v>0.21221443999201767</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3885807555246439</v>
+        <v>6.3953088514136374</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.3865045422207749</v>
+        <v>3.389605047238744</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.1989031034891706</v>
+        <v>4.2027893682625965</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>5.1624490889886134</v>
+        <v>5.1672715216422498</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>5.8102737530218826</v>
+        <v>5.815727566361458</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20666,22 +20666,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20871,10 +20871,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20890,22 +20890,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>0.10508308716282604</v>
+        <v>0.10596534712555475</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.8689320388349508E-2</v>
+        <v>5.9119804400977992E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21040,22 +21040,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21063,13 +21063,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10265926568655152</v>
+        <v>-0.10276738068264599</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7739098593866502</v>
+        <v>1.7757780420220599</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.2033475808715382E-4</v>
+        <v>5.2088274554802443E-4</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>1.6717709284581856</v>
+        <v>1.6735315440849619</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21218,33 +21218,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21307,23 +21307,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.251484127469247</v>
+        <v>1.2528021205471123</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>7.6433891230905093</v>
+        <v>7.6514387129610855</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21367,13 +21367,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.53 HKD</v>
+        <v>8.54 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.99 HKD</v>
+        <v>8 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.84 HKD</v>
+        <v>6.85 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>6.3885807555246439</v>
+        <v>6.3953088514136374</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21537,13 +21537,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21556,22 +21556,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21636,11 +21636,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>2.9440464311173482</v>
+        <v>2.9471469361353173</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>3.3865045422207749</v>
+        <v>3.389605047238744</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21657,11 +21657,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>3.6901549490395071</v>
+        <v>3.694041213812933</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>4.1989031034891706</v>
+        <v>4.2027893682625965</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21697,11 +21697,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>4.5790816531366483</v>
+        <v>4.5839040857902846</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>5.1624490889886134</v>
+        <v>5.1672715216422498</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21718,11 +21718,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>5.1786014230914477</v>
+        <v>5.1840552364310231</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>5.8102737530218826</v>
+        <v>5.815727566361458</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21740,13 +21740,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21754,13 +21754,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21797,22 +21797,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21836,15 +21836,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21859,12 +21856,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/6186.HK_Valuation.xlsx
+++ b/financial_models/opportunities/6186.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AD302B-ED7D-4561-9795-30C3103F1B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3988701-E650-4383-8F04-658B63A32707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.09</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>37076.879469359999</v>
+        <v>37983.404639760003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.21221443999201767</v>
+        <v>0.20282532000570663</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>6.3953088514136374</v>
+        <v>6.4091043716429636</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,13 +5538,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>3.389605047238744</v>
+        <v>3.3959624298329043</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5553,13 +5553,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>4.2027893682625965</v>
+        <v>4.2107578998030011</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>5.1672715216422498</v>
+        <v>5.1771596041436654</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>5.815727566361458</v>
+        <v>5.8269102536320379</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.10596534712555475</v>
+        <v>0.10365946698599808</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.9119804400977992E-2</v>
+        <v>5.7708830548926005E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.10276738068264599</v>
+        <v>-0.10298906340541381</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.7757780420220599</v>
+        <v>1.779608628233091</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.2088274554802443E-4</v>
+        <v>5.2200635796773227E-4</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>1.6735315440849619</v>
+        <v>1.677141571185645</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.2528021205471123</v>
+        <v>1.2555045790833457</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.54 HKD</v>
+        <v>8.56 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.0561994090042481E-2</v>
+        <v>-6.0629043699543361E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>8 HKD</v>
+        <v>8.01 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.9156902442716877E-2</v>
+        <v>-3.9226919660912726E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.85 HKD</v>
+        <v>6.86 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.3634313793748026E-2</v>
+        <v>1.3556619565840968E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.46 HKD</v>
+        <v>5.47 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>9.6008777962922412E-2</v>
+        <v>9.5918053668701278E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>3.89 HKD</v>
+        <v>3.9 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.23329776977115066</v>
+        <v>0.23318233025755475</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3953088514136374</v>
+        <v>6.4091043716429636</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6562,19 +6562,19 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>0.44245811110342687</v>
+        <v>0.44245811110342698</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>2.9471469361353173</v>
+        <v>2.9535043187294772</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>3.389605047238744</v>
+        <v>3.3959624298329043</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6583,19 +6583,19 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>0.50874815444966315</v>
+        <v>0.50874815444966326</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>3.694041213812933</v>
+        <v>3.702009745353338</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>4.2027893682625965</v>
+        <v>4.2107578998030011</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>4.5839040857902846</v>
+        <v>4.5937921682917002</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>5.1672715216422498</v>
+        <v>5.1771596041436654</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>5.1840552364310231</v>
+        <v>5.1952379237016029</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>5.815727566361458</v>
+        <v>5.8269102536320379</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10169,11 +10169,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.1146601522141011</v>
+        <v>3.1213788827923517</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.2528021205471123</v>
+        <v>1.2555045790833457</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10578,12 +10578,12 @@
         <v>239</v>
       </c>
       <c r="C86" s="73">
-        <f>-DCF!F4*Exchange_Rate</f>
-        <v>931612.17284897331</v>
+        <f>DCF!F4*Exchange_Rate</f>
+        <v>-933621.78252929146</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.10276738068264599</v>
+        <v>-0.10298906340541381</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10596,11 +10596,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>16097874.921366261</v>
+        <v>16132600.149543131</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.7757780420220597</v>
+        <v>1.779608628233091</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>4721.9331966634272</v>
+        <v>4732.1190260658186</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>5.2088274554802443E-4</v>
+        <v>5.2200635796773227E-4</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10630,11 +10630,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17034209.027411897</v>
+        <v>15203710.486039907</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.8790663054502537</v>
+        <v>1.677141571185645</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14218,28 +14218,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.9119804400977992E-2</v>
+        <v>5.7708830548926005E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.9804400977995113E-2</v>
+        <v>7.7899761336515508E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>6.926650366748166E-2</v>
+        <v>6.7613365155131264E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.9731051344743278E-2</v>
+        <v>6.8066825775656314E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>0.11506112469437654</v>
+        <v>0.11231503579952266</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>7.2396088019559907E-2</v>
+        <v>7.0668257756563241E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15360,46 +15360,46 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.43339826974351892</v>
+        <v>0.43433316667133198</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.35498265714645522</v>
+        <v>0.3557484013101076</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.31896430428152944</v>
+        <v>0.31965235213260024</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49841546618080607</v>
+        <v>0.49949061373130893</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63535764394790739</v>
+        <v>0.63672819374207468</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.55165727163486666</v>
+        <v>0.55284726874482837</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.36820414425128467</v>
+        <v>0.36899840889722402</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.21556433856412457</v>
+        <v>0.21602933912351518</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>9.4686705187620804E-2</v>
+        <v>9.4890956833196205E-2</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>2.6514062780272473E-2</v>
+        <v>2.6571257092219747E-2</v>
       </c>
       <c r="P123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15417,46 +15417,46 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10596534712555475</v>
+        <v>0.10365946698599808</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.6792825708179769E-2</v>
+        <v>8.4904153057304907E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7986382464921622E-2</v>
+        <v>7.6289344184391455E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12186197217134623</v>
+        <v>0.11921017034160117</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.15534416722442723</v>
+        <v>0.15196376938951661</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13487952851708232</v>
+        <v>0.13194445554769171</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>9.0025463142123396E-2</v>
+        <v>8.806644603752363E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>5.2705217252842197E-2</v>
+        <v>5.1558314826614597E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>2.3150783664454964E-2</v>
+        <v>2.2647006404104105E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>6.4826559364969377E-3</v>
+        <v>6.3415888048257143E-3</v>
       </c>
       <c r="P124" s="74" t="str">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
@@ -15474,39 +15474,39 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.855521964893868E-2</v>
+        <v>9.6203066435360196E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8744037985157773E-2</v>
+        <v>8.6626041851860444E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13345529804063122</v>
+        <v>0.13027020739527009</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18650156374984059</v>
+        <v>0.18205045244316181</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20057329814246005</v>
+        <v>0.19578634591948965</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10611942149153893</v>
+        <v>0.10358673840104873</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0475801418319965E-2</v>
+        <v>5.9032464868956719E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1292439293840797E-2</v>
+        <v>3.0545603033844595E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0954319937729396E-2</v>
+        <v>1.0692880321077144E-2</v>
       </c>
       <c r="P125" s="22" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>1.6735315440849619</v>
+        <v>1.677141571185645</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>69362217.830722049</v>
+        <v>69511841.234605551</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.9713390130817086</v>
+        <v>7.9885342371380874</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18785,23 +18785,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18816,23 +18816,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.843426131713449</v>
+        <v>5.8560311685117599</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>6.7474324223372681</v>
+        <v>6.7619875193061656</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>7.3501032827531469</v>
+        <v>7.3659584198357688</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>7.7719728850442635</v>
+        <v>7.7887380502064918</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>7.9527741431690266</v>
+        <v>7.9699293203653729</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>4.6633713001299091</v>
+        <v>4.6734308038384098</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>6.0309705603044055</v>
+        <v>6.0439801550402041</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>7.0831861184663936</v>
+        <v>7.0984654802072731</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>7.8866067829695217</v>
+        <v>7.9036192284890454</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>8.2477878510649116</v>
+        <v>8.2655794115337091</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>3.8931723424530063</v>
+        <v>3.9015704259630302</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4631453083436279</v>
+        <v>5.4749300295147325</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>6.8467559962543518</v>
+        <v>6.8615253472030107</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>7.9956292313459922</v>
+        <v>8.0128768525899368</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>8.5366124601937479</v>
+        <v>8.5550270532369748</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18909,23 +18909,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>3.3904783840624861</v>
+        <v>3.3977920907529913</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.0131206331299563</v>
+        <v>5.0239345920353369</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.6373307131760848</v>
+        <v>6.6516483063134535</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>8.0993149165152207</v>
+        <v>8.1167862013851888</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>8.8193778117884172</v>
+        <v>8.8384023667926233</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18940,23 +18940,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>3.062379763201541</v>
+        <v>3.0689857181217306</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>4.6564577203732025</v>
+        <v>4.6665023105831365</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4518258004261062</v>
+        <v>6.4657432351292323</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>8.1979250786342082</v>
+        <v>8.2156090785610942</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>9.0962110231398388</v>
+        <v>9.1158327437002491</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>2.8482361411943979</v>
+        <v>2.8543801602272025</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>4.3737878128270564</v>
+        <v>4.3832226469613467</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2875090944937231</v>
+        <v>6.3010720765045134</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>8.2917081698802395</v>
+        <v>8.3095944722388779</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>9.3672365447426298</v>
+        <v>9.3874429029105109</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>2.7084687422153766</v>
+        <v>2.7143112646317058</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>4.1497603802730012</v>
+        <v>4.1587119578438418</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.14196049716434</v>
+        <v>6.1552095117553449</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>8.3809004804359066</v>
+        <v>8.3989791823100575</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>9.6325762162418691</v>
+        <v>9.6533549468925912</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19034,23 +19034,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>2.6172452650262716</v>
+        <v>2.6228910064341786</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>3.9722095013257306</v>
+        <v>3.9807780783567761</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.0130363316977542</v>
+        <v>6.0260072399495552</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>8.4657267338315005</v>
+        <v>8.4839884170630633</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>9.8923493212061544</v>
+        <v>9.9136884165253907</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19066,23 +19066,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>2.5577054663946881</v>
+        <v>2.5632227726455832</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>3.8314931870085474</v>
+        <v>3.8397582204882399</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>5.8988377702121984</v>
+        <v>5.9115623371845176</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>8.5464006531447971</v>
+        <v>8.5648363606043869</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>10.146672640751609</v>
+        <v>10.168560344837223</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19098,23 +19098,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>2.5188449917633511</v>
+        <v>2.5242784708721406</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>3.7199697677361878</v>
+        <v>3.72799423056912</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>5.7976828672646219</v>
+        <v>5.8101892298401987</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>8.6231254994847166</v>
+        <v>8.6417267125038304</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>10.395660506040867</v>
+        <v>10.418085309618039</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19130,23 +19130,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>2.4544679482351035</v>
+        <v>2.4597625576150133</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>3.4271433065316823</v>
+        <v>3.4345361042702329</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>5.4409819910620802</v>
+        <v>5.4527189030500782</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>8.9539579030868754</v>
+        <v>8.9732727650043387</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>11.564404498928461</v>
+        <v>11.589350436632444</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19162,23 +19162,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>2.4468430381995012</v>
+        <v>2.4521211996481092</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>3.3355806375831905</v>
+        <v>3.3427759226321929</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2464747837935883</v>
+        <v>5.2577921182170044</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>9.2113661132063616</v>
+        <v>9.2312362384038948</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>12.615590050106116</v>
+        <v>12.642803532954982</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19194,23 +19194,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>2.4459399328398166</v>
+        <v>2.4512161461716797</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>3.3069502934862616</v>
+        <v>3.31408381912687</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>5.1404109745813384</v>
+        <v>5.1514995154531711</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>9.4116457288530793</v>
+        <v>9.4319478834573793</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>13.561041808343258</v>
+        <v>13.590294754673817</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19226,23 +19226,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>2.4458329677363748</v>
+        <v>2.4511089503304766</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>3.2979979921551403</v>
+        <v>3.3051122065072747</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>5.0825749088509626</v>
+        <v>5.0935386897411732</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>9.5674757407434345</v>
+        <v>9.5881140411276071</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>14.411395036802569</v>
+        <v>14.442482306609577</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.5366124601937479</v>
+        <v>8.5550270532369748</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.9956292313459922</v>
+        <v>8.0128768525899368</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.8467559962543518</v>
+        <v>6.8615253472030107</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.4631453083436279</v>
+        <v>5.4749300295147325</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>3.8931723424530063</v>
+        <v>3.9015704259630302</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>7.9956292313459922</v>
+        <v>8.0128768525899368</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>6.8467559962543518</v>
+        <v>6.8615253472030107</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>5.4631453083436279</v>
+        <v>5.4749300295147325</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.7306279712949983</v>
+        <v>6.7451468188583261</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>8.5366124601937479</v>
+        <v>8.5550270532369748</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>3.8931723424530063</v>
+        <v>3.9015704259630302</v>
       </c>
       <c r="F30" s="331">
         <v>0.15</v>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.09</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21221443999201767</v>
+        <v>0.20282532000570663</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>7.6514387129610855</v>
+        <v>7.6679438701005695</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-2.4483061219574633E-2</v>
+        <v>-2.455516082391444E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3953088514136374</v>
+        <v>6.4091043716429636</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>7.9713390130817086</v>
+        <v>7.9885342371380874</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.29381947754327759</v>
+        <v>0.26168111391759291</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20219,23 +20219,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.44245811110342687</v>
+        <v>0.44245811110342698</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9471469361353173</v>
+        <v>2.9535043187294772</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>3.389605047238744</v>
+        <v>3.3959624298329043</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.46998571515596221</v>
+        <v>0.47013463458976956</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20244,23 +20244,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.50874815444966315</v>
+        <v>0.50874815444966326</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.694041213812933</v>
+        <v>3.702009745353338</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>4.2027893682625965</v>
+        <v>4.2107578998030011</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34283246268339329</v>
+        <v>0.34300369355296045</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20294,11 +20294,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5839040857902846</v>
+        <v>4.5937921682917002</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>5.1672715216422498</v>
+        <v>5.1771596041436654</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19202158305457584</v>
+        <v>0.19221792875616583</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20319,11 +20319,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1840552364310231</v>
+        <v>5.1952379237016029</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>5.815727566361458</v>
+        <v>5.8269102536320379</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.0626003922244847E-2</v>
+        <v>9.0838607744763711E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>4.09</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20460,14 +20460,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>37076.879469359999</v>
+        <v>37983.404639760003</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.21221443999201767</v>
+        <v>0.20282532000570663</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20475,13 +20475,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>6.3953088514136374</v>
+        <v>6.4091043716429636</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20597,14 +20597,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>3.389605047238744</v>
+        <v>3.3959624298329043</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20613,14 +20613,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>4.2027893682625965</v>
+        <v>4.2107578998030011</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>44